--- a/web/descargas/licitaciones.xlsx
+++ b/web/descargas/licitaciones.xlsx
@@ -412,7 +412,7 @@
         <v>46265.625</v>
       </c>
       <c r="J2" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K2" s="3">
         <v>4000000.0</v>
@@ -501,7 +501,7 @@
         <v>46265.625</v>
       </c>
       <c r="J3" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" s="3">
         <v>6000000.0</v>
@@ -589,7 +589,7 @@
         <v>46265.625</v>
       </c>
       <c r="J4" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" s="3"/>
       <c r="L4" s="0" t="inlineStr">
@@ -682,7 +682,7 @@
         <v>46265.625</v>
       </c>
       <c r="J5" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" s="3"/>
       <c r="L5" s="0" t="inlineStr">
@@ -775,7 +775,7 @@
         <v>46265.625</v>
       </c>
       <c r="J6" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" s="3"/>
       <c r="L6" s="0" t="inlineStr">
@@ -875,7 +875,7 @@
         <v>46265.625</v>
       </c>
       <c r="J7" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" s="3">
         <v>15000000.0</v>
@@ -970,7 +970,7 @@
         <v>46265.625</v>
       </c>
       <c r="J8" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" s="3">
         <v>14000000.0</v>
@@ -1065,7 +1065,7 @@
         <v>46265.625694</v>
       </c>
       <c r="J9" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K9" s="3"/>
       <c r="L9" s="0" t="inlineStr">
@@ -1159,7 +1159,7 @@
         <v>46265.625694</v>
       </c>
       <c r="J10" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" s="3">
         <v>4500000.0</v>
@@ -1242,7 +1242,7 @@
         <v>46265.625694</v>
       </c>
       <c r="J11" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" s="3">
         <v>42000000.0</v>
@@ -1337,7 +1337,7 @@
         <v>46265.631944</v>
       </c>
       <c r="J12" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12" s="3">
         <v>12000.0</v>
@@ -1436,7 +1436,7 @@
         <v>46265.645833</v>
       </c>
       <c r="J13" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" s="3">
         <v>49800000.0</v>
@@ -1531,7 +1531,7 @@
         <v>46265.645833</v>
       </c>
       <c r="J14" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" s="3"/>
       <c r="L14" s="0" t="inlineStr">
@@ -1624,7 +1624,7 @@
         <v>46265.646528</v>
       </c>
       <c r="J15" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K15" s="3">
         <v>3000000.0</v>
@@ -1719,7 +1719,7 @@
         <v>46265.666667</v>
       </c>
       <c r="J16" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" s="3">
         <v>175000000.0</v>
@@ -1814,7 +1814,7 @@
         <v>46265.666667</v>
       </c>
       <c r="J17" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K17" s="3">
         <v>4522419.0</v>
@@ -1901,7 +1901,7 @@
         <v>46265.708333</v>
       </c>
       <c r="J18" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" s="3">
         <v>434042600.0</v>
@@ -1998,7 +1998,7 @@
         <v>46265.854167</v>
       </c>
       <c r="J19" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K19" s="3">
         <v>4526046.0</v>
@@ -2085,7 +2085,7 @@
         <v>46266.604167</v>
       </c>
       <c r="J20" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K20" s="3"/>
       <c r="L20" s="0" t="inlineStr">
@@ -2178,7 +2178,7 @@
         <v>46266.625</v>
       </c>
       <c r="J21" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K21" s="3"/>
       <c r="L21" s="0" t="inlineStr">
@@ -2271,7 +2271,7 @@
         <v>46266.631944</v>
       </c>
       <c r="J22" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K22" s="3">
         <v>33150.0</v>
@@ -2366,7 +2366,7 @@
         <v>46266.666667</v>
       </c>
       <c r="J23" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K23" s="3">
         <v>12154650.0</v>
@@ -2460,7 +2460,7 @@
         <v>46266.666667</v>
       </c>
       <c r="J24" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K24" s="3">
         <v>190000000.0</v>
@@ -2555,7 +2555,7 @@
         <v>46266.692361</v>
       </c>
       <c r="J25" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K25" s="3"/>
       <c r="L25" s="0" t="inlineStr">
@@ -2648,7 +2648,7 @@
         <v>46267.625</v>
       </c>
       <c r="J26" s="0">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K26" s="3">
         <v>19800000.0</v>
@@ -2739,7 +2739,7 @@
         <v>46267.625</v>
       </c>
       <c r="J27" s="0">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K27" s="3"/>
       <c r="L27" s="0" t="inlineStr">
@@ -2832,7 +2832,7 @@
         <v>46267.645833</v>
       </c>
       <c r="J28" s="0">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K28" s="3">
         <v>22000000.0</v>
@@ -2927,7 +2927,7 @@
         <v>46267.708333</v>
       </c>
       <c r="J29" s="0">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K29" s="3">
         <v>15000000.0</v>
@@ -3018,7 +3018,7 @@
         <v>46267.709028</v>
       </c>
       <c r="J30" s="0">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K30" s="3"/>
       <c r="L30" s="0" t="inlineStr">
@@ -3116,7 +3116,7 @@
         <v>46267.749306</v>
       </c>
       <c r="J31" s="0">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K31" s="3">
         <v>250000000.0</v>
@@ -3211,7 +3211,7 @@
         <v>46268.500694</v>
       </c>
       <c r="J32" s="0">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K32" s="3">
         <v>70000000.0</v>
@@ -3307,7 +3307,7 @@
         <v>46268.600694</v>
       </c>
       <c r="J33" s="0">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K33" s="3">
         <v>10000000.0</v>
@@ -3406,7 +3406,7 @@
         <v>46268.600694</v>
       </c>
       <c r="J34" s="0">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K34" s="3">
         <v>32500000.0</v>
@@ -3505,7 +3505,7 @@
         <v>46268.625</v>
       </c>
       <c r="J35" s="0">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K35" s="3">
         <v>15000000.0</v>
@@ -3600,7 +3600,7 @@
         <v>46268.625</v>
       </c>
       <c r="J36" s="0">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K36" s="3">
         <v>269000000.0</v>
@@ -3702,7 +3702,7 @@
         <v>46268.625</v>
       </c>
       <c r="J37" s="0">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K37" s="3">
         <v>1989000.0</v>
@@ -3791,7 +3791,7 @@
         <v>46268.645833</v>
       </c>
       <c r="J38" s="0">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K38" s="3">
         <v>8000000.0</v>
@@ -3883,7 +3883,7 @@
         <v>46268.645833</v>
       </c>
       <c r="J39" s="0">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K39" s="3"/>
       <c r="L39" s="0" t="inlineStr">
@@ -3976,7 +3976,7 @@
         <v>46268.666667</v>
       </c>
       <c r="J40" s="0">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K40" s="3">
         <v>14000000.0</v>
@@ -4067,7 +4067,7 @@
         <v>46268.675</v>
       </c>
       <c r="J41" s="0">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K41" s="3"/>
       <c r="L41" s="0" t="inlineStr">
@@ -4156,7 +4156,7 @@
         <v>46268.708333</v>
       </c>
       <c r="J42" s="0">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K42" s="3">
         <v>202000000.0</v>
@@ -4247,7 +4247,7 @@
         <v>46268.75</v>
       </c>
       <c r="J43" s="0">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K43" s="3">
         <v>32000000.0</v>
@@ -4342,7 +4342,7 @@
         <v>46269.375</v>
       </c>
       <c r="J44" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K44" s="3">
         <v>13000000.0</v>
@@ -4437,7 +4437,7 @@
         <v>46269.5</v>
       </c>
       <c r="J45" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K45" s="3">
         <v>40856640.0</v>
@@ -4532,7 +4532,7 @@
         <v>46269.625</v>
       </c>
       <c r="J46" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K46" s="3">
         <v>2500000.0</v>
@@ -4619,7 +4619,7 @@
         <v>46269.625</v>
       </c>
       <c r="J47" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K47" s="3"/>
       <c r="L47" s="0" t="inlineStr">
@@ -4712,7 +4712,7 @@
         <v>46269.666667</v>
       </c>
       <c r="J48" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K48" s="3"/>
       <c r="L48" s="0" t="inlineStr">
@@ -4809,7 +4809,7 @@
         <v>46269.708333</v>
       </c>
       <c r="J49" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K49" s="3">
         <v>4000000.0</v>
@@ -4898,7 +4898,7 @@
         <v>46269.833333</v>
       </c>
       <c r="J50" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K50" s="3">
         <v>27000000.0</v>
@@ -4993,7 +4993,7 @@
         <v>46272.625</v>
       </c>
       <c r="J51" s="0">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K51" s="3">
         <v>60000000.0</v>
@@ -5088,7 +5088,7 @@
         <v>46272.625</v>
       </c>
       <c r="J52" s="0">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K52" s="3">
         <v>16000000.0</v>
@@ -5179,7 +5179,7 @@
         <v>46272.625</v>
       </c>
       <c r="J53" s="0">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K53" s="3"/>
       <c r="L53" s="0" t="inlineStr">
@@ -5272,7 +5272,7 @@
         <v>46272.625</v>
       </c>
       <c r="J54" s="0">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K54" s="3">
         <v>4728.0</v>
@@ -5367,7 +5367,7 @@
         <v>46272.625694</v>
       </c>
       <c r="J55" s="0">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K55" s="3"/>
       <c r="L55" s="0" t="inlineStr">
@@ -5464,7 +5464,7 @@
         <v>46272.625694</v>
       </c>
       <c r="J56" s="0">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K56" s="3"/>
       <c r="L56" s="0" t="inlineStr">
@@ -5553,7 +5553,7 @@
         <v>46272.63125</v>
       </c>
       <c r="J57" s="0">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K57" s="3">
         <v>14000000.0</v>
@@ -5649,7 +5649,7 @@
         <v>46272.631944</v>
       </c>
       <c r="J58" s="0">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K58" s="3"/>
       <c r="L58" s="0" t="inlineStr">
@@ -5742,7 +5742,7 @@
         <v>46272.645833</v>
       </c>
       <c r="J59" s="0">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K59" s="3">
         <v>11300000.0</v>
@@ -5841,7 +5841,7 @@
         <v>46272.645833</v>
       </c>
       <c r="J60" s="0">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K60" s="3">
         <v>21500000.0</v>
@@ -5940,7 +5940,7 @@
         <v>46272.666667</v>
       </c>
       <c r="J61" s="0">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K61" s="3">
         <v>29790000.0</v>
@@ -6039,7 +6039,7 @@
         <v>46272.666667</v>
       </c>
       <c r="J62" s="0">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K62" s="3">
         <v>272160000.0</v>
@@ -6138,7 +6138,7 @@
         <v>46272.666667</v>
       </c>
       <c r="J63" s="0">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K63" s="3">
         <v>927900000.0</v>
@@ -6229,7 +6229,7 @@
         <v>46272.666667</v>
       </c>
       <c r="J64" s="0">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K64" s="3">
         <v>30000000.0</v>
@@ -6331,7 +6331,7 @@
         <v>46272.706944</v>
       </c>
       <c r="J65" s="0">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K65" s="3">
         <v>1500000.0</v>
@@ -6418,7 +6418,7 @@
         <v>46273.375</v>
       </c>
       <c r="J66" s="0">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K66" s="3"/>
       <c r="L66" s="0" t="inlineStr">
@@ -6524,7 +6524,7 @@
         <v>46273.416667</v>
       </c>
       <c r="J67" s="0">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K67" s="3">
         <v>124000000.0</v>
@@ -6623,7 +6623,7 @@
         <v>46273.625694</v>
       </c>
       <c r="J68" s="0">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K68" s="3"/>
       <c r="L68" s="0" t="inlineStr">
@@ -6714,7 +6714,7 @@
         <v>46273.645833</v>
       </c>
       <c r="J69" s="0">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K69" s="3">
         <v>19980000.0</v>
@@ -6809,7 +6809,7 @@
         <v>46273.645833</v>
       </c>
       <c r="J70" s="0">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K70" s="3">
         <v>52270.0</v>
@@ -6900,7 +6900,7 @@
         <v>46273.666667</v>
       </c>
       <c r="J71" s="0">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K71" s="3"/>
       <c r="L71" s="0" t="inlineStr">
@@ -6997,7 +6997,7 @@
         <v>46274.463194</v>
       </c>
       <c r="J72" s="0">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K72" s="3"/>
       <c r="L72" s="0" t="inlineStr">
@@ -7090,7 +7090,7 @@
         <v>46274.5</v>
       </c>
       <c r="J73" s="0">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K73" s="3">
         <v>7167631.0</v>
@@ -7185,7 +7185,7 @@
         <v>46274.625</v>
       </c>
       <c r="J74" s="0">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K74" s="3">
         <v>1800000.0</v>
@@ -7272,7 +7272,7 @@
         <v>46274.625</v>
       </c>
       <c r="J75" s="0">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K75" s="3">
         <v>30754000.0</v>
@@ -7365,7 +7365,7 @@
         <v>46274.645833</v>
       </c>
       <c r="J76" s="0">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K76" s="3">
         <v>180329688.0</v>
@@ -7460,7 +7460,7 @@
         <v>46274.666667</v>
       </c>
       <c r="J77" s="0">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K77" s="3">
         <v>232851.0</v>
@@ -7555,7 +7555,7 @@
         <v>46275.5</v>
       </c>
       <c r="J78" s="0">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K78" s="3"/>
       <c r="L78" s="0" t="inlineStr">
@@ -7644,7 +7644,7 @@
         <v>46275.625</v>
       </c>
       <c r="J79" s="0">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K79" s="3">
         <v>240000000.0</v>
@@ -7739,7 +7739,7 @@
         <v>46275.625</v>
       </c>
       <c r="J80" s="0">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K80" s="3">
         <v>26000000.0</v>
@@ -7834,7 +7834,7 @@
         <v>46275.666667</v>
       </c>
       <c r="J81" s="0">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K81" s="3"/>
       <c r="L81" s="0" t="inlineStr">
@@ -7927,7 +7927,7 @@
         <v>46276.625</v>
       </c>
       <c r="J82" s="0">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K82" s="3"/>
       <c r="L82" s="0" t="inlineStr">
@@ -8020,7 +8020,7 @@
         <v>46276.666667</v>
       </c>
       <c r="J83" s="0">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K83" s="3"/>
       <c r="L83" s="0" t="inlineStr">
@@ -8113,7 +8113,7 @@
         <v>46276.666667</v>
       </c>
       <c r="J84" s="0">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K84" s="3"/>
       <c r="L84" s="0" t="inlineStr">
@@ -8210,7 +8210,7 @@
         <v>46279.625</v>
       </c>
       <c r="J85" s="0">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K85" s="3">
         <v>540000000.0</v>
@@ -8305,7 +8305,7 @@
         <v>46279.625</v>
       </c>
       <c r="J86" s="0">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K86" s="3"/>
       <c r="L86" s="0" t="inlineStr">
@@ -8396,7 +8396,7 @@
         <v>46279.625</v>
       </c>
       <c r="J87" s="0">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K87" s="3"/>
       <c r="L87" s="0" t="inlineStr">
@@ -8485,7 +8485,7 @@
         <v>46279.666667</v>
       </c>
       <c r="J88" s="0">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K88" s="3">
         <v>225000000.0</v>
@@ -8580,7 +8580,7 @@
         <v>46280.458333</v>
       </c>
       <c r="J89" s="0">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K89" s="3">
         <v>163000000.0</v>
@@ -8677,7 +8677,7 @@
         <v>46280.5</v>
       </c>
       <c r="J90" s="0">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K90" s="3">
         <v>132232000.0</v>
@@ -8768,7 +8768,7 @@
         <v>46280.625</v>
       </c>
       <c r="J91" s="0">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K91" s="3">
         <v>295121.0</v>
@@ -8867,7 +8867,7 @@
         <v>46280.6375</v>
       </c>
       <c r="J92" s="0">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K92" s="3"/>
       <c r="L92" s="0" t="inlineStr">
@@ -8960,7 +8960,7 @@
         <v>46281.583333</v>
       </c>
       <c r="J93" s="0">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K93" s="3">
         <v>204000000.0</v>
@@ -9051,7 +9051,7 @@
         <v>46281.729167</v>
       </c>
       <c r="J94" s="0">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K94" s="3">
         <v>388644480.0</v>
@@ -9146,7 +9146,7 @@
         <v>46282.375</v>
       </c>
       <c r="J95" s="0">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K95" s="3">
         <v>80000000.0</v>
@@ -9241,7 +9241,7 @@
         <v>46282.4375</v>
       </c>
       <c r="J96" s="0">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K96" s="3">
         <v>177000000.0</v>
@@ -9336,7 +9336,7 @@
         <v>46286.625694</v>
       </c>
       <c r="J97" s="0">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K97" s="3">
         <v>453590167.0</v>
@@ -9427,7 +9427,7 @@
         <v>46286.645833</v>
       </c>
       <c r="J98" s="0">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K98" s="3"/>
       <c r="L98" s="0" t="inlineStr">
@@ -9516,7 +9516,7 @@
         <v>46286.666667</v>
       </c>
       <c r="J99" s="0">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K99" s="3"/>
       <c r="L99" s="0" t="inlineStr">
@@ -9612,7 +9612,7 @@
         <v>46287.625</v>
       </c>
       <c r="J100" s="0">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K100" s="3">
         <v>366678654.0</v>
@@ -9708,7 +9708,7 @@
         <v>46287.625</v>
       </c>
       <c r="J101" s="0">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K101" s="3"/>
       <c r="L101" s="0" t="inlineStr">
@@ -9801,7 +9801,7 @@
         <v>46287.625694</v>
       </c>
       <c r="J102" s="0">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K102" s="3">
         <v>10000000.0</v>
@@ -9896,7 +9896,7 @@
         <v>46289.625</v>
       </c>
       <c r="J103" s="0">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K103" s="3"/>
       <c r="L103" s="0" t="inlineStr">
@@ -9992,7 +9992,7 @@
         <v>46289.729167</v>
       </c>
       <c r="J104" s="0">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K104" s="3">
         <v>414000000.0</v>
@@ -10089,7 +10089,7 @@
         <v>46290.625</v>
       </c>
       <c r="J105" s="0">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K105" s="3"/>
       <c r="L105" s="0" t="inlineStr">
@@ -10182,7 +10182,7 @@
         <v>46293.645833</v>
       </c>
       <c r="J106" s="0">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K106" s="3">
         <v>450000000.0</v>
@@ -10277,7 +10277,7 @@
         <v>46295.625</v>
       </c>
       <c r="J107" s="0">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K107" s="3">
         <v>24000.0</v>
@@ -10377,7 +10377,7 @@
         <v>46297.625</v>
       </c>
       <c r="J108" s="0">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K108" s="3">
         <v>565250.0</v>

--- a/web/descargas/licitaciones.xlsx
+++ b/web/descargas/licitaciones.xlsx
@@ -219,8 +219,462 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1057531-10-L126</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Contratación de Convenio Prótesis Fijas con sistema digital CADCAM 2026-2027</t>
+        </is>
+      </c>
+      <c r="C2" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Publicada</t>
+        </is>
+      </c>
+      <c r="D2" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SERVICIO NACIONAL DE SALUD HOSPITAL DE RIO NEGRO</t>
+        </is>
+      </c>
+      <c r="E2" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bienes y Servicios</t>
+        </is>
+      </c>
+      <c r="F2" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="G2" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Santiago</t>
+        </is>
+      </c>
+      <c r="H2" s="2">
+        <v>46265.489178</v>
+      </c>
+      <c r="I2" s="2">
+        <v>46273.666667</v>
+      </c>
+      <c r="J2" s="0">
+        <v>8</v>
+      </c>
+      <c r="K2" s="3">
+        <v>7000000.0</v>
+      </c>
+      <c r="L2" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CLP</t>
+        </is>
+      </c>
+      <c r="M2" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L1</t>
+        </is>
+      </c>
+      <c r="N2" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Equipamiento y suministros médicos / Equipos y suministros odontológicos / Suministros y equipos de odontología cosmética</t>
+        </is>
+      </c>
+      <c r="O2" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15 Unidad no definida · Coronas o formas de coronas</t>
+        </is>
+      </c>
+      <c r="P2" s="2"/>
+      <c r="Q2" s="2"/>
+      <c r="R2" s="0"/>
+      <c r="S2" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="T2" s="4"/>
+      <c r="U2" s="0"/>
+      <c r="V2" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Servicios de Convenio Prótesis Fijas con sistema digital CADCAM, para Beneficiarios del HRN para los años 2026-2027.
+-Considerar en comodato de equipos complementarios como PC y escáner, compatible con sistema digital. 
+-Completar anexos adjuntos y documentos
+El valor a ingresar en el portal mercado público, debe ser el valor total ofertado en Anexo N°7 divido por la cantidad referencial, considerando que el monto total, no debe superar el monto permitido en licitación L1 (menor a 100 UTM), caso</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="str">
+        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=1057531-10-L126","descargar bases")</f>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2107-142-LE26</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARRIENDO DE TOTEMS AUTOADMINISTRADOS PARA HSC</t>
+        </is>
+      </c>
+      <c r="C3" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Publicada</t>
+        </is>
+      </c>
+      <c r="D3" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SERVICIO DE SALUD HOSPITAL DE SANTA CRUZ</t>
+        </is>
+      </c>
+      <c r="E3" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hospital de Santa Cruz</t>
+        </is>
+      </c>
+      <c r="F3" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región del Libertador General Bernardo O´Higgins</t>
+        </is>
+      </c>
+      <c r="G3" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Santa Cruz</t>
+        </is>
+      </c>
+      <c r="H3" s="2">
+        <v>46265.345752</v>
+      </c>
+      <c r="I3" s="2">
+        <v>46276.747222</v>
+      </c>
+      <c r="J3" s="0">
+        <v>11</v>
+      </c>
+      <c r="K3" s="3"/>
+      <c r="L3" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CLP</t>
+        </is>
+      </c>
+      <c r="M3" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LE</t>
+        </is>
+      </c>
+      <c r="N3" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Equipos informáticos y accesorios / Computadores</t>
+        </is>
+      </c>
+      <c r="O3" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">36 Mes · Servidores de gama alta</t>
+        </is>
+      </c>
+      <c r="P3" s="2"/>
+      <c r="Q3" s="2"/>
+      <c r="R3" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">36 meses</t>
+        </is>
+      </c>
+      <c r="S3" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="T3" s="4"/>
+      <c r="U3" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nicolás Salgado Marín</t>
+        </is>
+      </c>
+      <c r="V3" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARRIENDO DE TOTEMS AUTOADMINISTRADOS PARA EL HOSPITAL DE SANTA CRUZ
+El presente proceso de licitación pública tiene por objeto la contratación del Servicio de Arriendo de tres (3) Tótems de Marcaje mediante tecnología NFC/RFID, destinados a la implementación de una solución tecnológica para la identificación y registro de usuarios del Hospital de Santa Cruz.</t>
+        </is>
+      </c>
+      <c r="W3" s="5" t="str">
+        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=2107-142-LE26","descargar bases")</f>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">837-101-LP26</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CDP 477 SERVICIO DE OPERACIÓN SISTEMA DE CONTROL CENTRALIZADO BMS Y SISTEMA DE TELEVIGILANCIA SOFTWARE HIKCENTRAL PROFESSIONAL DE EDIFICIO INSTITUCIONAL SML SANTIAGO</t>
+        </is>
+      </c>
+      <c r="C4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Publicada</t>
+        </is>
+      </c>
+      <c r="D4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SERVICIO MEDICO LEGAL</t>
+        </is>
+      </c>
+      <c r="E4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SERVICIO MEDICO LEGAL</t>
+        </is>
+      </c>
+      <c r="F4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="G4" s="0"/>
+      <c r="H4" s="2">
+        <v>46265.419491</v>
+      </c>
+      <c r="I4" s="2">
+        <v>46287.645833</v>
+      </c>
+      <c r="J4" s="0">
+        <v>22</v>
+      </c>
+      <c r="K4" s="3">
+        <v>346885000.0</v>
+      </c>
+      <c r="L4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CLP</t>
+        </is>
+      </c>
+      <c r="M4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LP</t>
+        </is>
+      </c>
+      <c r="N4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Equipos y suministros de defensa, orden público, protección y seguridad / Seguridad, vigilancia y detección / Equipo de vigilancia y detección, Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de administración de redes</t>
+        </is>
+      </c>
+      <c r="O4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12 Mes · Software de administración · 12 Mes · Sistemas de control de acceso o de seguridad</t>
+        </is>
+      </c>
+      <c r="P4" s="2"/>
+      <c r="Q4" s="2"/>
+      <c r="R4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12 meses</t>
+        </is>
+      </c>
+      <c r="S4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="T4" s="4"/>
+      <c r="U4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vicente Muñoz, profesional DLI</t>
+        </is>
+      </c>
+      <c r="V4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Se requiere contar con el SERVICIO DE OPERACIÓN PARA EL SISTEMA DE CONTROL CENTRALIZADO (BMS) SOFTWARE ENTELIWEB Y EL SISTEMA DE TELEVIGILANCIA SOFTWARE HIKCENTRAL) Y SU EQUIPAMIENTO ASOCIADO PERTENECIENTES AL EDIFICIO INSTITUCIONAL DEL SERVICIO MÉDICO LEGAL METROPOLITANO (SML), con el objeto de asegurar su correcta operación, revisión de instalaciones y programación en los sistemas y equipamiento instalados</t>
+        </is>
+      </c>
+      <c r="W4" s="5" t="str">
+        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=837-101-LP26","descargar bases")</f>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1274285-45-LP26</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Software de gestión Droguería Comunal</t>
+        </is>
+      </c>
+      <c r="C5" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Publicada</t>
+        </is>
+      </c>
+      <c r="D5" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CORPORACION MUNICIPAL DE EDUCACION Y SALUD DE SAN BERNARDO</t>
+        </is>
+      </c>
+      <c r="E5" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SALUD</t>
+        </is>
+      </c>
+      <c r="F5" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="G5" s="0"/>
+      <c r="H5" s="2">
+        <v>46265.493137</v>
+      </c>
+      <c r="I5" s="2">
+        <v>46293.75</v>
+      </c>
+      <c r="J5" s="0">
+        <v>28</v>
+      </c>
+      <c r="K5" s="3"/>
+      <c r="L5" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CLP</t>
+        </is>
+      </c>
+      <c r="M5" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LP</t>
+        </is>
+      </c>
+      <c r="N5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de gestión</t>
+        </is>
+      </c>
+      <c r="O5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 Unidad · Software de cadena de suministro y logística de planificación de requisitos de materiales</t>
+        </is>
+      </c>
+      <c r="P5" s="2"/>
+      <c r="Q5" s="2"/>
+      <c r="R5" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">36 meses</t>
+        </is>
+      </c>
+      <c r="S5" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="T5" s="4"/>
+      <c r="U5" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Erwin Rodriguez Basulto</t>
+        </is>
+      </c>
+      <c r="V5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">La Corporación Municipal de Educación y Salud de San Bernardo requiere contratar para la Droguería Comunal y Centros de Salud un Sistema Informático que permita controlar los procesos de bodega y la gestión de la Droguería y Centros de Salud donde se encuentran contempladas, entre otras, las siguientes áreas:
+•Recepción
+•Almacenamiento
+•Despacho
+•Inventario 
+•Reportes de Gestión</t>
+        </is>
+      </c>
+      <c r="W5" s="5" t="str">
+        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=1274285-45-LP26","descargar bases")</f>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">976-15-O126</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ampliación Plataformas Comercial y General Ad. El Loa</t>
+        </is>
+      </c>
+      <c r="C6" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Publicada</t>
+        </is>
+      </c>
+      <c r="D6" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+        </is>
+      </c>
+      <c r="E6" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dirección de Aeropuertos - MOPTT</t>
+        </is>
+      </c>
+      <c r="F6" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Antofagasta </t>
+        </is>
+      </c>
+      <c r="G6" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Santiago</t>
+        </is>
+      </c>
+      <c r="H6" s="2">
+        <v>46265.342303</v>
+      </c>
+      <c r="I6" s="2">
+        <v>46304.458333</v>
+      </c>
+      <c r="J6" s="0">
+        <v>39</v>
+      </c>
+      <c r="K6" s="3"/>
+      <c r="L6" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CLP</t>
+        </is>
+      </c>
+      <c r="M6" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">O1</t>
+        </is>
+      </c>
+      <c r="N6" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Consultoria / Consultoria / Planificación y Factibilidad</t>
+        </is>
+      </c>
+      <c r="O6" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 Unidad · Licitación Pública de Obra</t>
+        </is>
+      </c>
+      <c r="P6" s="2"/>
+      <c r="Q6" s="2"/>
+      <c r="R6" s="0"/>
+      <c r="S6" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="T6" s="4"/>
+      <c r="U6" s="0"/>
+      <c r="V6" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Esta Dirección necesita llamar a licitación para contratar la obra Ampliación Plataformas Comercial y General Aeródromo El Loa.</t>
+        </is>
+      </c>
+      <c r="W6" s="5" t="str">
+        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=976-15-O126","descargar bases")</f>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:W1"/>
+  <autoFilter ref="A1:W6"/>
 </worksheet>
 </file>
 
@@ -6957,12 +7411,12 @@
     <row r="72">
       <c r="A72" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1978-85-LE26</t>
+          <t xml:space="preserve">1057531-10-L126</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Soporte Acronis Backup Cloud y Acronis Storage</t>
+          <t xml:space="preserve">Contratación de Convenio Prótesis Fijas con sistema digital CADCAM 2026-2027</t>
         </is>
       </c>
       <c r="C72" s="0" t="inlineStr">
@@ -6972,34 +7426,36 @@
       </c>
       <c r="D72" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">SERVICIO DE SALUD DEL MAULE</t>
+          <t xml:space="preserve">SERVICIO NACIONAL DE SALUD HOSPITAL DE RIO NEGRO</t>
         </is>
       </c>
       <c r="E72" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Servicio de Salud del Maule</t>
+          <t xml:space="preserve">Bienes y Servicios</t>
         </is>
       </c>
       <c r="F72" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t xml:space="preserve">Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="G72" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Maule</t>
+          <t xml:space="preserve">Santiago</t>
         </is>
       </c>
       <c r="H72" s="2">
-        <v>46260.668773</v>
+        <v>46265.489178</v>
       </c>
       <c r="I72" s="2">
-        <v>46274.463194</v>
+        <v>46273.666667</v>
       </c>
       <c r="J72" s="0">
-        <v>9</v>
-      </c>
-      <c r="K72" s="3"/>
+        <v>8</v>
+      </c>
+      <c r="K72" s="3">
+        <v>7000000.0</v>
+      </c>
       <c r="L72" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">CLP</t>
@@ -7007,55 +7463,50 @@
       </c>
       <c r="M72" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">LE</t>
+          <t xml:space="preserve">L1</t>
         </is>
       </c>
       <c r="N72" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de gestión</t>
+          <t xml:space="preserve">Equipamiento y suministros médicos / Equipos y suministros odontológicos / Suministros y equipos de odontología cosmética</t>
         </is>
       </c>
       <c r="O72" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">36 Mes · Software de sistema experto</t>
+          <t xml:space="preserve">15 Unidad no definida · Coronas o formas de coronas</t>
         </is>
       </c>
       <c r="P72" s="2"/>
       <c r="Q72" s="2"/>
-      <c r="R72" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">36 meses</t>
-        </is>
-      </c>
+      <c r="R72" s="0"/>
       <c r="S72" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">No</t>
         </is>
       </c>
       <c r="T72" s="4"/>
-      <c r="U72" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Hector Bastidas V</t>
-        </is>
-      </c>
+      <c r="U72" s="0"/>
       <c r="V72" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">El propósito general de la contratación es asegurar de manera continua la disponibilidad, integridad y resguardo de la información institucional, constituyendo una herramienta estratégica e indispensable para la correcta operación y seguridad de las plataformas tecnológicas administradas por el Departamento TIC</t>
+          <t xml:space="preserve">Servicios de Convenio Prótesis Fijas con sistema digital CADCAM, para Beneficiarios del HRN para los años 2026-2027.
+-Considerar en comodato de equipos complementarios como PC y escáner, compatible con sistema digital. 
+-Completar anexos adjuntos y documentos
+El valor a ingresar en el portal mercado público, debe ser el valor total ofertado en Anexo N°7 divido por la cantidad referencial, considerando que el monto total, no debe superar el monto permitido en licitación L1 (menor a 100 UTM), caso</t>
         </is>
       </c>
       <c r="W72" s="5" t="str">
-        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=1978-85-LE26","descargar bases")</f>
+        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=1057531-10-L126","descargar bases")</f>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">742475-4-LE26</t>
+          <t xml:space="preserve">1978-85-LE26</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adquisición de equipos informáticos para el programa Oficina Local de la Niñez</t>
+          <t xml:space="preserve">Soporte Acronis Backup Cloud y Acronis Storage</t>
         </is>
       </c>
       <c r="C73" s="0" t="inlineStr">
@@ -7065,36 +7516,34 @@
       </c>
       <c r="D73" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">I MUNICIPALIDAD DE VILLA ALEMANA</t>
+          <t xml:space="preserve">SERVICIO DE SALUD DEL MAULE</t>
         </is>
       </c>
       <c r="E73" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ABASTECIMIENTO PROGRAMAS</t>
+          <t xml:space="preserve">Servicio de Salud del Maule</t>
         </is>
       </c>
       <c r="F73" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t xml:space="preserve">Región del Maule </t>
         </is>
       </c>
       <c r="G73" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Villa Alemana</t>
+          <t xml:space="preserve">Maule</t>
         </is>
       </c>
       <c r="H73" s="2">
-        <v>46261.5564</v>
+        <v>46260.668773</v>
       </c>
       <c r="I73" s="2">
-        <v>46274.5</v>
+        <v>46274.463194</v>
       </c>
       <c r="J73" s="0">
         <v>9</v>
       </c>
-      <c r="K73" s="3">
-        <v>7167631.0</v>
-      </c>
+      <c r="K73" s="3"/>
       <c r="L73" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">CLP</t>
@@ -7107,17 +7556,21 @@
       </c>
       <c r="N73" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Equipos informáticos y accesorios / Computadores</t>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de gestión</t>
         </is>
       </c>
       <c r="O73" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 Unidad · Notebook, laptop o computador portátil excepto Tablet PC</t>
+          <t xml:space="preserve">36 Mes · Software de sistema experto</t>
         </is>
       </c>
       <c r="P73" s="2"/>
       <c r="Q73" s="2"/>
-      <c r="R73" s="0"/>
+      <c r="R73" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">36 meses</t>
+        </is>
+      </c>
       <c r="S73" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">No</t>
@@ -7126,10 +7579,101 @@
       <c r="T73" s="4"/>
       <c r="U73" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hector Bastidas V</t>
+        </is>
+      </c>
+      <c r="V73" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">El propósito general de la contratación es asegurar de manera continua la disponibilidad, integridad y resguardo de la información institucional, constituyendo una herramienta estratégica e indispensable para la correcta operación y seguridad de las plataformas tecnológicas administradas por el Departamento TIC</t>
+        </is>
+      </c>
+      <c r="W73" s="5" t="str">
+        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=1978-85-LE26","descargar bases")</f>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">742475-4-LE26</t>
+        </is>
+      </c>
+      <c r="B74" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Adquisición de equipos informáticos para el programa Oficina Local de la Niñez</t>
+        </is>
+      </c>
+      <c r="C74" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Publicada</t>
+        </is>
+      </c>
+      <c r="D74" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">I MUNICIPALIDAD DE VILLA ALEMANA</t>
+        </is>
+      </c>
+      <c r="E74" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ABASTECIMIENTO PROGRAMAS</t>
+        </is>
+      </c>
+      <c r="F74" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Valparaíso </t>
+        </is>
+      </c>
+      <c r="G74" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Villa Alemana</t>
+        </is>
+      </c>
+      <c r="H74" s="2">
+        <v>46261.5564</v>
+      </c>
+      <c r="I74" s="2">
+        <v>46274.5</v>
+      </c>
+      <c r="J74" s="0">
+        <v>9</v>
+      </c>
+      <c r="K74" s="3">
+        <v>7167631.0</v>
+      </c>
+      <c r="L74" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CLP</t>
+        </is>
+      </c>
+      <c r="M74" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LE</t>
+        </is>
+      </c>
+      <c r="N74" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Equipos informáticos y accesorios / Computadores</t>
+        </is>
+      </c>
+      <c r="O74" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 Unidad · Notebook, laptop o computador portátil excepto Tablet PC</t>
+        </is>
+      </c>
+      <c r="P74" s="2"/>
+      <c r="Q74" s="2"/>
+      <c r="R74" s="0"/>
+      <c r="S74" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="T74" s="4"/>
+      <c r="U74" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">ALAN RAAD</t>
         </is>
       </c>
-      <c r="V73" s="4" t="inlineStr">
+      <c r="V74" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Adquisición de equipamiento informático por la necesidad de fortalecer la capacidad operativa, técnica y administrativa de la Oficina Local de la Niñez, asegurando la disponibilidad de herramientas tecnológicas adecuadas para el desarrollo de sus funciones institucionales.
 Estos equipos permitirán la gestión, registro, análisis y seguimiento de casos, la elaboración de informes técnicos, el acceso a plataformas institucionales, la coordinación intersectorial y la ejecución de actividades de promoción y protección de derechos dirigidas a niños, niñas, adolescentes y sus familias.
@@ -7138,106 +7682,19 @@
 La adquisición considera, además, equipamientos indispensables para el correcto funcionamiento de los puestos de trabaj</t>
         </is>
       </c>
-      <c r="W73" s="5" t="str">
+      <c r="W74" s="5" t="str">
         <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=742475-4-LE26","descargar bases")</f>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1469-175-L126</t>
-        </is>
-      </c>
-      <c r="B74" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TABLERO PARA BOMBA SUMERGIBLE, CAMPUS TALCA, UNIVERSIDAD DE TALCA.</t>
-        </is>
-      </c>
-      <c r="C74" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Publicada</t>
-        </is>
-      </c>
-      <c r="D74" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UNIVERSIDAD DE TALCA</t>
-        </is>
-      </c>
-      <c r="E74" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Universidad de Talca</t>
-        </is>
-      </c>
-      <c r="F74" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Región del Maule </t>
-        </is>
-      </c>
-      <c r="G74" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Talca</t>
-        </is>
-      </c>
-      <c r="H74" s="2">
-        <v>46260.508333</v>
-      </c>
-      <c r="I74" s="2">
-        <v>46274.625</v>
-      </c>
-      <c r="J74" s="0">
-        <v>9</v>
-      </c>
-      <c r="K74" s="3">
-        <v>1800000.0</v>
-      </c>
-      <c r="L74" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CLP</t>
-        </is>
-      </c>
-      <c r="M74" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">L1</t>
-        </is>
-      </c>
-      <c r="N74" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Equipamiento para el acondicionamiento, distribución y filtrado de fluidos / Bombas y compresores industriales / Bombas</t>
-        </is>
-      </c>
-      <c r="O74" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1 Unidad · Bombas sumergibles</t>
-        </is>
-      </c>
-      <c r="P74" s="2"/>
-      <c r="Q74" s="2"/>
-      <c r="R74" s="0"/>
-      <c r="S74" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">No</t>
-        </is>
-      </c>
-      <c r="T74" s="4"/>
-      <c r="U74" s="0"/>
-      <c r="V74" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">La presente contratación considera la ejecución de obras menores en jardín botánico, para instalar un tablero eléctrico nuevo, el cual debe cumplir con la normativa eléctrica chilena y protecciones para la bomba.</t>
-        </is>
-      </c>
-      <c r="W74" s="5" t="str">
-        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=1469-175-L126","descargar bases")</f>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1562-52-LE26</t>
+          <t xml:space="preserve">1469-175-L126</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADQUISICIÓN RENOVACIÓN PLATAFORMA ROCSCIENCE</t>
+          <t xml:space="preserve">TABLERO PARA BOMBA SUMERGIBLE, CAMPUS TALCA, UNIVERSIDAD DE TALCA.</t>
         </is>
       </c>
       <c r="C75" s="0" t="inlineStr">
@@ -7247,26 +7704,26 @@
       </c>
       <c r="D75" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">SERVICIO NACIONAL DE GEOLOGIA Y MINERIA</t>
+          <t xml:space="preserve">UNIVERSIDAD DE TALCA</t>
         </is>
       </c>
       <c r="E75" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Servicio Nacional de Geología y Minería</t>
+          <t xml:space="preserve">Universidad de Talca</t>
         </is>
       </c>
       <c r="F75" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región Metropolitana de Santiago</t>
+          <t xml:space="preserve">Región del Maule </t>
         </is>
       </c>
       <c r="G75" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Providencia</t>
+          <t xml:space="preserve">Talca</t>
         </is>
       </c>
       <c r="H75" s="2">
-        <v>46262.475579</v>
+        <v>46260.508333</v>
       </c>
       <c r="I75" s="2">
         <v>46274.625</v>
@@ -7275,7 +7732,7 @@
         <v>9</v>
       </c>
       <c r="K75" s="3">
-        <v>30754000.0</v>
+        <v>1800000.0</v>
       </c>
       <c r="L75" s="0" t="inlineStr">
         <is>
@@ -7284,148 +7741,144 @@
       </c>
       <c r="M75" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">LE</t>
+          <t xml:space="preserve">L1</t>
         </is>
       </c>
       <c r="N75" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de gestión</t>
+          <t xml:space="preserve">Equipamiento para el acondicionamiento, distribución y filtrado de fluidos / Bombas y compresores industriales / Bombas</t>
         </is>
       </c>
       <c r="O75" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 Unidad · Software de gestión de licencias</t>
+          <t xml:space="preserve">1 Unidad · Bombas sumergibles</t>
         </is>
       </c>
       <c r="P75" s="2"/>
       <c r="Q75" s="2"/>
-      <c r="R75" s="0" t="inlineStr">
+      <c r="R75" s="0"/>
+      <c r="S75" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="T75" s="4"/>
+      <c r="U75" s="0"/>
+      <c r="V75" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">La presente contratación considera la ejecución de obras menores en jardín botánico, para instalar un tablero eléctrico nuevo, el cual debe cumplir con la normativa eléctrica chilena y protecciones para la bomba.</t>
+        </is>
+      </c>
+      <c r="W75" s="5" t="str">
+        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=1469-175-L126","descargar bases")</f>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1562-52-LE26</t>
+        </is>
+      </c>
+      <c r="B76" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADQUISICIÓN RENOVACIÓN PLATAFORMA ROCSCIENCE</t>
+        </is>
+      </c>
+      <c r="C76" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Publicada</t>
+        </is>
+      </c>
+      <c r="D76" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SERVICIO NACIONAL DE GEOLOGIA Y MINERIA</t>
+        </is>
+      </c>
+      <c r="E76" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Servicio Nacional de Geología y Minería</t>
+        </is>
+      </c>
+      <c r="F76" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="G76" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Providencia</t>
+        </is>
+      </c>
+      <c r="H76" s="2">
+        <v>46262.475579</v>
+      </c>
+      <c r="I76" s="2">
+        <v>46274.625</v>
+      </c>
+      <c r="J76" s="0">
+        <v>9</v>
+      </c>
+      <c r="K76" s="3">
+        <v>30754000.0</v>
+      </c>
+      <c r="L76" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CLP</t>
+        </is>
+      </c>
+      <c r="M76" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LE</t>
+        </is>
+      </c>
+      <c r="N76" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de gestión</t>
+        </is>
+      </c>
+      <c r="O76" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 Unidad · Software de gestión de licencias</t>
+        </is>
+      </c>
+      <c r="P76" s="2"/>
+      <c r="Q76" s="2"/>
+      <c r="R76" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">12 meses</t>
         </is>
       </c>
-      <c r="S75" s="0" t="inlineStr">
+      <c r="S76" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">No</t>
         </is>
       </c>
-      <c r="T75" s="4"/>
-      <c r="U75" s="0" t="inlineStr">
+      <c r="T76" s="4"/>
+      <c r="U76" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Hugo Neira</t>
         </is>
       </c>
-      <c r="V75" s="4" t="inlineStr">
+      <c r="V76" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">El objetivo de la contratación es mantener la continuidad operativa y disponibilidad de las herramientas especializadas Rocscience utilizadas por SERNAGEOMIN, mediante la renovación de las respectivas licencias de software.
 La renovación permitirá disponer de herramientas especializadas para el desarrollo de análisis geotécnicos y geomecánicos relacionados con materias de competencia institucional, incluyendo estabilidad de taludes, depósitos de relaves, macizos rocosos, caída de rocas, sostenimiento y modelación numérica.
 Asimismo, se busca asegurar que las licencias cuenten con los servicios de mantenimiento asociados durante su período de vigencia.</t>
         </is>
       </c>
-      <c r="W75" s="5" t="str">
+      <c r="W76" s="5" t="str">
         <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=1562-52-LE26","descargar bases")</f>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1057390-48-LP26</t>
-        </is>
-      </c>
-      <c r="B76" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CONV. RADIOCOMUNICACIÓN DIGITAL SAMU</t>
-        </is>
-      </c>
-      <c r="C76" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Publicada</t>
-        </is>
-      </c>
-      <c r="D76" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SERVICIO DE SALUD ARAUCANIA NORTE</t>
-        </is>
-      </c>
-      <c r="E76" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bienes y Servicios</t>
-        </is>
-      </c>
-      <c r="F76" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
-        </is>
-      </c>
-      <c r="G76" s="0"/>
-      <c r="H76" s="2">
-        <v>46254.446921</v>
-      </c>
-      <c r="I76" s="2">
-        <v>46274.645833</v>
-      </c>
-      <c r="J76" s="0">
-        <v>9</v>
-      </c>
-      <c r="K76" s="3">
-        <v>180329688.0</v>
-      </c>
-      <c r="L76" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CLP</t>
-        </is>
-      </c>
-      <c r="M76" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LP</t>
-        </is>
-      </c>
-      <c r="N76" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Servicios básicos y de información pública / Telecomunicaciones / Servicios de radio</t>
-        </is>
-      </c>
-      <c r="O76" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1 Mes · Sistemas de radio a pequeña escala</t>
-        </is>
-      </c>
-      <c r="P76" s="2"/>
-      <c r="Q76" s="2"/>
-      <c r="R76" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24 meses</t>
-        </is>
-      </c>
-      <c r="S76" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">No</t>
-        </is>
-      </c>
-      <c r="T76" s="4"/>
-      <c r="U76" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gastón Lorca Troncoso</t>
-        </is>
-      </c>
-      <c r="V76" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">La presente licitación tiene como objetivo, contratar un servicio mensual de comunicaciones digitales de voz para SAMU Malleco, según Especificaciones Técnicas (Anexo 4).</t>
-        </is>
-      </c>
-      <c r="W76" s="5" t="str">
-        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=1057390-48-LP26","descargar bases")</f>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1605-36-LR26</t>
+          <t xml:space="preserve">1057390-48-LP26</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">LR-4252 Servicio de Red Datos WAN</t>
+          <t xml:space="preserve">CONV. RADIOCOMUNICACIÓN DIGITAL SAMU</t>
         </is>
       </c>
       <c r="C77" s="0" t="inlineStr">
@@ -7435,61 +7888,57 @@
       </c>
       <c r="D77" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
+          <t xml:space="preserve">SERVICIO DE SALUD ARAUCANIA NORTE</t>
         </is>
       </c>
       <c r="E77" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">SII Dirección Nacional</t>
+          <t xml:space="preserve">Bienes y Servicios</t>
         </is>
       </c>
       <c r="F77" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región Metropolitana de Santiago</t>
-        </is>
-      </c>
-      <c r="G77" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Santiago</t>
-        </is>
-      </c>
+          <t xml:space="preserve">Región de la Araucanía </t>
+        </is>
+      </c>
+      <c r="G77" s="0"/>
       <c r="H77" s="2">
-        <v>46195.661111</v>
+        <v>46254.446921</v>
       </c>
       <c r="I77" s="2">
-        <v>46274.666667</v>
+        <v>46274.645833</v>
       </c>
       <c r="J77" s="0">
         <v>9</v>
       </c>
       <c r="K77" s="3">
-        <v>232851.0</v>
+        <v>180329688.0</v>
       </c>
       <c r="L77" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">CLF</t>
+          <t xml:space="preserve">CLP</t>
         </is>
       </c>
       <c r="M77" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">LR</t>
+          <t xml:space="preserve">LP</t>
         </is>
       </c>
       <c r="N77" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Servicios basados en ingeniería, ciencias sociales y tecnología de la información / Servicios informáticos / Servicios para internet</t>
+          <t xml:space="preserve">Servicios básicos y de información pública / Telecomunicaciones / Servicios de radio</t>
         </is>
       </c>
       <c r="O77" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">72 Mes · Proveedores de servicio de Internet (ISP) · 72 Mes · Proveedores de servicio de Internet (ISP)</t>
+          <t xml:space="preserve">1 Mes · Sistemas de radio a pequeña escala</t>
         </is>
       </c>
       <c r="P77" s="2"/>
       <c r="Q77" s="2"/>
       <c r="R77" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">72 meses</t>
+          <t xml:space="preserve">24 meses</t>
         </is>
       </c>
       <c r="S77" s="0" t="inlineStr">
@@ -7500,27 +7949,27 @@
       <c r="T77" s="4"/>
       <c r="U77" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Luis Venegas</t>
+          <t xml:space="preserve">Gastón Lorca Troncoso</t>
         </is>
       </c>
       <c r="V77" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">El objetivo de la presente licitación es disponer de la prestación de servicios de red de transmisión de datos y voz con cobertura en todo el territorio nacional, y de servicios de red adicionales con facilidades de interconexión con otras redes yo sistemas análogos y digitales, en el Servicio de Impuestos Internos.</t>
+          <t xml:space="preserve">La presente licitación tiene como objetivo, contratar un servicio mensual de comunicaciones digitales de voz para SAMU Malleco, según Especificaciones Técnicas (Anexo 4).</t>
         </is>
       </c>
       <c r="W77" s="5" t="str">
-        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=1605-36-LR26","descargar bases")</f>
+        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=1057390-48-LP26","descargar bases")</f>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1057501-488-LE26</t>
+          <t xml:space="preserve">1605-36-LR26</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ARRIENDO MODULOS BODEGA PARA INFORMÁTICA HSR</t>
+          <t xml:space="preserve">LR-4252 Servicio de Red Datos WAN</t>
         </is>
       </c>
       <c r="C78" s="0" t="inlineStr">
@@ -7530,12 +7979,12 @@
       </c>
       <c r="D78" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
+          <t xml:space="preserve">SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
         </is>
       </c>
       <c r="E78" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
+          <t xml:space="preserve">SII Dirección Nacional</t>
         </is>
       </c>
       <c r="F78" s="0" t="inlineStr">
@@ -7545,75 +7994,77 @@
       </c>
       <c r="G78" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Puente Alto</t>
+          <t xml:space="preserve">Santiago</t>
         </is>
       </c>
       <c r="H78" s="2">
-        <v>46261.515278</v>
+        <v>46195.661111</v>
       </c>
       <c r="I78" s="2">
-        <v>46275.5</v>
+        <v>46274.666667</v>
       </c>
       <c r="J78" s="0">
-        <v>10</v>
-      </c>
-      <c r="K78" s="3"/>
+        <v>9</v>
+      </c>
+      <c r="K78" s="3">
+        <v>232851.0</v>
+      </c>
       <c r="L78" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">CLP</t>
+          <t xml:space="preserve">CLF</t>
         </is>
       </c>
       <c r="M78" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">LE</t>
+          <t xml:space="preserve">LR</t>
         </is>
       </c>
       <c r="N78" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Servicios de construcción y mantenimiento / Construcción de edificios en general / Construcción de obras civiles y infraestructuras</t>
+          <t xml:space="preserve">Servicios basados en ingeniería, ciencias sociales y tecnología de la información / Servicios informáticos / Servicios para internet</t>
         </is>
       </c>
       <c r="O78" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 Unidad · Construcción de obras civiles</t>
+          <t xml:space="preserve">72 Mes · Proveedores de servicio de Internet (ISP) · 72 Mes · Proveedores de servicio de Internet (ISP)</t>
         </is>
       </c>
       <c r="P78" s="2"/>
       <c r="Q78" s="2"/>
-      <c r="R78" s="0"/>
+      <c r="R78" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">72 meses</t>
+        </is>
+      </c>
       <c r="S78" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">No</t>
         </is>
       </c>
-      <c r="T78" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16.- PROHIBICIÓN DE CESIÓN</t>
-        </is>
-      </c>
+      <c r="T78" s="4"/>
       <c r="U78" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cristian Diaz</t>
+          <t xml:space="preserve">Luis Venegas</t>
         </is>
       </c>
       <c r="V78" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">El Hospital Dr. Sótero del Río en adelante HSR, requiere contratar a una persona natural o jurídica para el “ARRIENDO DE DOS 02 MODULOS BODEGAS PARA LA UNIDAD DE IN-FORMATICA HSR.”, en dependencias del Hospital Dr. Sótero del Rio, ubicado en Av. Concha y Toro 3459 comuna de Puente Alto, de acuerdo a los requerimientos señalados en las Bases Técnicas que se adjuntan, siendo responsabilidad de la Empresa Contratista adjudicada la man-tención, instalación y habilitación de los módulos en las condiciones estipuladas en las Bases de licitación, administrativas y técnicas</t>
+          <t xml:space="preserve">El objetivo de la presente licitación es disponer de la prestación de servicios de red de transmisión de datos y voz con cobertura en todo el territorio nacional, y de servicios de red adicionales con facilidades de interconexión con otras redes yo sistemas análogos y digitales, en el Servicio de Impuestos Internos.</t>
         </is>
       </c>
       <c r="W78" s="5" t="str">
-        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=1057501-488-LE26","descargar bases")</f>
+        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=1605-36-LR26","descargar bases")</f>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1020-38-LP26</t>
+          <t xml:space="preserve">1057501-488-LE26</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adquisición de Plataforma Next Generation Firewall</t>
+          <t xml:space="preserve">ARRIENDO MODULOS BODEGA PARA INFORMÁTICA HSR</t>
         </is>
       </c>
       <c r="C79" s="0" t="inlineStr">
@@ -7623,12 +8074,12 @@
       </c>
       <c r="D79" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t xml:space="preserve">COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
         </is>
       </c>
       <c r="E79" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">MOP Subsecretaría </t>
+          <t xml:space="preserve">COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
         </is>
       </c>
       <c r="F79" s="0" t="inlineStr">
@@ -7636,19 +8087,21 @@
           <t xml:space="preserve">Región Metropolitana de Santiago</t>
         </is>
       </c>
-      <c r="G79" s="0"/>
+      <c r="G79" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Puente Alto</t>
+        </is>
+      </c>
       <c r="H79" s="2">
-        <v>46252.442905</v>
+        <v>46261.515278</v>
       </c>
       <c r="I79" s="2">
-        <v>46275.625</v>
+        <v>46275.5</v>
       </c>
       <c r="J79" s="0">
         <v>10</v>
       </c>
-      <c r="K79" s="3">
-        <v>240000000.0</v>
-      </c>
+      <c r="K79" s="3"/>
       <c r="L79" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">CLP</t>
@@ -7656,26 +8109,22 @@
       </c>
       <c r="M79" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">LP</t>
+          <t xml:space="preserve">LE</t>
         </is>
       </c>
       <c r="N79" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Equipos, plataformas y accesorios de redes multimedia, voz y datos / Equipos de seguridad de red, Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de administración de redes</t>
+          <t xml:space="preserve">Servicios de construcción y mantenimiento / Construcción de edificios en general / Construcción de obras civiles y infraestructuras</t>
         </is>
       </c>
       <c r="O79" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 Unidad · Equipo de seguridad de red de firewall · 1 Unidad · Software de vigilancia de redes</t>
+          <t xml:space="preserve">2 Unidad · Construcción de obras civiles</t>
         </is>
       </c>
       <c r="P79" s="2"/>
       <c r="Q79" s="2"/>
-      <c r="R79" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16 meses</t>
-        </is>
-      </c>
+      <c r="R79" s="0"/>
       <c r="S79" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">No</t>
@@ -7683,32 +8132,32 @@
       </c>
       <c r="T79" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Conforme al punto 10.5 de las Bases Administrativas, el oferente adjudicado no podrá subcontratar los servicios derivados de la ejecución del Contrato</t>
+          <t xml:space="preserve">16.- PROHIBICIÓN DE CESIÓN</t>
         </is>
       </c>
       <c r="U79" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Francisco Borques</t>
+          <t xml:space="preserve">Cristian Diaz</t>
         </is>
       </c>
       <c r="V79" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Se requiere adquirir una solución consistente en dos 2 Firewall de Seguridad en alta disponibilidad, con la capacidad de crear instancias virtuales de NGFW, que deben proveer funcionalidades de IPS, filtrado de URL, control de identidad, control de QoS, protección de malware y seguridad DNS. Lo anterior administrado a través de una sola consola, además de incluir soporte 7X24 por 1 año de misión critica. Esta solución debe incluir el proceso de migración de firewall de datacenter.</t>
+          <t xml:space="preserve">El Hospital Dr. Sótero del Río en adelante HSR, requiere contratar a una persona natural o jurídica para el “ARRIENDO DE DOS 02 MODULOS BODEGAS PARA LA UNIDAD DE IN-FORMATICA HSR.”, en dependencias del Hospital Dr. Sótero del Rio, ubicado en Av. Concha y Toro 3459 comuna de Puente Alto, de acuerdo a los requerimientos señalados en las Bases Técnicas que se adjuntan, siendo responsabilidad de la Empresa Contratista adjudicada la man-tención, instalación y habilitación de los módulos en las condiciones estipuladas en las Bases de licitación, administrativas y técnicas</t>
         </is>
       </c>
       <c r="W79" s="5" t="str">
-        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=1020-38-LP26","descargar bases")</f>
+        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=1057501-488-LE26","descargar bases")</f>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1020-45-LE26</t>
+          <t xml:space="preserve">1020-38-LP26</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Renovación Licencias Software Solarwinds Dameware</t>
+          <t xml:space="preserve">Adquisición de Plataforma Next Generation Firewall</t>
         </is>
       </c>
       <c r="C80" s="0" t="inlineStr">
@@ -7733,7 +8182,7 @@
       </c>
       <c r="G80" s="0"/>
       <c r="H80" s="2">
-        <v>46262.529931</v>
+        <v>46252.442905</v>
       </c>
       <c r="I80" s="2">
         <v>46275.625</v>
@@ -7742,7 +8191,7 @@
         <v>10</v>
       </c>
       <c r="K80" s="3">
-        <v>26000000.0</v>
+        <v>240000000.0</v>
       </c>
       <c r="L80" s="0" t="inlineStr">
         <is>
@@ -7751,22 +8200,26 @@
       </c>
       <c r="M80" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">LE</t>
+          <t xml:space="preserve">LP</t>
         </is>
       </c>
       <c r="N80" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de gestión</t>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Equipos, plataformas y accesorios de redes multimedia, voz y datos / Equipos de seguridad de red, Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de administración de redes</t>
         </is>
       </c>
       <c r="O80" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">60 Unidad · Software de gestión de licencias</t>
+          <t xml:space="preserve">2 Unidad · Equipo de seguridad de red de firewall · 1 Unidad · Software de vigilancia de redes</t>
         </is>
       </c>
       <c r="P80" s="2"/>
       <c r="Q80" s="2"/>
-      <c r="R80" s="0"/>
+      <c r="R80" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16 meses</t>
+        </is>
+      </c>
       <c r="S80" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">No</t>
@@ -7774,32 +8227,32 @@
       </c>
       <c r="T80" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">No permite subcontratación Conforme a lo señalado en el punto 10.5 de las Bases Administrativas, adjuntas.</t>
+          <t xml:space="preserve">Conforme al punto 10.5 de las Bases Administrativas, el oferente adjudicado no podrá subcontratar los servicios derivados de la ejecución del Contrato</t>
         </is>
       </c>
       <c r="U80" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Juan Carlos Poblete</t>
+          <t xml:space="preserve">Francisco Borques</t>
         </is>
       </c>
       <c r="V80" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">El objetivo es adquirir la Renovación Anual de la Suscripción para 60 Licencias del software SolarWinds Dameware Remote Everywhere, lo que permitirá gestionar el soporte, monitoreo de redes, diagnosticar y resolver rápidamente problemas en los equipos computacionales.</t>
+          <t xml:space="preserve">Se requiere adquirir una solución consistente en dos 2 Firewall de Seguridad en alta disponibilidad, con la capacidad de crear instancias virtuales de NGFW, que deben proveer funcionalidades de IPS, filtrado de URL, control de identidad, control de QoS, protección de malware y seguridad DNS. Lo anterior administrado a través de una sola consola, además de incluir soporte 7X24 por 1 año de misión critica. Esta solución debe incluir el proceso de migración de firewall de datacenter.</t>
         </is>
       </c>
       <c r="W80" s="5" t="str">
-        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=1020-45-LE26","descargar bases")</f>
+        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=1020-38-LP26","descargar bases")</f>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1057494-50-LR26</t>
+          <t xml:space="preserve">1020-45-LE26</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">SOFTWARE PARA LA GESTIÓN DE LA UNIDAD DE LABORATOR</t>
+          <t xml:space="preserve">Renovación Licencias Software Solarwinds Dameware</t>
         </is>
       </c>
       <c r="C81" s="0" t="inlineStr">
@@ -7809,12 +8262,12 @@
       </c>
       <c r="D81" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">SERVICIO DE SALUD SUR HOSPITAL EXEQUIEL</t>
+          <t xml:space="preserve">MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="E81" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bienes y Servicios</t>
+          <t xml:space="preserve">MOP Subsecretaría </t>
         </is>
       </c>
       <c r="F81" s="0" t="inlineStr">
@@ -7822,21 +8275,19 @@
           <t xml:space="preserve">Región Metropolitana de Santiago</t>
         </is>
       </c>
-      <c r="G81" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">San Miguel</t>
-        </is>
-      </c>
+      <c r="G81" s="0"/>
       <c r="H81" s="2">
-        <v>46245.521528</v>
+        <v>46262.529931</v>
       </c>
       <c r="I81" s="2">
-        <v>46275.666667</v>
+        <v>46275.625</v>
       </c>
       <c r="J81" s="0">
         <v>10</v>
       </c>
-      <c r="K81" s="3"/>
+      <c r="K81" s="3">
+        <v>26000000.0</v>
+      </c>
       <c r="L81" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">CLP</t>
@@ -7844,55 +8295,55 @@
       </c>
       <c r="M81" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">LR</t>
+          <t xml:space="preserve">LE</t>
         </is>
       </c>
       <c r="N81" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Equipamiento y suministros médicos / Productos para imágenes y de medicina nuclear / Artículos para archivar información e imágenes radiológicas</t>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de gestión</t>
         </is>
       </c>
       <c r="O81" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 Unidad · Software de sistemas de archivado de película radiográfica médica</t>
+          <t xml:space="preserve">60 Unidad · Software de gestión de licencias</t>
         </is>
       </c>
       <c r="P81" s="2"/>
       <c r="Q81" s="2"/>
-      <c r="R81" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">60 meses</t>
-        </is>
-      </c>
+      <c r="R81" s="0"/>
       <c r="S81" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">No</t>
         </is>
       </c>
-      <c r="T81" s="4"/>
+      <c r="T81" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No permite subcontratación Conforme a lo señalado en el punto 10.5 de las Bases Administrativas, adjuntas.</t>
+        </is>
+      </c>
       <c r="U81" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Damaris Medinelli Tapia</t>
+          <t xml:space="preserve">Juan Carlos Poblete</t>
         </is>
       </c>
       <c r="V81" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ARRIENDO DE SOFTWARE PARA LA GESTIÓN DE LA UNIDAD DE LABORATORIO CLÍNICO DEL HOSPITAL DR. EXEQUIEL GONZÁLEZ CORTÉS</t>
+          <t xml:space="preserve">El objetivo es adquirir la Renovación Anual de la Suscripción para 60 Licencias del software SolarWinds Dameware Remote Everywhere, lo que permitirá gestionar el soporte, monitoreo de redes, diagnosticar y resolver rápidamente problemas en los equipos computacionales.</t>
         </is>
       </c>
       <c r="W81" s="5" t="str">
-        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=1057494-50-LR26","descargar bases")</f>
+        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=1020-45-LE26","descargar bases")</f>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">3671-58-LE26</t>
+          <t xml:space="preserve">1057494-50-LR26</t>
         </is>
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">“HABILITACIÓN DE NUEVAS DEPENDENCIAS DE SEGURIDAD MUNICIPAL E INFORMÁTICA DE LA MUNICIPALIDAD DE CHILLÁN VIEJO”</t>
+          <t xml:space="preserve">SOFTWARE PARA LA GESTIÓN DE LA UNIDAD DE LABORATOR</t>
         </is>
       </c>
       <c r="C82" s="0" t="inlineStr">
@@ -7902,32 +8353,32 @@
       </c>
       <c r="D82" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ILUSTRE MUNICIPALIDAD DE CHILLAN VIEJO</t>
+          <t xml:space="preserve">SERVICIO DE SALUD SUR HOSPITAL EXEQUIEL</t>
         </is>
       </c>
       <c r="E82" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Secplan</t>
+          <t xml:space="preserve">Bienes y Servicios</t>
         </is>
       </c>
       <c r="F82" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Ñuble</t>
+          <t xml:space="preserve">Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="G82" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chillán Viejo</t>
+          <t xml:space="preserve">San Miguel</t>
         </is>
       </c>
       <c r="H82" s="2">
-        <v>46261.573044</v>
+        <v>46245.521528</v>
       </c>
       <c r="I82" s="2">
-        <v>46276.625</v>
+        <v>46275.666667</v>
       </c>
       <c r="J82" s="0">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K82" s="3"/>
       <c r="L82" s="0" t="inlineStr">
@@ -7937,24 +8388,24 @@
       </c>
       <c r="M82" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">LE</t>
+          <t xml:space="preserve">LR</t>
         </is>
       </c>
       <c r="N82" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Servicios de construcción y mantenimiento / Construcción de edificios en general / Construcción de obras civiles y infraestructuras</t>
+          <t xml:space="preserve">Equipamiento y suministros médicos / Productos para imágenes y de medicina nuclear / Artículos para archivar información e imágenes radiológicas</t>
         </is>
       </c>
       <c r="O82" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 Unidad · Construcción de obras civiles</t>
+          <t xml:space="preserve">1 Unidad · Software de sistemas de archivado de película radiográfica médica</t>
         </is>
       </c>
       <c r="P82" s="2"/>
       <c r="Q82" s="2"/>
       <c r="R82" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">60 días</t>
+          <t xml:space="preserve">60 meses</t>
         </is>
       </c>
       <c r="S82" s="0" t="inlineStr">
@@ -7965,27 +8416,27 @@
       <c r="T82" s="4"/>
       <c r="U82" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARIA PAZ VASQUEZ RAMIREZ</t>
+          <t xml:space="preserve">Damaris Medinelli Tapia</t>
         </is>
       </c>
       <c r="V82" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">La presente licitación pública tiene como objeto la contratación de un servicio especializado de adquisición, instalación, cambio de equipamiento tecnológico y servicio de traslado de  infraestructura tecnológica y la habilitación de su nueva central de monitoreo. El proyecto debe garantizar la continuidad operativa y la integridad del equipamiento crítico.</t>
+          <t xml:space="preserve">ARRIENDO DE SOFTWARE PARA LA GESTIÓN DE LA UNIDAD DE LABORATORIO CLÍNICO DEL HOSPITAL DR. EXEQUIEL GONZÁLEZ CORTÉS</t>
         </is>
       </c>
       <c r="W82" s="5" t="str">
-        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=3671-58-LE26","descargar bases")</f>
+        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=1057494-50-LR26","descargar bases")</f>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">425-39-LR26</t>
+          <t xml:space="preserve">3671-58-LE26</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADQUISICIÓN Y RENOVACIÓN DE LICENCIAS DE SOFTWARE PARA EL PODER JUDICIAL</t>
+          <t xml:space="preserve">“HABILITACIÓN DE NUEVAS DEPENDENCIAS DE SEGURIDAD MUNICIPAL E INFORMÁTICA DE LA MUNICIPALIDAD DE CHILLÁN VIEJO”</t>
         </is>
       </c>
       <c r="C83" s="0" t="inlineStr">
@@ -7995,29 +8446,29 @@
       </c>
       <c r="D83" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t xml:space="preserve">ILUSTRE MUNICIPALIDAD DE CHILLAN VIEJO</t>
         </is>
       </c>
       <c r="E83" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Servicios</t>
+          <t xml:space="preserve">Secplan</t>
         </is>
       </c>
       <c r="F83" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región Metropolitana de Santiago</t>
+          <t xml:space="preserve">Región del Ñuble</t>
         </is>
       </c>
       <c r="G83" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Santiago Centro</t>
+          <t xml:space="preserve">Chillán Viejo</t>
         </is>
       </c>
       <c r="H83" s="2">
-        <v>46232.502083</v>
+        <v>46261.573044</v>
       </c>
       <c r="I83" s="2">
-        <v>46276.666667</v>
+        <v>46276.625</v>
       </c>
       <c r="J83" s="0">
         <v>11</v>
@@ -8025,60 +8476,60 @@
       <c r="K83" s="3"/>
       <c r="L83" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">USD</t>
+          <t xml:space="preserve">CLP</t>
         </is>
       </c>
       <c r="M83" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">LR</t>
+          <t xml:space="preserve">LE</t>
         </is>
       </c>
       <c r="N83" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de gestión</t>
+          <t xml:space="preserve">Servicios de construcción y mantenimiento / Construcción de edificios en general / Construcción de obras civiles y infraestructuras</t>
         </is>
       </c>
       <c r="O83" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">12 Unidad · Software de gestión de licencias · 4480 Unidad · Software de gestión de licencias · 30 Unidad · Software de gestión de licencias · y 30 más</t>
+          <t xml:space="preserve">1 Unidad · Construcción de obras civiles</t>
         </is>
       </c>
       <c r="P83" s="2"/>
       <c r="Q83" s="2"/>
-      <c r="R83" s="0"/>
+      <c r="R83" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">60 días</t>
+        </is>
+      </c>
       <c r="S83" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">No</t>
         </is>
       </c>
-      <c r="T83" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">No se permite subcontratación.</t>
-        </is>
-      </c>
+      <c r="T83" s="4"/>
       <c r="U83" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lisette Ávila</t>
+          <t xml:space="preserve">MARIA PAZ VASQUEZ RAMIREZ</t>
         </is>
       </c>
       <c r="V83" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">UR(1804) ADQUISICIÓN Y RENOVACIÓN DE LICENCIAS DE SOFTWARE PARA EL PODER JUDICIAL</t>
+          <t xml:space="preserve">La presente licitación pública tiene como objeto la contratación de un servicio especializado de adquisición, instalación, cambio de equipamiento tecnológico y servicio de traslado de  infraestructura tecnológica y la habilitación de su nueva central de monitoreo. El proyecto debe garantizar la continuidad operativa y la integridad del equipamiento crítico.</t>
         </is>
       </c>
       <c r="W83" s="5" t="str">
-        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=425-39-LR26","descargar bases")</f>
+        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=3671-58-LE26","descargar bases")</f>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">4778-14-LP26</t>
+          <t xml:space="preserve">425-39-LR26</t>
         </is>
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">SERV. ADMINISTRADO CONTACT CENTER OMNICANAL CON IA</t>
+          <t xml:space="preserve">ADQUISICIÓN Y RENOVACIÓN DE LICENCIAS DE SOFTWARE PARA EL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="C84" s="0" t="inlineStr">
@@ -8088,26 +8539,26 @@
       </c>
       <c r="D84" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t xml:space="preserve">CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="E84" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Compras de Insumos y Servicios Generales</t>
+          <t xml:space="preserve">Servicios</t>
         </is>
       </c>
       <c r="F84" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t xml:space="preserve">Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="G84" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Coyhaique</t>
+          <t xml:space="preserve">Santiago Centro</t>
         </is>
       </c>
       <c r="H84" s="2">
-        <v>46254.698993</v>
+        <v>46232.502083</v>
       </c>
       <c r="I84" s="2">
         <v>46276.666667</v>
@@ -8118,31 +8569,27 @@
       <c r="K84" s="3"/>
       <c r="L84" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">CLP</t>
+          <t xml:space="preserve">USD</t>
         </is>
       </c>
       <c r="M84" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">LP</t>
+          <t xml:space="preserve">LR</t>
         </is>
       </c>
       <c r="N84" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software para trabajo en redes</t>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de gestión</t>
         </is>
       </c>
       <c r="O84" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">24 Unidad · Software para centrales de comunicación digital</t>
+          <t xml:space="preserve">12 Unidad · Software de gestión de licencias · 4480 Unidad · Software de gestión de licencias · 30 Unidad · Software de gestión de licencias · y 30 más</t>
         </is>
       </c>
       <c r="P84" s="2"/>
       <c r="Q84" s="2"/>
-      <c r="R84" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24 meses</t>
-        </is>
-      </c>
+      <c r="R84" s="0"/>
       <c r="S84" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">No</t>
@@ -8150,32 +8597,32 @@
       </c>
       <c r="T84" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ver Bases Administrativas Especiales, punto 3.</t>
+          <t xml:space="preserve">No se permite subcontratación.</t>
         </is>
       </c>
       <c r="U84" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carolina Pérez Alfaro</t>
+          <t xml:space="preserve">Lisette Ávila</t>
         </is>
       </c>
       <c r="V84" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Servicio Administrado de Contact Center Omnicanal con Inteligencia Artificial para la Gestión Integral de la Contactabilidad de Usuarios del Hospital Regional Coyhaique.</t>
+          <t xml:space="preserve">UR(1804) ADQUISICIÓN Y RENOVACIÓN DE LICENCIAS DE SOFTWARE PARA EL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="W84" s="5" t="str">
-        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=4778-14-LP26","descargar bases")</f>
+        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=425-39-LR26","descargar bases")</f>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1607-10-LR26</t>
+          <t xml:space="preserve">4778-14-LP26</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">servicio hospedaje soporte mantención plataforma</t>
+          <t xml:space="preserve">SERV. ADMINISTRADO CONTACT CENTER OMNICANAL CON IA</t>
         </is>
       </c>
       <c r="C85" s="0" t="inlineStr">
@@ -8185,36 +8632,34 @@
       </c>
       <c r="D85" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">SUPERINTENDENCIA DE SEGURIDAD SOCIAL</t>
+          <t xml:space="preserve">SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="E85" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Superintendencia de Seguridad Social</t>
+          <t xml:space="preserve">Compras de Insumos y Servicios Generales</t>
         </is>
       </c>
       <c r="F85" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región Metropolitana de Santiago</t>
+          <t xml:space="preserve">Región Aysén del General Carlos Ibáñez del Campo</t>
         </is>
       </c>
       <c r="G85" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Santiago Centro</t>
+          <t xml:space="preserve">Coyhaique</t>
         </is>
       </c>
       <c r="H85" s="2">
-        <v>46248.628472</v>
+        <v>46254.698993</v>
       </c>
       <c r="I85" s="2">
-        <v>46279.625</v>
+        <v>46276.666667</v>
       </c>
       <c r="J85" s="0">
-        <v>14</v>
-      </c>
-      <c r="K85" s="3">
-        <v>540000000.0</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="K85" s="3"/>
       <c r="L85" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">CLP</t>
@@ -8222,22 +8667,26 @@
       </c>
       <c r="M85" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">LR</t>
+          <t xml:space="preserve">LP</t>
         </is>
       </c>
       <c r="N85" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Servicios profesionales, administrativos y consultorías de gestión empresarial / Servicios de recursos humanos / Contratación de personal</t>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software para trabajo en redes</t>
         </is>
       </c>
       <c r="O85" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 Unidad · Desarrolladores de software</t>
+          <t xml:space="preserve">24 Unidad · Software para centrales de comunicación digital</t>
         </is>
       </c>
       <c r="P85" s="2"/>
       <c r="Q85" s="2"/>
-      <c r="R85" s="0"/>
+      <c r="R85" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24 meses</t>
+        </is>
+      </c>
       <c r="S85" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">No</t>
@@ -8245,32 +8694,32 @@
       </c>
       <c r="T85" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">El oferente adjudicado no podrá ceder ni transferir en forma alguna, total ni parcialmente, los derechos y obligaciones que nacen del desarrollo de la presente licitación, y en especial los que se establecerán en el contrato definitivo</t>
+          <t xml:space="preserve">Ver Bases Administrativas Especiales, punto 3.</t>
         </is>
       </c>
       <c r="U85" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Melissa Pino</t>
+          <t xml:space="preserve">Carolina Pérez Alfaro</t>
         </is>
       </c>
       <c r="V85" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">contratación del servicio hospedaje, soporte, mantención y actualización de la Plataforma Integrada de Asignación Familiar, Subsidio Único Familiar y Regímenes relacionados PIAS, de la Superintendencia de Seguridad Social.</t>
+          <t xml:space="preserve">Servicio Administrado de Contact Center Omnicanal con Inteligencia Artificial para la Gestión Integral de la Contactabilidad de Usuarios del Hospital Regional Coyhaique.</t>
         </is>
       </c>
       <c r="W85" s="5" t="str">
-        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=1607-10-LR26","descargar bases")</f>
+        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=4778-14-LP26","descargar bases")</f>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2413-20-LE26</t>
+          <t xml:space="preserve">2107-142-LE26</t>
         </is>
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">SISTEMA DE GESTIÓN DOCUMENTAL</t>
+          <t xml:space="preserve">ARRIENDO DE TOTEMS AUTOADMINISTRADOS PARA HSC</t>
         </is>
       </c>
       <c r="C86" s="0" t="inlineStr">
@@ -8280,37 +8729,37 @@
       </c>
       <c r="D86" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">I MUNICIPALIDAD DE LO PRADO</t>
+          <t xml:space="preserve">SERVICIO DE SALUD HOSPITAL DE SANTA CRUZ</t>
         </is>
       </c>
       <c r="E86" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">SECRETARIA PLANIFICACION COMUNAL</t>
+          <t xml:space="preserve">Hospital de Santa Cruz</t>
         </is>
       </c>
       <c r="F86" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región Metropolitana de Santiago</t>
+          <t xml:space="preserve">Región del Libertador General Bernardo O´Higgins</t>
         </is>
       </c>
       <c r="G86" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lo Prado</t>
+          <t xml:space="preserve">Santa Cruz</t>
         </is>
       </c>
       <c r="H86" s="2">
-        <v>46262.778414</v>
+        <v>46265.345752</v>
       </c>
       <c r="I86" s="2">
-        <v>46279.625</v>
+        <v>46276.747222</v>
       </c>
       <c r="J86" s="0">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="K86" s="3"/>
       <c r="L86" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">CLF</t>
+          <t xml:space="preserve">CLP</t>
         </is>
       </c>
       <c r="M86" s="0" t="inlineStr">
@@ -8320,17 +8769,21 @@
       </c>
       <c r="N86" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Servicios profesionales, administrativos y consultorías de gestión empresarial / Servicios de recursos humanos / Contratación de personal</t>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Equipos informáticos y accesorios / Computadores</t>
         </is>
       </c>
       <c r="O86" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 Mes · Desarrolladores de software</t>
+          <t xml:space="preserve">36 Mes · Servidores de gama alta</t>
         </is>
       </c>
       <c r="P86" s="2"/>
       <c r="Q86" s="2"/>
-      <c r="R86" s="0"/>
+      <c r="R86" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">36 meses</t>
+        </is>
+      </c>
       <c r="S86" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">No</t>
@@ -8339,29 +8792,28 @@
       <c r="T86" s="4"/>
       <c r="U86" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Paola Moncada Venegas</t>
+          <t xml:space="preserve">Nicolás Salgado Marín</t>
         </is>
       </c>
       <c r="V86" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">El propósito de esta contratación pública consiste en la provisión de un Sistema de Gestión Documental Integral bajo la modalidad de software como servicio (SaaS) con licenciamiento ilimitado para la Municipalidad de Lo Prado.
-La solución tecnológica deberá posibilitar la tramitación electrónica completa de actas, decretos, resoluciones, oficios y demás actos administrativos, asegurando el ciclo de vida documental que comprende el ingreso, confección, visación jurídica y técnica, suscripción mediante firma electrónica avanzada y su posterior archivo digital seguro.
-Asimismo, el sistema debe contemplar la automatización de flujos de trabajo (workflows) parametrizables en función de la estructura orgánica municipal, garantizando la inmutabilidad de los registros y el almacenamiento cronológico completo de las trazas de auditoría para cada documento gestionado.</t>
+          <t xml:space="preserve">ARRIENDO DE TOTEMS AUTOADMINISTRADOS PARA EL HOSPITAL DE SANTA CRUZ
+El presente proceso de licitación pública tiene por objeto la contratación del Servicio de Arriendo de tres (3) Tótems de Marcaje mediante tecnología NFC/RFID, destinados a la implementación de una solución tecnológica para la identificación y registro de usuarios del Hospital de Santa Cruz.</t>
         </is>
       </c>
       <c r="W86" s="5" t="str">
-        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=2413-20-LE26","descargar bases")</f>
+        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=2107-142-LE26","descargar bases")</f>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">906973-8-LP26</t>
+          <t xml:space="preserve">1607-10-LR26</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">SISTEMAS INFORMÁTICOS DE GESTIÓN MUNICIPAL</t>
+          <t xml:space="preserve">servicio hospedaje soporte mantención plataforma</t>
         </is>
       </c>
       <c r="C87" s="0" t="inlineStr">
@@ -8371,26 +8823,26 @@
       </c>
       <c r="D87" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">I MUNICIPALIDAD DE VICHUQUEN</t>
+          <t xml:space="preserve">SUPERINTENDENCIA DE SEGURIDAD SOCIAL</t>
         </is>
       </c>
       <c r="E87" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">SECPLAC</t>
+          <t xml:space="preserve">Superintendencia de Seguridad Social</t>
         </is>
       </c>
       <c r="F87" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t xml:space="preserve">Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="G87" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vichuquén</t>
+          <t xml:space="preserve">Santiago Centro</t>
         </is>
       </c>
       <c r="H87" s="2">
-        <v>46259.547662</v>
+        <v>46248.628472</v>
       </c>
       <c r="I87" s="2">
         <v>46279.625</v>
@@ -8398,7 +8850,9 @@
       <c r="J87" s="0">
         <v>14</v>
       </c>
-      <c r="K87" s="3"/>
+      <c r="K87" s="3">
+        <v>540000000.0</v>
+      </c>
       <c r="L87" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">CLP</t>
@@ -8406,17 +8860,17 @@
       </c>
       <c r="M87" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">LP</t>
+          <t xml:space="preserve">LR</t>
         </is>
       </c>
       <c r="N87" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Organizaciones y consultorías políticas, demográficas, económicas, sociales y de administración pública / Administración y finanzas públicas / Finanzas públicas</t>
+          <t xml:space="preserve">Servicios profesionales, administrativos y consultorías de gestión empresarial / Servicios de recursos humanos / Contratación de personal</t>
         </is>
       </c>
       <c r="O87" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">36 Mes · Servicios contables gubernamentales</t>
+          <t xml:space="preserve">1 Unidad · Desarrolladores de software</t>
         </is>
       </c>
       <c r="P87" s="2"/>
@@ -8427,30 +8881,34 @@
           <t xml:space="preserve">No</t>
         </is>
       </c>
-      <c r="T87" s="4"/>
+      <c r="T87" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">El oferente adjudicado no podrá ceder ni transferir en forma alguna, total ni parcialmente, los derechos y obligaciones que nacen del desarrollo de la presente licitación, y en especial los que se establecerán en el contrato definitivo</t>
+        </is>
+      </c>
       <c r="U87" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ariel Munoz Vasquez</t>
+          <t xml:space="preserve">Melissa Pino</t>
         </is>
       </c>
       <c r="V87" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contratar el suministro integral de sistemas informáticos de gestión municipal, incluyendo Contabilidad Gubernamental y los demás módulos administrativos, financieros, de ingresos municipales, recursos humanos, remuneraciones, asistencia y atención de usuarios requeridos por la Municipalidad de Vichuquén, junto con infraestructura local, servidor, UPS, licencias, implementación, migración, capacitación, soporte, mantención y actualizaciones normativas.</t>
+          <t xml:space="preserve">contratación del servicio hospedaje, soporte, mantención y actualización de la Plataforma Integrada de Asignación Familiar, Subsidio Único Familiar y Regímenes relacionados PIAS, de la Superintendencia de Seguridad Social.</t>
         </is>
       </c>
       <c r="W87" s="5" t="str">
-        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=906973-8-LP26","descargar bases")</f>
+        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=1607-10-LR26","descargar bases")</f>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">875-6-LP26</t>
+          <t xml:space="preserve">2413-20-LE26</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">SERVICIO DE MARKETING DIGITAL</t>
+          <t xml:space="preserve">SISTEMA DE GESTIÓN DOCUMENTAL</t>
         </is>
       </c>
       <c r="C88" s="0" t="inlineStr">
@@ -8460,12 +8918,12 @@
       </c>
       <c r="D88" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">AGENCIA DE PROMOCION DE LA INVERSION EXTRANJERA</t>
+          <t xml:space="preserve">I MUNICIPALIDAD DE LO PRADO</t>
         </is>
       </c>
       <c r="E88" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Agencia de Promoción de la Inversión Extranjera</t>
+          <t xml:space="preserve">SECRETARIA PLANIFICACION COMUNAL</t>
         </is>
       </c>
       <c r="F88" s="0" t="inlineStr">
@@ -8475,48 +8933,42 @@
       </c>
       <c r="G88" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Santiago</t>
+          <t xml:space="preserve">Lo Prado</t>
         </is>
       </c>
       <c r="H88" s="2">
-        <v>46258.740845</v>
+        <v>46262.778414</v>
       </c>
       <c r="I88" s="2">
-        <v>46279.666667</v>
+        <v>46279.625</v>
       </c>
       <c r="J88" s="0">
         <v>14</v>
       </c>
-      <c r="K88" s="3">
-        <v>225000000.0</v>
-      </c>
+      <c r="K88" s="3"/>
       <c r="L88" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">CLP</t>
+          <t xml:space="preserve">CLF</t>
         </is>
       </c>
       <c r="M88" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">LP</t>
+          <t xml:space="preserve">LE</t>
         </is>
       </c>
       <c r="N88" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Servicios profesionales, administrativos y consultorías de gestión empresarial / Servicios para la comercialización y distribución / Ventas y marketing</t>
+          <t xml:space="preserve">Servicios profesionales, administrativos y consultorías de gestión empresarial / Servicios de recursos humanos / Contratación de personal</t>
         </is>
       </c>
       <c r="O88" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 Unidad · Campañas publicitarias o de marketing</t>
+          <t xml:space="preserve">1 Mes · Desarrolladores de software</t>
         </is>
       </c>
       <c r="P88" s="2"/>
       <c r="Q88" s="2"/>
-      <c r="R88" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12 meses</t>
-        </is>
-      </c>
+      <c r="R88" s="0"/>
       <c r="S88" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">No</t>
@@ -8525,27 +8977,29 @@
       <c r="T88" s="4"/>
       <c r="U88" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Claudio Álvarez M., o ella funcionarioa que desi</t>
+          <t xml:space="preserve">Paola Moncada Venegas</t>
         </is>
       </c>
       <c r="V88" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contratar la adquisición y planificación de pauta de medios para campañas digitales, junto con un servicio especializado de asesoría y soporte en marketing digital, orientado a fortalecer las acciones de promoción y atracción de inversión extranjera, la generación y gestión de contactos de potenciales inversionistas y el posicionamiento de Chile como destino atractivo para la inversión.</t>
+          <t xml:space="preserve">El propósito de esta contratación pública consiste en la provisión de un Sistema de Gestión Documental Integral bajo la modalidad de software como servicio (SaaS) con licenciamiento ilimitado para la Municipalidad de Lo Prado.
+La solución tecnológica deberá posibilitar la tramitación electrónica completa de actas, decretos, resoluciones, oficios y demás actos administrativos, asegurando el ciclo de vida documental que comprende el ingreso, confección, visación jurídica y técnica, suscripción mediante firma electrónica avanzada y su posterior archivo digital seguro.
+Asimismo, el sistema debe contemplar la automatización de flujos de trabajo (workflows) parametrizables en función de la estructura orgánica municipal, garantizando la inmutabilidad de los registros y el almacenamiento cronológico completo de las trazas de auditoría para cada documento gestionado.</t>
         </is>
       </c>
       <c r="W88" s="5" t="str">
-        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=875-6-LP26","descargar bases")</f>
+        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=2413-20-LE26","descargar bases")</f>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2348-34-LP26</t>
+          <t xml:space="preserve">906973-8-LP26</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADQUISICIÓN DE LICENCIAS DE SOFTWARE</t>
+          <t xml:space="preserve">SISTEMAS INFORMÁTICOS DE GESTIÓN MUNICIPAL</t>
         </is>
       </c>
       <c r="C89" s="0" t="inlineStr">
@@ -8555,36 +9009,34 @@
       </c>
       <c r="D89" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">I MUNICIPALIDAD DE PUNTA ARENAS</t>
+          <t xml:space="preserve">I MUNICIPALIDAD DE VICHUQUEN</t>
         </is>
       </c>
       <c r="E89" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dirección de Administración y Finanzas</t>
+          <t xml:space="preserve">SECPLAC</t>
         </is>
       </c>
       <c r="F89" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Magallanes y de la Antártica</t>
+          <t xml:space="preserve">Región del Maule </t>
         </is>
       </c>
       <c r="G89" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Punta Arenas</t>
+          <t xml:space="preserve">Vichuquén</t>
         </is>
       </c>
       <c r="H89" s="2">
-        <v>46259.485648</v>
+        <v>46259.547662</v>
       </c>
       <c r="I89" s="2">
-        <v>46280.458333</v>
+        <v>46279.625</v>
       </c>
       <c r="J89" s="0">
-        <v>15</v>
-      </c>
-      <c r="K89" s="3">
-        <v>163000000.0</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="K89" s="3"/>
       <c r="L89" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">CLP</t>
@@ -8597,12 +9049,12 @@
       </c>
       <c r="N89" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de entorno operativo</t>
+          <t xml:space="preserve">Organizaciones y consultorías políticas, demográficas, económicas, sociales y de administración pública / Administración y finanzas públicas / Finanzas públicas</t>
         </is>
       </c>
       <c r="O89" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 Unidad · Software de sistema operativo · 22 Unidad · Software de sistema operativo · 5 Unidad · Software de sistema operativo · y 7 más</t>
+          <t xml:space="preserve">36 Mes · Servicios contables gubernamentales</t>
         </is>
       </c>
       <c r="P89" s="2"/>
@@ -8613,226 +9065,222 @@
           <t xml:space="preserve">No</t>
         </is>
       </c>
-      <c r="T89" s="4" t="inlineStr">
+      <c r="T89" s="4"/>
+      <c r="U89" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ariel Munoz Vasquez</t>
+        </is>
+      </c>
+      <c r="V89" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Contratar el suministro integral de sistemas informáticos de gestión municipal, incluyendo Contabilidad Gubernamental y los demás módulos administrativos, financieros, de ingresos municipales, recursos humanos, remuneraciones, asistencia y atención de usuarios requeridos por la Municipalidad de Vichuquén, junto con infraestructura local, servidor, UPS, licencias, implementación, migración, capacitación, soporte, mantención y actualizaciones normativas.</t>
+        </is>
+      </c>
+      <c r="W89" s="5" t="str">
+        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=906973-8-LP26","descargar bases")</f>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">875-6-LP26</t>
+        </is>
+      </c>
+      <c r="B90" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SERVICIO DE MARKETING DIGITAL</t>
+        </is>
+      </c>
+      <c r="C90" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Publicada</t>
+        </is>
+      </c>
+      <c r="D90" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AGENCIA DE PROMOCION DE LA INVERSION EXTRANJERA</t>
+        </is>
+      </c>
+      <c r="E90" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Agencia de Promoción de la Inversión Extranjera</t>
+        </is>
+      </c>
+      <c r="F90" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="G90" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Santiago</t>
+        </is>
+      </c>
+      <c r="H90" s="2">
+        <v>46258.740845</v>
+      </c>
+      <c r="I90" s="2">
+        <v>46279.666667</v>
+      </c>
+      <c r="J90" s="0">
+        <v>14</v>
+      </c>
+      <c r="K90" s="3">
+        <v>225000000.0</v>
+      </c>
+      <c r="L90" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CLP</t>
+        </is>
+      </c>
+      <c r="M90" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LP</t>
+        </is>
+      </c>
+      <c r="N90" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Servicios profesionales, administrativos y consultorías de gestión empresarial / Servicios para la comercialización y distribución / Ventas y marketing</t>
+        </is>
+      </c>
+      <c r="O90" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 Unidad · Campañas publicitarias o de marketing</t>
+        </is>
+      </c>
+      <c r="P90" s="2"/>
+      <c r="Q90" s="2"/>
+      <c r="R90" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12 meses</t>
+        </is>
+      </c>
+      <c r="S90" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="T90" s="4"/>
+      <c r="U90" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Claudio Álvarez M., o ella funcionarioa que desi</t>
+        </is>
+      </c>
+      <c r="V90" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Contratar la adquisición y planificación de pauta de medios para campañas digitales, junto con un servicio especializado de asesoría y soporte en marketing digital, orientado a fortalecer las acciones de promoción y atracción de inversión extranjera, la generación y gestión de contactos de potenciales inversionistas y el posicionamiento de Chile como destino atractivo para la inversión.</t>
+        </is>
+      </c>
+      <c r="W90" s="5" t="str">
+        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=875-6-LP26","descargar bases")</f>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2348-34-LP26</t>
+        </is>
+      </c>
+      <c r="B91" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADQUISICIÓN DE LICENCIAS DE SOFTWARE</t>
+        </is>
+      </c>
+      <c r="C91" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Publicada</t>
+        </is>
+      </c>
+      <c r="D91" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">I MUNICIPALIDAD DE PUNTA ARENAS</t>
+        </is>
+      </c>
+      <c r="E91" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dirección de Administración y Finanzas</t>
+        </is>
+      </c>
+      <c r="F91" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Magallanes y de la Antártica</t>
+        </is>
+      </c>
+      <c r="G91" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Punta Arenas</t>
+        </is>
+      </c>
+      <c r="H91" s="2">
+        <v>46259.485648</v>
+      </c>
+      <c r="I91" s="2">
+        <v>46280.458333</v>
+      </c>
+      <c r="J91" s="0">
+        <v>15</v>
+      </c>
+      <c r="K91" s="3">
+        <v>163000000.0</v>
+      </c>
+      <c r="L91" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CLP</t>
+        </is>
+      </c>
+      <c r="M91" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LP</t>
+        </is>
+      </c>
+      <c r="N91" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de entorno operativo</t>
+        </is>
+      </c>
+      <c r="O91" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 Unidad · Software de sistema operativo · 22 Unidad · Software de sistema operativo · 5 Unidad · Software de sistema operativo · y 7 más</t>
+        </is>
+      </c>
+      <c r="P91" s="2"/>
+      <c r="Q91" s="2"/>
+      <c r="R91" s="0"/>
+      <c r="S91" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="T91" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">SEGÚN ART. N°43 DE LAS BASES ADMINISTRATIVAS.-</t>
         </is>
       </c>
-      <c r="U89" s="0" t="inlineStr">
+      <c r="U91" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">CLAUDIO RADONICH JIMENEZ</t>
         </is>
       </c>
-      <c r="V89" s="4" t="inlineStr">
+      <c r="V91" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">ADQUISICIÓN DE LICENCIAS DE SOFTWARE PARA LA MUNICIPALIDAD DE PUNTA ARENAS.
 LICENCIAS DE SOFTWARE POR LÍNEA DE PRODUCTO, DE DIFERENTES CARACTERÍSTICAS, CON LA FINALIDAD DE SATISFACER DE MANERA ADECUADA Y EFICIENTE LA LABOR DEL DEPARTAMENTO DE INFORMÁTICA DEPENDIENTE DE LA DIRECCIÓN DE SERVICIOS GENERALES.
 OFERTAR SEGÚN ESPECIFICACIONES TÉCNICAS ADJUNTAS.</t>
         </is>
       </c>
-      <c r="W89" s="5" t="str">
+      <c r="W91" s="5" t="str">
         <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=2348-34-LP26","descargar bases")</f>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2445-109-LP26</t>
-        </is>
-      </c>
-      <c r="B90" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SERVICIO SOFTWARE GESTIÓN  ASISTENCIA DEPTO. SALUD</t>
-        </is>
-      </c>
-      <c r="C90" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Publicada</t>
-        </is>
-      </c>
-      <c r="D90" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">I MUNICIPALIDAD DE CURICO</t>
-        </is>
-      </c>
-      <c r="E90" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Salud - Adquisiciones</t>
-        </is>
-      </c>
-      <c r="F90" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Región del Maule </t>
-        </is>
-      </c>
-      <c r="G90" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Curicó</t>
-        </is>
-      </c>
-      <c r="H90" s="2">
-        <v>46260.403657</v>
-      </c>
-      <c r="I90" s="2">
-        <v>46280.5</v>
-      </c>
-      <c r="J90" s="0">
-        <v>15</v>
-      </c>
-      <c r="K90" s="3">
-        <v>132232000.0</v>
-      </c>
-      <c r="L90" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CLP</t>
-        </is>
-      </c>
-      <c r="M90" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LP</t>
-        </is>
-      </c>
-      <c r="N90" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de gestión</t>
-        </is>
-      </c>
-      <c r="O90" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1 Unidad · Software de gestión de recursos humanos</t>
-        </is>
-      </c>
-      <c r="P90" s="2"/>
-      <c r="Q90" s="2"/>
-      <c r="R90" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">36 semanas</t>
-        </is>
-      </c>
-      <c r="S90" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">No</t>
-        </is>
-      </c>
-      <c r="T90" s="4"/>
-      <c r="U90" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PABLO LEPE</t>
-        </is>
-      </c>
-      <c r="V90" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SERVICIO DE ARRIENDO, IMPLEMENTACIÓN, MANTENCIÓN Y SOPORTE DE SOFTWARE CLOUD PARA GESTIÓN DE ASISTENCIA Y TERMINALES BIOMÉTRICOS PARA EL  DEPARTAMENTO DE SALUD DE CURICO, SP  0815, Contacto Encargado de Informática Enrique Ibarra fono 75-2-289153</t>
-        </is>
-      </c>
-      <c r="W90" s="5" t="str">
-        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=2445-109-LP26","descargar bases")</f>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1020-40-LP26</t>
-        </is>
-      </c>
-      <c r="B91" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Serv.Cloud Amazon Web Services AWS o Equivalente</t>
-        </is>
-      </c>
-      <c r="C91" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Publicada</t>
-        </is>
-      </c>
-      <c r="D91" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
-        </is>
-      </c>
-      <c r="E91" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MOP Subsecretaría </t>
-        </is>
-      </c>
-      <c r="F91" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Región Metropolitana de Santiago</t>
-        </is>
-      </c>
-      <c r="G91" s="0"/>
-      <c r="H91" s="2">
-        <v>46254.652164</v>
-      </c>
-      <c r="I91" s="2">
-        <v>46280.625</v>
-      </c>
-      <c r="J91" s="0">
-        <v>15</v>
-      </c>
-      <c r="K91" s="3">
-        <v>295121.0</v>
-      </c>
-      <c r="L91" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">USD</t>
-        </is>
-      </c>
-      <c r="M91" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LP</t>
-        </is>
-      </c>
-      <c r="N91" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de consultas y gestión de datos</t>
-        </is>
-      </c>
-      <c r="O91" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1 Unidad · Software del sistema de administración de bases de datos</t>
-        </is>
-      </c>
-      <c r="P91" s="2"/>
-      <c r="Q91" s="2"/>
-      <c r="R91" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">36 meses</t>
-        </is>
-      </c>
-      <c r="S91" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">No</t>
-        </is>
-      </c>
-      <c r="T91" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ver numeral 10.5 de las Bases Administrativas, en archivo adjunto.</t>
-        </is>
-      </c>
-      <c r="U91" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Carmen Gloria Ponce Pérez</t>
-        </is>
-      </c>
-      <c r="V91" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">El objetivo de la presente contratación es disponer de un servicio en la nube destinado a alojar los gestores documentales del Ministerio de Obras Públicas MOP y los datos institucionales del MOP, incluyendo el respaldo de repositorios, la gestión de contenedores, aplicaciones y otros datos actualmente alojados en infraestructura propia del Ministerio.</t>
-        </is>
-      </c>
-      <c r="W91" s="5" t="str">
-        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=1020-40-LP26","descargar bases")</f>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">3902-39-LP26</t>
+          <t xml:space="preserve">2445-109-LP26</t>
         </is>
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">SERVICIO SOFTWARE SISTEMAS DE INFORMACIÓN BULNES.</t>
+          <t xml:space="preserve">SERVICIO SOFTWARE GESTIÓN  ASISTENCIA DEPTO. SALUD</t>
         </is>
       </c>
       <c r="C92" s="0" t="inlineStr">
@@ -8842,34 +9290,36 @@
       </c>
       <c r="D92" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">I MUNICIPALIDAD DE BULNES</t>
+          <t xml:space="preserve">I MUNICIPALIDAD DE CURICO</t>
         </is>
       </c>
       <c r="E92" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">I MUNICIPALIDAD DE BULNES</t>
+          <t xml:space="preserve">Salud - Adquisiciones</t>
         </is>
       </c>
       <c r="F92" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Ñuble</t>
+          <t xml:space="preserve">Región del Maule </t>
         </is>
       </c>
       <c r="G92" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bulnes</t>
+          <t xml:space="preserve">Curicó</t>
         </is>
       </c>
       <c r="H92" s="2">
-        <v>46261.708333</v>
+        <v>46260.403657</v>
       </c>
       <c r="I92" s="2">
-        <v>46280.6375</v>
+        <v>46280.5</v>
       </c>
       <c r="J92" s="0">
         <v>15</v>
       </c>
-      <c r="K92" s="3"/>
+      <c r="K92" s="3">
+        <v>132232000.0</v>
+      </c>
       <c r="L92" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">CLP</t>
@@ -8887,14 +9337,14 @@
       </c>
       <c r="O92" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 Global · Paquetes de software para oficinas</t>
+          <t xml:space="preserve">1 Unidad · Software de gestión de recursos humanos</t>
         </is>
       </c>
       <c r="P92" s="2"/>
       <c r="Q92" s="2"/>
       <c r="R92" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24 meses</t>
+          <t xml:space="preserve">36 semanas</t>
         </is>
       </c>
       <c r="S92" s="0" t="inlineStr">
@@ -8905,27 +9355,27 @@
       <c r="T92" s="4"/>
       <c r="U92" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ULISES AEDO VALDÉS</t>
+          <t xml:space="preserve">PABLO LEPE</t>
         </is>
       </c>
       <c r="V92" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">La Municipalidad de Bulnes, ha dispuesto la Licitación de la contratación por “SERVICIO DE SOFTWARE DE SISTEMAS DE INFORMACIÓN PARA MUNICIPALIDAD DE BULNES”, conforme a las exigencias de las presentes bases administrativas especiales, especificaciones técnicas, anexos, aclaraciones y demás antecedentes.</t>
+          <t xml:space="preserve">SERVICIO DE ARRIENDO, IMPLEMENTACIÓN, MANTENCIÓN Y SOPORTE DE SOFTWARE CLOUD PARA GESTIÓN DE ASISTENCIA Y TERMINALES BIOMÉTRICOS PARA EL  DEPARTAMENTO DE SALUD DE CURICO, SP  0815, Contacto Encargado de Informática Enrique Ibarra fono 75-2-289153</t>
         </is>
       </c>
       <c r="W92" s="5" t="str">
-        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=3902-39-LP26","descargar bases")</f>
+        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=2445-109-LP26","descargar bases")</f>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2434-20-LP26</t>
+          <t xml:space="preserve">1020-40-LP26</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">SERV. PLATAFORMA INTEGRAL PARA GESTION MUNICIPAL</t>
+          <t xml:space="preserve">Serv.Cloud Amazon Web Services AWS o Equivalente</t>
         </is>
       </c>
       <c r="C93" s="0" t="inlineStr">
@@ -8935,12 +9385,12 @@
       </c>
       <c r="D93" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">I MUNICIPALIDAD ESTACION CENTRAL</t>
+          <t xml:space="preserve">MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="E93" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">SECRETARIA COMUNAL DE PLANIFICACION</t>
+          <t xml:space="preserve">MOP Subsecretaría </t>
         </is>
       </c>
       <c r="F93" s="0" t="inlineStr">
@@ -8948,26 +9398,22 @@
           <t xml:space="preserve">Región Metropolitana de Santiago</t>
         </is>
       </c>
-      <c r="G93" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Estación Central</t>
-        </is>
-      </c>
+      <c r="G93" s="0"/>
       <c r="H93" s="2">
-        <v>46261.839757</v>
+        <v>46254.652164</v>
       </c>
       <c r="I93" s="2">
-        <v>46281.583333</v>
+        <v>46280.625</v>
       </c>
       <c r="J93" s="0">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K93" s="3">
-        <v>204000000.0</v>
+        <v>295121.0</v>
       </c>
       <c r="L93" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">CLP</t>
+          <t xml:space="preserve">USD</t>
         </is>
       </c>
       <c r="M93" s="0" t="inlineStr">
@@ -8977,19 +9423,19 @@
       </c>
       <c r="N93" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software para trabajo en redes</t>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de consultas y gestión de datos</t>
         </is>
       </c>
       <c r="O93" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 Global · Software de interconectividad de plataformas</t>
+          <t xml:space="preserve">1 Unidad · Software del sistema de administración de bases de datos</t>
         </is>
       </c>
       <c r="P93" s="2"/>
       <c r="Q93" s="2"/>
       <c r="R93" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">12 meses</t>
+          <t xml:space="preserve">36 meses</t>
         </is>
       </c>
       <c r="S93" s="0" t="inlineStr">
@@ -8997,30 +9443,34 @@
           <t xml:space="preserve">No</t>
         </is>
       </c>
-      <c r="T93" s="4"/>
+      <c r="T93" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ver numeral 10.5 de las Bases Administrativas, en archivo adjunto.</t>
+        </is>
+      </c>
       <c r="U93" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Iván Ahumada</t>
+          <t xml:space="preserve">Carmen Gloria Ponce Pérez</t>
         </is>
       </c>
       <c r="V93" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">El suministro y mantención de sistemas informáticos,  busca además, establecer una relación de colaboración de largo plazo, orientada a fortalecer la transformación digital institucional, garantizando la continuidad operacional, la seguridad de la información, la interoperabilidad entre sistemas y la permanente modernización de la plataforma tecnológica municipal</t>
+          <t xml:space="preserve">El objetivo de la presente contratación es disponer de un servicio en la nube destinado a alojar los gestores documentales del Ministerio de Obras Públicas MOP y los datos institucionales del MOP, incluyendo el respaldo de repositorios, la gestión de contenedores, aplicaciones y otros datos actualmente alojados en infraestructura propia del Ministerio.</t>
         </is>
       </c>
       <c r="W93" s="5" t="str">
-        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=2434-20-LP26","descargar bases")</f>
+        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=1020-40-LP26","descargar bases")</f>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1133353-43-LR26</t>
+          <t xml:space="preserve">3902-39-LP26</t>
         </is>
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ARRIENDO DE SOFTWARE INTEGRAL PARA LA GESTIÓN MUNICIPAL ÁREAS DE SALUD Y MUNICIPAL COMUNA DE RAUCO</t>
+          <t xml:space="preserve">SERVICIO SOFTWARE SISTEMAS DE INFORMACIÓN BULNES.</t>
         </is>
       </c>
       <c r="C94" s="0" t="inlineStr">
@@ -9030,32 +9480,34 @@
       </c>
       <c r="D94" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">I MUNICIPALIDAD DE RAUCO</t>
+          <t xml:space="preserve">I MUNICIPALIDAD DE BULNES</t>
         </is>
       </c>
       <c r="E94" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">SECPLAC</t>
+          <t xml:space="preserve">I MUNICIPALIDAD DE BULNES</t>
         </is>
       </c>
       <c r="F94" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
-        </is>
-      </c>
-      <c r="G94" s="0"/>
+          <t xml:space="preserve">Región del Ñuble</t>
+        </is>
+      </c>
+      <c r="G94" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bulnes</t>
+        </is>
+      </c>
       <c r="H94" s="2">
-        <v>46251.511435</v>
+        <v>46261.708333</v>
       </c>
       <c r="I94" s="2">
-        <v>46281.729167</v>
+        <v>46280.6375</v>
       </c>
       <c r="J94" s="0">
-        <v>16</v>
-      </c>
-      <c r="K94" s="3">
-        <v>388644480.0</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="K94" s="3"/>
       <c r="L94" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">CLP</t>
@@ -9063,24 +9515,24 @@
       </c>
       <c r="M94" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">LR</t>
+          <t xml:space="preserve">LP</t>
         </is>
       </c>
       <c r="N94" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de administración de redes</t>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de gestión</t>
         </is>
       </c>
       <c r="O94" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 Global · Software de administración</t>
+          <t xml:space="preserve">1 Global · Paquetes de software para oficinas</t>
         </is>
       </c>
       <c r="P94" s="2"/>
       <c r="Q94" s="2"/>
       <c r="R94" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">72 meses</t>
+          <t xml:space="preserve">24 meses</t>
         </is>
       </c>
       <c r="S94" s="0" t="inlineStr">
@@ -9091,27 +9543,27 @@
       <c r="T94" s="4"/>
       <c r="U94" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUIS GALLARDO NARANJO</t>
+          <t xml:space="preserve">ULISES AEDO VALDÉS</t>
         </is>
       </c>
       <c r="V94" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.2La Ilustre Municipalidad de Rauco, requiere la “ARRIENDO DE SOFTWARE INTEGRAL PARA LA GESTIÓN MUNICIPAL ÁREAS DE SALUD Y MUNICIPAL”, cuyos detalles y reglamentación se encuentran contenidos en las presentes Bases Administrativas, Términos de Referencia y en los documentos anexos.</t>
+          <t xml:space="preserve">La Municipalidad de Bulnes, ha dispuesto la Licitación de la contratación por “SERVICIO DE SOFTWARE DE SISTEMAS DE INFORMACIÓN PARA MUNICIPALIDAD DE BULNES”, conforme a las exigencias de las presentes bases administrativas especiales, especificaciones técnicas, anexos, aclaraciones y demás antecedentes.</t>
         </is>
       </c>
       <c r="W94" s="5" t="str">
-        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=1133353-43-LR26","descargar bases")</f>
+        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=3902-39-LP26","descargar bases")</f>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2408-160-LP26</t>
+          <t xml:space="preserve">2434-20-LP26</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">EQUIPOS INFORMÁTICOS PARA DEPENDENCIAS MUNICIPALES</t>
+          <t xml:space="preserve">SERV. PLATAFORMA INTEGRAL PARA GESTION MUNICIPAL</t>
         </is>
       </c>
       <c r="C95" s="0" t="inlineStr">
@@ -9121,35 +9573,35 @@
       </c>
       <c r="D95" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">I MUNICIPALIDAD DE LOS ANGELES</t>
+          <t xml:space="preserve">I MUNICIPALIDAD ESTACION CENTRAL</t>
         </is>
       </c>
       <c r="E95" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">IMUNI_LOSANGELES ADQUISICIONES</t>
+          <t xml:space="preserve">SECRETARIA COMUNAL DE PLANIFICACION</t>
         </is>
       </c>
       <c r="F95" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t xml:space="preserve">Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="G95" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Los Angeles</t>
+          <t xml:space="preserve">Estación Central</t>
         </is>
       </c>
       <c r="H95" s="2">
-        <v>46261.357963</v>
+        <v>46261.839757</v>
       </c>
       <c r="I95" s="2">
-        <v>46282.375</v>
+        <v>46281.583333</v>
       </c>
       <c r="J95" s="0">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K95" s="3">
-        <v>80000000.0</v>
+        <v>204000000.0</v>
       </c>
       <c r="L95" s="0" t="inlineStr">
         <is>
@@ -9163,50 +9615,50 @@
       </c>
       <c r="N95" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Equipos informáticos y accesorios / Computadores, Tecnologías de la información, telecomunicaciones y radiodifusión / Equipos informáticos y accesorios / Dispositivos informáticos de entrada de datos, Tecnologías de la información, telecomunicaciones y radiodifusión / Equipos informáticos y accesorios / Impresoras</t>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software para trabajo en redes</t>
         </is>
       </c>
       <c r="O95" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">40 Unidad · Escáner · 70 Unidad · Impresoras de chorro de tinta · 3 Unidad · Trazadoras de gráficos · y 3 más</t>
+          <t xml:space="preserve">1 Global · Software de interconectividad de plataformas</t>
         </is>
       </c>
       <c r="P95" s="2"/>
       <c r="Q95" s="2"/>
-      <c r="R95" s="0"/>
+      <c r="R95" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12 meses</t>
+        </is>
+      </c>
       <c r="S95" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">No</t>
         </is>
       </c>
-      <c r="T95" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">De acuerdo a lo señalado en la cláusula N°9.27 de las bases administrativas.</t>
-        </is>
-      </c>
+      <c r="T95" s="4"/>
       <c r="U95" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">María Pamela Vega Garcés</t>
+          <t xml:space="preserve">Iván Ahumada</t>
         </is>
       </c>
       <c r="V95" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Se requiere la adquisición de equipos informáticos para la municipalidad de los ángeles.</t>
+          <t xml:space="preserve">El suministro y mantención de sistemas informáticos,  busca además, establecer una relación de colaboración de largo plazo, orientada a fortalecer la transformación digital institucional, garantizando la continuidad operacional, la seguridad de la información, la interoperabilidad entre sistemas y la permanente modernización de la plataforma tecnológica municipal</t>
         </is>
       </c>
       <c r="W95" s="5" t="str">
-        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=2408-160-LP26","descargar bases")</f>
+        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=2434-20-LP26","descargar bases")</f>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1593-24-LP26</t>
+          <t xml:space="preserve">1133353-43-LR26</t>
         </is>
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adquisición instalación plataforma almacenamiento</t>
+          <t xml:space="preserve">ARRIENDO DE SOFTWARE INTEGRAL PARA LA GESTIÓN MUNICIPAL ÁREAS DE SALUD Y MUNICIPAL COMUNA DE RAUCO</t>
         </is>
       </c>
       <c r="C96" s="0" t="inlineStr">
@@ -9216,35 +9668,31 @@
       </c>
       <c r="D96" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">SUPERINTENDENCIA DE SERVICIOS SANITARIOS</t>
+          <t xml:space="preserve">I MUNICIPALIDAD DE RAUCO</t>
         </is>
       </c>
       <c r="E96" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Superintendencia de Servicios Sanitarios - SISS</t>
+          <t xml:space="preserve">SECPLAC</t>
         </is>
       </c>
       <c r="F96" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región Metropolitana de Santiago</t>
-        </is>
-      </c>
-      <c r="G96" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Santiago</t>
-        </is>
-      </c>
+          <t xml:space="preserve">Región del Maule </t>
+        </is>
+      </c>
+      <c r="G96" s="0"/>
       <c r="H96" s="2">
-        <v>46262.944537</v>
+        <v>46251.511435</v>
       </c>
       <c r="I96" s="2">
-        <v>46282.4375</v>
+        <v>46281.729167</v>
       </c>
       <c r="J96" s="0">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K96" s="3">
-        <v>177000000.0</v>
+        <v>388644480.0</v>
       </c>
       <c r="L96" s="0" t="inlineStr">
         <is>
@@ -9253,24 +9701,24 @@
       </c>
       <c r="M96" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">LP</t>
+          <t xml:space="preserve">LR</t>
         </is>
       </c>
       <c r="N96" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Servicios basados en ingeniería, ciencias sociales y tecnología de la información / Servicios informáticos / Administración de sistemas</t>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de administración de redes</t>
         </is>
       </c>
       <c r="O96" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 Unidad · Almacenamiento de datos</t>
+          <t xml:space="preserve">1 Global · Software de administración</t>
         </is>
       </c>
       <c r="P96" s="2"/>
       <c r="Q96" s="2"/>
       <c r="R96" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">60 días</t>
+          <t xml:space="preserve">72 meses</t>
         </is>
       </c>
       <c r="S96" s="0" t="inlineStr">
@@ -9281,27 +9729,27 @@
       <c r="T96" s="4"/>
       <c r="U96" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fernando Iriarte</t>
+          <t xml:space="preserve">LUIS GALLARDO NARANJO</t>
         </is>
       </c>
       <c r="V96" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">El objeto de la licitación es la adquisición e instalación de plataforma de almacenamiento para cubrir las necesidades de obsolescencia de infraestructura y que permita a la vez contar con nuevas funcionalidades y prestaciones para la SiSS.</t>
+          <t xml:space="preserve">1.2La Ilustre Municipalidad de Rauco, requiere la “ARRIENDO DE SOFTWARE INTEGRAL PARA LA GESTIÓN MUNICIPAL ÁREAS DE SALUD Y MUNICIPAL”, cuyos detalles y reglamentación se encuentran contenidos en las presentes Bases Administrativas, Términos de Referencia y en los documentos anexos.</t>
         </is>
       </c>
       <c r="W96" s="5" t="str">
-        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=1593-24-LP26","descargar bases")</f>
+        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=1133353-43-LR26","descargar bases")</f>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2563-34-LR26</t>
+          <t xml:space="preserve">2408-160-LP26</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">EQUIPOS PARA REDES INFORMÁTICAS Y LICENCIAS</t>
+          <t xml:space="preserve">EQUIPOS INFORMÁTICOS PARA DEPENDENCIAS MUNICIPALES</t>
         </is>
       </c>
       <c r="C97" s="0" t="inlineStr">
@@ -9311,35 +9759,35 @@
       </c>
       <c r="D97" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
+          <t xml:space="preserve">I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="E97" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">UNIDAD DE COMPRA CONTRATOS NACIONALES</t>
+          <t xml:space="preserve">IMUNI_LOSANGELES ADQUISICIONES</t>
         </is>
       </c>
       <c r="F97" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región Metropolitana de Santiago</t>
+          <t xml:space="preserve">Región del Biobío </t>
         </is>
       </c>
       <c r="G97" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Providencia</t>
+          <t xml:space="preserve">Los Angeles</t>
         </is>
       </c>
       <c r="H97" s="2">
-        <v>46254.631817</v>
+        <v>46261.357963</v>
       </c>
       <c r="I97" s="2">
-        <v>46286.625694</v>
+        <v>46282.375</v>
       </c>
       <c r="J97" s="0">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="K97" s="3">
-        <v>453590167.0</v>
+        <v>80000000.0</v>
       </c>
       <c r="L97" s="0" t="inlineStr">
         <is>
@@ -9348,17 +9796,17 @@
       </c>
       <c r="M97" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">LR</t>
+          <t xml:space="preserve">LP</t>
         </is>
       </c>
       <c r="N97" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Equipos informáticos y accesorios / Accesorios de computador</t>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Equipos informáticos y accesorios / Computadores, Tecnologías de la información, telecomunicaciones y radiodifusión / Equipos informáticos y accesorios / Dispositivos informáticos de entrada de datos, Tecnologías de la información, telecomunicaciones y radiodifusión / Equipos informáticos y accesorios / Impresoras</t>
         </is>
       </c>
       <c r="O97" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">10 Unidad · Cajas de conmutación de computadores · 11 Unidad · Cajas de conmutación de computadores · 1 Unidad · Cajas de conmutación de computadores · y 14 más</t>
+          <t xml:space="preserve">40 Unidad · Escáner · 70 Unidad · Impresoras de chorro de tinta · 3 Unidad · Trazadoras de gráficos · y 3 más</t>
         </is>
       </c>
       <c r="P97" s="2"/>
@@ -9369,30 +9817,34 @@
           <t xml:space="preserve">No</t>
         </is>
       </c>
-      <c r="T97" s="4"/>
+      <c r="T97" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">De acuerdo a lo señalado en la cláusula N°9.27 de las bases administrativas.</t>
+        </is>
+      </c>
       <c r="U97" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Javier Pacheco Barahona</t>
+          <t xml:space="preserve">María Pamela Vega Garcés</t>
         </is>
       </c>
       <c r="V97" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADQUISICIÓN DE EQUIPOS DE COMUNICACIONES PARA REDES INFORMÁTICAS Y LICENCIAS DE SOFTWARE MODALIDAD LLAVE EN MANO, PARA EL PROYECTO CONTROL DE ACCESO A LA RED Y PROYECTOS AEROPORTUARIOS PARA LA DIRECCIÓN GENERAL DE AERONÁUTICA CIVIL</t>
+          <t xml:space="preserve">Se requiere la adquisición de equipos informáticos para la municipalidad de los ángeles.</t>
         </is>
       </c>
       <c r="W97" s="5" t="str">
-        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=2563-34-LR26","descargar bases")</f>
+        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=2408-160-LP26","descargar bases")</f>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1259850-4-LP26</t>
+          <t xml:space="preserve">1593-24-LP26</t>
         </is>
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">GORE COMPRA DE EQUIPOS INFORMATICOS</t>
+          <t xml:space="preserve">Adquisición instalación plataforma almacenamiento</t>
         </is>
       </c>
       <c r="C98" s="0" t="inlineStr">
@@ -9402,34 +9854,36 @@
       </c>
       <c r="D98" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t xml:space="preserve">SUPERINTENDENCIA DE SERVICIOS SANITARIOS</t>
         </is>
       </c>
       <c r="E98" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Compras GORE Arica y Parinacota</t>
+          <t xml:space="preserve">Superintendencia de Servicios Sanitarios - SISS</t>
         </is>
       </c>
       <c r="F98" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Arica y Parinacota</t>
+          <t xml:space="preserve">Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="G98" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arica</t>
+          <t xml:space="preserve">Santiago</t>
         </is>
       </c>
       <c r="H98" s="2">
-        <v>46255.670162</v>
+        <v>46262.944537</v>
       </c>
       <c r="I98" s="2">
-        <v>46286.645833</v>
+        <v>46282.4375</v>
       </c>
       <c r="J98" s="0">
-        <v>21</v>
-      </c>
-      <c r="K98" s="3"/>
+        <v>17</v>
+      </c>
+      <c r="K98" s="3">
+        <v>177000000.0</v>
+      </c>
       <c r="L98" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">CLP</t>
@@ -9442,17 +9896,21 @@
       </c>
       <c r="N98" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Equipos informáticos y accesorios / Computadores, Tecnologías de la información, telecomunicaciones y radiodifusión / Equipos informáticos y accesorios / Dispositivos informáticos de entrada de datos, Tecnologías de la información, telecomunicaciones y radiodifusión / Equipos informáticos y accesorios / Impresoras</t>
+          <t xml:space="preserve">Servicios basados en ingeniería, ciencias sociales y tecnología de la información / Servicios informáticos / Administración de sistemas</t>
         </is>
       </c>
       <c r="O98" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">66 Unidad · Computadores de escritorio · 15 Unidad · Impresoras multifunción o multifuncionales · 4 Unidad · Escáner</t>
+          <t xml:space="preserve">1 Unidad · Almacenamiento de datos</t>
         </is>
       </c>
       <c r="P98" s="2"/>
       <c r="Q98" s="2"/>
-      <c r="R98" s="0"/>
+      <c r="R98" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">60 días</t>
+        </is>
+      </c>
       <c r="S98" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">No</t>
@@ -9461,27 +9919,27 @@
       <c r="T98" s="4"/>
       <c r="U98" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALEX MEDINA MEDINA</t>
+          <t xml:space="preserve">Fernando Iriarte</t>
         </is>
       </c>
       <c r="V98" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">GOBIERNO REGIONAL ADQUISICION DE COMPUTADORES IMPRESORAS Y ESCANER PROYECTO REPOSICION E INCORPORACION DE EQUIPOS INFORMATICOS DE ALTA SEGURIDAD PARA RECINTOS PENITENCIARIOS.</t>
+          <t xml:space="preserve">El objeto de la licitación es la adquisición e instalación de plataforma de almacenamiento para cubrir las necesidades de obsolescencia de infraestructura y que permita a la vez contar con nuevas funcionalidades y prestaciones para la SiSS.</t>
         </is>
       </c>
       <c r="W98" s="5" t="str">
-        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=1259850-4-LP26","descargar bases")</f>
+        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=1593-24-LP26","descargar bases")</f>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2069-141-LR26</t>
+          <t xml:space="preserve">2563-34-LR26</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">CGM ADQ. TORRE DE ENDOSCOPIA DIGESTIVA CON IA</t>
+          <t xml:space="preserve">EQUIPOS PARA REDES INFORMÁTICAS Y LICENCIAS</t>
         </is>
       </c>
       <c r="C99" s="0" t="inlineStr">
@@ -9491,12 +9949,12 @@
       </c>
       <c r="D99" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+          <t xml:space="preserve">DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
         </is>
       </c>
       <c r="E99" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">HOSPITAL BARROS LUCO TRUDEAU</t>
+          <t xml:space="preserve">UNIDAD DE COMPRA CONTRATOS NACIONALES</t>
         </is>
       </c>
       <c r="F99" s="0" t="inlineStr">
@@ -9506,19 +9964,21 @@
       </c>
       <c r="G99" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">San Miguel</t>
+          <t xml:space="preserve">Providencia</t>
         </is>
       </c>
       <c r="H99" s="2">
-        <v>46252.66316</v>
+        <v>46254.631817</v>
       </c>
       <c r="I99" s="2">
-        <v>46286.666667</v>
+        <v>46286.625694</v>
       </c>
       <c r="J99" s="0">
         <v>21</v>
       </c>
-      <c r="K99" s="3"/>
+      <c r="K99" s="3">
+        <v>453590167.0</v>
+      </c>
       <c r="L99" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">CLP</t>
@@ -9531,12 +9991,12 @@
       </c>
       <c r="N99" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Equipamiento y suministros médicos / Productos quirúrgicos / Equipo endoscópico, accesorios y productos relacionados</t>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Equipos informáticos y accesorios / Accesorios de computador</t>
         </is>
       </c>
       <c r="O99" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 Unidad · Equipo endoscópico o carritos de procedimiento o accesorios</t>
+          <t xml:space="preserve">10 Unidad · Cajas de conmutación de computadores · 11 Unidad · Cajas de conmutación de computadores · 1 Unidad · Cajas de conmutación de computadores · y 14 más</t>
         </is>
       </c>
       <c r="P99" s="2"/>
@@ -9547,17 +10007,195 @@
           <t xml:space="preserve">No</t>
         </is>
       </c>
-      <c r="T99" s="4" t="inlineStr">
+      <c r="T99" s="4"/>
+      <c r="U99" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Javier Pacheco Barahona</t>
+        </is>
+      </c>
+      <c r="V99" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADQUISICIÓN DE EQUIPOS DE COMUNICACIONES PARA REDES INFORMÁTICAS Y LICENCIAS DE SOFTWARE MODALIDAD LLAVE EN MANO, PARA EL PROYECTO CONTROL DE ACCESO A LA RED Y PROYECTOS AEROPORTUARIOS PARA LA DIRECCIÓN GENERAL DE AERONÁUTICA CIVIL</t>
+        </is>
+      </c>
+      <c r="W99" s="5" t="str">
+        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=2563-34-LR26","descargar bases")</f>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1259850-4-LP26</t>
+        </is>
+      </c>
+      <c r="B100" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GORE COMPRA DE EQUIPOS INFORMATICOS</t>
+        </is>
+      </c>
+      <c r="C100" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Publicada</t>
+        </is>
+      </c>
+      <c r="D100" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+        </is>
+      </c>
+      <c r="E100" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Compras GORE Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="F100" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="G100" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Arica</t>
+        </is>
+      </c>
+      <c r="H100" s="2">
+        <v>46255.670162</v>
+      </c>
+      <c r="I100" s="2">
+        <v>46286.645833</v>
+      </c>
+      <c r="J100" s="0">
+        <v>21</v>
+      </c>
+      <c r="K100" s="3"/>
+      <c r="L100" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CLP</t>
+        </is>
+      </c>
+      <c r="M100" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LP</t>
+        </is>
+      </c>
+      <c r="N100" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Equipos informáticos y accesorios / Computadores, Tecnologías de la información, telecomunicaciones y radiodifusión / Equipos informáticos y accesorios / Dispositivos informáticos de entrada de datos, Tecnologías de la información, telecomunicaciones y radiodifusión / Equipos informáticos y accesorios / Impresoras</t>
+        </is>
+      </c>
+      <c r="O100" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">66 Unidad · Computadores de escritorio · 15 Unidad · Impresoras multifunción o multifuncionales · 4 Unidad · Escáner</t>
+        </is>
+      </c>
+      <c r="P100" s="2"/>
+      <c r="Q100" s="2"/>
+      <c r="R100" s="0"/>
+      <c r="S100" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="T100" s="4"/>
+      <c r="U100" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ALEX MEDINA MEDINA</t>
+        </is>
+      </c>
+      <c r="V100" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GOBIERNO REGIONAL ADQUISICION DE COMPUTADORES IMPRESORAS Y ESCANER PROYECTO REPOSICION E INCORPORACION DE EQUIPOS INFORMATICOS DE ALTA SEGURIDAD PARA RECINTOS PENITENCIARIOS.</t>
+        </is>
+      </c>
+      <c r="W100" s="5" t="str">
+        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=1259850-4-LP26","descargar bases")</f>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2069-141-LR26</t>
+        </is>
+      </c>
+      <c r="B101" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CGM ADQ. TORRE DE ENDOSCOPIA DIGESTIVA CON IA</t>
+        </is>
+      </c>
+      <c r="C101" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Publicada</t>
+        </is>
+      </c>
+      <c r="D101" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+        </is>
+      </c>
+      <c r="E101" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HOSPITAL BARROS LUCO TRUDEAU</t>
+        </is>
+      </c>
+      <c r="F101" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="G101" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">San Miguel</t>
+        </is>
+      </c>
+      <c r="H101" s="2">
+        <v>46252.66316</v>
+      </c>
+      <c r="I101" s="2">
+        <v>46286.666667</v>
+      </c>
+      <c r="J101" s="0">
+        <v>21</v>
+      </c>
+      <c r="K101" s="3"/>
+      <c r="L101" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CLP</t>
+        </is>
+      </c>
+      <c r="M101" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LR</t>
+        </is>
+      </c>
+      <c r="N101" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Equipamiento y suministros médicos / Productos quirúrgicos / Equipo endoscópico, accesorios y productos relacionados</t>
+        </is>
+      </c>
+      <c r="O101" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 Unidad · Equipo endoscópico o carritos de procedimiento o accesorios</t>
+        </is>
+      </c>
+      <c r="P101" s="2"/>
+      <c r="Q101" s="2"/>
+      <c r="R101" s="0"/>
+      <c r="S101" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="T101" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Véase numeral 16 Subcontratación</t>
         </is>
       </c>
-      <c r="U99" s="0" t="inlineStr">
+      <c r="U101" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Jefa de unidad de adquisiciones de mantención y se</t>
         </is>
       </c>
-      <c r="V99" s="4" t="inlineStr">
+      <c r="V101" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">El Hospital Barros Luco Trudeau requiere adquirir dos 2 torres de endoscopía digestiva con Inteligencia Artificial, destinadas a la Unidad de Endoscopía, con el objeto de fortalecer la capacidad diagnóstica y terapéutica institucional mediante la incorporación de equipamiento de última generación que permita apoyar la detección y caracterización de lesiones durante los procedimientos endoscópicos.
 La solución requerida deberá proporcionar imágenes endoscópicas de alta calidad e incorporar herramientas avanzadas de visualización e Inteligencia Artificial para el análisis en tiempo real y apoyo al operador en la identificación de lesiones y hallazgos de interés clínico, de acuerdo con las prestaciones establecidas en las Especificaciones Técnicas.
@@ -9565,303 +10203,115 @@
 La presente adquisición considera una solución integral, cuya</t>
         </is>
       </c>
-      <c r="W99" s="5" t="str">
+      <c r="W101" s="5" t="str">
         <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=2069-141-LR26","descargar bases")</f>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="0" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">1562-49-LR26</t>
         </is>
       </c>
-      <c r="B100" s="4" t="inlineStr">
+      <c r="B102" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Sistema de monitoreo integral de ciberseguridad</t>
         </is>
       </c>
-      <c r="C100" s="0" t="inlineStr">
+      <c r="C102" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Publicada</t>
         </is>
       </c>
-      <c r="D100" s="0" t="inlineStr">
+      <c r="D102" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">SERVICIO NACIONAL DE GEOLOGIA Y MINERIA</t>
         </is>
       </c>
-      <c r="E100" s="0" t="inlineStr">
+      <c r="E102" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Servicio Nacional de Geología y Minería</t>
         </is>
       </c>
-      <c r="F100" s="0" t="inlineStr">
+      <c r="F102" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Región Metropolitana de Santiago</t>
         </is>
       </c>
-      <c r="G100" s="0" t="inlineStr">
+      <c r="G102" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Providencia</t>
         </is>
       </c>
-      <c r="H100" s="2">
+      <c r="H102" s="2">
         <v>46254.764514</v>
       </c>
-      <c r="I100" s="2">
+      <c r="I102" s="2">
         <v>46287.625</v>
       </c>
-      <c r="J100" s="0">
+      <c r="J102" s="0">
         <v>22</v>
       </c>
-      <c r="K100" s="3">
+      <c r="K102" s="3">
         <v>366678654.0</v>
       </c>
-      <c r="L100" s="0" t="inlineStr">
+      <c r="L102" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">CLP</t>
         </is>
       </c>
-      <c r="M100" s="0" t="inlineStr">
+      <c r="M102" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">LR</t>
         </is>
       </c>
-      <c r="N100" s="4" t="inlineStr">
+      <c r="N102" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Equipos, plataformas y accesorios de redes multimedia, voz y datos / Equipos de seguridad de red</t>
         </is>
       </c>
-      <c r="O100" s="4" t="inlineStr">
+      <c r="O102" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">1 Unidad · Equipo de seguridad de evaluación de vulnerabilidad</t>
         </is>
       </c>
-      <c r="P100" s="2"/>
-      <c r="Q100" s="2"/>
-      <c r="R100" s="0" t="inlineStr">
+      <c r="P102" s="2"/>
+      <c r="Q102" s="2"/>
+      <c r="R102" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">12 meses</t>
         </is>
       </c>
-      <c r="S100" s="0" t="inlineStr">
+      <c r="S102" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">No</t>
         </is>
       </c>
-      <c r="T100" s="4"/>
-      <c r="U100" s="0" t="inlineStr">
+      <c r="T102" s="4"/>
+      <c r="U102" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Gonzalo Palet</t>
         </is>
       </c>
-      <c r="V100" s="4" t="inlineStr">
+      <c r="V102" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">El Servicio Nacional de Geología y Minería SERNAGEOMIN requiere contratar un Servicio de Monitoreo integral de ciberseguridad que incluye suscripciones de software, implementación, capacitación, soporte y operación continua, orientado a fortalecer su postura institucional de ciberdefensa, proteger activos críticos de información y asegurar la continuidad operativa.
 El requerimiento se enmarca en la Ley Marco de Ciberseguridad e Infraestructura Crítica OIV, la Estrategia Nacional de Ciberseguridad y los estándares internacionales aplicables. Contempla una plataforma de protección avanzada con capacidades de prevención, detección, respuesta y monitoreo continuo, integrada a un modelo de Servicio de Monitoreo y alineada a un enfoque de Zero Trust.</t>
         </is>
       </c>
-      <c r="W100" s="5" t="str">
+      <c r="W102" s="5" t="str">
         <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=1562-49-LR26","descargar bases")</f>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">586-52-LP26</t>
-        </is>
-      </c>
-      <c r="B101" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Adquisición de licencias de software Redhat</t>
-        </is>
-      </c>
-      <c r="C101" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Publicada</t>
-        </is>
-      </c>
-      <c r="D101" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SERVICIO NACIONAL DE ADUANAS</t>
-        </is>
-      </c>
-      <c r="E101" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Dirección Nacional de Aduanas</t>
-        </is>
-      </c>
-      <c r="F101" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
-        </is>
-      </c>
-      <c r="G101" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Valparaíso</t>
-        </is>
-      </c>
-      <c r="H101" s="2">
-        <v>46261.817222</v>
-      </c>
-      <c r="I101" s="2">
-        <v>46287.625</v>
-      </c>
-      <c r="J101" s="0">
-        <v>22</v>
-      </c>
-      <c r="K101" s="3"/>
-      <c r="L101" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">USD</t>
-        </is>
-      </c>
-      <c r="M101" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LP</t>
-        </is>
-      </c>
-      <c r="N101" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de gestión</t>
-        </is>
-      </c>
-      <c r="O101" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1 Unidad · Software de gestión de licencias</t>
-        </is>
-      </c>
-      <c r="P101" s="2"/>
-      <c r="Q101" s="2"/>
-      <c r="R101" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12 meses</t>
-        </is>
-      </c>
-      <c r="S101" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">No</t>
-        </is>
-      </c>
-      <c r="T101" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Conforme a numeral VII.1 de las Bases Administrativas</t>
-        </is>
-      </c>
-      <c r="U101" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Marcelo Reyes</t>
-        </is>
-      </c>
-      <c r="V101" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Adquisición de suscripciones de licencias de software Redhat, conforme a bases de licitación</t>
-        </is>
-      </c>
-      <c r="W101" s="5" t="str">
-        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=586-52-LP26","descargar bases")</f>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3084-31-LE26</t>
-        </is>
-      </c>
-      <c r="B102" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SERVICIO REPARACIÓN DE OFICINAS PARA LA DIRECCIÓN DE TELECOMUNICACIONES E INFORMÁTICA DE LA ARMADA.</t>
-        </is>
-      </c>
-      <c r="C102" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Publicada</t>
-        </is>
-      </c>
-      <c r="D102" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
-        </is>
-      </c>
-      <c r="E102" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Dirección de Telecomunicaciones e Informática de la Armada</t>
-        </is>
-      </c>
-      <c r="F102" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
-        </is>
-      </c>
-      <c r="G102" s="0"/>
-      <c r="H102" s="2">
-        <v>46262.346319</v>
-      </c>
-      <c r="I102" s="2">
-        <v>46287.625694</v>
-      </c>
-      <c r="J102" s="0">
-        <v>22</v>
-      </c>
-      <c r="K102" s="3">
-        <v>10000000.0</v>
-      </c>
-      <c r="L102" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CLP</t>
-        </is>
-      </c>
-      <c r="M102" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LE</t>
-        </is>
-      </c>
-      <c r="N102" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Servicios profesionales, administrativos y consultorías de gestión empresarial / Servicios de recursos humanos / Servicios de personal temporal</t>
-        </is>
-      </c>
-      <c r="O102" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1 Unidad · Mano de obra temporal</t>
-        </is>
-      </c>
-      <c r="P102" s="2"/>
-      <c r="Q102" s="2"/>
-      <c r="R102" s="0"/>
-      <c r="S102" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">No</t>
-        </is>
-      </c>
-      <c r="T102" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1.Los derechos y obligaciones que nacen con ocasión del desarrollo del presente procedimiento de contratación pública, serán intransferibles, sin perjuicio de que una norma legal especial permita expresamente la cesión de derechos y obligaciones.</t>
-        </is>
-      </c>
-      <c r="U102" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Karen Arellano</t>
-        </is>
-      </c>
-      <c r="V102" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SERVICIO REPARACIÓN DE OFICINAS PARA LA DIRECCIÓN DE TELECOMUNICACIONES E INFORMÁTICA DE LA ARMADA.</t>
-        </is>
-      </c>
-      <c r="W102" s="5" t="str">
-        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=3084-31-LE26","descargar bases")</f>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2200-23-LR26</t>
+          <t xml:space="preserve">586-52-LP26</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">SERVICIO DE ARRIENDO DE SOFTWARE DE REGISTRO CLÍNICO ELECTRÓNICO RCE ATENCIÓN PRIMARIA - TIC</t>
+          <t xml:space="preserve">Adquisición de licencias de software Redhat</t>
         </is>
       </c>
       <c r="C103" s="0" t="inlineStr">
@@ -9871,12 +10321,12 @@
       </c>
       <c r="D103" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">SERVICIO DE SALUD ACONCAGUA</t>
+          <t xml:space="preserve">SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="E103" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Servicio de Salud Aconcagua</t>
+          <t xml:space="preserve">Dirección Nacional de Aduanas</t>
         </is>
       </c>
       <c r="F103" s="0" t="inlineStr">
@@ -9886,58 +10336,337 @@
       </c>
       <c r="G103" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">San Felipe</t>
+          <t xml:space="preserve">Valparaíso</t>
         </is>
       </c>
       <c r="H103" s="2">
-        <v>46259.424259</v>
+        <v>46261.817222</v>
       </c>
       <c r="I103" s="2">
-        <v>46289.625</v>
+        <v>46287.625</v>
       </c>
       <c r="J103" s="0">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="K103" s="3"/>
       <c r="L103" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">CLP</t>
+          <t xml:space="preserve">USD</t>
         </is>
       </c>
       <c r="M103" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">LR</t>
+          <t xml:space="preserve">LP</t>
         </is>
       </c>
       <c r="N103" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Servicios profesionales, administrativos y consultorías de gestión empresarial / Servicios de recursos humanos / Contratación de personal</t>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de gestión</t>
         </is>
       </c>
       <c r="O103" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1700 Unidad · Desarrolladores de software</t>
+          <t xml:space="preserve">1 Unidad · Software de gestión de licencias</t>
         </is>
       </c>
       <c r="P103" s="2"/>
       <c r="Q103" s="2"/>
       <c r="R103" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">12 meses</t>
+        </is>
+      </c>
+      <c r="S103" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="T103" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Conforme a numeral VII.1 de las Bases Administrativas</t>
+        </is>
+      </c>
+      <c r="U103" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Marcelo Reyes</t>
+        </is>
+      </c>
+      <c r="V103" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Adquisición de suscripciones de licencias de software Redhat, conforme a bases de licitación</t>
+        </is>
+      </c>
+      <c r="W103" s="5" t="str">
+        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=586-52-LP26","descargar bases")</f>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3084-31-LE26</t>
+        </is>
+      </c>
+      <c r="B104" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SERVICIO REPARACIÓN DE OFICINAS PARA LA DIRECCIÓN DE TELECOMUNICACIONES E INFORMÁTICA DE LA ARMADA.</t>
+        </is>
+      </c>
+      <c r="C104" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Publicada</t>
+        </is>
+      </c>
+      <c r="D104" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+        </is>
+      </c>
+      <c r="E104" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dirección de Telecomunicaciones e Informática de la Armada</t>
+        </is>
+      </c>
+      <c r="F104" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Valparaíso </t>
+        </is>
+      </c>
+      <c r="G104" s="0"/>
+      <c r="H104" s="2">
+        <v>46262.346319</v>
+      </c>
+      <c r="I104" s="2">
+        <v>46287.625694</v>
+      </c>
+      <c r="J104" s="0">
+        <v>22</v>
+      </c>
+      <c r="K104" s="3">
+        <v>10000000.0</v>
+      </c>
+      <c r="L104" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CLP</t>
+        </is>
+      </c>
+      <c r="M104" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LE</t>
+        </is>
+      </c>
+      <c r="N104" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Servicios profesionales, administrativos y consultorías de gestión empresarial / Servicios de recursos humanos / Servicios de personal temporal</t>
+        </is>
+      </c>
+      <c r="O104" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 Unidad · Mano de obra temporal</t>
+        </is>
+      </c>
+      <c r="P104" s="2"/>
+      <c r="Q104" s="2"/>
+      <c r="R104" s="0"/>
+      <c r="S104" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="T104" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.Los derechos y obligaciones que nacen con ocasión del desarrollo del presente procedimiento de contratación pública, serán intransferibles, sin perjuicio de que una norma legal especial permita expresamente la cesión de derechos y obligaciones.</t>
+        </is>
+      </c>
+      <c r="U104" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Karen Arellano</t>
+        </is>
+      </c>
+      <c r="V104" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SERVICIO REPARACIÓN DE OFICINAS PARA LA DIRECCIÓN DE TELECOMUNICACIONES E INFORMÁTICA DE LA ARMADA.</t>
+        </is>
+      </c>
+      <c r="W104" s="5" t="str">
+        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=3084-31-LE26","descargar bases")</f>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">837-101-LP26</t>
+        </is>
+      </c>
+      <c r="B105" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CDP 477 SERVICIO DE OPERACIÓN SISTEMA DE CONTROL CENTRALIZADO BMS Y SISTEMA DE TELEVIGILANCIA SOFTWARE HIKCENTRAL PROFESSIONAL DE EDIFICIO INSTITUCIONAL SML SANTIAGO</t>
+        </is>
+      </c>
+      <c r="C105" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Publicada</t>
+        </is>
+      </c>
+      <c r="D105" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SERVICIO MEDICO LEGAL</t>
+        </is>
+      </c>
+      <c r="E105" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SERVICIO MEDICO LEGAL</t>
+        </is>
+      </c>
+      <c r="F105" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="G105" s="0"/>
+      <c r="H105" s="2">
+        <v>46265.419491</v>
+      </c>
+      <c r="I105" s="2">
+        <v>46287.645833</v>
+      </c>
+      <c r="J105" s="0">
+        <v>22</v>
+      </c>
+      <c r="K105" s="3">
+        <v>346885000.0</v>
+      </c>
+      <c r="L105" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CLP</t>
+        </is>
+      </c>
+      <c r="M105" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LP</t>
+        </is>
+      </c>
+      <c r="N105" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Equipos y suministros de defensa, orden público, protección y seguridad / Seguridad, vigilancia y detección / Equipo de vigilancia y detección, Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de administración de redes</t>
+        </is>
+      </c>
+      <c r="O105" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12 Mes · Software de administración · 12 Mes · Sistemas de control de acceso o de seguridad</t>
+        </is>
+      </c>
+      <c r="P105" s="2"/>
+      <c r="Q105" s="2"/>
+      <c r="R105" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12 meses</t>
+        </is>
+      </c>
+      <c r="S105" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="T105" s="4"/>
+      <c r="U105" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vicente Muñoz, profesional DLI</t>
+        </is>
+      </c>
+      <c r="V105" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Se requiere contar con el SERVICIO DE OPERACIÓN PARA EL SISTEMA DE CONTROL CENTRALIZADO (BMS) SOFTWARE ENTELIWEB Y EL SISTEMA DE TELEVIGILANCIA SOFTWARE HIKCENTRAL) Y SU EQUIPAMIENTO ASOCIADO PERTENECIENTES AL EDIFICIO INSTITUCIONAL DEL SERVICIO MÉDICO LEGAL METROPOLITANO (SML), con el objeto de asegurar su correcta operación, revisión de instalaciones y programación en los sistemas y equipamiento instalados</t>
+        </is>
+      </c>
+      <c r="W105" s="5" t="str">
+        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=837-101-LP26","descargar bases")</f>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2200-23-LR26</t>
+        </is>
+      </c>
+      <c r="B106" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SERVICIO DE ARRIENDO DE SOFTWARE DE REGISTRO CLÍNICO ELECTRÓNICO RCE ATENCIÓN PRIMARIA - TIC</t>
+        </is>
+      </c>
+      <c r="C106" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Publicada</t>
+        </is>
+      </c>
+      <c r="D106" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SERVICIO DE SALUD ACONCAGUA</t>
+        </is>
+      </c>
+      <c r="E106" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Servicio de Salud Aconcagua</t>
+        </is>
+      </c>
+      <c r="F106" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Valparaíso </t>
+        </is>
+      </c>
+      <c r="G106" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">San Felipe</t>
+        </is>
+      </c>
+      <c r="H106" s="2">
+        <v>46259.424259</v>
+      </c>
+      <c r="I106" s="2">
+        <v>46289.625</v>
+      </c>
+      <c r="J106" s="0">
+        <v>24</v>
+      </c>
+      <c r="K106" s="3"/>
+      <c r="L106" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CLP</t>
+        </is>
+      </c>
+      <c r="M106" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LR</t>
+        </is>
+      </c>
+      <c r="N106" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Servicios profesionales, administrativos y consultorías de gestión empresarial / Servicios de recursos humanos / Contratación de personal</t>
+        </is>
+      </c>
+      <c r="O106" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1700 Unidad · Desarrolladores de software</t>
+        </is>
+      </c>
+      <c r="P106" s="2"/>
+      <c r="Q106" s="2"/>
+      <c r="R106" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">18 meses</t>
         </is>
       </c>
-      <c r="S103" s="0" t="inlineStr">
+      <c r="S106" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">No</t>
         </is>
       </c>
-      <c r="T103" s="4"/>
-      <c r="U103" s="0" t="inlineStr">
+      <c r="T106" s="4"/>
+      <c r="U106" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">MASIEL BALBOA GONZALEZ</t>
         </is>
       </c>
-      <c r="V103" s="4" t="inlineStr">
+      <c r="V106" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">1.El Servicio de Salud Aconcagua requiere el Servicio de Arriendo de Software de Registro Clínico Electrónico (RCE) y sus servicios complementarios de configuración, entrenamiento, instalación, mantención, soporte, data center, entre otros, para toda la red de establecimientos de Atención Primaria de Salud del Servicio de Salud Aconcagua, mediante un  contrato de suministro de servicio por un perido de 18 meses.
 2.La Solicitud de Compra N°14 de fecha 11.08.2026, Oficina de Partes N°438 de fecha 12.08.2026 (Interno N°459),  presentada por la requirente del Departamento TIC, fue debidamente aprobada y autorizada por la Subdirectora de Gestión Asistencial, el Subdirector de Recursos Físicos y Financieros y el Jefe del Departamento de Finanzas quienes respaldan la Contratación.
@@ -9945,404 +10674,116 @@
 4.Que, según lo establecido en el reglamento, los organismos de la administración del Estado deberán adjudicar los contratos celebrados para la ad</t>
         </is>
       </c>
-      <c r="W103" s="5" t="str">
+      <c r="W106" s="5" t="str">
         <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=2200-23-LR26","descargar bases")</f>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="0" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">1973-93-LR26</t>
         </is>
       </c>
-      <c r="B104" s="4" t="inlineStr">
+      <c r="B107" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">SISTEMA DE INFORMACIÓN DE GESTIÓN ADMINISTRATIVA Y FARMACIA</t>
         </is>
       </c>
-      <c r="C104" s="0" t="inlineStr">
+      <c r="C107" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Publicada</t>
         </is>
       </c>
-      <c r="D104" s="0" t="inlineStr">
+      <c r="D107" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">CENTRO DE REFERENCIA DE SALUD DE PENALOLEN CORDILLERA ORIENTE</t>
         </is>
       </c>
-      <c r="E104" s="0" t="inlineStr">
+      <c r="E107" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">CRS de Peñalolen Cordillera Oriente</t>
         </is>
       </c>
-      <c r="F104" s="0" t="inlineStr">
+      <c r="F107" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Región Metropolitana de Santiago</t>
         </is>
       </c>
-      <c r="G104" s="0" t="inlineStr">
+      <c r="G107" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Peñalolén</t>
         </is>
       </c>
-      <c r="H104" s="2">
+      <c r="H107" s="2">
         <v>46259.456759</v>
       </c>
-      <c r="I104" s="2">
+      <c r="I107" s="2">
         <v>46289.729167</v>
       </c>
-      <c r="J104" s="0">
+      <c r="J107" s="0">
         <v>24</v>
       </c>
-      <c r="K104" s="3">
+      <c r="K107" s="3">
         <v>414000000.0</v>
       </c>
-      <c r="L104" s="0" t="inlineStr">
+      <c r="L107" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">CLP</t>
         </is>
       </c>
-      <c r="M104" s="0" t="inlineStr">
+      <c r="M107" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">LR</t>
         </is>
       </c>
-      <c r="N104" s="4" t="inlineStr">
+      <c r="N107" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de planificación de recursos empresariales (ERP) y contabilidad financiera</t>
         </is>
       </c>
-      <c r="O104" s="4" t="inlineStr">
+      <c r="O107" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">1 Global · Software de planificación de recursos empresariales (ERP)</t>
         </is>
       </c>
-      <c r="P104" s="2"/>
-      <c r="Q104" s="2"/>
-      <c r="R104" s="0" t="inlineStr">
+      <c r="P107" s="2"/>
+      <c r="Q107" s="2"/>
+      <c r="R107" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">60 meses</t>
         </is>
       </c>
-      <c r="S104" s="0" t="inlineStr">
+      <c r="S107" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">No</t>
         </is>
       </c>
-      <c r="T104" s="4"/>
-      <c r="U104" s="0" t="inlineStr">
+      <c r="T107" s="4"/>
+      <c r="U107" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">JEFE TICS</t>
         </is>
       </c>
-      <c r="V104" s="4" t="inlineStr">
+      <c r="V107" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Las presentes bases regirán la Propuesta Pública convocada por el CRSCO para la contratación de SISTEMA DE INFORMACIÓN DE GESTIÓN ADMINISTRATIVA Y FARMACIA por un periodo de 60 meses. 
 Se entenderá que todo proveedor conoce y acepta irrevocablemente el contenido de estas Bases, por el solo hecho de presentar sus ofertas en este proceso de compra. 
 Las características o especificaciones técnicas que presenten los oferentes deberán cumplir con los requisitos señalados en las bases y la idoneidad y calidad técnica del oferente, con el fin de asegurar que el adjudicatario se ajuste a los requisitos que el CRSCO ha especificado para la ejecución del contrato licitado.</t>
         </is>
       </c>
-      <c r="W104" s="5" t="str">
+      <c r="W107" s="5" t="str">
         <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=1973-93-LR26","descargar bases")</f>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2239-2-LR26</t>
-        </is>
-      </c>
-      <c r="B105" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Convenio Marco Desarrollo de software</t>
-        </is>
-      </c>
-      <c r="C105" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Publicada</t>
-        </is>
-      </c>
-      <c r="D105" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DIRECCION DE COMPRAS Y CONTRATACION PUBLICA</t>
-        </is>
-      </c>
-      <c r="E105" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">División de Convenio Marco</t>
-        </is>
-      </c>
-      <c r="F105" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Región Metropolitana de Santiago</t>
-        </is>
-      </c>
-      <c r="G105" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Santiago</t>
-        </is>
-      </c>
-      <c r="H105" s="2">
-        <v>46217.7375</v>
-      </c>
-      <c r="I105" s="2">
-        <v>46290.625</v>
-      </c>
-      <c r="J105" s="0">
-        <v>25</v>
-      </c>
-      <c r="K105" s="3"/>
-      <c r="L105" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UTM</t>
-        </is>
-      </c>
-      <c r="M105" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LR</t>
-        </is>
-      </c>
-      <c r="N105" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Servicios profesionales, administrativos y consultorías de gestión empresarial / Servicios de recursos humanos / Contratación de personal</t>
-        </is>
-      </c>
-      <c r="O105" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1 Unidad · Desarrolladores de software</t>
-        </is>
-      </c>
-      <c r="P105" s="2"/>
-      <c r="Q105" s="2"/>
-      <c r="R105" s="0"/>
-      <c r="S105" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">No</t>
-        </is>
-      </c>
-      <c r="T105" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">De conformidad con el artículo 126 del Reglamento de la Ley N° 19.886, el proveedor no podrá ceder ni transferir en forma alguna, total ni parcialmente, los derechos y obligaciones que nacen del desarrollo de esta licitación y de los respectivos contrato</t>
-        </is>
-      </c>
-      <c r="U105" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Convenio Marco</t>
-        </is>
-      </c>
-      <c r="V105" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Convenio Marco para la adquisición de los Servicios de Desarrollo y Mantención de Software, Servicios Profesionales TI y Cloud Computing</t>
-        </is>
-      </c>
-      <c r="W105" s="5" t="str">
-        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=2239-2-LR26","descargar bases")</f>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1607-13-LR26</t>
-        </is>
-      </c>
-      <c r="B106" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">servicio SD-WAN LAN telefonía en la nube y enlaces</t>
-        </is>
-      </c>
-      <c r="C106" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Publicada</t>
-        </is>
-      </c>
-      <c r="D106" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SUPERINTENDENCIA DE SEGURIDAD SOCIAL</t>
-        </is>
-      </c>
-      <c r="E106" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Superintendencia de Seguridad Social</t>
-        </is>
-      </c>
-      <c r="F106" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Región Metropolitana de Santiago</t>
-        </is>
-      </c>
-      <c r="G106" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Santiago Centro</t>
-        </is>
-      </c>
-      <c r="H106" s="2">
-        <v>46262.635741</v>
-      </c>
-      <c r="I106" s="2">
-        <v>46293.645833</v>
-      </c>
-      <c r="J106" s="0">
-        <v>28</v>
-      </c>
-      <c r="K106" s="3">
-        <v>450000000.0</v>
-      </c>
-      <c r="L106" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CLP</t>
-        </is>
-      </c>
-      <c r="M106" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LR</t>
-        </is>
-      </c>
-      <c r="N106" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Servicios basados en ingeniería, ciencias sociales y tecnología de la información / Servicios informáticos / Sistemas de información</t>
-        </is>
-      </c>
-      <c r="O106" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1 Unidad · Diseño de redes de comunicación de cobertura amplia (WAN)</t>
-        </is>
-      </c>
-      <c r="P106" s="2"/>
-      <c r="Q106" s="2"/>
-      <c r="R106" s="0"/>
-      <c r="S106" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">No</t>
-        </is>
-      </c>
-      <c r="T106" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">El oferente adjudicado no podrá ceder ni transferir en forma alguna, total ni parcialmente, los derechos y obligaciones que nacen del desarrollo de la presente licitación, y en especial los que se establecerán en el contrato definitivo.</t>
-        </is>
-      </c>
-      <c r="U106" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Henry Gonzalez</t>
-        </is>
-      </c>
-      <c r="V106" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">contratar el servicio de SD-WAN, LAN, Telefonía en la Nube y Enlaces Internet, a objeto de optimizar la plataforma de comunicaciones institucional y con ello dar plena cobertura a los actuales requerimientos institucionales tanto a nivel central como respecto de las oficinas existentes en las distintas regiones del país.</t>
-        </is>
-      </c>
-      <c r="W106" s="5" t="str">
-        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=1607-13-LR26","descargar bases")</f>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">548874-72-LR26</t>
-        </is>
-      </c>
-      <c r="B107" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SERV. DE ADMINISTRACION PLATAFORMAS TECNOLOGICAS</t>
-        </is>
-      </c>
-      <c r="C107" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Publicada</t>
-        </is>
-      </c>
-      <c r="D107" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">INSTITUTO DE PREVISION SOCIAL</t>
-        </is>
-      </c>
-      <c r="E107" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">IPS Oficina Central de Compras</t>
-        </is>
-      </c>
-      <c r="F107" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Región Metropolitana de Santiago</t>
-        </is>
-      </c>
-      <c r="G107" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Santiago</t>
-        </is>
-      </c>
-      <c r="H107" s="2">
-        <v>46258.545255</v>
-      </c>
-      <c r="I107" s="2">
-        <v>46295.625</v>
-      </c>
-      <c r="J107" s="0">
-        <v>30</v>
-      </c>
-      <c r="K107" s="3">
-        <v>24000.0</v>
-      </c>
-      <c r="L107" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CLF</t>
-        </is>
-      </c>
-      <c r="M107" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LR</t>
-        </is>
-      </c>
-      <c r="N107" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de consultas y gestión de datos</t>
-        </is>
-      </c>
-      <c r="O107" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1 Global · Software del sistema de administración de bases de datos</t>
-        </is>
-      </c>
-      <c r="P107" s="2"/>
-      <c r="Q107" s="2"/>
-      <c r="R107" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12 meses</t>
-        </is>
-      </c>
-      <c r="S107" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">No</t>
-        </is>
-      </c>
-      <c r="T107" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ver bases administrativas punto 16.</t>
-        </is>
-      </c>
-      <c r="U107" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Por Definir</t>
-        </is>
-      </c>
-      <c r="V107" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SERVICIO DE ADMINISTRACION, GESTION, CONFIGURACION, RESPALDOS Y
-MANTENCION DE LAS PLATAFORMAS TECNOLOGICAS DE IPS– E1O2RT8</t>
-        </is>
-      </c>
-      <c r="W107" s="5" t="str">
-        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=548874-72-LR26","descargar bases")</f>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">548874-74-LR26</t>
+          <t xml:space="preserve">2239-2-LR26</t>
         </is>
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">SERV DE PLATAFORMA SIEM NUEVA GENERACIÓN SAAS IPS</t>
+          <t xml:space="preserve">Convenio Marco Desarrollo de software</t>
         </is>
       </c>
       <c r="C108" s="0" t="inlineStr">
@@ -10352,12 +10793,12 @@
       </c>
       <c r="D108" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">INSTITUTO DE PREVISION SOCIAL</t>
+          <t xml:space="preserve">DIRECCION DE COMPRAS Y CONTRATACION PUBLICA</t>
         </is>
       </c>
       <c r="E108" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">IPS Oficina Central de Compras</t>
+          <t xml:space="preserve">División de Convenio Marco</t>
         </is>
       </c>
       <c r="F108" s="0" t="inlineStr">
@@ -10371,20 +10812,18 @@
         </is>
       </c>
       <c r="H108" s="2">
-        <v>46260.456458</v>
+        <v>46217.7375</v>
       </c>
       <c r="I108" s="2">
-        <v>46297.625</v>
+        <v>46290.625</v>
       </c>
       <c r="J108" s="0">
-        <v>32</v>
-      </c>
-      <c r="K108" s="3">
-        <v>565250.0</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="K108" s="3"/>
       <c r="L108" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">USD</t>
+          <t xml:space="preserve">UTM</t>
         </is>
       </c>
       <c r="M108" s="0" t="inlineStr">
@@ -10394,21 +10833,17 @@
       </c>
       <c r="N108" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de seguridad y protección</t>
+          <t xml:space="preserve">Servicios profesionales, administrativos y consultorías de gestión empresarial / Servicios de recursos humanos / Contratación de personal</t>
         </is>
       </c>
       <c r="O108" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 Global · Software de protección antivirus y de seguridad de transacciones</t>
+          <t xml:space="preserve">1 Unidad · Desarrolladores de software</t>
         </is>
       </c>
       <c r="P108" s="2"/>
       <c r="Q108" s="2"/>
-      <c r="R108" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12 meses</t>
-        </is>
-      </c>
+      <c r="R108" s="0"/>
       <c r="S108" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">No</t>
@@ -10416,32 +10851,32 @@
       </c>
       <c r="T108" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Según punto 16 de las bases</t>
+          <t xml:space="preserve">De conformidad con el artículo 126 del Reglamento de la Ley N° 19.886, el proveedor no podrá ceder ni transferir en forma alguna, total ni parcialmente, los derechos y obligaciones que nacen del desarrollo de esta licitación y de los respectivos contrato</t>
         </is>
       </c>
       <c r="U108" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">por definir</t>
+          <t xml:space="preserve">Convenio Marco</t>
         </is>
       </c>
       <c r="V108" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">E102RT8 - SERVICIO DE PLATAFORMA SIEM DE NUEVA GENERACIÓN EN MODALIDAD SAAS PARA EL INSTITUTO DE PREVISIÓN SOCIAL</t>
+          <t xml:space="preserve">Convenio Marco para la adquisición de los Servicios de Desarrollo y Mantención de Software, Servicios Profesionales TI y Cloud Computing</t>
         </is>
       </c>
       <c r="W108" s="5" t="str">
-        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=548874-74-LR26","descargar bases")</f>
+        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=2239-2-LR26","descargar bases")</f>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1969-34-LS19</t>
+          <t xml:space="preserve">1607-13-LR26</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTOMATIZACIÓN PORTÓN ACCESO A LINEA DE FUEGO</t>
+          <t xml:space="preserve">servicio SD-WAN LAN telefonía en la nube y enlaces</t>
         </is>
       </c>
       <c r="C109" s="0" t="inlineStr">
@@ -10451,30 +10886,36 @@
       </c>
       <c r="D109" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t xml:space="preserve">SUPERINTENDENCIA DE SEGURIDAD SOCIAL</t>
         </is>
       </c>
       <c r="E109" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Bio Bío</t>
+          <t xml:space="preserve">Superintendencia de Seguridad Social</t>
         </is>
       </c>
       <c r="F109" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t xml:space="preserve">Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="G109" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Concepción</t>
+          <t xml:space="preserve">Santiago Centro</t>
         </is>
       </c>
       <c r="H109" s="2">
-        <v>43588.74809</v>
-      </c>
-      <c r="I109" s="2"/>
-      <c r="J109" s="0"/>
-      <c r="K109" s="3"/>
+        <v>46262.635741</v>
+      </c>
+      <c r="I109" s="2">
+        <v>46293.645833</v>
+      </c>
+      <c r="J109" s="0">
+        <v>28</v>
+      </c>
+      <c r="K109" s="3">
+        <v>450000000.0</v>
+      </c>
       <c r="L109" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">CLP</t>
@@ -10482,17 +10923,17 @@
       </c>
       <c r="M109" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">LS</t>
+          <t xml:space="preserve">LR</t>
         </is>
       </c>
       <c r="N109" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Artículos para estructuras, obras y construcciones / Puertas, ventanas y vidrios / Puertas</t>
+          <t xml:space="preserve">Servicios basados en ingeniería, ciencias sociales y tecnología de la información / Servicios informáticos / Sistemas de información</t>
         </is>
       </c>
       <c r="O109" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 Unidad · Puertas de metal</t>
+          <t xml:space="preserve">1 Unidad · Diseño de redes de comunicación de cobertura amplia (WAN)</t>
         </is>
       </c>
       <c r="P109" s="2"/>
@@ -10503,23 +10944,490 @@
           <t xml:space="preserve">No</t>
         </is>
       </c>
-      <c r="T109" s="4"/>
+      <c r="T109" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">El oferente adjudicado no podrá ceder ni transferir en forma alguna, total ni parcialmente, los derechos y obligaciones que nacen del desarrollo de la presente licitación, y en especial los que se establecerán en el contrato definitivo.</t>
+        </is>
+      </c>
       <c r="U109" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">Henry Gonzalez</t>
+        </is>
+      </c>
+      <c r="V109" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">contratar el servicio de SD-WAN, LAN, Telefonía en la Nube y Enlaces Internet, a objeto de optimizar la plataforma de comunicaciones institucional y con ello dar plena cobertura a los actuales requerimientos institucionales tanto a nivel central como respecto de las oficinas existentes en las distintas regiones del país.</t>
+        </is>
+      </c>
+      <c r="W109" s="5" t="str">
+        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=1607-13-LR26","descargar bases")</f>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1274285-45-LP26</t>
+        </is>
+      </c>
+      <c r="B110" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Software de gestión Droguería Comunal</t>
+        </is>
+      </c>
+      <c r="C110" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Publicada</t>
+        </is>
+      </c>
+      <c r="D110" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CORPORACION MUNICIPAL DE EDUCACION Y SALUD DE SAN BERNARDO</t>
+        </is>
+      </c>
+      <c r="E110" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SALUD</t>
+        </is>
+      </c>
+      <c r="F110" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="G110" s="0"/>
+      <c r="H110" s="2">
+        <v>46265.493137</v>
+      </c>
+      <c r="I110" s="2">
+        <v>46293.75</v>
+      </c>
+      <c r="J110" s="0">
+        <v>28</v>
+      </c>
+      <c r="K110" s="3"/>
+      <c r="L110" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CLP</t>
+        </is>
+      </c>
+      <c r="M110" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LP</t>
+        </is>
+      </c>
+      <c r="N110" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de gestión</t>
+        </is>
+      </c>
+      <c r="O110" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 Unidad · Software de cadena de suministro y logística de planificación de requisitos de materiales</t>
+        </is>
+      </c>
+      <c r="P110" s="2"/>
+      <c r="Q110" s="2"/>
+      <c r="R110" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">36 meses</t>
+        </is>
+      </c>
+      <c r="S110" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="T110" s="4"/>
+      <c r="U110" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Erwin Rodriguez Basulto</t>
+        </is>
+      </c>
+      <c r="V110" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">La Corporación Municipal de Educación y Salud de San Bernardo requiere contratar para la Droguería Comunal y Centros de Salud un Sistema Informático que permita controlar los procesos de bodega y la gestión de la Droguería y Centros de Salud donde se encuentran contempladas, entre otras, las siguientes áreas:
+•Recepción
+•Almacenamiento
+•Despacho
+•Inventario 
+•Reportes de Gestión</t>
+        </is>
+      </c>
+      <c r="W110" s="5" t="str">
+        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=1274285-45-LP26","descargar bases")</f>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">548874-72-LR26</t>
+        </is>
+      </c>
+      <c r="B111" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SERV. DE ADMINISTRACION PLATAFORMAS TECNOLOGICAS</t>
+        </is>
+      </c>
+      <c r="C111" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Publicada</t>
+        </is>
+      </c>
+      <c r="D111" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">INSTITUTO DE PREVISION SOCIAL</t>
+        </is>
+      </c>
+      <c r="E111" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IPS Oficina Central de Compras</t>
+        </is>
+      </c>
+      <c r="F111" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="G111" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Santiago</t>
+        </is>
+      </c>
+      <c r="H111" s="2">
+        <v>46258.545255</v>
+      </c>
+      <c r="I111" s="2">
+        <v>46295.625</v>
+      </c>
+      <c r="J111" s="0">
+        <v>30</v>
+      </c>
+      <c r="K111" s="3">
+        <v>24000.0</v>
+      </c>
+      <c r="L111" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CLF</t>
+        </is>
+      </c>
+      <c r="M111" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LR</t>
+        </is>
+      </c>
+      <c r="N111" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de consultas y gestión de datos</t>
+        </is>
+      </c>
+      <c r="O111" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 Global · Software del sistema de administración de bases de datos</t>
+        </is>
+      </c>
+      <c r="P111" s="2"/>
+      <c r="Q111" s="2"/>
+      <c r="R111" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12 meses</t>
+        </is>
+      </c>
+      <c r="S111" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="T111" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ver bases administrativas punto 16.</t>
+        </is>
+      </c>
+      <c r="U111" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Por Definir</t>
+        </is>
+      </c>
+      <c r="V111" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SERVICIO DE ADMINISTRACION, GESTION, CONFIGURACION, RESPALDOS Y
+MANTENCION DE LAS PLATAFORMAS TECNOLOGICAS DE IPS– E1O2RT8</t>
+        </is>
+      </c>
+      <c r="W111" s="5" t="str">
+        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=548874-72-LR26","descargar bases")</f>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">548874-74-LR26</t>
+        </is>
+      </c>
+      <c r="B112" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SERV DE PLATAFORMA SIEM NUEVA GENERACIÓN SAAS IPS</t>
+        </is>
+      </c>
+      <c r="C112" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Publicada</t>
+        </is>
+      </c>
+      <c r="D112" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">INSTITUTO DE PREVISION SOCIAL</t>
+        </is>
+      </c>
+      <c r="E112" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IPS Oficina Central de Compras</t>
+        </is>
+      </c>
+      <c r="F112" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="G112" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Santiago</t>
+        </is>
+      </c>
+      <c r="H112" s="2">
+        <v>46260.456458</v>
+      </c>
+      <c r="I112" s="2">
+        <v>46297.625</v>
+      </c>
+      <c r="J112" s="0">
+        <v>32</v>
+      </c>
+      <c r="K112" s="3">
+        <v>565250.0</v>
+      </c>
+      <c r="L112" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">USD</t>
+        </is>
+      </c>
+      <c r="M112" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LR</t>
+        </is>
+      </c>
+      <c r="N112" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de seguridad y protección</t>
+        </is>
+      </c>
+      <c r="O112" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 Global · Software de protección antivirus y de seguridad de transacciones</t>
+        </is>
+      </c>
+      <c r="P112" s="2"/>
+      <c r="Q112" s="2"/>
+      <c r="R112" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12 meses</t>
+        </is>
+      </c>
+      <c r="S112" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="T112" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Según punto 16 de las bases</t>
+        </is>
+      </c>
+      <c r="U112" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">por definir</t>
+        </is>
+      </c>
+      <c r="V112" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E102RT8 - SERVICIO DE PLATAFORMA SIEM DE NUEVA GENERACIÓN EN MODALIDAD SAAS PARA EL INSTITUTO DE PREVISIÓN SOCIAL</t>
+        </is>
+      </c>
+      <c r="W112" s="5" t="str">
+        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=548874-74-LR26","descargar bases")</f>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">976-15-O126</t>
+        </is>
+      </c>
+      <c r="B113" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ampliación Plataformas Comercial y General Ad. El Loa</t>
+        </is>
+      </c>
+      <c r="C113" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Publicada</t>
+        </is>
+      </c>
+      <c r="D113" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+        </is>
+      </c>
+      <c r="E113" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dirección de Aeropuertos - MOPTT</t>
+        </is>
+      </c>
+      <c r="F113" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Antofagasta </t>
+        </is>
+      </c>
+      <c r="G113" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Santiago</t>
+        </is>
+      </c>
+      <c r="H113" s="2">
+        <v>46265.342303</v>
+      </c>
+      <c r="I113" s="2">
+        <v>46304.458333</v>
+      </c>
+      <c r="J113" s="0">
+        <v>39</v>
+      </c>
+      <c r="K113" s="3"/>
+      <c r="L113" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CLP</t>
+        </is>
+      </c>
+      <c r="M113" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">O1</t>
+        </is>
+      </c>
+      <c r="N113" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Consultoria / Consultoria / Planificación y Factibilidad</t>
+        </is>
+      </c>
+      <c r="O113" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 Unidad · Licitación Pública de Obra</t>
+        </is>
+      </c>
+      <c r="P113" s="2"/>
+      <c r="Q113" s="2"/>
+      <c r="R113" s="0"/>
+      <c r="S113" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="T113" s="4"/>
+      <c r="U113" s="0"/>
+      <c r="V113" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Esta Dirección necesita llamar a licitación para contratar la obra Ampliación Plataformas Comercial y General Aeródromo El Loa.</t>
+        </is>
+      </c>
+      <c r="W113" s="5" t="str">
+        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=976-15-O126","descargar bases")</f>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1969-34-LS19</t>
+        </is>
+      </c>
+      <c r="B114" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUTOMATIZACIÓN PORTÓN ACCESO A LINEA DE FUEGO</t>
+        </is>
+      </c>
+      <c r="C114" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Publicada</t>
+        </is>
+      </c>
+      <c r="D114" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+        </is>
+      </c>
+      <c r="E114" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región del Bio Bío</t>
+        </is>
+      </c>
+      <c r="F114" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región del Biobío </t>
+        </is>
+      </c>
+      <c r="G114" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Concepción</t>
+        </is>
+      </c>
+      <c r="H114" s="2">
+        <v>43588.74809</v>
+      </c>
+      <c r="I114" s="2"/>
+      <c r="J114" s="0"/>
+      <c r="K114" s="3"/>
+      <c r="L114" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CLP</t>
+        </is>
+      </c>
+      <c r="M114" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LS</t>
+        </is>
+      </c>
+      <c r="N114" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Artículos para estructuras, obras y construcciones / Puertas, ventanas y vidrios / Puertas</t>
+        </is>
+      </c>
+      <c r="O114" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 Unidad · Puertas de metal</t>
+        </is>
+      </c>
+      <c r="P114" s="2"/>
+      <c r="Q114" s="2"/>
+      <c r="R114" s="0"/>
+      <c r="S114" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="T114" s="4"/>
+      <c r="U114" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">Héctor Polma Lillo</t>
         </is>
       </c>
-      <c r="V109" s="4" t="inlineStr">
+      <c r="V114" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">AUTOMATIZACIÓN DE PORTÓN ACCESO A LINEA DE FUEGO C.P. CONCEPCIÓN</t>
         </is>
       </c>
-      <c r="W109" s="5" t="str">
+      <c r="W114" s="5" t="str">
         <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=1969-34-LS19","descargar bases")</f>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:W109"/>
+  <autoFilter ref="A1:W114"/>
 </worksheet>
 </file>
 
@@ -14045,12 +14953,12 @@
     <row r="93">
       <c r="A93" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1978-85-LE26</t>
+          <t xml:space="preserve">1057531-10-L126</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Soporte Acronis Backup Cloud y Acronis Storage</t>
+          <t xml:space="preserve">Contratación de Convenio Prótesis Fijas con sistema digital CADCAM 2026-2027</t>
         </is>
       </c>
       <c r="C93" s="0">
@@ -14058,37 +14966,37 @@
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Software de sistema experto</t>
+          <t xml:space="preserve">Coronas o formas de coronas</t>
         </is>
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de gestión</t>
+          <t xml:space="preserve">Equipamiento y suministros médicos / Equipos y suministros odontológicos / Suministros y equipos de odontología cosmética</t>
         </is>
       </c>
       <c r="F93" s="0">
-        <v>36.0</v>
+        <v>15.0</v>
       </c>
       <c r="G93" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mes</t>
+          <t xml:space="preserve">Unidad no definida</t>
         </is>
       </c>
       <c r="H93" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Soporte Acronis Backup Cloud y Acronis Storage</t>
+          <t xml:space="preserve">Contratación de servicios de convenio Prótesis Fijas con sistema digital CADCAM, para Beneficiarios del HRN para los años 2026-2027</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">742475-4-LE26</t>
+          <t xml:space="preserve">1978-85-LE26</t>
         </is>
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adquisición de equipos informáticos para el programa Oficina Local de la Niñez</t>
+          <t xml:space="preserve">Soporte Acronis Backup Cloud y Acronis Storage</t>
         </is>
       </c>
       <c r="C94" s="0">
@@ -14096,37 +15004,37 @@
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Notebook, laptop o computador portátil excepto Tablet PC</t>
+          <t xml:space="preserve">Software de sistema experto</t>
         </is>
       </c>
       <c r="E94" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Equipos informáticos y accesorios / Computadores</t>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de gestión</t>
         </is>
       </c>
       <c r="F94" s="0">
-        <v>1.0</v>
+        <v>36.0</v>
       </c>
       <c r="G94" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unidad</t>
+          <t xml:space="preserve">Mes</t>
         </is>
       </c>
       <c r="H94" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADQUISICIÓN DE EQUIPOS INFORMÁTICOS PARA EL PROGRAMA OFICINA LOCAL DE LA NIÑEZ. DE ACUERDO A BASES TÉCNICAS</t>
+          <t xml:space="preserve">Soporte Acronis Backup Cloud y Acronis Storage</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1469-175-L126</t>
+          <t xml:space="preserve">742475-4-LE26</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">TABLERO PARA BOMBA SUMERGIBLE, CAMPUS TALCA, UNIVERSIDAD DE TALCA.</t>
+          <t xml:space="preserve">Adquisición de equipos informáticos para el programa Oficina Local de la Niñez</t>
         </is>
       </c>
       <c r="C95" s="0">
@@ -14134,12 +15042,12 @@
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bombas sumergibles</t>
+          <t xml:space="preserve">Notebook, laptop o computador portátil excepto Tablet PC</t>
         </is>
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Equipamiento para el acondicionamiento, distribución y filtrado de fluidos / Bombas y compresores industriales / Bombas</t>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Equipos informáticos y accesorios / Computadores</t>
         </is>
       </c>
       <c r="F95" s="0">
@@ -14152,19 +15060,19 @@
       </c>
       <c r="H95" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">La Universidad de Talca requiere de los servicios de retiro e instalación de nuevo tablero de control para bomba sumergible.</t>
+          <t xml:space="preserve">ADQUISICIÓN DE EQUIPOS INFORMÁTICOS PARA EL PROGRAMA OFICINA LOCAL DE LA NIÑEZ. DE ACUERDO A BASES TÉCNICAS</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1562-52-LE26</t>
+          <t xml:space="preserve">1469-175-L126</t>
         </is>
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADQUISICIÓN RENOVACIÓN PLATAFORMA ROCSCIENCE</t>
+          <t xml:space="preserve">TABLERO PARA BOMBA SUMERGIBLE, CAMPUS TALCA, UNIVERSIDAD DE TALCA.</t>
         </is>
       </c>
       <c r="C96" s="0">
@@ -14172,12 +15080,12 @@
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Software de gestión de licencias</t>
+          <t xml:space="preserve">Bombas sumergibles</t>
         </is>
       </c>
       <c r="E96" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de gestión</t>
+          <t xml:space="preserve">Equipamiento para el acondicionamiento, distribución y filtrado de fluidos / Bombas y compresores industriales / Bombas</t>
         </is>
       </c>
       <c r="F96" s="0">
@@ -14190,58 +15098,58 @@
       </c>
       <c r="H96" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">La Universidad de Talca requiere de los servicios de retiro e instalación de nuevo tablero de control para bomba sumergible.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1562-52-LE26</t>
+        </is>
+      </c>
+      <c r="B97" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADQUISICIÓN RENOVACIÓN PLATAFORMA ROCSCIENCE</t>
+        </is>
+      </c>
+      <c r="C97" s="0">
+        <v>1</v>
+      </c>
+      <c r="D97" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Software de gestión de licencias</t>
+        </is>
+      </c>
+      <c r="E97" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de gestión</t>
+        </is>
+      </c>
+      <c r="F97" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G97" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidad</t>
+        </is>
+      </c>
+      <c r="H97" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">el Servicio Nacional de Geología y Minería requiere contratar la renovación de licencias de software Rocscience, destinadas al desarrollo de análisis geotécnicos y geomecánicos especializados.
 Estas herramientas permiten efectuar análisis asociados, entr</t>
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1057390-48-LP26</t>
-        </is>
-      </c>
-      <c r="B97" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CONV. RADIOCOMUNICACIÓN DIGITAL SAMU</t>
-        </is>
-      </c>
-      <c r="C97" s="0">
-        <v>1</v>
-      </c>
-      <c r="D97" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Sistemas de radio a pequeña escala</t>
-        </is>
-      </c>
-      <c r="E97" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Servicios básicos y de información pública / Telecomunicaciones / Servicios de radio</t>
-        </is>
-      </c>
-      <c r="F97" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="G97" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Mes</t>
-        </is>
-      </c>
-      <c r="H97" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prestación mensual de servicio de comunicaciones digitales de voz tipo PTT (Push To Talk) sobre redes de banda ancha, para el SAMU Malleco, dependiente del Servicio de Salud Araucanía Norte. Total Anexo 1 .</t>
-        </is>
-      </c>
-    </row>
     <row r="98">
       <c r="A98" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1605-36-LR26</t>
+          <t xml:space="preserve">1057390-48-LP26</t>
         </is>
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">LR-4252 Servicio de Red Datos WAN</t>
+          <t xml:space="preserve">CONV. RADIOCOMUNICACIÓN DIGITAL SAMU</t>
         </is>
       </c>
       <c r="C98" s="0">
@@ -14249,23 +15157,61 @@
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sistemas de radio a pequeña escala</t>
+        </is>
+      </c>
+      <c r="E98" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Servicios básicos y de información pública / Telecomunicaciones / Servicios de radio</t>
+        </is>
+      </c>
+      <c r="F98" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G98" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mes</t>
+        </is>
+      </c>
+      <c r="H98" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prestación mensual de servicio de comunicaciones digitales de voz tipo PTT (Push To Talk) sobre redes de banda ancha, para el SAMU Malleco, dependiente del Servicio de Salud Araucanía Norte. Total Anexo 1 .</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1605-36-LR26</t>
+        </is>
+      </c>
+      <c r="B99" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LR-4252 Servicio de Red Datos WAN</t>
+        </is>
+      </c>
+      <c r="C99" s="0">
+        <v>1</v>
+      </c>
+      <c r="D99" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">Proveedores de servicio de Internet (ISP)</t>
         </is>
       </c>
-      <c r="E98" s="4" t="inlineStr">
+      <c r="E99" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Servicios basados en ingeniería, ciencias sociales y tecnología de la información / Servicios informáticos / Servicios para internet</t>
         </is>
       </c>
-      <c r="F98" s="0">
+      <c r="F99" s="0">
         <v>72.0</v>
       </c>
-      <c r="G98" s="0" t="inlineStr">
+      <c r="G99" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Mes</t>
         </is>
       </c>
-      <c r="H98" s="4" t="inlineStr">
+      <c r="H99" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Servicio de conectividad de datos.
 2. Infraestructura tipo SD-WAN y LAN
@@ -14274,121 +15220,83 @@
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1605-36-LR26</t>
-        </is>
-      </c>
-      <c r="B99" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LR-4252 Servicio de Red Datos WAN</t>
-        </is>
-      </c>
-      <c r="C99" s="0">
-        <v>2</v>
-      </c>
-      <c r="D99" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Proveedores de servicio de Internet (ISP)</t>
-        </is>
-      </c>
-      <c r="E99" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Servicios basados en ingeniería, ciencias sociales y tecnología de la información / Servicios informáticos / Servicios para internet</t>
-        </is>
-      </c>
-      <c r="F99" s="0">
-        <v>72.0</v>
-      </c>
-      <c r="G99" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Mes</t>
-        </is>
-      </c>
-      <c r="H99" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5. Monitoreo y gestión de las componentes 1 a 4.</t>
-        </is>
-      </c>
-    </row>
     <row r="100">
       <c r="A100" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">1605-36-LR26</t>
+        </is>
+      </c>
+      <c r="B100" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LR-4252 Servicio de Red Datos WAN</t>
+        </is>
+      </c>
+      <c r="C100" s="0">
+        <v>2</v>
+      </c>
+      <c r="D100" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proveedores de servicio de Internet (ISP)</t>
+        </is>
+      </c>
+      <c r="E100" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Servicios basados en ingeniería, ciencias sociales y tecnología de la información / Servicios informáticos / Servicios para internet</t>
+        </is>
+      </c>
+      <c r="F100" s="0">
+        <v>72.0</v>
+      </c>
+      <c r="G100" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mes</t>
+        </is>
+      </c>
+      <c r="H100" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5. Monitoreo y gestión de las componentes 1 a 4.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">1057501-488-LE26</t>
         </is>
       </c>
-      <c r="B100" s="4" t="inlineStr">
+      <c r="B101" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">ARRIENDO MODULOS BODEGA PARA INFORMÁTICA HSR</t>
         </is>
       </c>
-      <c r="C100" s="0">
+      <c r="C101" s="0">
         <v>1</v>
       </c>
-      <c r="D100" s="4" t="inlineStr">
+      <c r="D101" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Construcción de obras civiles</t>
         </is>
       </c>
-      <c r="E100" s="4" t="inlineStr">
+      <c r="E101" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Servicios de construcción y mantenimiento / Construcción de edificios en general / Construcción de obras civiles y infraestructuras</t>
         </is>
       </c>
-      <c r="F100" s="0">
+      <c r="F101" s="0">
         <v>2.0</v>
       </c>
-      <c r="G100" s="0" t="inlineStr">
+      <c r="G101" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Unidad</t>
         </is>
       </c>
-      <c r="H100" s="4" t="inlineStr">
+      <c r="H101" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">77-002-004-017-00 ARRIENDO MODULOS BODEGA PARA LA UNIDAD DE
 INFORMATICA</t>
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1020-38-LP26</t>
-        </is>
-      </c>
-      <c r="B101" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Adquisición de Plataforma Next Generation Firewall</t>
-        </is>
-      </c>
-      <c r="C101" s="0">
-        <v>1</v>
-      </c>
-      <c r="D101" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Equipo de seguridad de red de firewall</t>
-        </is>
-      </c>
-      <c r="E101" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Equipos, plataformas y accesorios de redes multimedia, voz y datos / Equipos de seguridad de red</t>
-        </is>
-      </c>
-      <c r="F101" s="0">
-        <v>2.0</v>
-      </c>
-      <c r="G101" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Unidad</t>
-        </is>
-      </c>
-      <c r="H101" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Equipos.</t>
-        </is>
-      </c>
-    </row>
     <row r="102">
       <c r="A102" s="0" t="inlineStr">
         <is>
@@ -14401,20 +15309,20 @@
         </is>
       </c>
       <c r="C102" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Software de vigilancia de redes</t>
+          <t xml:space="preserve">Equipo de seguridad de red de firewall</t>
         </is>
       </c>
       <c r="E102" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de administración de redes</t>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Equipos, plataformas y accesorios de redes multimedia, voz y datos / Equipos de seguridad de red</t>
         </is>
       </c>
       <c r="F102" s="0">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G102" s="0" t="inlineStr">
         <is>
@@ -14423,96 +15331,96 @@
       </c>
       <c r="H102" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Licenciamiento de software para la Plataforma Next Generation Firewall (NGFW)</t>
+          <t xml:space="preserve">Equipos.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">1020-38-LP26</t>
+        </is>
+      </c>
+      <c r="B103" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Adquisición de Plataforma Next Generation Firewall</t>
+        </is>
+      </c>
+      <c r="C103" s="0">
+        <v>2</v>
+      </c>
+      <c r="D103" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Software de vigilancia de redes</t>
+        </is>
+      </c>
+      <c r="E103" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de administración de redes</t>
+        </is>
+      </c>
+      <c r="F103" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G103" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidad</t>
+        </is>
+      </c>
+      <c r="H103" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Licenciamiento de software para la Plataforma Next Generation Firewall (NGFW)</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">1020-45-LE26</t>
         </is>
       </c>
-      <c r="B103" s="4" t="inlineStr">
+      <c r="B104" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Renovación Licencias Software Solarwinds Dameware</t>
         </is>
       </c>
-      <c r="C103" s="0">
+      <c r="C104" s="0">
         <v>1</v>
       </c>
-      <c r="D103" s="4" t="inlineStr">
+      <c r="D104" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Software de gestión de licencias</t>
         </is>
       </c>
-      <c r="E103" s="4" t="inlineStr">
+      <c r="E104" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de gestión</t>
         </is>
       </c>
-      <c r="F103" s="0">
+      <c r="F104" s="0">
         <v>60.0</v>
       </c>
-      <c r="G103" s="0" t="inlineStr">
+      <c r="G104" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Unidad</t>
         </is>
       </c>
-      <c r="H103" s="4" t="inlineStr">
+      <c r="H104" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Renovación Anual de Licencias del 
 Software SolarWinds Dameware Remote Everywhere para el Ministerio de Obras Públicas (MOP)  Los oferentes deberán revisar Resolución SOP [Ex] Electrónica 1229 que aprueba las BA, BT, Formularios y Anexo adjunto.</t>
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1057494-50-LR26</t>
-        </is>
-      </c>
-      <c r="B104" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SOFTWARE PARA LA GESTIÓN DE LA UNIDAD DE LABORATOR</t>
-        </is>
-      </c>
-      <c r="C104" s="0">
-        <v>1</v>
-      </c>
-      <c r="D104" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Software de sistemas de archivado de película radiográfica médica</t>
-        </is>
-      </c>
-      <c r="E104" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Equipamiento y suministros médicos / Productos para imágenes y de medicina nuclear / Artículos para archivar información e imágenes radiológicas</t>
-        </is>
-      </c>
-      <c r="F104" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="G104" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Unidad</t>
-        </is>
-      </c>
-      <c r="H104" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ARRIENDO DE SOFTWARE PARA LA GESTIÓN DE LA UNIDAD DE LABORATORIO CLÍNICO DEL HOSPITAL DR. EXEQUIEL GONZÁLEZ CORTÉS</t>
-        </is>
-      </c>
-    </row>
     <row r="105">
       <c r="A105" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">3671-58-LE26</t>
+          <t xml:space="preserve">1057494-50-LR26</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">“HABILITACIÓN DE NUEVAS DEPENDENCIAS DE SEGURIDAD MUNICIPAL E INFORMÁTICA DE LA MUNICIPALIDAD DE CHILLÁN VIEJO”</t>
+          <t xml:space="preserve">SOFTWARE PARA LA GESTIÓN DE LA UNIDAD DE LABORATOR</t>
         </is>
       </c>
       <c r="C105" s="0">
@@ -14520,12 +15428,12 @@
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Construcción de obras civiles</t>
+          <t xml:space="preserve">Software de sistemas de archivado de película radiográfica médica</t>
         </is>
       </c>
       <c r="E105" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Servicios de construcción y mantenimiento / Construcción de edificios en general / Construcción de obras civiles y infraestructuras</t>
+          <t xml:space="preserve">Equipamiento y suministros médicos / Productos para imágenes y de medicina nuclear / Artículos para archivar información e imágenes radiológicas</t>
         </is>
       </c>
       <c r="F105" s="0">
@@ -14538,19 +15446,19 @@
       </c>
       <c r="H105" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">HABILITACION DE NUEVAS DEPENDENCIAS DE SEGURIDAD MUNICIPAL E INFORMATICA DE LA MUNICIPALIDAD DE CHILLAN VIEJO</t>
+          <t xml:space="preserve">ARRIENDO DE SOFTWARE PARA LA GESTIÓN DE LA UNIDAD DE LABORATORIO CLÍNICO DEL HOSPITAL DR. EXEQUIEL GONZÁLEZ CORTÉS</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">425-39-LR26</t>
+          <t xml:space="preserve">3671-58-LE26</t>
         </is>
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADQUISICIÓN Y RENOVACIÓN DE LICENCIAS DE SOFTWARE PARA EL PODER JUDICIAL</t>
+          <t xml:space="preserve">“HABILITACIÓN DE NUEVAS DEPENDENCIAS DE SEGURIDAD MUNICIPAL E INFORMÁTICA DE LA MUNICIPALIDAD DE CHILLÁN VIEJO”</t>
         </is>
       </c>
       <c r="C106" s="0">
@@ -14558,16 +15466,16 @@
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Software de gestión de licencias</t>
+          <t xml:space="preserve">Construcción de obras civiles</t>
         </is>
       </c>
       <c r="E106" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de gestión</t>
+          <t xml:space="preserve">Servicios de construcción y mantenimiento / Construcción de edificios en general / Construcción de obras civiles y infraestructuras</t>
         </is>
       </c>
       <c r="F106" s="0">
-        <v>12.0</v>
+        <v>1.0</v>
       </c>
       <c r="G106" s="0" t="inlineStr">
         <is>
@@ -14576,7 +15484,7 @@
       </c>
       <c r="H106" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Item 1 Adquisición licencias NETBACKUP ENTERPRISE XPLAT 1 FRONT END TB ONPREM STANDARD, Valor neto según Formulario Económico N°1 (en caso de discrepancia entre el valor y el Formulario Económico N° 1 primará este último)</t>
+          <t xml:space="preserve">HABILITACION DE NUEVAS DEPENDENCIAS DE SEGURIDAD MUNICIPAL E INFORMATICA DE LA MUNICIPALIDAD DE CHILLAN VIEJO</t>
         </is>
       </c>
     </row>
@@ -14592,7 +15500,7 @@
         </is>
       </c>
       <c r="C107" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
@@ -14605,7 +15513,7 @@
         </is>
       </c>
       <c r="F107" s="0">
-        <v>4480.0</v>
+        <v>12.0</v>
       </c>
       <c r="G107" s="0" t="inlineStr">
         <is>
@@ -14614,7 +15522,7 @@
       </c>
       <c r="H107" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Item 2 Renovación Licencias WAS,Valor neto según Formulario Económico N°1 (en caso de discrepancia entre el valor y el Formulario Económico N° 1 primará este último)</t>
+          <t xml:space="preserve">Item 1 Adquisición licencias NETBACKUP ENTERPRISE XPLAT 1 FRONT END TB ONPREM STANDARD, Valor neto según Formulario Económico N°1 (en caso de discrepancia entre el valor y el Formulario Económico N° 1 primará este último)</t>
         </is>
       </c>
     </row>
@@ -14630,7 +15538,7 @@
         </is>
       </c>
       <c r="C108" s="0">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
@@ -14643,7 +15551,7 @@
         </is>
       </c>
       <c r="F108" s="0">
-        <v>30.0</v>
+        <v>4480.0</v>
       </c>
       <c r="G108" s="0" t="inlineStr">
         <is>
@@ -14652,7 +15560,7 @@
       </c>
       <c r="H108" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Item 3 Suscripción Licencias Instana,Valor neto según Formulario Económico N°1 (en caso de discrepancia entre el valor y el Formulario Económico N° 1 primará este último)</t>
+          <t xml:space="preserve">Item 2 Renovación Licencias WAS,Valor neto según Formulario Económico N°1 (en caso de discrepancia entre el valor y el Formulario Económico N° 1 primará este último)</t>
         </is>
       </c>
     </row>
@@ -14668,7 +15576,7 @@
         </is>
       </c>
       <c r="C109" s="0">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
@@ -14681,7 +15589,7 @@
         </is>
       </c>
       <c r="F109" s="0">
-        <v>74.0</v>
+        <v>30.0</v>
       </c>
       <c r="G109" s="0" t="inlineStr">
         <is>
@@ -14690,7 +15598,7 @@
       </c>
       <c r="H109" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Item 3 Suscripción Licencias Instana, Valor neto según Formulario Económico N°1 (en caso de discrepancia entre el valor y el Formulario Económico N° 1 primará este último)</t>
+          <t xml:space="preserve">Item 3 Suscripción Licencias Instana,Valor neto según Formulario Económico N°1 (en caso de discrepancia entre el valor y el Formulario Económico N° 1 primará este último)</t>
         </is>
       </c>
     </row>
@@ -14706,7 +15614,7 @@
         </is>
       </c>
       <c r="C110" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
@@ -14719,7 +15627,7 @@
         </is>
       </c>
       <c r="F110" s="0">
-        <v>4.0</v>
+        <v>74.0</v>
       </c>
       <c r="G110" s="0" t="inlineStr">
         <is>
@@ -14728,7 +15636,7 @@
       </c>
       <c r="H110" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Item 4, Suscripción Licencias Red Hat Openshift, Valor neto según Formulario Económico N°1 (en caso de discrepancia entre el valor y el Formulario Económico N° 1 primará este último)</t>
+          <t xml:space="preserve">Item 3 Suscripción Licencias Instana, Valor neto según Formulario Económico N°1 (en caso de discrepancia entre el valor y el Formulario Económico N° 1 primará este último)</t>
         </is>
       </c>
     </row>
@@ -14744,7 +15652,7 @@
         </is>
       </c>
       <c r="C111" s="0">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
@@ -14757,7 +15665,7 @@
         </is>
       </c>
       <c r="F111" s="0">
-        <v>8.0</v>
+        <v>4.0</v>
       </c>
       <c r="G111" s="0" t="inlineStr">
         <is>
@@ -14782,7 +15690,7 @@
         </is>
       </c>
       <c r="C112" s="0">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
@@ -14795,7 +15703,7 @@
         </is>
       </c>
       <c r="F112" s="0">
-        <v>19.0</v>
+        <v>8.0</v>
       </c>
       <c r="G112" s="0" t="inlineStr">
         <is>
@@ -14820,7 +15728,7 @@
         </is>
       </c>
       <c r="C113" s="0">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
@@ -14833,7 +15741,7 @@
         </is>
       </c>
       <c r="F113" s="0">
-        <v>17.0</v>
+        <v>19.0</v>
       </c>
       <c r="G113" s="0" t="inlineStr">
         <is>
@@ -14858,7 +15766,7 @@
         </is>
       </c>
       <c r="C114" s="0">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D114" s="4" t="inlineStr">
         <is>
@@ -14871,7 +15779,7 @@
         </is>
       </c>
       <c r="F114" s="0">
-        <v>2.0</v>
+        <v>17.0</v>
       </c>
       <c r="G114" s="0" t="inlineStr">
         <is>
@@ -14880,7 +15788,7 @@
       </c>
       <c r="H114" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Item 5 Red Hat Enterprise Linux Server, Standard (Physical or Virtual Nodes) ,Valor neto según Formulario Económico N°1 (en caso de discrepancia entre el valor y el Formulario Económico N° 1 primará este último)</t>
+          <t xml:space="preserve">Item 4, Suscripción Licencias Red Hat Openshift, Valor neto según Formulario Económico N°1 (en caso de discrepancia entre el valor y el Formulario Económico N° 1 primará este último)</t>
         </is>
       </c>
     </row>
@@ -14896,7 +15804,7 @@
         </is>
       </c>
       <c r="C115" s="0">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
@@ -14909,7 +15817,7 @@
         </is>
       </c>
       <c r="F115" s="0">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G115" s="0" t="inlineStr">
         <is>
@@ -14918,7 +15826,7 @@
       </c>
       <c r="H115" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Item 5 Red Hat Enterprise Linux for Virtual Datacenters, Standard, Valor neto según Formulario Económico N°1 (en caso de discrepancia entre el valor y el Formulario Económico N° 1 primará este último)</t>
+          <t xml:space="preserve">Item 5 Red Hat Enterprise Linux Server, Standard (Physical or Virtual Nodes) ,Valor neto según Formulario Económico N°1 (en caso de discrepancia entre el valor y el Formulario Económico N° 1 primará este último)</t>
         </is>
       </c>
     </row>
@@ -14934,7 +15842,7 @@
         </is>
       </c>
       <c r="C116" s="0">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D116" s="4" t="inlineStr">
         <is>
@@ -14972,7 +15880,7 @@
         </is>
       </c>
       <c r="C117" s="0">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
@@ -14985,7 +15893,7 @@
         </is>
       </c>
       <c r="F117" s="0">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="G117" s="0" t="inlineStr">
         <is>
@@ -14994,7 +15902,7 @@
       </c>
       <c r="H117" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Item 5 Red Hat Enterprise Linux Server, Standard (Physical or Virtual Nodes), Valor neto según Formulario Económico N°1 (en caso de discrepancia entre el valor y el Formulario Económico N° 1 primará este último)</t>
+          <t xml:space="preserve">Item 5 Red Hat Enterprise Linux for Virtual Datacenters, Standard, Valor neto según Formulario Económico N°1 (en caso de discrepancia entre el valor y el Formulario Económico N° 1 primará este último)</t>
         </is>
       </c>
     </row>
@@ -15010,7 +15918,7 @@
         </is>
       </c>
       <c r="C118" s="0">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D118" s="4" t="inlineStr">
         <is>
@@ -15023,7 +15931,7 @@
         </is>
       </c>
       <c r="F118" s="0">
-        <v>28.0</v>
+        <v>5.0</v>
       </c>
       <c r="G118" s="0" t="inlineStr">
         <is>
@@ -15032,7 +15940,7 @@
       </c>
       <c r="H118" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Item 6 Suscripción Arquitecture Enginering Collection, Valor neto según Formulario Económico N°1 (en caso de discrepancia entre el valor y el Formulario Económico N° 1 primará este último)</t>
+          <t xml:space="preserve">Item 5 Red Hat Enterprise Linux Server, Standard (Physical or Virtual Nodes), Valor neto según Formulario Económico N°1 (en caso de discrepancia entre el valor y el Formulario Económico N° 1 primará este último)</t>
         </is>
       </c>
     </row>
@@ -15048,7 +15956,7 @@
         </is>
       </c>
       <c r="C119" s="0">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
@@ -15061,7 +15969,7 @@
         </is>
       </c>
       <c r="F119" s="0">
-        <v>12.0</v>
+        <v>28.0</v>
       </c>
       <c r="G119" s="0" t="inlineStr">
         <is>
@@ -15086,7 +15994,7 @@
         </is>
       </c>
       <c r="C120" s="0">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D120" s="4" t="inlineStr">
         <is>
@@ -15099,7 +16007,7 @@
         </is>
       </c>
       <c r="F120" s="0">
-        <v>4500.0</v>
+        <v>12.0</v>
       </c>
       <c r="G120" s="0" t="inlineStr">
         <is>
@@ -15108,36 +16016,36 @@
       </c>
       <c r="H120" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ítem 7 Suscripción Licencias Kaspersky, Valor neto según Formulario Económico N°1 (en caso de discrepancia entre el valor y el Formulario Económico N° 1 primará este último)</t>
+          <t xml:space="preserve">Item 6 Suscripción Arquitecture Enginering Collection, Valor neto según Formulario Económico N°1 (en caso de discrepancia entre el valor y el Formulario Económico N° 1 primará este último)</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">4778-14-LP26</t>
+          <t xml:space="preserve">425-39-LR26</t>
         </is>
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">SERV. ADMINISTRADO CONTACT CENTER OMNICANAL CON IA</t>
+          <t xml:space="preserve">ADQUISICIÓN Y RENOVACIÓN DE LICENCIAS DE SOFTWARE PARA EL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="C121" s="0">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Software para centrales de comunicación digital</t>
+          <t xml:space="preserve">Software de gestión de licencias</t>
         </is>
       </c>
       <c r="E121" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software para trabajo en redes</t>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de gestión</t>
         </is>
       </c>
       <c r="F121" s="0">
-        <v>24.0</v>
+        <v>4500.0</v>
       </c>
       <c r="G121" s="0" t="inlineStr">
         <is>
@@ -15146,19 +16054,19 @@
       </c>
       <c r="H121" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Servicio Administrado de Contact Center Omnicanal con IA</t>
+          <t xml:space="preserve">Ítem 7 Suscripción Licencias Kaspersky, Valor neto según Formulario Económico N°1 (en caso de discrepancia entre el valor y el Formulario Económico N° 1 primará este último)</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1607-10-LR26</t>
+          <t xml:space="preserve">4778-14-LP26</t>
         </is>
       </c>
       <c r="B122" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">servicio hospedaje soporte mantención plataforma</t>
+          <t xml:space="preserve">SERV. ADMINISTRADO CONTACT CENTER OMNICANAL CON IA</t>
         </is>
       </c>
       <c r="C122" s="0">
@@ -15166,16 +16074,16 @@
       </c>
       <c r="D122" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Desarrolladores de software</t>
+          <t xml:space="preserve">Software para centrales de comunicación digital</t>
         </is>
       </c>
       <c r="E122" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Servicios profesionales, administrativos y consultorías de gestión empresarial / Servicios de recursos humanos / Contratación de personal</t>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software para trabajo en redes</t>
         </is>
       </c>
       <c r="F122" s="0">
-        <v>1.0</v>
+        <v>24.0</v>
       </c>
       <c r="G122" s="0" t="inlineStr">
         <is>
@@ -15184,19 +16092,19 @@
       </c>
       <c r="H122" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">servicio hospedaje, soporte, mantención y actualización de la Plataforma Integrada de Asignación Familiar, Subsidio Único Familiar y Regímenes relacionados (PIAS), de la Superintendencia de Seguridad Social.</t>
+          <t xml:space="preserve">Servicio Administrado de Contact Center Omnicanal con IA</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2413-20-LE26</t>
+          <t xml:space="preserve">2107-142-LE26</t>
         </is>
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">SISTEMA DE GESTIÓN DOCUMENTAL</t>
+          <t xml:space="preserve">ARRIENDO DE TOTEMS AUTOADMINISTRADOS PARA HSC</t>
         </is>
       </c>
       <c r="C123" s="0">
@@ -15204,16 +16112,16 @@
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Desarrolladores de software</t>
+          <t xml:space="preserve">Servidores de gama alta</t>
         </is>
       </c>
       <c r="E123" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Servicios profesionales, administrativos y consultorías de gestión empresarial / Servicios de recursos humanos / Contratación de personal</t>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Equipos informáticos y accesorios / Computadores</t>
         </is>
       </c>
       <c r="F123" s="0">
-        <v>1.0</v>
+        <v>36.0</v>
       </c>
       <c r="G123" s="0" t="inlineStr">
         <is>
@@ -15222,19 +16130,19 @@
       </c>
       <c r="H123" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valor Mensual por el arriendo del “Sistema de Gestión Documental”.</t>
+          <t xml:space="preserve">SERVICIO MENSUAL DE ARRIENDO DE 3 TOTEMS AUTOADMINISTRADOS SEGUN BASES</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">906973-8-LP26</t>
+          <t xml:space="preserve">1607-10-LR26</t>
         </is>
       </c>
       <c r="B124" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">SISTEMAS INFORMÁTICOS DE GESTIÓN MUNICIPAL</t>
+          <t xml:space="preserve">servicio hospedaje soporte mantención plataforma</t>
         </is>
       </c>
       <c r="C124" s="0">
@@ -15242,37 +16150,37 @@
       </c>
       <c r="D124" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Servicios contables gubernamentales</t>
+          <t xml:space="preserve">Desarrolladores de software</t>
         </is>
       </c>
       <c r="E124" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Organizaciones y consultorías políticas, demográficas, económicas, sociales y de administración pública / Administración y finanzas públicas / Finanzas públicas</t>
+          <t xml:space="preserve">Servicios profesionales, administrativos y consultorías de gestión empresarial / Servicios de recursos humanos / Contratación de personal</t>
         </is>
       </c>
       <c r="F124" s="0">
-        <v>36.0</v>
+        <v>1.0</v>
       </c>
       <c r="G124" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mes</t>
+          <t xml:space="preserve">Unidad</t>
         </is>
       </c>
       <c r="H124" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">La presente licitación tiene por objeto contratar el suministro integral de sistemas informáticos de gestión municipal para la Municipalidad de Vichuquén, incluyendo software, módulos funcionales, servidor o infraestructura local destinada al servicio mun</t>
+          <t xml:space="preserve">servicio hospedaje, soporte, mantención y actualización de la Plataforma Integrada de Asignación Familiar, Subsidio Único Familiar y Regímenes relacionados (PIAS), de la Superintendencia de Seguridad Social.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">875-6-LP26</t>
+          <t xml:space="preserve">2413-20-LE26</t>
         </is>
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">SERVICIO DE MARKETING DIGITAL</t>
+          <t xml:space="preserve">SISTEMA DE GESTIÓN DOCUMENTAL</t>
         </is>
       </c>
       <c r="C125" s="0">
@@ -15280,12 +16188,12 @@
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Campañas publicitarias o de marketing</t>
+          <t xml:space="preserve">Desarrolladores de software</t>
         </is>
       </c>
       <c r="E125" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Servicios profesionales, administrativos y consultorías de gestión empresarial / Servicios para la comercialización y distribución / Ventas y marketing</t>
+          <t xml:space="preserve">Servicios profesionales, administrativos y consultorías de gestión empresarial / Servicios de recursos humanos / Contratación de personal</t>
         </is>
       </c>
       <c r="F125" s="0">
@@ -15293,24 +16201,24 @@
       </c>
       <c r="G125" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unidad</t>
+          <t xml:space="preserve">Mes</t>
         </is>
       </c>
       <c r="H125" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">SERVICIO DE MARKETING DIGITAL</t>
+          <t xml:space="preserve">Valor Mensual por el arriendo del “Sistema de Gestión Documental”.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2348-34-LP26</t>
+          <t xml:space="preserve">906973-8-LP26</t>
         </is>
       </c>
       <c r="B126" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADQUISICIÓN DE LICENCIAS DE SOFTWARE</t>
+          <t xml:space="preserve">SISTEMAS INFORMÁTICOS DE GESTIÓN MUNICIPAL</t>
         </is>
       </c>
       <c r="C126" s="0">
@@ -15318,100 +16226,176 @@
       </c>
       <c r="D126" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Software de sistema operativo</t>
+          <t xml:space="preserve">Servicios contables gubernamentales</t>
         </is>
       </c>
       <c r="E126" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de entorno operativo</t>
+          <t xml:space="preserve">Organizaciones y consultorías políticas, demográficas, económicas, sociales y de administración pública / Administración y finanzas públicas / Finanzas públicas</t>
         </is>
       </c>
       <c r="F126" s="0">
-        <v>2.0</v>
+        <v>36.0</v>
       </c>
       <c r="G126" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unidad</t>
+          <t xml:space="preserve">Mes</t>
         </is>
       </c>
       <c r="H126" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">AutoCAD 2026 o Superior - including specialized toolsets AD Commercial-New Single-   suscripción por 3 años, o similar con las mismas funcionalidades, debe cumplir con las actualizaciones del producto. Licenciamiento debe ser a nombre de la IL.Municipalid</t>
+          <t xml:space="preserve">La presente licitación tiene por objeto contratar el suministro integral de sistemas informáticos de gestión municipal para la Municipalidad de Vichuquén, incluyendo software, módulos funcionales, servidor o infraestructura local destinada al servicio mun</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">875-6-LP26</t>
+        </is>
+      </c>
+      <c r="B127" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SERVICIO DE MARKETING DIGITAL</t>
+        </is>
+      </c>
+      <c r="C127" s="0">
+        <v>1</v>
+      </c>
+      <c r="D127" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Campañas publicitarias o de marketing</t>
+        </is>
+      </c>
+      <c r="E127" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Servicios profesionales, administrativos y consultorías de gestión empresarial / Servicios para la comercialización y distribución / Ventas y marketing</t>
+        </is>
+      </c>
+      <c r="F127" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G127" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidad</t>
+        </is>
+      </c>
+      <c r="H127" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SERVICIO DE MARKETING DIGITAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">2348-34-LP26</t>
         </is>
       </c>
-      <c r="B127" s="4" t="inlineStr">
+      <c r="B128" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">ADQUISICIÓN DE LICENCIAS DE SOFTWARE</t>
         </is>
       </c>
-      <c r="C127" s="0">
+      <c r="C128" s="0">
+        <v>1</v>
+      </c>
+      <c r="D128" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Software de sistema operativo</t>
+        </is>
+      </c>
+      <c r="E128" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de entorno operativo</t>
+        </is>
+      </c>
+      <c r="F128" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="G128" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidad</t>
+        </is>
+      </c>
+      <c r="H128" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AutoCAD 2026 o Superior - including specialized toolsets AD Commercial-New Single-   suscripción por 3 años, o similar con las mismas funcionalidades, debe cumplir con las actualizaciones del producto. Licenciamiento debe ser a nombre de la IL.Municipalid</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2348-34-LP26</t>
+        </is>
+      </c>
+      <c r="B129" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADQUISICIÓN DE LICENCIAS DE SOFTWARE</t>
+        </is>
+      </c>
+      <c r="C129" s="0">
         <v>2</v>
       </c>
-      <c r="D127" s="4" t="inlineStr">
+      <c r="D129" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Software de sistema operativo</t>
         </is>
       </c>
-      <c r="E127" s="4" t="inlineStr">
+      <c r="E129" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de entorno operativo</t>
         </is>
       </c>
-      <c r="F127" s="0">
+      <c r="F129" s="0">
         <v>22.0</v>
       </c>
-      <c r="G127" s="0" t="inlineStr">
+      <c r="G129" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Unidad</t>
         </is>
       </c>
-      <c r="H127" s="4" t="inlineStr">
+      <c r="H129" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">AutoCAD LT 2026 o Superior - Commercial New Single- suscripción por 3 años, o similar con las mismas funcionalidades, debe cumplir con las actualizaciones del producto. Licenciamiento debe ser a nombre de la IL.Municipalidad de Punta Arenas.
 Se requiere</t>
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="0" t="inlineStr">
+    <row r="130">
+      <c r="A130" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">2348-34-LP26</t>
         </is>
       </c>
-      <c r="B128" s="4" t="inlineStr">
+      <c r="B130" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">ADQUISICIÓN DE LICENCIAS DE SOFTWARE</t>
         </is>
       </c>
-      <c r="C128" s="0">
+      <c r="C130" s="0">
         <v>3</v>
       </c>
-      <c r="D128" s="4" t="inlineStr">
+      <c r="D130" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Software de sistema operativo</t>
         </is>
       </c>
-      <c r="E128" s="4" t="inlineStr">
+      <c r="E130" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de entorno operativo</t>
         </is>
       </c>
-      <c r="F128" s="0">
+      <c r="F130" s="0">
         <v>5.0</v>
       </c>
-      <c r="G128" s="0" t="inlineStr">
+      <c r="G130" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Unidad</t>
         </is>
       </c>
-      <c r="H128" s="4" t="inlineStr">
+      <c r="H130" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Paquete suscripcion por 36 MESES, o similar con las mismas funcionalidades de:
 2 licencias ArGIS pro 3.2 Professional Advanced
@@ -15421,39 +16405,39 @@
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="0" t="inlineStr">
+    <row r="131">
+      <c r="A131" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">2348-34-LP26</t>
         </is>
       </c>
-      <c r="B129" s="4" t="inlineStr">
+      <c r="B131" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">ADQUISICIÓN DE LICENCIAS DE SOFTWARE</t>
         </is>
       </c>
-      <c r="C129" s="0">
+      <c r="C131" s="0">
         <v>4</v>
       </c>
-      <c r="D129" s="4" t="inlineStr">
+      <c r="D131" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Software de sistema operativo</t>
         </is>
       </c>
-      <c r="E129" s="4" t="inlineStr">
+      <c r="E131" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de entorno operativo</t>
         </is>
       </c>
-      <c r="F129" s="0">
+      <c r="F131" s="0">
         <v>1.0</v>
       </c>
-      <c r="G129" s="0" t="inlineStr">
+      <c r="G131" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Unidad</t>
         </is>
       </c>
-      <c r="H129" s="4" t="inlineStr">
+      <c r="H131" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Licencia RENOVACION de Adobe creative Cloud
 Productos: Creative Cloud for teams All Apps ALL Multiple
@@ -15462,82 +16446,6 @@
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2348-34-LP26</t>
-        </is>
-      </c>
-      <c r="B130" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ADQUISICIÓN DE LICENCIAS DE SOFTWARE</t>
-        </is>
-      </c>
-      <c r="C130" s="0">
-        <v>5</v>
-      </c>
-      <c r="D130" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Software de sistema operativo</t>
-        </is>
-      </c>
-      <c r="E130" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de entorno operativo</t>
-        </is>
-      </c>
-      <c r="F130" s="0">
-        <v>2.0</v>
-      </c>
-      <c r="G130" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Unidad</t>
-        </is>
-      </c>
-      <c r="H130" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ZOOM PRO - Licencias de usuario Pro, hasta 100 Invitados por Videoconferencia, duración llamadas ilimitadas, Agendamiento de Reuniones, Presentaciones en calidad HD - 36 meses de Suscripción.</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2348-34-LP26</t>
-        </is>
-      </c>
-      <c r="B131" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ADQUISICIÓN DE LICENCIAS DE SOFTWARE</t>
-        </is>
-      </c>
-      <c r="C131" s="0">
-        <v>6</v>
-      </c>
-      <c r="D131" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Software de sistema operativo</t>
-        </is>
-      </c>
-      <c r="E131" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de entorno operativo</t>
-        </is>
-      </c>
-      <c r="F131" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="G131" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Unidad</t>
-        </is>
-      </c>
-      <c r="H131" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Protocolo DMARC por un periodo de 36 meses, con soporte técnico y con correos emitidos ilimitadamente</t>
-        </is>
-      </c>
-    </row>
     <row r="132">
       <c r="A132" s="0" t="inlineStr">
         <is>
@@ -15550,7 +16458,7 @@
         </is>
       </c>
       <c r="C132" s="0">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D132" s="4" t="inlineStr">
         <is>
@@ -15563,7 +16471,7 @@
         </is>
       </c>
       <c r="F132" s="0">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G132" s="0" t="inlineStr">
         <is>
@@ -15572,7 +16480,7 @@
       </c>
       <c r="H132" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">LICENCIA CLOUD VNNOX, para pantallas HITO 500 AÑOS. LICENCIA POR 36 MESES</t>
+          <t xml:space="preserve">ZOOM PRO - Licencias de usuario Pro, hasta 100 Invitados por Videoconferencia, duración llamadas ilimitadas, Agendamiento de Reuniones, Presentaciones en calidad HD - 36 meses de Suscripción.</t>
         </is>
       </c>
     </row>
@@ -15588,7 +16496,7 @@
         </is>
       </c>
       <c r="C133" s="0">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
@@ -15601,7 +16509,7 @@
         </is>
       </c>
       <c r="F133" s="0">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="G133" s="0" t="inlineStr">
         <is>
@@ -15610,7 +16518,7 @@
       </c>
       <c r="H133" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">SQL Server 2025 - 1 User CAL Perpetua</t>
+          <t xml:space="preserve">Protocolo DMARC por un periodo de 36 meses, con soporte técnico y con correos emitidos ilimitadamente</t>
         </is>
       </c>
     </row>
@@ -15626,7 +16534,7 @@
         </is>
       </c>
       <c r="C134" s="0">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D134" s="4" t="inlineStr">
         <is>
@@ -15639,7 +16547,7 @@
         </is>
       </c>
       <c r="F134" s="0">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G134" s="0" t="inlineStr">
         <is>
@@ -15648,7 +16556,7 @@
       </c>
       <c r="H134" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">SQL Server 2025 Standard Edition Perpetuo</t>
+          <t xml:space="preserve">LICENCIA CLOUD VNNOX, para pantallas HITO 500 AÑOS. LICENCIA POR 36 MESES</t>
         </is>
       </c>
     </row>
@@ -15664,7 +16572,7 @@
         </is>
       </c>
       <c r="C135" s="0">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
@@ -15677,7 +16585,7 @@
         </is>
       </c>
       <c r="F135" s="0">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
       <c r="G135" s="0" t="inlineStr">
         <is>
@@ -15686,36 +16594,36 @@
       </c>
       <c r="H135" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">SQL Server 2025 Standard Core - License Pack 2 Core Perpetuo</t>
+          <t xml:space="preserve">SQL Server 2025 - 1 User CAL Perpetua</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2445-109-LP26</t>
+          <t xml:space="preserve">2348-34-LP26</t>
         </is>
       </c>
       <c r="B136" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">SERVICIO SOFTWARE GESTIÓN  ASISTENCIA DEPTO. SALUD</t>
+          <t xml:space="preserve">ADQUISICIÓN DE LICENCIAS DE SOFTWARE</t>
         </is>
       </c>
       <c r="C136" s="0">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D136" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Software de gestión de recursos humanos</t>
+          <t xml:space="preserve">Software de sistema operativo</t>
         </is>
       </c>
       <c r="E136" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de gestión</t>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de entorno operativo</t>
         </is>
       </c>
       <c r="F136" s="0">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G136" s="0" t="inlineStr">
         <is>
@@ -15724,36 +16632,36 @@
       </c>
       <c r="H136" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">SERVICIO DE ARRIENDO, IMPLEMENTACIÓN, MANTENCIÓN Y SOPORTE DE SOFTWARE  CLOUD PARA GESTIÓN DE ASISTENCIA Y TERMINALES BIOMÉTRICOS PARA EL DEPARTAMENTO DE SALUD CURICO, POR UN PERIODO DE 36 MESES</t>
+          <t xml:space="preserve">SQL Server 2025 Standard Edition Perpetuo</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1020-40-LP26</t>
+          <t xml:space="preserve">2348-34-LP26</t>
         </is>
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Serv.Cloud Amazon Web Services AWS o Equivalente</t>
+          <t xml:space="preserve">ADQUISICIÓN DE LICENCIAS DE SOFTWARE</t>
         </is>
       </c>
       <c r="C137" s="0">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Software del sistema de administración de bases de datos</t>
+          <t xml:space="preserve">Software de sistema operativo</t>
         </is>
       </c>
       <c r="E137" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de consultas y gestión de datos</t>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de entorno operativo</t>
         </is>
       </c>
       <c r="F137" s="0">
-        <v>1.0</v>
+        <v>8.0</v>
       </c>
       <c r="G137" s="0" t="inlineStr">
         <is>
@@ -15762,19 +16670,19 @@
       </c>
       <c r="H137" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">PRECIO TOTAL NETO OFERTADO (SIN IVA), según Formulario N°1 "Oferta Económica" (Incluye los señalado en el numeral 5.1.1 de las Bases Administrativas, en archivo adjunto).</t>
+          <t xml:space="preserve">SQL Server 2025 Standard Core - License Pack 2 Core Perpetuo</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">3902-39-LP26</t>
+          <t xml:space="preserve">2445-109-LP26</t>
         </is>
       </c>
       <c r="B138" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">SERVICIO SOFTWARE SISTEMAS DE INFORMACIÓN BULNES.</t>
+          <t xml:space="preserve">SERVICIO SOFTWARE GESTIÓN  ASISTENCIA DEPTO. SALUD</t>
         </is>
       </c>
       <c r="C138" s="0">
@@ -15782,7 +16690,7 @@
       </c>
       <c r="D138" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Paquetes de software para oficinas</t>
+          <t xml:space="preserve">Software de gestión de recursos humanos</t>
         </is>
       </c>
       <c r="E138" s="4" t="inlineStr">
@@ -15795,24 +16703,24 @@
       </c>
       <c r="G138" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Global</t>
+          <t xml:space="preserve">Unidad</t>
         </is>
       </c>
       <c r="H138" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">La Municipalidad de Bulnes, ha dispuesto la Licitación de la contratación por “SERVICIO DE SOFTWARE DE SISTEMAS DE INFORMACIÓN PARA MUNICIPALIDAD DE BULNES”, conforme a las exigencias de las presentes bases administrativas especiales, especificaciones téc</t>
+          <t xml:space="preserve">SERVICIO DE ARRIENDO, IMPLEMENTACIÓN, MANTENCIÓN Y SOPORTE DE SOFTWARE  CLOUD PARA GESTIÓN DE ASISTENCIA Y TERMINALES BIOMÉTRICOS PARA EL DEPARTAMENTO DE SALUD CURICO, POR UN PERIODO DE 36 MESES</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2434-20-LP26</t>
+          <t xml:space="preserve">1020-40-LP26</t>
         </is>
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">SERV. PLATAFORMA INTEGRAL PARA GESTION MUNICIPAL</t>
+          <t xml:space="preserve">Serv.Cloud Amazon Web Services AWS o Equivalente</t>
         </is>
       </c>
       <c r="C139" s="0">
@@ -15820,12 +16728,12 @@
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Software de interconectividad de plataformas</t>
+          <t xml:space="preserve">Software del sistema de administración de bases de datos</t>
         </is>
       </c>
       <c r="E139" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software para trabajo en redes</t>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de consultas y gestión de datos</t>
         </is>
       </c>
       <c r="F139" s="0">
@@ -15833,24 +16741,24 @@
       </c>
       <c r="G139" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Global</t>
+          <t xml:space="preserve">Unidad</t>
         </is>
       </c>
       <c r="H139" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Servicio de Plataforma Integral de Gestión Municipal y Servicios Digitales, Municipalidad de Estación Central.</t>
+          <t xml:space="preserve">PRECIO TOTAL NETO OFERTADO (SIN IVA), según Formulario N°1 "Oferta Económica" (Incluye los señalado en el numeral 5.1.1 de las Bases Administrativas, en archivo adjunto).</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1133353-43-LR26</t>
+          <t xml:space="preserve">3902-39-LP26</t>
         </is>
       </c>
       <c r="B140" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ARRIENDO DE SOFTWARE INTEGRAL PARA LA GESTIÓN MUNICIPAL ÁREAS DE SALUD Y MUNICIPAL COMUNA DE RAUCO</t>
+          <t xml:space="preserve">SERVICIO SOFTWARE SISTEMAS DE INFORMACIÓN BULNES.</t>
         </is>
       </c>
       <c r="C140" s="0">
@@ -15858,12 +16766,12 @@
       </c>
       <c r="D140" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Software de administración</t>
+          <t xml:space="preserve">Paquetes de software para oficinas</t>
         </is>
       </c>
       <c r="E140" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de administración de redes</t>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de gestión</t>
         </is>
       </c>
       <c r="F140" s="0">
@@ -15876,19 +16784,19 @@
       </c>
       <c r="H140" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">SOFTWARE INTEGRAL PARA LA GESTIÓN MUNICIPAL</t>
+          <t xml:space="preserve">La Municipalidad de Bulnes, ha dispuesto la Licitación de la contratación por “SERVICIO DE SOFTWARE DE SISTEMAS DE INFORMACIÓN PARA MUNICIPALIDAD DE BULNES”, conforme a las exigencias de las presentes bases administrativas especiales, especificaciones téc</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2408-160-LP26</t>
+          <t xml:space="preserve">2434-20-LP26</t>
         </is>
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">EQUIPOS INFORMÁTICOS PARA DEPENDENCIAS MUNICIPALES</t>
+          <t xml:space="preserve">SERV. PLATAFORMA INTEGRAL PARA GESTION MUNICIPAL</t>
         </is>
       </c>
       <c r="C141" s="0">
@@ -15896,63 +16804,63 @@
       </c>
       <c r="D141" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Escáner</t>
+          <t xml:space="preserve">Software de interconectividad de plataformas</t>
         </is>
       </c>
       <c r="E141" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Equipos informáticos y accesorios / Dispositivos informáticos de entrada de datos</t>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software para trabajo en redes</t>
         </is>
       </c>
       <c r="F141" s="0">
-        <v>40.0</v>
+        <v>1.0</v>
       </c>
       <c r="G141" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unidad</t>
+          <t xml:space="preserve">Global</t>
         </is>
       </c>
       <c r="H141" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Se requiere scanner, según bases técnicas adjuntas.</t>
+          <t xml:space="preserve">Servicio de Plataforma Integral de Gestión Municipal y Servicios Digitales, Municipalidad de Estación Central.</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2408-160-LP26</t>
+          <t xml:space="preserve">1133353-43-LR26</t>
         </is>
       </c>
       <c r="B142" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">EQUIPOS INFORMÁTICOS PARA DEPENDENCIAS MUNICIPALES</t>
+          <t xml:space="preserve">ARRIENDO DE SOFTWARE INTEGRAL PARA LA GESTIÓN MUNICIPAL ÁREAS DE SALUD Y MUNICIPAL COMUNA DE RAUCO</t>
         </is>
       </c>
       <c r="C142" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D142" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Impresoras de chorro de tinta</t>
+          <t xml:space="preserve">Software de administración</t>
         </is>
       </c>
       <c r="E142" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Equipos informáticos y accesorios / Impresoras</t>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de administración de redes</t>
         </is>
       </c>
       <c r="F142" s="0">
-        <v>70.0</v>
+        <v>1.0</v>
       </c>
       <c r="G142" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unidad</t>
+          <t xml:space="preserve">Global</t>
         </is>
       </c>
       <c r="H142" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Se requiere impresoras, según bases técnicas adjuntas.</t>
+          <t xml:space="preserve">SOFTWARE INTEGRAL PARA LA GESTIÓN MUNICIPAL</t>
         </is>
       </c>
     </row>
@@ -15968,20 +16876,20 @@
         </is>
       </c>
       <c r="C143" s="0">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D143" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trazadoras de gráficos</t>
+          <t xml:space="preserve">Escáner</t>
         </is>
       </c>
       <c r="E143" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Equipos informáticos y accesorios / Impresoras</t>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Equipos informáticos y accesorios / Dispositivos informáticos de entrada de datos</t>
         </is>
       </c>
       <c r="F143" s="0">
-        <v>3.0</v>
+        <v>40.0</v>
       </c>
       <c r="G143" s="0" t="inlineStr">
         <is>
@@ -15990,7 +16898,7 @@
       </c>
       <c r="H143" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Se requiere plóter, según bases técnicas adjuntas.</t>
+          <t xml:space="preserve">Se requiere scanner, según bases técnicas adjuntas.</t>
         </is>
       </c>
     </row>
@@ -16006,20 +16914,20 @@
         </is>
       </c>
       <c r="C144" s="0">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D144" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Computadores personales</t>
+          <t xml:space="preserve">Impresoras de chorro de tinta</t>
         </is>
       </c>
       <c r="E144" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Equipos informáticos y accesorios / Computadores</t>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Equipos informáticos y accesorios / Impresoras</t>
         </is>
       </c>
       <c r="F144" s="0">
-        <v>12.0</v>
+        <v>70.0</v>
       </c>
       <c r="G144" s="0" t="inlineStr">
         <is>
@@ -16028,7 +16936,7 @@
       </c>
       <c r="H144" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Se requiere computadores touch, según bases técnicas adjuntas.</t>
+          <t xml:space="preserve">Se requiere impresoras, según bases técnicas adjuntas.</t>
         </is>
       </c>
     </row>
@@ -16044,20 +16952,20 @@
         </is>
       </c>
       <c r="C145" s="0">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D145" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Computadores de escritorio</t>
+          <t xml:space="preserve">Trazadoras de gráficos</t>
         </is>
       </c>
       <c r="E145" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Equipos informáticos y accesorios / Computadores</t>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Equipos informáticos y accesorios / Impresoras</t>
         </is>
       </c>
       <c r="F145" s="0">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G145" s="0" t="inlineStr">
         <is>
@@ -16066,7 +16974,7 @@
       </c>
       <c r="H145" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Se requiere PC para streaming, según bases técnicas adjuntas.</t>
+          <t xml:space="preserve">Se requiere plóter, según bases técnicas adjuntas.</t>
         </is>
       </c>
     </row>
@@ -16082,11 +16990,11 @@
         </is>
       </c>
       <c r="C146" s="0">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D146" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Computadores de escritorio</t>
+          <t xml:space="preserve">Computadores personales</t>
         </is>
       </c>
       <c r="E146" s="4" t="inlineStr">
@@ -16095,7 +17003,7 @@
         </is>
       </c>
       <c r="F146" s="0">
-        <v>6.0</v>
+        <v>12.0</v>
       </c>
       <c r="G146" s="0" t="inlineStr">
         <is>
@@ -16104,32 +17012,32 @@
       </c>
       <c r="H146" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Se requiere PC, según bases técnicas adjuntas.</t>
+          <t xml:space="preserve">Se requiere computadores touch, según bases técnicas adjuntas.</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1593-24-LP26</t>
+          <t xml:space="preserve">2408-160-LP26</t>
         </is>
       </c>
       <c r="B147" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adquisición instalación plataforma almacenamiento</t>
+          <t xml:space="preserve">EQUIPOS INFORMÁTICOS PARA DEPENDENCIAS MUNICIPALES</t>
         </is>
       </c>
       <c r="C147" s="0">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D147" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Almacenamiento de datos</t>
+          <t xml:space="preserve">Computadores de escritorio</t>
         </is>
       </c>
       <c r="E147" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Servicios basados en ingeniería, ciencias sociales y tecnología de la información / Servicios informáticos / Administración de sistemas</t>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Equipos informáticos y accesorios / Computadores</t>
         </is>
       </c>
       <c r="F147" s="0">
@@ -16142,87 +17050,87 @@
       </c>
       <c r="H147" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">Se requiere PC para streaming, según bases técnicas adjuntas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2408-160-LP26</t>
+        </is>
+      </c>
+      <c r="B148" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EQUIPOS INFORMÁTICOS PARA DEPENDENCIAS MUNICIPALES</t>
+        </is>
+      </c>
+      <c r="C148" s="0">
+        <v>6</v>
+      </c>
+      <c r="D148" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Computadores de escritorio</t>
+        </is>
+      </c>
+      <c r="E148" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Equipos informáticos y accesorios / Computadores</t>
+        </is>
+      </c>
+      <c r="F148" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="G148" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidad</t>
+        </is>
+      </c>
+      <c r="H148" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Se requiere PC, según bases técnicas adjuntas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1593-24-LP26</t>
+        </is>
+      </c>
+      <c r="B149" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Adquisición instalación plataforma almacenamiento</t>
+        </is>
+      </c>
+      <c r="C149" s="0">
+        <v>1</v>
+      </c>
+      <c r="D149" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Almacenamiento de datos</t>
+        </is>
+      </c>
+      <c r="E149" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Servicios basados en ingeniería, ciencias sociales y tecnología de la información / Servicios informáticos / Administración de sistemas</t>
+        </is>
+      </c>
+      <c r="F149" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G149" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidad</t>
+        </is>
+      </c>
+      <c r="H149" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">Adquisición e instalación de plataforma de almacenamiento para la Superintendencia de
 Servicios Sanitarios.</t>
         </is>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2563-34-LR26</t>
-        </is>
-      </c>
-      <c r="B148" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">EQUIPOS PARA REDES INFORMÁTICAS Y LICENCIAS</t>
-        </is>
-      </c>
-      <c r="C148" s="0">
-        <v>1</v>
-      </c>
-      <c r="D148" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Cajas de conmutación de computadores</t>
-        </is>
-      </c>
-      <c r="E148" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Equipos informáticos y accesorios / Accesorios de computador</t>
-        </is>
-      </c>
-      <c r="F148" s="0">
-        <v>10.0</v>
-      </c>
-      <c r="G148" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Unidad</t>
-        </is>
-      </c>
-      <c r="H148" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Switch 48G PoE 4SFP+ (equivalente al modelo JL727B) / Control de Acceso</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2563-34-LR26</t>
-        </is>
-      </c>
-      <c r="B149" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">EQUIPOS PARA REDES INFORMÁTICAS Y LICENCIAS</t>
-        </is>
-      </c>
-      <c r="C149" s="0">
-        <v>2</v>
-      </c>
-      <c r="D149" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Cajas de conmutación de computadores</t>
-        </is>
-      </c>
-      <c r="E149" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Equipos informáticos y accesorios / Accesorios de computador</t>
-        </is>
-      </c>
-      <c r="F149" s="0">
-        <v>11.0</v>
-      </c>
-      <c r="G149" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Unidad</t>
-        </is>
-      </c>
-      <c r="H149" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Switch 48G PoE 4SFP+ (equivalente al modelo JL727B) /Aeroportuarios</t>
-        </is>
-      </c>
-    </row>
     <row r="150">
       <c r="A150" s="0" t="inlineStr">
         <is>
@@ -16235,7 +17143,7 @@
         </is>
       </c>
       <c r="C150" s="0">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D150" s="4" t="inlineStr">
         <is>
@@ -16248,7 +17156,7 @@
         </is>
       </c>
       <c r="F150" s="0">
-        <v>1.0</v>
+        <v>10.0</v>
       </c>
       <c r="G150" s="0" t="inlineStr">
         <is>
@@ -16257,7 +17165,7 @@
       </c>
       <c r="H150" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Switch 24G PoE 4SFP+(equivalente al modelo JL261A) /Aeroportuario</t>
+          <t xml:space="preserve">Switch 48G PoE 4SFP+ (equivalente al modelo JL727B) / Control de Acceso</t>
         </is>
       </c>
     </row>
@@ -16273,7 +17181,7 @@
         </is>
       </c>
       <c r="C151" s="0">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D151" s="4" t="inlineStr">
         <is>
@@ -16286,7 +17194,7 @@
         </is>
       </c>
       <c r="F151" s="0">
-        <v>7.0</v>
+        <v>11.0</v>
       </c>
       <c r="G151" s="0" t="inlineStr">
         <is>
@@ -16295,7 +17203,7 @@
       </c>
       <c r="H151" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Switch 12G PoE 2SFP+ (equivalente al modelo R8Q72A) /Aeroportuario</t>
+          <t xml:space="preserve">Switch 48G PoE 4SFP+ (equivalente al modelo JL727B) /Aeroportuarios</t>
         </is>
       </c>
     </row>
@@ -16311,7 +17219,7 @@
         </is>
       </c>
       <c r="C152" s="0">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D152" s="4" t="inlineStr">
         <is>
@@ -16324,7 +17232,7 @@
         </is>
       </c>
       <c r="F152" s="0">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="G152" s="0" t="inlineStr">
         <is>
@@ -16333,7 +17241,7 @@
       </c>
       <c r="H152" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Access Point Desktop (equivalente al modelo R3V46A) /Control de acceso</t>
+          <t xml:space="preserve">Switch 24G PoE 4SFP+(equivalente al modelo JL261A) /Aeroportuario</t>
         </is>
       </c>
     </row>
@@ -16349,187 +17257,187 @@
         </is>
       </c>
       <c r="C153" s="0">
+        <v>4</v>
+      </c>
+      <c r="D153" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cajas de conmutación de computadores</t>
+        </is>
+      </c>
+      <c r="E153" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Equipos informáticos y accesorios / Accesorios de computador</t>
+        </is>
+      </c>
+      <c r="F153" s="0">
+        <v>7.0</v>
+      </c>
+      <c r="G153" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidad</t>
+        </is>
+      </c>
+      <c r="H153" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Switch 12G PoE 2SFP+ (equivalente al modelo R8Q72A) /Aeroportuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2563-34-LR26</t>
+        </is>
+      </c>
+      <c r="B154" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EQUIPOS PARA REDES INFORMÁTICAS Y LICENCIAS</t>
+        </is>
+      </c>
+      <c r="C154" s="0">
+        <v>5</v>
+      </c>
+      <c r="D154" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cajas de conmutación de computadores</t>
+        </is>
+      </c>
+      <c r="E154" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Equipos informáticos y accesorios / Accesorios de computador</t>
+        </is>
+      </c>
+      <c r="F154" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="G154" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidad</t>
+        </is>
+      </c>
+      <c r="H154" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Access Point Desktop (equivalente al modelo R3V46A) /Control de acceso</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2563-34-LR26</t>
+        </is>
+      </c>
+      <c r="B155" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EQUIPOS PARA REDES INFORMÁTICAS Y LICENCIAS</t>
+        </is>
+      </c>
+      <c r="C155" s="0">
         <v>6</v>
       </c>
-      <c r="D153" s="4" t="inlineStr">
+      <c r="D155" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Cajas de conmutación de computadores</t>
         </is>
       </c>
-      <c r="E153" s="4" t="inlineStr">
+      <c r="E155" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Equipos informáticos y accesorios / Accesorios de computador</t>
         </is>
       </c>
-      <c r="F153" s="0">
+      <c r="F155" s="0">
         <v>20.0</v>
       </c>
-      <c r="G153" s="0" t="inlineStr">
+      <c r="G155" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Unidad</t>
         </is>
       </c>
-      <c r="H153" s="4" t="inlineStr">
+      <c r="H155" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Access Point
 (equivalente al modelo JZ336A) /Control de Acceso</t>
         </is>
       </c>
     </row>
-    <row r="154">
-      <c r="A154" s="0" t="inlineStr">
+    <row r="156">
+      <c r="A156" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">2563-34-LR26</t>
         </is>
       </c>
-      <c r="B154" s="4" t="inlineStr">
+      <c r="B156" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">EQUIPOS PARA REDES INFORMÁTICAS Y LICENCIAS</t>
         </is>
       </c>
-      <c r="C154" s="0">
+      <c r="C156" s="0">
         <v>7</v>
       </c>
-      <c r="D154" s="4" t="inlineStr">
+      <c r="D156" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Cajas de conmutación de computadores</t>
         </is>
       </c>
-      <c r="E154" s="4" t="inlineStr">
+      <c r="E156" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Equipos informáticos y accesorios / Accesorios de computador</t>
         </is>
       </c>
-      <c r="F154" s="0">
+      <c r="F156" s="0">
         <v>11.0</v>
       </c>
-      <c r="G154" s="0" t="inlineStr">
+      <c r="G156" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Unidad</t>
         </is>
       </c>
-      <c r="H154" s="4" t="inlineStr">
+      <c r="H156" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Access Point
 (equivalente al modelo JZ336A) /Aeroportuarios</t>
         </is>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" s="0" t="inlineStr">
+    <row r="157">
+      <c r="A157" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">2563-34-LR26</t>
         </is>
       </c>
-      <c r="B155" s="4" t="inlineStr">
+      <c r="B157" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">EQUIPOS PARA REDES INFORMÁTICAS Y LICENCIAS</t>
         </is>
       </c>
-      <c r="C155" s="0">
+      <c r="C157" s="0">
         <v>8</v>
       </c>
-      <c r="D155" s="4" t="inlineStr">
+      <c r="D157" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Cajas de conmutación de computadores</t>
         </is>
       </c>
-      <c r="E155" s="4" t="inlineStr">
+      <c r="E157" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Equipos informáticos y accesorios / Accesorios de computador</t>
         </is>
       </c>
-      <c r="F155" s="0">
+      <c r="F157" s="0">
         <v>6.0</v>
       </c>
-      <c r="G155" s="0" t="inlineStr">
+      <c r="G157" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Unidad</t>
         </is>
       </c>
-      <c r="H155" s="4" t="inlineStr">
+      <c r="H157" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Access Point Exterior
 (equivalente al modelo R7T05A) /Control de Acceso</t>
         </is>
       </c>
     </row>
-    <row r="156">
-      <c r="A156" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2563-34-LR26</t>
-        </is>
-      </c>
-      <c r="B156" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">EQUIPOS PARA REDES INFORMÁTICAS Y LICENCIAS</t>
-        </is>
-      </c>
-      <c r="C156" s="0">
-        <v>9</v>
-      </c>
-      <c r="D156" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Cajas de conmutación de computadores</t>
-        </is>
-      </c>
-      <c r="E156" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Equipos informáticos y accesorios / Accesorios de computador</t>
-        </is>
-      </c>
-      <c r="F156" s="0">
-        <v>3.0</v>
-      </c>
-      <c r="G156" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Unidad</t>
-        </is>
-      </c>
-      <c r="H156" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Soporte anclaje para riel cielo falso plano 9/16'' Pack 10 unidades. /Aeroportuarios</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2563-34-LR26</t>
-        </is>
-      </c>
-      <c r="B157" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">EQUIPOS PARA REDES INFORMÁTICAS Y LICENCIAS</t>
-        </is>
-      </c>
-      <c r="C157" s="0">
-        <v>10</v>
-      </c>
-      <c r="D157" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Cajas de conmutación de computadores</t>
-        </is>
-      </c>
-      <c r="E157" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Equipos informáticos y accesorios / Accesorios de computador</t>
-        </is>
-      </c>
-      <c r="F157" s="0">
-        <v>3.0</v>
-      </c>
-      <c r="G157" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Unidad</t>
-        </is>
-      </c>
-      <c r="H157" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Soporte anclaje para superficie sólida Pack 10 unidades. /Aeroportuarios</t>
-        </is>
-      </c>
-    </row>
     <row r="158">
       <c r="A158" s="0" t="inlineStr">
         <is>
@@ -16542,148 +17450,148 @@
         </is>
       </c>
       <c r="C158" s="0">
+        <v>9</v>
+      </c>
+      <c r="D158" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cajas de conmutación de computadores</t>
+        </is>
+      </c>
+      <c r="E158" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Equipos informáticos y accesorios / Accesorios de computador</t>
+        </is>
+      </c>
+      <c r="F158" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="G158" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidad</t>
+        </is>
+      </c>
+      <c r="H158" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Soporte anclaje para riel cielo falso plano 9/16'' Pack 10 unidades. /Aeroportuarios</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2563-34-LR26</t>
+        </is>
+      </c>
+      <c r="B159" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EQUIPOS PARA REDES INFORMÁTICAS Y LICENCIAS</t>
+        </is>
+      </c>
+      <c r="C159" s="0">
+        <v>10</v>
+      </c>
+      <c r="D159" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cajas de conmutación de computadores</t>
+        </is>
+      </c>
+      <c r="E159" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Equipos informáticos y accesorios / Accesorios de computador</t>
+        </is>
+      </c>
+      <c r="F159" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="G159" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidad</t>
+        </is>
+      </c>
+      <c r="H159" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Soporte anclaje para superficie sólida Pack 10 unidades. /Aeroportuarios</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2563-34-LR26</t>
+        </is>
+      </c>
+      <c r="B160" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EQUIPOS PARA REDES INFORMÁTICAS Y LICENCIAS</t>
+        </is>
+      </c>
+      <c r="C160" s="0">
         <v>11</v>
       </c>
-      <c r="D158" s="4" t="inlineStr">
+      <c r="D160" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Cajas de conmutación de computadores</t>
         </is>
       </c>
-      <c r="E158" s="4" t="inlineStr">
+      <c r="E160" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Equipos informáticos y accesorios / Accesorios de computador</t>
         </is>
       </c>
-      <c r="F158" s="0">
+      <c r="F160" s="0">
         <v>10.0</v>
       </c>
-      <c r="G158" s="0" t="inlineStr">
+      <c r="G160" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Unidad</t>
         </is>
       </c>
-      <c r="H158" s="4" t="inlineStr">
+      <c r="H160" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Módulo 10G SFP+ LC LR 10km
 (equivalente al modelo J9151E) /Control de Acceso</t>
         </is>
       </c>
     </row>
-    <row r="159">
-      <c r="A159" s="0" t="inlineStr">
+    <row r="161">
+      <c r="A161" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">2563-34-LR26</t>
         </is>
       </c>
-      <c r="B159" s="4" t="inlineStr">
+      <c r="B161" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">EQUIPOS PARA REDES INFORMÁTICAS Y LICENCIAS</t>
         </is>
       </c>
-      <c r="C159" s="0">
+      <c r="C161" s="0">
         <v>12</v>
       </c>
-      <c r="D159" s="4" t="inlineStr">
+      <c r="D161" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Cajas de conmutación de computadores</t>
         </is>
       </c>
-      <c r="E159" s="4" t="inlineStr">
+      <c r="E161" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Equipos informáticos y accesorios / Accesorios de computador</t>
         </is>
       </c>
-      <c r="F159" s="0">
+      <c r="F161" s="0">
         <v>10.0</v>
       </c>
-      <c r="G159" s="0" t="inlineStr">
+      <c r="G161" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Unidad</t>
         </is>
       </c>
-      <c r="H159" s="4" t="inlineStr">
+      <c r="H161" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Módulo FO (SM) 1G SFP LC LX 10km
 (equivalente al modelo J4859D) /Control de Acceso</t>
         </is>
       </c>
     </row>
-    <row r="160">
-      <c r="A160" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2563-34-LR26</t>
-        </is>
-      </c>
-      <c r="B160" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">EQUIPOS PARA REDES INFORMÁTICAS Y LICENCIAS</t>
-        </is>
-      </c>
-      <c r="C160" s="0">
-        <v>13</v>
-      </c>
-      <c r="D160" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Cajas de conmutación de computadores</t>
-        </is>
-      </c>
-      <c r="E160" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Equipos informáticos y accesorios / Accesorios de computador</t>
-        </is>
-      </c>
-      <c r="F160" s="0">
-        <v>24.0</v>
-      </c>
-      <c r="G160" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Unidad</t>
-        </is>
-      </c>
-      <c r="H160" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Módulo FO (SM) 1G SFP LC LX 10km (equivalente al modelo J4859D) /Aeroportuarios</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2563-34-LR26</t>
-        </is>
-      </c>
-      <c r="B161" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">EQUIPOS PARA REDES INFORMÁTICAS Y LICENCIAS</t>
-        </is>
-      </c>
-      <c r="C161" s="0">
-        <v>14</v>
-      </c>
-      <c r="D161" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Cajas de conmutación de computadores</t>
-        </is>
-      </c>
-      <c r="E161" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Equipos informáticos y accesorios / Accesorios de computador</t>
-        </is>
-      </c>
-      <c r="F161" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="G161" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Unidad</t>
-        </is>
-      </c>
-      <c r="H161" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Equipo de protección de enlaces de red frente a ataques DDoS y amenazas avanzadas, actuando directamente en el borde de la red (edge), donde se conectan los enlaces de Internet principal y de respaldo. /Control de Acceso</t>
-        </is>
-      </c>
-    </row>
     <row r="162">
       <c r="A162" s="0" t="inlineStr">
         <is>
@@ -16696,7 +17604,7 @@
         </is>
       </c>
       <c r="C162" s="0">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D162" s="4" t="inlineStr">
         <is>
@@ -16709,7 +17617,7 @@
         </is>
       </c>
       <c r="F162" s="0">
-        <v>1.0</v>
+        <v>24.0</v>
       </c>
       <c r="G162" s="0" t="inlineStr">
         <is>
@@ -16718,212 +17626,212 @@
       </c>
       <c r="H162" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Licencia para el funcionamiento del equipo de protección de enlaces de red frente a ataques DDoS y amenazas avanzadas. /Control de Acceso</t>
+          <t xml:space="preserve">Módulo FO (SM) 1G SFP LC LX 10km (equivalente al modelo J4859D) /Aeroportuarios</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">2563-34-LR26</t>
+        </is>
+      </c>
+      <c r="B163" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EQUIPOS PARA REDES INFORMÁTICAS Y LICENCIAS</t>
+        </is>
+      </c>
+      <c r="C163" s="0">
+        <v>14</v>
+      </c>
+      <c r="D163" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cajas de conmutación de computadores</t>
+        </is>
+      </c>
+      <c r="E163" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Equipos informáticos y accesorios / Accesorios de computador</t>
+        </is>
+      </c>
+      <c r="F163" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G163" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidad</t>
+        </is>
+      </c>
+      <c r="H163" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Equipo de protección de enlaces de red frente a ataques DDoS y amenazas avanzadas, actuando directamente en el borde de la red (edge), donde se conectan los enlaces de Internet principal y de respaldo. /Control de Acceso</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2563-34-LR26</t>
+        </is>
+      </c>
+      <c r="B164" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EQUIPOS PARA REDES INFORMÁTICAS Y LICENCIAS</t>
+        </is>
+      </c>
+      <c r="C164" s="0">
+        <v>15</v>
+      </c>
+      <c r="D164" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cajas de conmutación de computadores</t>
+        </is>
+      </c>
+      <c r="E164" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Equipos informáticos y accesorios / Accesorios de computador</t>
+        </is>
+      </c>
+      <c r="F164" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G164" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidad</t>
+        </is>
+      </c>
+      <c r="H164" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Licencia para el funcionamiento del equipo de protección de enlaces de red frente a ataques DDoS y amenazas avanzadas. /Control de Acceso</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">1259850-4-LP26</t>
         </is>
       </c>
-      <c r="B163" s="4" t="inlineStr">
+      <c r="B165" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">GORE COMPRA DE EQUIPOS INFORMATICOS</t>
         </is>
       </c>
-      <c r="C163" s="0">
+      <c r="C165" s="0">
         <v>1</v>
       </c>
-      <c r="D163" s="4" t="inlineStr">
+      <c r="D165" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Computadores de escritorio</t>
         </is>
       </c>
-      <c r="E163" s="4" t="inlineStr">
+      <c r="E165" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Equipos informáticos y accesorios / Computadores</t>
         </is>
       </c>
-      <c r="F163" s="0">
+      <c r="F165" s="0">
         <v>66.0</v>
       </c>
-      <c r="G163" s="0" t="inlineStr">
+      <c r="G165" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Unidad</t>
         </is>
       </c>
-      <c r="H163" s="4" t="inlineStr">
+      <c r="H165" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">EQUIPOS INFORMATICOS INTEL CORE I7.
 SE ADJUNTA BASES DE LICITACION.</t>
         </is>
       </c>
     </row>
-    <row r="164">
-      <c r="A164" s="0" t="inlineStr">
+    <row r="166">
+      <c r="A166" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">1259850-4-LP26</t>
         </is>
       </c>
-      <c r="B164" s="4" t="inlineStr">
+      <c r="B166" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">GORE COMPRA DE EQUIPOS INFORMATICOS</t>
         </is>
       </c>
-      <c r="C164" s="0">
+      <c r="C166" s="0">
         <v>2</v>
       </c>
-      <c r="D164" s="4" t="inlineStr">
+      <c r="D166" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Impresoras multifunción o multifuncionales</t>
         </is>
       </c>
-      <c r="E164" s="4" t="inlineStr">
+      <c r="E166" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Equipos informáticos y accesorios / Impresoras</t>
         </is>
       </c>
-      <c r="F164" s="0">
+      <c r="F166" s="0">
         <v>15.0</v>
       </c>
-      <c r="G164" s="0" t="inlineStr">
+      <c r="G166" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Unidad</t>
         </is>
       </c>
-      <c r="H164" s="4" t="inlineStr">
+      <c r="H166" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">IMPRESORA MULTIFUNCIONAL.
 SE ADJUNTA BASES DE LICITACION.</t>
         </is>
       </c>
     </row>
-    <row r="165">
-      <c r="A165" s="0" t="inlineStr">
+    <row r="167">
+      <c r="A167" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">1259850-4-LP26</t>
         </is>
       </c>
-      <c r="B165" s="4" t="inlineStr">
+      <c r="B167" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">GORE COMPRA DE EQUIPOS INFORMATICOS</t>
         </is>
       </c>
-      <c r="C165" s="0">
+      <c r="C167" s="0">
         <v>3</v>
       </c>
-      <c r="D165" s="4" t="inlineStr">
+      <c r="D167" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Escáner</t>
         </is>
       </c>
-      <c r="E165" s="4" t="inlineStr">
+      <c r="E167" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Equipos informáticos y accesorios / Dispositivos informáticos de entrada de datos</t>
         </is>
       </c>
-      <c r="F165" s="0">
+      <c r="F167" s="0">
         <v>4.0</v>
       </c>
-      <c r="G165" s="0" t="inlineStr">
+      <c r="G167" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Unidad</t>
         </is>
       </c>
-      <c r="H165" s="4" t="inlineStr">
+      <c r="H167" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">ESCANER DE ALTO RENDIMIENTO.
 SE ADJUNTA ESPECIFICACIONES TECNICAS.</t>
         </is>
       </c>
     </row>
-    <row r="166">
-      <c r="A166" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2069-141-LR26</t>
-        </is>
-      </c>
-      <c r="B166" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CGM ADQ. TORRE DE ENDOSCOPIA DIGESTIVA CON IA</t>
-        </is>
-      </c>
-      <c r="C166" s="0">
-        <v>1</v>
-      </c>
-      <c r="D166" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Equipo endoscópico o carritos de procedimiento o accesorios</t>
-        </is>
-      </c>
-      <c r="E166" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Equipamiento y suministros médicos / Productos quirúrgicos / Equipo endoscópico, accesorios y productos relacionados</t>
-        </is>
-      </c>
-      <c r="F166" s="0">
-        <v>2.0</v>
-      </c>
-      <c r="G166" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Unidad</t>
-        </is>
-      </c>
-      <c r="H166" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TORRE DE ENDOSCOPIA DIGESTIVA CON INTELIGENCIA ARTIFICIAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1562-49-LR26</t>
-        </is>
-      </c>
-      <c r="B167" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Sistema de monitoreo integral de ciberseguridad</t>
-        </is>
-      </c>
-      <c r="C167" s="0">
-        <v>1</v>
-      </c>
-      <c r="D167" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Equipo de seguridad de evaluación de vulnerabilidad</t>
-        </is>
-      </c>
-      <c r="E167" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Equipos, plataformas y accesorios de redes multimedia, voz y datos / Equipos de seguridad de red</t>
-        </is>
-      </c>
-      <c r="F167" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="G167" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Unidad</t>
-        </is>
-      </c>
-      <c r="H167" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">El Servicio Nacional de Geología y Minería (SERNAGEOMIN) requiere contratar un Servicio de Monitoreo integral de ciberseguridad que incluye suscripciones de software, implementación, capacitación, soporte y operación continua, orientado a fortalecer su po</t>
-        </is>
-      </c>
-    </row>
     <row r="168">
       <c r="A168" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">586-52-LP26</t>
+          <t xml:space="preserve">2069-141-LR26</t>
         </is>
       </c>
       <c r="B168" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adquisición de licencias de software Redhat</t>
+          <t xml:space="preserve">CGM ADQ. TORRE DE ENDOSCOPIA DIGESTIVA CON IA</t>
         </is>
       </c>
       <c r="C168" s="0">
@@ -16931,16 +17839,16 @@
       </c>
       <c r="D168" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Software de gestión de licencias</t>
+          <t xml:space="preserve">Equipo endoscópico o carritos de procedimiento o accesorios</t>
         </is>
       </c>
       <c r="E168" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de gestión</t>
+          <t xml:space="preserve">Equipamiento y suministros médicos / Productos quirúrgicos / Equipo endoscópico, accesorios y productos relacionados</t>
         </is>
       </c>
       <c r="F168" s="0">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G168" s="0" t="inlineStr">
         <is>
@@ -16949,19 +17857,19 @@
       </c>
       <c r="H168" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adquisición de suscripciones de licencias de software Redhat, conforme a bases de licitación</t>
+          <t xml:space="preserve">TORRE DE ENDOSCOPIA DIGESTIVA CON INTELIGENCIA ARTIFICIAL</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">3084-31-LE26</t>
+          <t xml:space="preserve">1562-49-LR26</t>
         </is>
       </c>
       <c r="B169" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">SERVICIO REPARACIÓN DE OFICINAS PARA LA DIRECCIÓN DE TELECOMUNICACIONES E INFORMÁTICA DE LA ARMADA.</t>
+          <t xml:space="preserve">Sistema de monitoreo integral de ciberseguridad</t>
         </is>
       </c>
       <c r="C169" s="0">
@@ -16969,12 +17877,12 @@
       </c>
       <c r="D169" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mano de obra temporal</t>
+          <t xml:space="preserve">Equipo de seguridad de evaluación de vulnerabilidad</t>
         </is>
       </c>
       <c r="E169" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Servicios profesionales, administrativos y consultorías de gestión empresarial / Servicios de recursos humanos / Servicios de personal temporal</t>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Equipos, plataformas y accesorios de redes multimedia, voz y datos / Equipos de seguridad de red</t>
         </is>
       </c>
       <c r="F169" s="0">
@@ -16987,19 +17895,19 @@
       </c>
       <c r="H169" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contratación del Servicio de Reparación de Oficinas, de acuerdo a Especificaciones Técnicas.</t>
+          <t xml:space="preserve">El Servicio Nacional de Geología y Minería (SERNAGEOMIN) requiere contratar un Servicio de Monitoreo integral de ciberseguridad que incluye suscripciones de software, implementación, capacitación, soporte y operación continua, orientado a fortalecer su po</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2200-23-LR26</t>
+          <t xml:space="preserve">586-52-LP26</t>
         </is>
       </c>
       <c r="B170" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">SERVICIO DE ARRIENDO DE SOFTWARE DE REGISTRO CLÍNICO ELECTRÓNICO RCE ATENCIÓN PRIMARIA - TIC</t>
+          <t xml:space="preserve">Adquisición de licencias de software Redhat</t>
         </is>
       </c>
       <c r="C170" s="0">
@@ -17007,16 +17915,16 @@
       </c>
       <c r="D170" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Desarrolladores de software</t>
+          <t xml:space="preserve">Software de gestión de licencias</t>
         </is>
       </c>
       <c r="E170" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Servicios profesionales, administrativos y consultorías de gestión empresarial / Servicios de recursos humanos / Contratación de personal</t>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de gestión</t>
         </is>
       </c>
       <c r="F170" s="0">
-        <v>1700.0</v>
+        <v>1.0</v>
       </c>
       <c r="G170" s="0" t="inlineStr">
         <is>
@@ -17025,19 +17933,19 @@
       </c>
       <c r="H170" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">SERVICIO DE ARRIENDO DE SOFTWARE DE REGISTRO CLÍNICO ELECTRÓNICO (RCE) ATENCIÓN PRIMARIA - TIC, SE ADJUNTA ESPECIFICACIONES TÉCNICAS, ANEXOS</t>
+          <t xml:space="preserve">Adquisición de suscripciones de licencias de software Redhat, conforme a bases de licitación</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1973-93-LR26</t>
+          <t xml:space="preserve">3084-31-LE26</t>
         </is>
       </c>
       <c r="B171" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">SISTEMA DE INFORMACIÓN DE GESTIÓN ADMINISTRATIVA Y FARMACIA</t>
+          <t xml:space="preserve">SERVICIO REPARACIÓN DE OFICINAS PARA LA DIRECCIÓN DE TELECOMUNICACIONES E INFORMÁTICA DE LA ARMADA.</t>
         </is>
       </c>
       <c r="C171" s="0">
@@ -17045,12 +17953,12 @@
       </c>
       <c r="D171" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Software de planificación de recursos empresariales (ERP)</t>
+          <t xml:space="preserve">Mano de obra temporal</t>
         </is>
       </c>
       <c r="E171" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de planificación de recursos empresariales (ERP) y contabilidad financiera</t>
+          <t xml:space="preserve">Servicios profesionales, administrativos y consultorías de gestión empresarial / Servicios de recursos humanos / Servicios de personal temporal</t>
         </is>
       </c>
       <c r="F171" s="0">
@@ -17058,24 +17966,24 @@
       </c>
       <c r="G171" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Global</t>
+          <t xml:space="preserve">Unidad</t>
         </is>
       </c>
       <c r="H171" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">TOTAL PROYECTO (Parametrización, implementación y puesta en marcha  / Arriendo, operación, soporte y mantenimiento por el período de 60 meses)</t>
+          <t xml:space="preserve">Contratación del Servicio de Reparación de Oficinas, de acuerdo a Especificaciones Técnicas.</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2239-2-LR26</t>
+          <t xml:space="preserve">837-101-LP26</t>
         </is>
       </c>
       <c r="B172" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convenio Marco Desarrollo de software</t>
+          <t xml:space="preserve">CDP 477 SERVICIO DE OPERACIÓN SISTEMA DE CONTROL CENTRALIZADO BMS Y SISTEMA DE TELEVIGILANCIA SOFTWARE HIKCENTRAL PROFESSIONAL DE EDIFICIO INSTITUCIONAL SML SANTIAGO</t>
         </is>
       </c>
       <c r="C172" s="0">
@@ -17083,75 +17991,75 @@
       </c>
       <c r="D172" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Desarrolladores de software</t>
+          <t xml:space="preserve">Software de administración</t>
         </is>
       </c>
       <c r="E172" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Servicios profesionales, administrativos y consultorías de gestión empresarial / Servicios de recursos humanos / Contratación de personal</t>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de administración de redes</t>
         </is>
       </c>
       <c r="F172" s="0">
-        <v>1.0</v>
+        <v>12.0</v>
       </c>
       <c r="G172" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unidad</t>
+          <t xml:space="preserve">Mes</t>
         </is>
       </c>
       <c r="H172" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convenio Marco para la adquisición de los Servicios de Desarrollo y Mantención de Software, Servicios Profesionales TI y Cloud Computing</t>
+          <t xml:space="preserve">SERVICIO DE OPERACIÓN PARA EL SISTEMA DE CONTROL CENTRALIZADO (BMS) SOFTWARE ENTELIWEB</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1607-13-LR26</t>
+          <t xml:space="preserve">837-101-LP26</t>
         </is>
       </c>
       <c r="B173" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">servicio SD-WAN LAN telefonía en la nube y enlaces</t>
+          <t xml:space="preserve">CDP 477 SERVICIO DE OPERACIÓN SISTEMA DE CONTROL CENTRALIZADO BMS Y SISTEMA DE TELEVIGILANCIA SOFTWARE HIKCENTRAL PROFESSIONAL DE EDIFICIO INSTITUCIONAL SML SANTIAGO</t>
         </is>
       </c>
       <c r="C173" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D173" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Diseño de redes de comunicación de cobertura amplia (WAN)</t>
+          <t xml:space="preserve">Sistemas de control de acceso o de seguridad</t>
         </is>
       </c>
       <c r="E173" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Servicios basados en ingeniería, ciencias sociales y tecnología de la información / Servicios informáticos / Sistemas de información</t>
+          <t xml:space="preserve">Equipos y suministros de defensa, orden público, protección y seguridad / Seguridad, vigilancia y detección / Equipo de vigilancia y detección</t>
         </is>
       </c>
       <c r="F173" s="0">
-        <v>1.0</v>
+        <v>12.0</v>
       </c>
       <c r="G173" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unidad</t>
+          <t xml:space="preserve">Mes</t>
         </is>
       </c>
       <c r="H173" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">servicios SD-WAN, LAN, telefonía en la nube y enlaces internet para la Superintendencia de Seguridad Social.</t>
+          <t xml:space="preserve">SERVICIO DE OPERACIÓN PARA EL SISTEMA DE TELEVIGILANCIA SOFTWARE HIKCENTRAL PROFESSIONAL</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">548874-72-LR26</t>
+          <t xml:space="preserve">2200-23-LR26</t>
         </is>
       </c>
       <c r="B174" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">SERV. DE ADMINISTRACION PLATAFORMAS TECNOLOGICAS</t>
+          <t xml:space="preserve">SERVICIO DE ARRIENDO DE SOFTWARE DE REGISTRO CLÍNICO ELECTRÓNICO RCE ATENCIÓN PRIMARIA - TIC</t>
         </is>
       </c>
       <c r="C174" s="0">
@@ -17159,23 +18067,213 @@
       </c>
       <c r="D174" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">Desarrolladores de software</t>
+        </is>
+      </c>
+      <c r="E174" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Servicios profesionales, administrativos y consultorías de gestión empresarial / Servicios de recursos humanos / Contratación de personal</t>
+        </is>
+      </c>
+      <c r="F174" s="0">
+        <v>1700.0</v>
+      </c>
+      <c r="G174" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidad</t>
+        </is>
+      </c>
+      <c r="H174" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SERVICIO DE ARRIENDO DE SOFTWARE DE REGISTRO CLÍNICO ELECTRÓNICO (RCE) ATENCIÓN PRIMARIA - TIC, SE ADJUNTA ESPECIFICACIONES TÉCNICAS, ANEXOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1973-93-LR26</t>
+        </is>
+      </c>
+      <c r="B175" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SISTEMA DE INFORMACIÓN DE GESTIÓN ADMINISTRATIVA Y FARMACIA</t>
+        </is>
+      </c>
+      <c r="C175" s="0">
+        <v>1</v>
+      </c>
+      <c r="D175" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Software de planificación de recursos empresariales (ERP)</t>
+        </is>
+      </c>
+      <c r="E175" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de planificación de recursos empresariales (ERP) y contabilidad financiera</t>
+        </is>
+      </c>
+      <c r="F175" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G175" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Global</t>
+        </is>
+      </c>
+      <c r="H175" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TOTAL PROYECTO (Parametrización, implementación y puesta en marcha  / Arriendo, operación, soporte y mantenimiento por el período de 60 meses)</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2239-2-LR26</t>
+        </is>
+      </c>
+      <c r="B176" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Convenio Marco Desarrollo de software</t>
+        </is>
+      </c>
+      <c r="C176" s="0">
+        <v>1</v>
+      </c>
+      <c r="D176" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Desarrolladores de software</t>
+        </is>
+      </c>
+      <c r="E176" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Servicios profesionales, administrativos y consultorías de gestión empresarial / Servicios de recursos humanos / Contratación de personal</t>
+        </is>
+      </c>
+      <c r="F176" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G176" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidad</t>
+        </is>
+      </c>
+      <c r="H176" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Convenio Marco para la adquisición de los Servicios de Desarrollo y Mantención de Software, Servicios Profesionales TI y Cloud Computing</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1607-13-LR26</t>
+        </is>
+      </c>
+      <c r="B177" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">servicio SD-WAN LAN telefonía en la nube y enlaces</t>
+        </is>
+      </c>
+      <c r="C177" s="0">
+        <v>1</v>
+      </c>
+      <c r="D177" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Diseño de redes de comunicación de cobertura amplia (WAN)</t>
+        </is>
+      </c>
+      <c r="E177" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Servicios basados en ingeniería, ciencias sociales y tecnología de la información / Servicios informáticos / Sistemas de información</t>
+        </is>
+      </c>
+      <c r="F177" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G177" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidad</t>
+        </is>
+      </c>
+      <c r="H177" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">servicios SD-WAN, LAN, telefonía en la nube y enlaces internet para la Superintendencia de Seguridad Social.</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1274285-45-LP26</t>
+        </is>
+      </c>
+      <c r="B178" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Software de gestión Droguería Comunal</t>
+        </is>
+      </c>
+      <c r="C178" s="0">
+        <v>1</v>
+      </c>
+      <c r="D178" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Software de cadena de suministro y logística de planificación de requisitos de materiales</t>
+        </is>
+      </c>
+      <c r="E178" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de gestión</t>
+        </is>
+      </c>
+      <c r="F178" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G178" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidad</t>
+        </is>
+      </c>
+      <c r="H178" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Software de cadena de suministro para droguería comunal y centros de salud de la corporación municipal de salud de San Bernardo, para las siguientes áreas: recepción, Almacenamiento, Despacho, Inventario y Reportes de gestión</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">548874-72-LR26</t>
+        </is>
+      </c>
+      <c r="B179" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SERV. DE ADMINISTRACION PLATAFORMAS TECNOLOGICAS</t>
+        </is>
+      </c>
+      <c r="C179" s="0">
+        <v>1</v>
+      </c>
+      <c r="D179" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">Software del sistema de administración de bases de datos</t>
         </is>
       </c>
-      <c r="E174" s="4" t="inlineStr">
+      <c r="E179" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de consultas y gestión de datos</t>
         </is>
       </c>
-      <c r="F174" s="0">
+      <c r="F179" s="0">
         <v>1.0</v>
       </c>
-      <c r="G174" s="0" t="inlineStr">
+      <c r="G179" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Global</t>
         </is>
       </c>
-      <c r="H174" s="4" t="inlineStr">
+      <c r="H179" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">SERVICIO DE
 ADMINISTRACION,
@@ -17189,83 +18287,121 @@
         </is>
       </c>
     </row>
-    <row r="175">
-      <c r="A175" s="0" t="inlineStr">
+    <row r="180">
+      <c r="A180" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">548874-74-LR26</t>
         </is>
       </c>
-      <c r="B175" s="4" t="inlineStr">
+      <c r="B180" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">SERV DE PLATAFORMA SIEM NUEVA GENERACIÓN SAAS IPS</t>
         </is>
       </c>
-      <c r="C175" s="0">
+      <c r="C180" s="0">
         <v>1</v>
       </c>
-      <c r="D175" s="4" t="inlineStr">
+      <c r="D180" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Software de protección antivirus y de seguridad de transacciones</t>
         </is>
       </c>
-      <c r="E175" s="4" t="inlineStr">
+      <c r="E180" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de seguridad y protección</t>
         </is>
       </c>
-      <c r="F175" s="0">
+      <c r="F180" s="0">
         <v>1.0</v>
       </c>
-      <c r="G175" s="0" t="inlineStr">
+      <c r="G180" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Global</t>
         </is>
       </c>
-      <c r="H175" s="4" t="inlineStr">
+      <c r="H180" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">SERVICIO DE PLATAFORMA SIEM DE NUEVA GENERACIÓN EN MODALIDAD SAAS PARA EL INSTITUTO DE PREVISIÓN SOCIAL</t>
         </is>
       </c>
     </row>
-    <row r="176">
-      <c r="A176" s="0" t="inlineStr">
+    <row r="181">
+      <c r="A181" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">976-15-O126</t>
+        </is>
+      </c>
+      <c r="B181" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ampliación Plataformas Comercial y General Ad. El Loa</t>
+        </is>
+      </c>
+      <c r="C181" s="0">
+        <v>1</v>
+      </c>
+      <c r="D181" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Licitación Pública de Obra</t>
+        </is>
+      </c>
+      <c r="E181" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Consultoria / Consultoria / Planificación y Factibilidad</t>
+        </is>
+      </c>
+      <c r="F181" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G181" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidad</t>
+        </is>
+      </c>
+      <c r="H181" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Licitación Pública de Obra</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">1969-34-LS19</t>
         </is>
       </c>
-      <c r="B176" s="4" t="inlineStr">
+      <c r="B182" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">AUTOMATIZACIÓN PORTÓN ACCESO A LINEA DE FUEGO</t>
         </is>
       </c>
-      <c r="C176" s="0">
+      <c r="C182" s="0">
         <v>1</v>
       </c>
-      <c r="D176" s="4" t="inlineStr">
+      <c r="D182" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Puertas de metal</t>
         </is>
       </c>
-      <c r="E176" s="4" t="inlineStr">
+      <c r="E182" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Artículos para estructuras, obras y construcciones / Puertas, ventanas y vidrios / Puertas</t>
         </is>
       </c>
-      <c r="F176" s="0">
+      <c r="F182" s="0">
         <v>1.0</v>
       </c>
-      <c r="G176" s="0" t="inlineStr">
+      <c r="G182" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Unidad</t>
         </is>
       </c>
-      <c r="H176" s="4" t="inlineStr">
+      <c r="H182" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">AUTOMATIZACIÓN DE PORTÓN ACCESO A LINEA DE FUEGO C.P. CONCEPCIÓN</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H176"/>
+  <autoFilter ref="A1:H182"/>
 </worksheet>
 </file>
--- a/web/descargas/licitaciones.xlsx
+++ b/web/descargas/licitaciones.xlsx
@@ -222,12 +222,12 @@
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">564162-115-L126</t>
+          <t xml:space="preserve">2422-149-L126</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Solicitud N°92870 - Bolsas, etiquetas y cajas con impresión digital - CC112 / PS1772</t>
+          <t xml:space="preserve">SOL. 945841, SERVISIO DE FABRICACION E INSTALACION DE TABLERO PARA BALNEARIO</t>
         </is>
       </c>
       <c r="C2" s="0" t="inlineStr">
@@ -237,12 +237,12 @@
       </c>
       <c r="D2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">UNIVERSIDAD DE SANTIAGO DE CHILE</t>
+          <t xml:space="preserve">I MUNICIPALIDAD DE PUENTE ALTO</t>
         </is>
       </c>
       <c r="E2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">VICERRECTORIA DE INVESTIGACION Y DESARROLLO</t>
+          <t xml:space="preserve">I MUNICIPALIDAD DE PUENTE ALTO</t>
         </is>
       </c>
       <c r="F2" s="0" t="inlineStr">
@@ -252,20 +252,20 @@
       </c>
       <c r="G2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Estación Central</t>
+          <t xml:space="preserve">Puente Alto</t>
         </is>
       </c>
       <c r="H2" s="2">
-        <v>46265.7214</v>
+        <v>46265.753669</v>
       </c>
       <c r="I2" s="2">
-        <v>46272.625</v>
+        <v>46272.65</v>
       </c>
       <c r="J2" s="0">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K2" s="3">
-        <v>5210000.0</v>
+        <v>4000000.0</v>
       </c>
       <c r="L2" s="0" t="inlineStr">
         <is>
@@ -279,12 +279,12 @@
       </c>
       <c r="N2" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Equipamiento para manejo y estiba de materiales / Materiales para envasado / Cajas, bolsas y sacos para envasado, Productos de papel / Productos de papel / Papel fantasía, Productos impresos y publicaciones / Etiquetado y accesorios / Etiquetas</t>
+          <t xml:space="preserve">Servicios de producción y fabricación industrial / Fabricación de maquinarias y equipos de transporte / Fabricación de maquinarias</t>
         </is>
       </c>
       <c r="O2" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 Unidad · Cajas para empaquetado · 1 Unidad · Cajas para empaquetado · 1 Unidad · Papel, bolsas o cajas de regalo · y 2 más</t>
+          <t xml:space="preserve">1 Kit · Servicios de fabricación de calderas para central eléctrica</t>
         </is>
       </c>
       <c r="P2" s="2"/>
@@ -299,846 +299,15 @@
       <c r="U2" s="0"/>
       <c r="V2" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">La Universidad de Santiago de chile requiere la compra de bolsas, etiquetas y cajas con impresión digital según especificaciones técnicas.</t>
+          <t xml:space="preserve">NECESIDAD DE SERVICIO, PARA ACONDICIONAMIENTO DE AMBIENTE DE LA PISCINA TEMPERADA BALNEARIO MUNICIPAL, SE REQUIERE SERVICIO DE FABRICACION, INSTALACION Y PUESTA EN MARCHA DE TABLERO DE FUERZA Y COMANDO DE MOTOR TRIFASICO.</t>
         </is>
       </c>
       <c r="W2" s="5" t="str">
-        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=564162-115-L126","descargar bases")</f>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">932-22-L126</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SERVICIO DE REPARACIÓN DE LUMINARIAS, INSTALACIONES ELECTRICAS Y NORMALIZACIÓN DE TABLERO ELECTRONICO DEL COMPLEJO DEPORTIVO HERMOGENES LIZANA, DEL INSTITUTO NACIONAL DE DEPORTES DE O¨HIGGINS.</t>
-        </is>
-      </c>
-      <c r="C3" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Publicada</t>
-        </is>
-      </c>
-      <c r="D3" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
-        </is>
-      </c>
-      <c r="E3" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">I.N.D. REGION VI</t>
-        </is>
-      </c>
-      <c r="F3" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Región del Libertador General Bernardo O´Higgins</t>
-        </is>
-      </c>
-      <c r="G3" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Rancagua</t>
-        </is>
-      </c>
-      <c r="H3" s="2">
-        <v>46265.704213</v>
-      </c>
-      <c r="I3" s="2">
-        <v>46272.666667</v>
-      </c>
-      <c r="J3" s="0">
-        <v>7</v>
-      </c>
-      <c r="K3" s="3">
-        <v>5200000.0</v>
-      </c>
-      <c r="L3" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CLP</t>
-        </is>
-      </c>
-      <c r="M3" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">L1</t>
-        </is>
-      </c>
-      <c r="N3" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Servicios de producción y fabricación industrial / Servicios de apoyo o soporte a la fabricación / Servicios de mantenimiento y reparación de equipo de fabricación</t>
-        </is>
-      </c>
-      <c r="O3" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1 Unidad · Servicio de reparación de equipo de fabricación</t>
-        </is>
-      </c>
-      <c r="P3" s="2"/>
-      <c r="Q3" s="2"/>
-      <c r="R3" s="0"/>
-      <c r="S3" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">No</t>
-        </is>
-      </c>
-      <c r="T3" s="4"/>
-      <c r="U3" s="0"/>
-      <c r="V3" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">EL IND DE RANCAGUA,  REQUIERE CONTRATAR  EL "SERVICIO DE REPARACIÓN DE LUMINARIAS, INSTALACIONES ELECTRICAS Y NORMALIZACIÓN DE TABLERO ELECTRONICO DEL COMPLEJO DEPORTIVO HERMOGENES LIZANA, DEL INSTITUTO NACIONAL DE DEPORTES DE O¨HIGGINS",  mediante un proceso de Licitación Publica, siendo necesario, aprobar,  previamente, las Bases Administrativas, Técnicas y Anexos que regulan dicho proceso de contratación.</t>
-        </is>
-      </c>
-      <c r="W3" s="5" t="str">
-        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=932-22-L126","descargar bases")</f>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2448-122-L126</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ADQ. BOLSA DE CREDITOS DE CONSUMO EN NUBE PUBLICA</t>
-        </is>
-      </c>
-      <c r="C4" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Publicada</t>
-        </is>
-      </c>
-      <c r="D4" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">I MUNICIPALIDAD DE COQUIMBO</t>
-        </is>
-      </c>
-      <c r="E4" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Departamento de Salud</t>
-        </is>
-      </c>
-      <c r="F4" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
-        </is>
-      </c>
-      <c r="G4" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Coquimbo</t>
-        </is>
-      </c>
-      <c r="H4" s="2">
-        <v>46265.640903</v>
-      </c>
-      <c r="I4" s="2">
-        <v>46273.625</v>
-      </c>
-      <c r="J4" s="0">
-        <v>8</v>
-      </c>
-      <c r="K4" s="3">
-        <v>3000000.0</v>
-      </c>
-      <c r="L4" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CLP</t>
-        </is>
-      </c>
-      <c r="M4" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">L1</t>
-        </is>
-      </c>
-      <c r="N4" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de consultas y gestión de datos</t>
-        </is>
-      </c>
-      <c r="O4" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1 Año · Software del sistema de administración de bases de datos</t>
-        </is>
-      </c>
-      <c r="P4" s="2"/>
-      <c r="Q4" s="2"/>
-      <c r="R4" s="0"/>
-      <c r="S4" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">No</t>
-        </is>
-      </c>
-      <c r="T4" s="4"/>
-      <c r="U4" s="0"/>
-      <c r="V4" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">El objetivo de esta contratación es adquirir una bolsa de créditos de consumo en nube pública para fortalecer la resiliencia institucional mediante un Plan de Recuperación ante Desastres (DRP). 
-De acuerdo a nuestra estrategia DevSecOps, esta infraestructura externa nos permitirá garantizar el Uptime de servicios críticos (CENDRIS, APSGO) frente a eventuales caídas de nuestro Datacenter local. Adicionalmente, posibilitará el almacenamiento seguro de respaldos fuera del sitio y brindará un entor</t>
-        </is>
-      </c>
-      <c r="W4" s="5" t="str">
-        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=2448-122-L126","descargar bases")</f>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">520149-35-L126</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SERVICIO DE INSTALACIÓN, TRASLADO Y REPARACIÓN DE PUNTOS DE DATOS, PARA LOS EDIFICIOS JOSÉ MIGUEL CARRERA Y SEDE DE LA ACADEMIA DIPLOMÁTICA BAJO LA MODALIDAD DE CONTRATO DE SUMINISTRO.</t>
-        </is>
-      </c>
-      <c r="C5" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Publicada</t>
-        </is>
-      </c>
-      <c r="D5" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SUBSECRETARIA DE RELACIONES EXTERIORES</t>
-        </is>
-      </c>
-      <c r="E5" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DICOMPRAS</t>
-        </is>
-      </c>
-      <c r="F5" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Región Metropolitana de Santiago</t>
-        </is>
-      </c>
-      <c r="G5" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Santiago</t>
-        </is>
-      </c>
-      <c r="H5" s="2">
-        <v>46265.729988</v>
-      </c>
-      <c r="I5" s="2">
-        <v>46273.666667</v>
-      </c>
-      <c r="J5" s="0">
-        <v>8</v>
-      </c>
-      <c r="K5" s="3">
-        <v>5000000.0</v>
-      </c>
-      <c r="L5" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CLP</t>
-        </is>
-      </c>
-      <c r="M5" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">L1</t>
-        </is>
-      </c>
-      <c r="N5" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Componentes para tecnología de la información, difusión o telecomunicaciones / Subconjuntos para dispositivos electrónicos</t>
-        </is>
-      </c>
-      <c r="O5" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1 Unidad · Conjuntos de cableado</t>
-        </is>
-      </c>
-      <c r="P5" s="2"/>
-      <c r="Q5" s="2"/>
-      <c r="R5" s="0"/>
-      <c r="S5" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">No</t>
-        </is>
-      </c>
-      <c r="T5" s="4"/>
-      <c r="U5" s="0"/>
-      <c r="V5" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SERVICIO DE INSTALACIÓN, TRASLADO Y REPARACIÓN DE PUNTOS DE DATOS, PARA LOS EDIFICIOS JOSÉ MIGUEL CARRERA Y SEDE DE LA ACADEMIA DIPLOMÁTICA BAJO LA MODALIDAD DE CONTRATO DE SUMINISTRO.</t>
-        </is>
-      </c>
-      <c r="W5" s="5" t="str">
-        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=520149-35-L126","descargar bases")</f>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2793-121-LE26</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LICENCIAS DE SOFTWARE</t>
-        </is>
-      </c>
-      <c r="C6" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Publicada</t>
-        </is>
-      </c>
-      <c r="D6" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Municipalidad de Huechuraba</t>
-        </is>
-      </c>
-      <c r="E6" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Municipalidad de Huechuraba</t>
-        </is>
-      </c>
-      <c r="F6" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Región Metropolitana de Santiago</t>
-        </is>
-      </c>
-      <c r="G6" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Huechuraba</t>
-        </is>
-      </c>
-      <c r="H6" s="2">
-        <v>46265.69294</v>
-      </c>
-      <c r="I6" s="2">
-        <v>46274.375</v>
-      </c>
-      <c r="J6" s="0">
-        <v>9</v>
-      </c>
-      <c r="K6" s="3"/>
-      <c r="L6" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CLP</t>
-        </is>
-      </c>
-      <c r="M6" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LE</t>
-        </is>
-      </c>
-      <c r="N6" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de gestión</t>
-        </is>
-      </c>
-      <c r="O6" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1 Unidad · Software de gestión de licencias</t>
-        </is>
-      </c>
-      <c r="P6" s="2"/>
-      <c r="Q6" s="2"/>
-      <c r="R6" s="0"/>
-      <c r="S6" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">No</t>
-        </is>
-      </c>
-      <c r="T6" s="4"/>
-      <c r="U6" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ASESORIA JURIDICA</t>
-        </is>
-      </c>
-      <c r="V6" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LA MUNICIPALIDAD DE HUECHURABA REQUIERE LA ADQUISICIÓN DE LICENCIAS DE SOFTWARE LECTOR, MODIFICADOR Y CREADOR DE DOCUMENTOS PDF, SOLICITADA POR EL DEPARTAMENTO DE INFORMATICA, SEGÚN LO INDICADO EN DOCUMENTACIÓN ADJUNTA.</t>
-        </is>
-      </c>
-      <c r="W6" s="5" t="str">
-        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=2793-121-LE26","descargar bases")</f>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5586-128-LE26</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BR CONTRATACIÓN DE PLATAFORMA TECNOLÓGICA TIPO SAAS DE GESTIÓN DIGITAL</t>
-        </is>
-      </c>
-      <c r="C7" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Publicada</t>
-        </is>
-      </c>
-      <c r="D7" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UNIVERSIDAD DE LA FRONTERA</t>
-        </is>
-      </c>
-      <c r="E7" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Universidad de la Frontera</t>
-        </is>
-      </c>
-      <c r="F7" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
-        </is>
-      </c>
-      <c r="G7" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Temuco</t>
-        </is>
-      </c>
-      <c r="H7" s="2">
-        <v>46265.697917</v>
-      </c>
-      <c r="I7" s="2">
-        <v>46276.416667</v>
-      </c>
-      <c r="J7" s="0">
-        <v>11</v>
-      </c>
-      <c r="K7" s="3">
-        <v>13000000.0</v>
-      </c>
-      <c r="L7" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CLP</t>
-        </is>
-      </c>
-      <c r="M7" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LE</t>
-        </is>
-      </c>
-      <c r="N7" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de administración de redes</t>
-        </is>
-      </c>
-      <c r="O7" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1 Global · Software de administración</t>
-        </is>
-      </c>
-      <c r="P7" s="2"/>
-      <c r="Q7" s="2"/>
-      <c r="R7" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18 meses</t>
-        </is>
-      </c>
-      <c r="S7" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">No</t>
-        </is>
-      </c>
-      <c r="T7" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Lo anterior de acuerdo a lo
-indicado en el Art. 128 del Reglamento de Compras públicas.</t>
-        </is>
-      </c>
-      <c r="U7" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FERNANDO GONZALEZ</t>
-        </is>
-      </c>
-      <c r="V7" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CONTRATACIÓN DE PLATAFORMA TECNOLÓGICA TIPO SAAS DE GESTIÓN DIGITAL, DE ACUERDO A REQUERIMIENTO ADJUNTO</t>
-        </is>
-      </c>
-      <c r="W7" s="5" t="str">
-        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=5586-128-LE26","descargar bases")</f>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29-73-LE26</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ALR - ADQ. REPUESTOS Y TABLERO ELECT.   GPO. ELECT</t>
-        </is>
-      </c>
-      <c r="C8" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Publicada</t>
-        </is>
-      </c>
-      <c r="D8" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
-        </is>
-      </c>
-      <c r="E8" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Comando Logístico</t>
-        </is>
-      </c>
-      <c r="F8" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Región Metropolitana de Santiago</t>
-        </is>
-      </c>
-      <c r="G8" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">El Bosque</t>
-        </is>
-      </c>
-      <c r="H8" s="2">
-        <v>46265.630394</v>
-      </c>
-      <c r="I8" s="2">
-        <v>46279.625694</v>
-      </c>
-      <c r="J8" s="0">
-        <v>14</v>
-      </c>
-      <c r="K8" s="3"/>
-      <c r="L8" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">USD</t>
-        </is>
-      </c>
-      <c r="M8" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LE</t>
-        </is>
-      </c>
-      <c r="N8" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Equipamiento para el acondicionamiento, distribución y filtrado de fluidos / Filtros y purificación industrial / Filtros, Maquinaria para generación y distribución de energía / Generación de energía / Equipo para control de producción de energía, Maquinaria para generación y distribución de energía / Transmisión de energía eléctrica, mecánica y cinética / Baterías, pilas y accesorios</t>
-        </is>
-      </c>
-      <c r="O8" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1 Unidad · Paneles de control eléctrico para generadores · 2 Unidad · Filtros de aceite · 2 Unidad · Filtros de combustible · y 9 más</t>
-        </is>
-      </c>
-      <c r="P8" s="2"/>
-      <c r="Q8" s="2"/>
-      <c r="R8" s="0"/>
-      <c r="S8" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">No</t>
-        </is>
-      </c>
-      <c r="T8" s="4"/>
-      <c r="U8" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SERGIO ROMEROCALQUIN</t>
-        </is>
-      </c>
-      <c r="V8" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ADQUISICIÓN DE REPUESTOS Y TABLERO CON INSTALACIÓN PARA GRUPOS ELECTRÓGENOS DE LA FUERZA AÉREA DE CHILE</t>
-        </is>
-      </c>
-      <c r="W8" s="5" t="str">
-        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=29-73-LE26","descargar bases")</f>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1020-46-LE26</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Adq. Sopor. y Actual. Software ServiceTonic MOP.</t>
-        </is>
-      </c>
-      <c r="C9" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Publicada</t>
-        </is>
-      </c>
-      <c r="D9" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
-        </is>
-      </c>
-      <c r="E9" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MOP Subsecretaría </t>
-        </is>
-      </c>
-      <c r="F9" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Región Metropolitana de Santiago</t>
-        </is>
-      </c>
-      <c r="G9" s="0"/>
-      <c r="H9" s="2">
-        <v>46265.634387</v>
-      </c>
-      <c r="I9" s="2">
-        <v>46281.625</v>
-      </c>
-      <c r="J9" s="0">
-        <v>16</v>
-      </c>
-      <c r="K9" s="3">
-        <v>22500000.0</v>
-      </c>
-      <c r="L9" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CLP</t>
-        </is>
-      </c>
-      <c r="M9" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LE</t>
-        </is>
-      </c>
-      <c r="N9" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de gestión</t>
-        </is>
-      </c>
-      <c r="O9" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">50 Unidad · Software de gestión de licencias</t>
-        </is>
-      </c>
-      <c r="P9" s="2"/>
-      <c r="Q9" s="2"/>
-      <c r="R9" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12 meses</t>
-        </is>
-      </c>
-      <c r="S9" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">No</t>
-        </is>
-      </c>
-      <c r="T9" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">No permite subcontratación El oferente adjudicado, no podrá subcontratar los servicios derivados de la ejecución del Contrato.</t>
-        </is>
-      </c>
-      <c r="U9" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Carmen Gloria Ponce</t>
-        </is>
-      </c>
-      <c r="V9" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">El objetivo de la Adquisición de Soporte y Actualizaciones Software ServiceTonic Licencias en modalidad On-Premise, usuarios nombrados, por 12 meses.</t>
-        </is>
-      </c>
-      <c r="W9" s="5" t="str">
-        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=1020-46-LE26","descargar bases")</f>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5531-4-B226</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Servicios de publicidad digital para el DII</t>
-        </is>
-      </c>
-      <c r="C10" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Publicada</t>
-        </is>
-      </c>
-      <c r="D10" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UNIVERSIDAD DE CHILE</t>
-        </is>
-      </c>
-      <c r="E10" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FCFM Departamento de Ingeniería Industrial</t>
-        </is>
-      </c>
-      <c r="F10" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Región Metropolitana de Santiago</t>
-        </is>
-      </c>
-      <c r="G10" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">San Joaquín</t>
-        </is>
-      </c>
-      <c r="H10" s="2">
-        <v>46265.698692</v>
-      </c>
-      <c r="I10" s="2">
-        <v>46286.666667</v>
-      </c>
-      <c r="J10" s="0">
-        <v>21</v>
-      </c>
-      <c r="K10" s="3"/>
-      <c r="L10" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CLP</t>
-        </is>
-      </c>
-      <c r="M10" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">B2</t>
-        </is>
-      </c>
-      <c r="N10" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Servicios editoriales, de diseño, publicidad, gráficos y artistas / Publicidad / Agencias de publicidad</t>
-        </is>
-      </c>
-      <c r="O10" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1 Unidad · Campañas publicitarias</t>
-        </is>
-      </c>
-      <c r="P10" s="2"/>
-      <c r="Q10" s="2"/>
-      <c r="R10" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">36 meses</t>
-        </is>
-      </c>
-      <c r="S10" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">No</t>
-        </is>
-      </c>
-      <c r="T10" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ver bases administrativas numeral 29 Subcontratación</t>
-        </is>
-      </c>
-      <c r="U10" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Karina Pérez</t>
-        </is>
-      </c>
-      <c r="V10" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Servicios de publicidad digital para el Departamento de Ingeniería Industrial de la Facultad de Ciencias Físicas y Matemáticas de la Universidad de Chile 2026, a prestarse por un periodo de 36 meses o hasta el agotamiento de los recursos según las características y especificaciones establecidas en las presentes bases administrativas, bases técnicas y anexos</t>
-        </is>
-      </c>
-      <c r="W10" s="5" t="str">
-        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=5531-4-B226","descargar bases")</f>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">548874-77-LR26</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MANTENCIÓN Y MEJORA SISTEMA CIBERSEGURIDAD NCH ISO</t>
-        </is>
-      </c>
-      <c r="C11" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Publicada</t>
-        </is>
-      </c>
-      <c r="D11" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">INSTITUTO DE PREVISION SOCIAL</t>
-        </is>
-      </c>
-      <c r="E11" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">IPS Oficina Central de Compras</t>
-        </is>
-      </c>
-      <c r="F11" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Región Metropolitana de Santiago</t>
-        </is>
-      </c>
-      <c r="G11" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Santiago</t>
-        </is>
-      </c>
-      <c r="H11" s="2">
-        <v>46265.660069</v>
-      </c>
-      <c r="I11" s="2">
-        <v>46301.625</v>
-      </c>
-      <c r="J11" s="0">
-        <v>36</v>
-      </c>
-      <c r="K11" s="3">
-        <v>11000.0</v>
-      </c>
-      <c r="L11" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CLF</t>
-        </is>
-      </c>
-      <c r="M11" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LR</t>
-        </is>
-      </c>
-      <c r="N11" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de seguridad y protección</t>
-        </is>
-      </c>
-      <c r="O11" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1 Global · Software de administración de red privada virtual (VPN) o de seguridad de red</t>
-        </is>
-      </c>
-      <c r="P11" s="2"/>
-      <c r="Q11" s="2"/>
-      <c r="R11" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24 meses</t>
-        </is>
-      </c>
-      <c r="S11" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">No</t>
-        </is>
-      </c>
-      <c r="T11" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ver bases punto 16</t>
-        </is>
-      </c>
-      <c r="U11" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">por definir</t>
-        </is>
-      </c>
-      <c r="V11" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">E1O2RT8 - SERVICIO DE MANTENCIÓN Y MEJORA DEL SISTEMA DE GESTIÓN DE SEGURIDAD DE LA INFORMACIÓN Y CIBERSEGURIDAD INSTITUCIONAL NCH ISOIEC 27001</t>
-        </is>
-      </c>
-      <c r="W11" s="5" t="str">
-        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=548874-77-LR26","descargar bases")</f>
+        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=2422-149-L126","descargar bases")</f>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:W11"/>
+  <autoFilter ref="A1:W2"/>
 </worksheet>
 </file>
 
@@ -1330,7 +499,7 @@
         <v>46265.666667</v>
       </c>
       <c r="J2" s="0">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K2" s="3">
         <v>4522419.0</v>
@@ -1417,7 +586,7 @@
         <v>46265.708333</v>
       </c>
       <c r="J3" s="0">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K3" s="3">
         <v>434042600.0</v>
@@ -1474,12 +643,12 @@
     <row r="4">
       <c r="A4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2448-116-L126</t>
+          <t xml:space="preserve">2713-159-LE26</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">MANTENIMIENTO Y ACTUALIZACIÓN DE SOFTWARE DE CONTROL RESOLUTIVIDAD.</t>
+          <t xml:space="preserve">DAF-informatica sevicio plataforma documental</t>
         </is>
       </c>
       <c r="C4" s="0" t="inlineStr">
@@ -1489,36 +658,34 @@
       </c>
       <c r="D4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">I MUNICIPALIDAD DE COQUIMBO</t>
+          <t xml:space="preserve">I MUNICIPALIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="E4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Departamento de Salud</t>
+          <t xml:space="preserve">I.MUNICIPALIDAD AYSEN-ADQUISICIONES</t>
         </is>
       </c>
       <c r="F4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t xml:space="preserve">Región Aysén del General Carlos Ibáñez del Campo</t>
         </is>
       </c>
       <c r="G4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Coquimbo</t>
+          <t xml:space="preserve">Aysén</t>
         </is>
       </c>
       <c r="H4" s="2">
-        <v>46255.394016</v>
+        <v>46252.663449</v>
       </c>
       <c r="I4" s="2">
-        <v>46265.854167</v>
+        <v>46266.604167</v>
       </c>
       <c r="J4" s="0">
         <v>0</v>
       </c>
-      <c r="K4" s="3">
-        <v>4526046.0</v>
-      </c>
+      <c r="K4" s="3"/>
       <c r="L4" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">CLP</t>
@@ -1526,47 +693,55 @@
       </c>
       <c r="M4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">L1</t>
+          <t xml:space="preserve">LE</t>
         </is>
       </c>
       <c r="N4" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Equipamiento y suministros médicos / Productos para imágenes y de medicina nuclear / Artículos para archivar información e imágenes radiológicas</t>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de gestión de contenidos</t>
         </is>
       </c>
       <c r="O4" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 Unidad · Software de sistemas de archivado de película radiográfica médica</t>
+          <t xml:space="preserve">1 Unidad · Programas de gestión de documentos</t>
         </is>
       </c>
       <c r="P4" s="2"/>
       <c r="Q4" s="2"/>
-      <c r="R4" s="0"/>
+      <c r="R4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">48 meses</t>
+        </is>
+      </c>
       <c r="S4" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">No</t>
         </is>
       </c>
       <c r="T4" s="4"/>
-      <c r="U4" s="0"/>
+      <c r="U4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Victor Godoy Tapia</t>
+        </is>
+      </c>
       <c r="V4" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contratar el servicio de Mantenimiento Evolutivo y Actualización de Software de Control para el equipo médico OCT HEIDELBERG, Número de Serie SPEC-CAM-15583-S2610 , de propiedad de la I. Municipalidad de Coquimbo. El Sistema de Tomografía de Coherencia Óptica (OCT) Heidelberg Engineering SPECTRALIS, N.° de serie SPEC-CAM-15583-S2610, plataforma de diagnóstico oftalmológico basada en tecnología Spectral Domain OCT (SD-OCT) con oftalmoscopía láser confocal (cSLO), seguimiento ocular TruTrack, func</t>
+          <t xml:space="preserve">Que, el Director de Administración y Finanzas a través de la unidad de informática y mediante solicitud N°961, de fecha 10 de agosto de 2026, solicita licitar un servicio integral en modalidad SaaS para la continuidad, ampliación, migración y soporte técnico de la Plataforma Documental y de Correspondencia de la Ilustre Municipalidad de Aysén.</t>
         </is>
       </c>
       <c r="W4" s="5" t="str">
-        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=2448-116-L126","descargar bases")</f>
+        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=2713-159-LE26","descargar bases")</f>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2713-159-LE26</t>
+          <t xml:space="preserve">869591-10-LP26</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">DAF-informatica sevicio plataforma documental</t>
+          <t xml:space="preserve">CONTRATACIÓN DEL SERVICIO DE DISEÑO Y DESARROLLO DEL NUEVO PORTAL API Y CAPA DE DATOS DE NEGOCIO PARA MERCADO PÚBLICO</t>
         </is>
       </c>
       <c r="C5" s="0" t="inlineStr">
@@ -1576,59 +751,59 @@
       </c>
       <c r="D5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">I MUNICIPALIDAD DE AYSEN</t>
+          <t xml:space="preserve">DIRECCION DE COMPRAS Y CONTRATACION PUBLICA</t>
         </is>
       </c>
       <c r="E5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">I.MUNICIPALIDAD AYSEN-ADQUISICIONES</t>
+          <t xml:space="preserve">Calidad del Gasto en las Compras Públicas</t>
         </is>
       </c>
       <c r="F5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t xml:space="preserve">Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="G5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aysén</t>
+          <t xml:space="preserve">Santiago Centro</t>
         </is>
       </c>
       <c r="H5" s="2">
-        <v>46252.663449</v>
+        <v>46246.440972</v>
       </c>
       <c r="I5" s="2">
-        <v>46266.604167</v>
+        <v>46266.625</v>
       </c>
       <c r="J5" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" s="3"/>
       <c r="L5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">CLP</t>
+          <t xml:space="preserve">CLF</t>
         </is>
       </c>
       <c r="M5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">LE</t>
+          <t xml:space="preserve">LP</t>
         </is>
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de gestión de contenidos</t>
+          <t xml:space="preserve">Servicios profesionales, administrativos y consultorías de gestión empresarial / Servicios de recursos humanos / Contratación de personal</t>
         </is>
       </c>
       <c r="O5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 Unidad · Programas de gestión de documentos</t>
+          <t xml:space="preserve">1 Unidad · Desarrolladores de software</t>
         </is>
       </c>
       <c r="P5" s="2"/>
       <c r="Q5" s="2"/>
       <c r="R5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">48 meses</t>
+          <t xml:space="preserve">12 meses</t>
         </is>
       </c>
       <c r="S5" s="0" t="inlineStr">
@@ -1636,30 +811,34 @@
           <t xml:space="preserve">No</t>
         </is>
       </c>
-      <c r="T5" s="4"/>
+      <c r="T5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ver clausula 10 de las bases especiales</t>
+        </is>
+      </c>
       <c r="U5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Victor Godoy Tapia</t>
+          <t xml:space="preserve">Christian Zarria</t>
         </is>
       </c>
       <c r="V5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Que, el Director de Administración y Finanzas a través de la unidad de informática y mediante solicitud N°961, de fecha 10 de agosto de 2026, solicita licitar un servicio integral en modalidad SaaS para la continuidad, ampliación, migración y soporte técnico de la Plataforma Documental y de Correspondencia de la Ilustre Municipalidad de Aysén.</t>
+          <t xml:space="preserve">CONTRATACIÓN DEL SERVICIO DE DISEÑO Y DESARROLLO DEL NUEVO PORTAL API Y CAPA DE DATOS DE NEGOCIO PARA MERCADO PÚBLICO</t>
         </is>
       </c>
       <c r="W5" s="5" t="str">
-        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=2713-159-LE26","descargar bases")</f>
+        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=869591-10-LP26","descargar bases")</f>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">869591-10-LP26</t>
+          <t xml:space="preserve">587-37-LE26</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">CONTRATACIÓN DEL SERVICIO DE DISEÑO Y DESARROLLO DEL NUEVO PORTAL API Y CAPA DE DATOS DE NEGOCIO PARA MERCADO PÚBLICO</t>
+          <t xml:space="preserve">SELICO 326-2026. Renovación Software Estadístico</t>
         </is>
       </c>
       <c r="C6" s="0" t="inlineStr">
@@ -1669,12 +848,12 @@
       </c>
       <c r="D6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">DIRECCION DE COMPRAS Y CONTRATACION PUBLICA</t>
+          <t xml:space="preserve">SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
         </is>
       </c>
       <c r="E6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Calidad del Gasto en las Compras Públicas</t>
+          <t xml:space="preserve">Ministerio de Vivienda y Urbanismo(766)</t>
         </is>
       </c>
       <c r="F6" s="0" t="inlineStr">
@@ -1682,39 +861,37 @@
           <t xml:space="preserve">Región Metropolitana de Santiago</t>
         </is>
       </c>
-      <c r="G6" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Santiago Centro</t>
-        </is>
-      </c>
+      <c r="G6" s="0"/>
       <c r="H6" s="2">
-        <v>46246.440972</v>
+        <v>46247.621076</v>
       </c>
       <c r="I6" s="2">
-        <v>46266.625</v>
+        <v>46266.631944</v>
       </c>
       <c r="J6" s="0">
-        <v>1</v>
-      </c>
-      <c r="K6" s="3"/>
+        <v>0</v>
+      </c>
+      <c r="K6" s="3">
+        <v>33150.0</v>
+      </c>
       <c r="L6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">CLF</t>
+          <t xml:space="preserve">USD</t>
         </is>
       </c>
       <c r="M6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">LP</t>
+          <t xml:space="preserve">LE</t>
         </is>
       </c>
       <c r="N6" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Servicios profesionales, administrativos y consultorías de gestión empresarial / Servicios de recursos humanos / Contratación de personal</t>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de gestión</t>
         </is>
       </c>
       <c r="O6" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 Unidad · Desarrolladores de software</t>
+          <t xml:space="preserve">1 Global · Software de gestión de licencias</t>
         </is>
       </c>
       <c r="P6" s="2"/>
@@ -1731,32 +908,32 @@
       </c>
       <c r="T6" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ver clausula 10 de las bases especiales</t>
+          <t xml:space="preserve">VER PUNTO 1.13.5.7.- SUBCONTRATACIÓN, DE LAS PRESENTES BASES.</t>
         </is>
       </c>
       <c r="U6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Christian Zarria</t>
+          <t xml:space="preserve">Adrián Muñoz Brevis</t>
         </is>
       </c>
       <c r="V6" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">CONTRATACIÓN DEL SERVICIO DE DISEÑO Y DESARROLLO DEL NUEVO PORTAL API Y CAPA DE DATOS DE NEGOCIO PARA MERCADO PÚBLICO</t>
+          <t xml:space="preserve">Se requiere contratar la renovación anual de uso de licencias de software Statistics Smart Pack IBM SPSS o equivalente, que incluye once 11 licencias autorizadas de los módulos Base y Custom Tables, y tres 03 licencias concurrentes de los mismos módulos, por doce 12 meses, para el periodo comprendido entre el 01 de enero de 2027 al 31 de diciembre del 2027.</t>
         </is>
       </c>
       <c r="W6" s="5" t="str">
-        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=869591-10-LP26","descargar bases")</f>
+        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=587-37-LE26","descargar bases")</f>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">587-37-LE26</t>
+          <t xml:space="preserve">1110404-154-LE26</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">SELICO 326-2026. Renovación Software Estadístico</t>
+          <t xml:space="preserve">ADQUISICIÓN DE LICENCIAS PERMANENTES DE SOFTWARE FACTORY IO PARA LA ESPECIALIDAD DE ELECTRÓNICA DEL LICEO POLITÉCNICO ARICA SERVICIO LOCAL DE EDUCACIÓN PÚBLICA CHINCHORRO</t>
         </is>
       </c>
       <c r="C7" s="0" t="inlineStr">
@@ -1766,35 +943,35 @@
       </c>
       <c r="D7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
+          <t xml:space="preserve">SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="E7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ministerio de Vivienda y Urbanismo(766)</t>
+          <t xml:space="preserve">SLEPCH - EE - Programa 02</t>
         </is>
       </c>
       <c r="F7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región Metropolitana de Santiago</t>
+          <t xml:space="preserve">Región de Arica y Parinacota</t>
         </is>
       </c>
       <c r="G7" s="0"/>
       <c r="H7" s="2">
-        <v>46247.621076</v>
+        <v>46258.46338</v>
       </c>
       <c r="I7" s="2">
-        <v>46266.631944</v>
+        <v>46266.666667</v>
       </c>
       <c r="J7" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" s="3">
-        <v>33150.0</v>
+        <v>12154650.0</v>
       </c>
       <c r="L7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">USD</t>
+          <t xml:space="preserve">CLP</t>
         </is>
       </c>
       <c r="M7" s="0" t="inlineStr">
@@ -1804,21 +981,17 @@
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de gestión</t>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software educativo o de referencia</t>
         </is>
       </c>
       <c r="O7" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 Global · Software de gestión de licencias</t>
+          <t xml:space="preserve">15 Unidad · Software de mapa electrónico</t>
         </is>
       </c>
       <c r="P7" s="2"/>
       <c r="Q7" s="2"/>
-      <c r="R7" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12 meses</t>
-        </is>
-      </c>
+      <c r="R7" s="0"/>
       <c r="S7" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">No</t>
@@ -1826,106 +999,15 @@
       </c>
       <c r="T7" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">VER PUNTO 1.13.5.7.- SUBCONTRATACIÓN, DE LAS PRESENTES BASES.</t>
+          <t xml:space="preserve">Según el punto 10.8 de las Bases Administrativas</t>
         </is>
       </c>
       <c r="U7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adrián Muñoz Brevis</t>
+          <t xml:space="preserve">IGNACIO PARRA TESTA</t>
         </is>
       </c>
       <c r="V7" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Se requiere contratar la renovación anual de uso de licencias de software Statistics Smart Pack IBM SPSS o equivalente, que incluye once 11 licencias autorizadas de los módulos Base y Custom Tables, y tres 03 licencias concurrentes de los mismos módulos, por doce 12 meses, para el periodo comprendido entre el 01 de enero de 2027 al 31 de diciembre del 2027.</t>
-        </is>
-      </c>
-      <c r="W7" s="5" t="str">
-        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=587-37-LE26","descargar bases")</f>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1110404-154-LE26</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ADQUISICIÓN DE LICENCIAS PERMANENTES DE SOFTWARE FACTORY IO PARA LA ESPECIALIDAD DE ELECTRÓNICA DEL LICEO POLITÉCNICO ARICA SERVICIO LOCAL DE EDUCACIÓN PÚBLICA CHINCHORRO</t>
-        </is>
-      </c>
-      <c r="C8" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Publicada</t>
-        </is>
-      </c>
-      <c r="D8" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
-        </is>
-      </c>
-      <c r="E8" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SLEPCH - EE - Programa 02</t>
-        </is>
-      </c>
-      <c r="F8" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Región de Arica y Parinacota</t>
-        </is>
-      </c>
-      <c r="G8" s="0"/>
-      <c r="H8" s="2">
-        <v>46258.46338</v>
-      </c>
-      <c r="I8" s="2">
-        <v>46266.666667</v>
-      </c>
-      <c r="J8" s="0">
-        <v>1</v>
-      </c>
-      <c r="K8" s="3">
-        <v>12154650.0</v>
-      </c>
-      <c r="L8" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CLP</t>
-        </is>
-      </c>
-      <c r="M8" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LE</t>
-        </is>
-      </c>
-      <c r="N8" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software educativo o de referencia</t>
-        </is>
-      </c>
-      <c r="O8" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15 Unidad · Software de mapa electrónico</t>
-        </is>
-      </c>
-      <c r="P8" s="2"/>
-      <c r="Q8" s="2"/>
-      <c r="R8" s="0"/>
-      <c r="S8" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">No</t>
-        </is>
-      </c>
-      <c r="T8" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Según el punto 10.8 de las Bases Administrativas</t>
-        </is>
-      </c>
-      <c r="U8" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">IGNACIO PARRA TESTA</t>
-        </is>
-      </c>
-      <c r="V8" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">SOL-2026-1260
 LICEO POLITECNICO ARICA
@@ -1933,19 +1015,110 @@
 Materia de compra : 2907001 Programas computacionales</t>
         </is>
       </c>
+      <c r="W7" s="5" t="str">
+        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=1110404-154-LE26","descargar bases")</f>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">885-74-LP26</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Servicio de actualización de software arquitectura y migración de base de datos del Sistema DIP.</t>
+        </is>
+      </c>
+      <c r="C8" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Publicada</t>
+        </is>
+      </c>
+      <c r="D8" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CONTRALORIA GENERAL DE LA REPUBLICA</t>
+        </is>
+      </c>
+      <c r="E8" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Contraloría General de la República</t>
+        </is>
+      </c>
+      <c r="F8" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="G8" s="0"/>
+      <c r="H8" s="2">
+        <v>46246.420336</v>
+      </c>
+      <c r="I8" s="2">
+        <v>46266.666667</v>
+      </c>
+      <c r="J8" s="0">
+        <v>0</v>
+      </c>
+      <c r="K8" s="3">
+        <v>190000000.0</v>
+      </c>
+      <c r="L8" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CLP</t>
+        </is>
+      </c>
+      <c r="M8" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LP</t>
+        </is>
+      </c>
+      <c r="N8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Servicios profesionales, administrativos y consultorías de gestión empresarial / Servicios de recursos humanos / Contratación de personal</t>
+        </is>
+      </c>
+      <c r="O8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 Unidad · Desarrolladores de software</t>
+        </is>
+      </c>
+      <c r="P8" s="2"/>
+      <c r="Q8" s="2"/>
+      <c r="R8" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10 meses</t>
+        </is>
+      </c>
+      <c r="S8" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="T8" s="4"/>
+      <c r="U8" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cristian Leon</t>
+        </is>
+      </c>
+      <c r="V8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">La Contraloría General de la República requiere contratar el servicio de actualización de software, arquitectura y migración de base de datos del Sistema de Declaraciones de Intereses y Patrimonio — DIP.</t>
+        </is>
+      </c>
       <c r="W8" s="5" t="str">
-        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=1110404-154-LE26","descargar bases")</f>
+        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=885-74-LP26","descargar bases")</f>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">885-74-LP26</t>
+          <t xml:space="preserve">1113265-12-LE26</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Servicio de actualización de software arquitectura y migración de base de datos del Sistema DIP.</t>
+          <t xml:space="preserve">ADQUISICIÓN E IMPLEMENTACIÓN DE PLATAFORMA</t>
         </is>
       </c>
       <c r="C9" s="0" t="inlineStr">
@@ -1955,32 +1128,34 @@
       </c>
       <c r="D9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">CONTRALORIA GENERAL DE LA REPUBLICA</t>
+          <t xml:space="preserve">CENTRO DE FORMACION TECNICA DE LA REGION DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="E9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contraloría General de la República</t>
+          <t xml:space="preserve">UNIDAD DE COMPRAS</t>
         </is>
       </c>
       <c r="F9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región Metropolitana de Santiago</t>
-        </is>
-      </c>
-      <c r="G9" s="0"/>
+          <t xml:space="preserve">Región de Antofagasta </t>
+        </is>
+      </c>
+      <c r="G9" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Calama</t>
+        </is>
+      </c>
       <c r="H9" s="2">
-        <v>46246.420336</v>
+        <v>46245.847222</v>
       </c>
       <c r="I9" s="2">
-        <v>46266.666667</v>
+        <v>46266.692361</v>
       </c>
       <c r="J9" s="0">
-        <v>1</v>
-      </c>
-      <c r="K9" s="3">
-        <v>190000000.0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K9" s="3"/>
       <c r="L9" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">CLP</t>
@@ -1988,24 +1163,24 @@
       </c>
       <c r="M9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">LP</t>
+          <t xml:space="preserve">LE</t>
         </is>
       </c>
       <c r="N9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Servicios profesionales, administrativos y consultorías de gestión empresarial / Servicios de recursos humanos / Contratación de personal</t>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de gestión</t>
         </is>
       </c>
       <c r="O9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 Unidad · Desarrolladores de software</t>
+          <t xml:space="preserve">1 Unidad · Software de gestión de licencias</t>
         </is>
       </c>
       <c r="P9" s="2"/>
       <c r="Q9" s="2"/>
       <c r="R9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">10 meses</t>
+          <t xml:space="preserve">12 meses</t>
         </is>
       </c>
       <c r="S9" s="0" t="inlineStr">
@@ -2016,27 +1191,27 @@
       <c r="T9" s="4"/>
       <c r="U9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cristian Leon</t>
+          <t xml:space="preserve">IVAN MELLA</t>
         </is>
       </c>
       <c r="V9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">La Contraloría General de la República requiere contratar el servicio de actualización de software, arquitectura y migración de base de datos del Sistema de Declaraciones de Intereses y Patrimonio — DIP.</t>
+          <t xml:space="preserve">ha requerido contratar el servicio de provisión, implementación, integración, soporte y mantención de una plataforma web tecnológica, en modalidad SaaS Software como Servicio, para la gestión estratégica de la permanencia y trayectoria estudiantil, que permita gestionar la retención, el seguimiento a la progresión y la trayectoria académica, como apoyo a los procesos asociados al Modelo de Acompañamiento a la Trayectoria del Estudiante MAPE del CFTE de la Región de Antofagasta.</t>
         </is>
       </c>
       <c r="W9" s="5" t="str">
-        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=885-74-LP26","descargar bases")</f>
+        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=1113265-12-LE26","descargar bases")</f>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1113265-12-LE26</t>
+          <t xml:space="preserve">1233623-38-LE26</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADQUISICIÓN E IMPLEMENTACIÓN DE PLATAFORMA</t>
+          <t xml:space="preserve">ADQUISICIÓN DE SOFTWARE AEC COLLECTION 2025</t>
         </is>
       </c>
       <c r="C10" s="0" t="inlineStr">
@@ -2046,12 +1221,12 @@
       </c>
       <c r="D10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">CENTRO DE FORMACION TECNICA DE LA REGION DE ANTOFAGASTA</t>
+          <t xml:space="preserve">Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="E10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">UNIDAD DE COMPRAS</t>
+          <t xml:space="preserve">Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="F10" s="0" t="inlineStr">
@@ -2065,15 +1240,17 @@
         </is>
       </c>
       <c r="H10" s="2">
-        <v>46245.847222</v>
+        <v>46258.779861</v>
       </c>
       <c r="I10" s="2">
-        <v>46266.692361</v>
+        <v>46267.625</v>
       </c>
       <c r="J10" s="0">
         <v>1</v>
       </c>
-      <c r="K10" s="3"/>
+      <c r="K10" s="3">
+        <v>19800000.0</v>
+      </c>
       <c r="L10" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">CLP</t>
@@ -2086,21 +1263,17 @@
       </c>
       <c r="N10" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de gestión</t>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software para trabajo en redes</t>
         </is>
       </c>
       <c r="O10" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 Unidad · Software de gestión de licencias</t>
+          <t xml:space="preserve">1 Global · Software de acceso</t>
         </is>
       </c>
       <c r="P10" s="2"/>
       <c r="Q10" s="2"/>
-      <c r="R10" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12 meses</t>
-        </is>
-      </c>
+      <c r="R10" s="0"/>
       <c r="S10" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">No</t>
@@ -2109,27 +1282,27 @@
       <c r="T10" s="4"/>
       <c r="U10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">IVAN MELLA</t>
+          <t xml:space="preserve">Barbara Lira Mac-Donald</t>
         </is>
       </c>
       <c r="V10" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ha requerido contratar el servicio de provisión, implementación, integración, soporte y mantención de una plataforma web tecnológica, en modalidad SaaS Software como Servicio, para la gestión estratégica de la permanencia y trayectoria estudiantil, que permita gestionar la retención, el seguimiento a la progresión y la trayectoria académica, como apoyo a los procesos asociados al Modelo de Acompañamiento a la Trayectoria del Estudiante MAPE del CFTE de la Región de Antofagasta.</t>
+          <t xml:space="preserve">El Servicio Local de Educación Pública Licancabur convoca a licitación pública para la adquisición de nueve licencias de software AEC Collection 2025, equivalente o superior, destinadas a la Subdirección de Infraestructura y Mantenimiento, Unidad de Diseño y Planificación.</t>
         </is>
       </c>
       <c r="W10" s="5" t="str">
-        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=1113265-12-LE26","descargar bases")</f>
+        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=1233623-38-LE26","descargar bases")</f>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1233623-38-LE26</t>
+          <t xml:space="preserve">652-37-LP26</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADQUISICIÓN DE SOFTWARE AEC COLLECTION 2025</t>
+          <t xml:space="preserve">ARRIENDO SERVIDOR INFORMATICO PARA PROGRAMA SISSA.</t>
         </is>
       </c>
       <c r="C11" s="0" t="inlineStr">
@@ -2139,36 +1312,34 @@
       </c>
       <c r="D11" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Servicio Local de Educación Pública Licancabur</t>
+          <t xml:space="preserve">SERVICIO DE SALUD ARAUCO</t>
         </is>
       </c>
       <c r="E11" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Servicio Local de Educación Pública Licancabur</t>
+          <t xml:space="preserve">SERVICIO DE SALUD ARAUCO</t>
         </is>
       </c>
       <c r="F11" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t xml:space="preserve">Región del Biobío </t>
         </is>
       </c>
       <c r="G11" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Calama</t>
+          <t xml:space="preserve">Lebu</t>
         </is>
       </c>
       <c r="H11" s="2">
-        <v>46258.779861</v>
+        <v>46247.795127</v>
       </c>
       <c r="I11" s="2">
         <v>46267.625</v>
       </c>
       <c r="J11" s="0">
-        <v>2</v>
-      </c>
-      <c r="K11" s="3">
-        <v>19800000.0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K11" s="3"/>
       <c r="L11" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">CLP</t>
@@ -2176,22 +1347,26 @@
       </c>
       <c r="M11" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">LE</t>
+          <t xml:space="preserve">LP</t>
         </is>
       </c>
       <c r="N11" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software para trabajo en redes</t>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Equipos informáticos y accesorios / Computadores</t>
         </is>
       </c>
       <c r="O11" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 Global · Software de acceso</t>
+          <t xml:space="preserve">1 Unidad · Servidores</t>
         </is>
       </c>
       <c r="P11" s="2"/>
       <c r="Q11" s="2"/>
-      <c r="R11" s="0"/>
+      <c r="R11" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">36 meses</t>
+        </is>
+      </c>
       <c r="S11" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">No</t>
@@ -2200,27 +1375,27 @@
       <c r="T11" s="4"/>
       <c r="U11" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Barbara Lira Mac-Donald</t>
+          <t xml:space="preserve">JEFE DEPARTAMENTO TIC SSA</t>
         </is>
       </c>
       <c r="V11" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">El Servicio Local de Educación Pública Licancabur convoca a licitación pública para la adquisición de nueve licencias de software AEC Collection 2025, equivalente o superior, destinadas a la Subdirección de Infraestructura y Mantenimiento, Unidad de Diseño y Planificación.</t>
+          <t xml:space="preserve">El Servicio de Salud Arauco a través de su Dirección, requiere contratar el CONVENIO ARRIENDO DE SERVIDOR INFORMATICO PROGRAMA SISSA, SERVICIO DE SALUD ARAUCO PARA EL SERVICIO DE SALUD ARAUCANIA SUR, por un periodo de 36 meses destinado al Programa SISSA.  Dicho servidor deberá instalarse en la Sala de Servidores del Servicio de Salud Araucanía Sur, ubicada en calle Prat Numero 969, de la ciudad de Temuco.</t>
         </is>
       </c>
       <c r="W11" s="5" t="str">
-        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=1233623-38-LE26","descargar bases")</f>
+        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=652-37-LP26","descargar bases")</f>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">652-37-LP26</t>
+          <t xml:space="preserve">609-25-LE26</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ARRIENDO SERVIDOR INFORMATICO PARA PROGRAMA SISSA.</t>
+          <t xml:space="preserve">ACTUALIZACIÓN DEL SGSI DE INDAP- CIBERSEGURIDAD</t>
         </is>
       </c>
       <c r="C12" s="0" t="inlineStr">
@@ -2230,34 +1405,36 @@
       </c>
       <c r="D12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">SERVICIO DE SALUD ARAUCO</t>
+          <t xml:space="preserve">INSTITUTO DE DESARROLLO AGROPECUARIO</t>
         </is>
       </c>
       <c r="E12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">SERVICIO DE SALUD ARAUCO</t>
+          <t xml:space="preserve">Instituto de Desarrollo Agropecuario - INDAP</t>
         </is>
       </c>
       <c r="F12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t xml:space="preserve">Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="G12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lebu</t>
+          <t xml:space="preserve">Santiago</t>
         </is>
       </c>
       <c r="H12" s="2">
-        <v>46247.795127</v>
+        <v>46255.533843</v>
       </c>
       <c r="I12" s="2">
-        <v>46267.625</v>
+        <v>46267.645833</v>
       </c>
       <c r="J12" s="0">
-        <v>2</v>
-      </c>
-      <c r="K12" s="3"/>
+        <v>1</v>
+      </c>
+      <c r="K12" s="3">
+        <v>22000000.0</v>
+      </c>
       <c r="L12" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">CLP</t>
@@ -2265,24 +1442,24 @@
       </c>
       <c r="M12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">LP</t>
+          <t xml:space="preserve">LE</t>
         </is>
       </c>
       <c r="N12" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Equipos informáticos y accesorios / Computadores</t>
+          <t xml:space="preserve">Servicios profesionales, administrativos y consultorías de gestión empresarial / Consultorías o asesorías en gestión empresarial / Servicios de consultoría en gestión de empresas</t>
         </is>
       </c>
       <c r="O12" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 Unidad · Servidores</t>
+          <t xml:space="preserve">1 Unidad · Asesorías Informáticas</t>
         </is>
       </c>
       <c r="P12" s="2"/>
       <c r="Q12" s="2"/>
       <c r="R12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">36 meses</t>
+          <t xml:space="preserve">3 meses</t>
         </is>
       </c>
       <c r="S12" s="0" t="inlineStr">
@@ -2293,27 +1470,27 @@
       <c r="T12" s="4"/>
       <c r="U12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">JEFE DEPARTAMENTO TIC SSA</t>
+          <t xml:space="preserve">José Miguel Reyes Canales</t>
         </is>
       </c>
       <c r="V12" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">El Servicio de Salud Arauco a través de su Dirección, requiere contratar el CONVENIO ARRIENDO DE SERVIDOR INFORMATICO PROGRAMA SISSA, SERVICIO DE SALUD ARAUCO PARA EL SERVICIO DE SALUD ARAUCANIA SUR, por un periodo de 36 meses destinado al Programa SISSA.  Dicho servidor deberá instalarse en la Sala de Servidores del Servicio de Salud Araucanía Sur, ubicada en calle Prat Numero 969, de la ciudad de Temuco.</t>
+          <t xml:space="preserve">Consultoría para actualización del SGSI de INDAP, modelado de procesos, matriz de riesgo, identificación e implementación de controles y otros referidos a la Ley Marco de Ciberseguridad.</t>
         </is>
       </c>
       <c r="W12" s="5" t="str">
-        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=652-37-LP26","descargar bases")</f>
+        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=609-25-LE26","descargar bases")</f>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">609-25-LE26</t>
+          <t xml:space="preserve">1075956-9-LE26</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ACTUALIZACIÓN DEL SGSI DE INDAP- CIBERSEGURIDAD</t>
+          <t xml:space="preserve">42 CUPOS - CURSO NUEVA LEY DE PROTECCIÓN DE DATOS PERSONALES: INTRODUCCIÓN Y PRINCIPIOS” SEGÚN BASES DE LICITACIÓN Y ANEXOS QUE SE ADJUNTAN - PRESUPUESTO ESTIMADO  15.000.000. -</t>
         </is>
       </c>
       <c r="C13" s="0" t="inlineStr">
@@ -2323,12 +1500,12 @@
       </c>
       <c r="D13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">INSTITUTO DE DESARROLLO AGROPECUARIO</t>
+          <t xml:space="preserve">DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="E13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Instituto de Desarrollo Agropecuario - INDAP</t>
+          <t xml:space="preserve">DEPTO ANALISIS FINANCIERO PROCESOS Y RIESGOS</t>
         </is>
       </c>
       <c r="F13" s="0" t="inlineStr">
@@ -2342,16 +1519,16 @@
         </is>
       </c>
       <c r="H13" s="2">
-        <v>46255.533843</v>
+        <v>46253.686806</v>
       </c>
       <c r="I13" s="2">
-        <v>46267.645833</v>
+        <v>46267.708333</v>
       </c>
       <c r="J13" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K13" s="3">
-        <v>22000000.0</v>
+        <v>15000000.0</v>
       </c>
       <c r="L13" s="0" t="inlineStr">
         <is>
@@ -2365,21 +1542,17 @@
       </c>
       <c r="N13" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Servicios profesionales, administrativos y consultorías de gestión empresarial / Consultorías o asesorías en gestión empresarial / Servicios de consultoría en gestión de empresas</t>
+          <t xml:space="preserve">Servicios profesionales, administrativos y consultorías de gestión empresarial / Servicios de recursos humanos / Consultorías para el desarrollo de recursos humanos</t>
         </is>
       </c>
       <c r="O13" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 Unidad · Asesorías Informáticas</t>
+          <t xml:space="preserve">42 Unidad · Formación, capacitación y entrenamiento de personal</t>
         </is>
       </c>
       <c r="P13" s="2"/>
       <c r="Q13" s="2"/>
-      <c r="R13" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3 meses</t>
-        </is>
-      </c>
+      <c r="R13" s="0"/>
       <c r="S13" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">No</t>
@@ -2388,27 +1561,27 @@
       <c r="T13" s="4"/>
       <c r="U13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">José Miguel Reyes Canales</t>
+          <t xml:space="preserve">YESICA SEPÚLVEDA NAVARRO.</t>
         </is>
       </c>
       <c r="V13" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Consultoría para actualización del SGSI de INDAP, modelado de procesos, matriz de riesgo, identificación e implementación de controles y otros referidos a la Ley Marco de Ciberseguridad.</t>
+          <t xml:space="preserve">42 CUPOS - CURSO NUEVA LEY DE PROTECCIÓN DE DATOS PERSONALES: "INTRODUCCIÓN Y PRINCIPIOS”, SEGÚN BASES DE LICITACIÓN Y ANEXOS QUE SE ADJUNTAN - PRESUPUESTO ESTIMADO $ 15.000.000. -</t>
         </is>
       </c>
       <c r="W13" s="5" t="str">
-        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=609-25-LE26","descargar bases")</f>
+        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=1075956-9-LE26","descargar bases")</f>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1075956-9-LE26</t>
+          <t xml:space="preserve">1057532-72-LE26</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">42 CUPOS - CURSO NUEVA LEY DE PROTECCIÓN DE DATOS PERSONALES: INTRODUCCIÓN Y PRINCIPIOS” SEGÚN BASES DE LICITACIÓN Y ANEXOS QUE SE ADJUNTAN - PRESUPUESTO ESTIMADO  15.000.000. -</t>
+          <t xml:space="preserve">SUSCRIPCIÓN LICENCIAS SOFTWARE CAD ARCHICAD COLLABORATE O EQUIVALENTE PARA EL SERVICIO DE SALUD OSORNO</t>
         </is>
       </c>
       <c r="C14" s="0" t="inlineStr">
@@ -2418,36 +1591,34 @@
       </c>
       <c r="D14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t xml:space="preserve">SERVICIO DE SALUD OSORNO</t>
         </is>
       </c>
       <c r="E14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEPTO ANALISIS FINANCIERO PROCESOS Y RIESGOS</t>
+          <t xml:space="preserve">Bienes y Servicios</t>
         </is>
       </c>
       <c r="F14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región Metropolitana de Santiago</t>
+          <t xml:space="preserve">Región de los Lagos </t>
         </is>
       </c>
       <c r="G14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Santiago</t>
+          <t xml:space="preserve">Osorno</t>
         </is>
       </c>
       <c r="H14" s="2">
-        <v>46253.686806</v>
+        <v>46261.607396</v>
       </c>
       <c r="I14" s="2">
-        <v>46267.708333</v>
+        <v>46267.709028</v>
       </c>
       <c r="J14" s="0">
-        <v>2</v>
-      </c>
-      <c r="K14" s="3">
-        <v>15000000.0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K14" s="3"/>
       <c r="L14" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">CLP</t>
@@ -2460,46 +1631,55 @@
       </c>
       <c r="N14" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Servicios profesionales, administrativos y consultorías de gestión empresarial / Servicios de recursos humanos / Consultorías para el desarrollo de recursos humanos</t>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software específico para la industria</t>
         </is>
       </c>
       <c r="O14" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">42 Unidad · Formación, capacitación y entrenamiento de personal</t>
+          <t xml:space="preserve">6 Unidad · Software de diseño asistido por computador (CAD)</t>
         </is>
       </c>
       <c r="P14" s="2"/>
       <c r="Q14" s="2"/>
-      <c r="R14" s="0"/>
+      <c r="R14" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12 meses</t>
+        </is>
+      </c>
       <c r="S14" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">No</t>
         </is>
       </c>
-      <c r="T14" s="4"/>
+      <c r="T14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DE ACUERDO A NUMERAL 7.7 DE LAS BASES ADJUNTAS</t>
+        </is>
+      </c>
       <c r="U14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">YESICA SEPÚLVEDA NAVARRO.</t>
+          <t xml:space="preserve">Bruno Ojeda Alvarez</t>
         </is>
       </c>
       <c r="V14" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">42 CUPOS - CURSO NUEVA LEY DE PROTECCIÓN DE DATOS PERSONALES: "INTRODUCCIÓN Y PRINCIPIOS”, SEGÚN BASES DE LICITACIÓN Y ANEXOS QUE SE ADJUNTAN - PRESUPUESTO ESTIMADO $ 15.000.000. -</t>
+          <t xml:space="preserve">Se requiere la Contratación de 06 licencia de suscripción a 12 meses para software CAD Archicad Collaborate o equivalente, los cuales se cancelarán en 12 cuotas.
+Lo anterior para normalizar y cumplir la Ley de propiedades intelectuales usando licencias originales para el trabajo de diseño, creación, modificación, análisis y documentar proyectos de inversión y construcción del Servicio de Salud Osorno.</t>
         </is>
       </c>
       <c r="W14" s="5" t="str">
-        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=1075956-9-LE26","descargar bases")</f>
+        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=1057532-72-LE26","descargar bases")</f>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1057532-72-LE26</t>
+          <t xml:space="preserve">564953-62-LP26</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">SUSCRIPCIÓN LICENCIAS SOFTWARE CAD ARCHICAD COLLABORATE O EQUIVALENTE PARA EL SERVICIO DE SALUD OSORNO</t>
+          <t xml:space="preserve">ACTUALIZACIÓN PLATAFORMA ERP PARA LA CORPORACIÓN</t>
         </is>
       </c>
       <c r="C15" s="0" t="inlineStr">
@@ -2509,34 +1689,36 @@
       </c>
       <c r="D15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">SERVICIO DE SALUD OSORNO</t>
+          <t xml:space="preserve">Corporación de Educación y Salud de Las Condes</t>
         </is>
       </c>
       <c r="E15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bienes y Servicios</t>
+          <t xml:space="preserve">Corporación de Educación y Salud de Las Condes</t>
         </is>
       </c>
       <c r="F15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t xml:space="preserve">Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="G15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Osorno</t>
+          <t xml:space="preserve">Las Condes</t>
         </is>
       </c>
       <c r="H15" s="2">
-        <v>46261.607396</v>
+        <v>46245.613889</v>
       </c>
       <c r="I15" s="2">
-        <v>46267.709028</v>
+        <v>46267.749306</v>
       </c>
       <c r="J15" s="0">
-        <v>2</v>
-      </c>
-      <c r="K15" s="3"/>
+        <v>1</v>
+      </c>
+      <c r="K15" s="3">
+        <v>250000000.0</v>
+      </c>
       <c r="L15" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">CLP</t>
@@ -2544,24 +1726,24 @@
       </c>
       <c r="M15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">LE</t>
+          <t xml:space="preserve">LP</t>
         </is>
       </c>
       <c r="N15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software específico para la industria</t>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de planificación de recursos empresariales (ERP) y contabilidad financiera</t>
         </is>
       </c>
       <c r="O15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">6 Unidad · Software de diseño asistido por computador (CAD)</t>
+          <t xml:space="preserve">1 Unidad · Software de planificación de recursos empresariales (ERP)</t>
         </is>
       </c>
       <c r="P15" s="2"/>
       <c r="Q15" s="2"/>
       <c r="R15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">12 meses</t>
+          <t xml:space="preserve">40 meses</t>
         </is>
       </c>
       <c r="S15" s="0" t="inlineStr">
@@ -2569,35 +1751,30 @@
           <t xml:space="preserve">No</t>
         </is>
       </c>
-      <c r="T15" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DE ACUERDO A NUMERAL 7.7 DE LAS BASES ADJUNTAS</t>
-        </is>
-      </c>
+      <c r="T15" s="4"/>
       <c r="U15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bruno Ojeda Alvarez</t>
+          <t xml:space="preserve">Cristián Seguel</t>
         </is>
       </c>
       <c r="V15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Se requiere la Contratación de 06 licencia de suscripción a 12 meses para software CAD Archicad Collaborate o equivalente, los cuales se cancelarán en 12 cuotas.
-Lo anterior para normalizar y cumplir la Ley de propiedades intelectuales usando licencias originales para el trabajo de diseño, creación, modificación, análisis y documentar proyectos de inversión y construcción del Servicio de Salud Osorno.</t>
+          <t xml:space="preserve">El objetivo de la presente licitación es contratar el servicio de implementación y soporte de ERP Dynamics Business Central</t>
         </is>
       </c>
       <c r="W15" s="5" t="str">
-        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=1057532-72-LE26","descargar bases")</f>
+        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=564953-62-LP26","descargar bases")</f>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">564953-62-LP26</t>
+          <t xml:space="preserve">3945-20-LE26</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ACTUALIZACIÓN PLATAFORMA ERP PARA LA CORPORACIÓN</t>
+          <t xml:space="preserve">ADQUISICION SERVICIO DE SISTEMA INFORMATIVO DE GESTION DOCUMENTAL - MUNICIPALIDAD LOS ALAMOS</t>
         </is>
       </c>
       <c r="C16" s="0" t="inlineStr">
@@ -2607,35 +1784,35 @@
       </c>
       <c r="D16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Corporación de Educación y Salud de Las Condes</t>
+          <t xml:space="preserve">I MUNICIPALIDAD DE LOS ALAMOS DEPTO COMUNAL</t>
         </is>
       </c>
       <c r="E16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Corporación de Educación y Salud de Las Condes</t>
+          <t xml:space="preserve">Administración y Finanzas</t>
         </is>
       </c>
       <c r="F16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región Metropolitana de Santiago</t>
+          <t xml:space="preserve">Región del Biobío </t>
         </is>
       </c>
       <c r="G16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Las Condes</t>
+          <t xml:space="preserve">Los Alamos</t>
         </is>
       </c>
       <c r="H16" s="2">
-        <v>46245.613889</v>
+        <v>46258.628264</v>
       </c>
       <c r="I16" s="2">
-        <v>46267.749306</v>
+        <v>46268.500694</v>
       </c>
       <c r="J16" s="0">
         <v>2</v>
       </c>
       <c r="K16" s="3">
-        <v>250000000.0</v>
+        <v>70000000.0</v>
       </c>
       <c r="L16" s="0" t="inlineStr">
         <is>
@@ -2644,24 +1821,24 @@
       </c>
       <c r="M16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">LP</t>
+          <t xml:space="preserve">LE</t>
         </is>
       </c>
       <c r="N16" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de planificación de recursos empresariales (ERP) y contabilidad financiera</t>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de entorno operativo</t>
         </is>
       </c>
       <c r="O16" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 Unidad · Software de planificación de recursos empresariales (ERP)</t>
+          <t xml:space="preserve">1 Global · Software de sistema operativo</t>
         </is>
       </c>
       <c r="P16" s="2"/>
       <c r="Q16" s="2"/>
       <c r="R16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">40 meses</t>
+          <t xml:space="preserve">36 meses</t>
         </is>
       </c>
       <c r="S16" s="0" t="inlineStr">
@@ -2672,27 +1849,28 @@
       <c r="T16" s="4"/>
       <c r="U16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cristián Seguel</t>
+          <t xml:space="preserve">Encargado de soporte informatico</t>
         </is>
       </c>
       <c r="V16" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">El objetivo de la presente licitación es contratar el servicio de implementación y soporte de ERP Dynamics Business Central</t>
+          <t xml:space="preserve">La   necesidad      de      contratar    “ADQUISICION SERVICIO   DE SISTEMA     INFORMATIVO    DE     GESTION   DOCUMENTAL – MUNICIPALIDAD   LOS     ALAMOS”, conforme     a           Bases  
+Administrativas, Técnicas y Anexos adjuntos.</t>
         </is>
       </c>
       <c r="W16" s="5" t="str">
-        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=564953-62-LP26","descargar bases")</f>
+        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=3945-20-LE26","descargar bases")</f>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">3945-20-LE26</t>
+          <t xml:space="preserve">4429-95-LE26</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADQUISICION SERVICIO DE SISTEMA INFORMATIVO DE GESTION DOCUMENTAL - MUNICIPALIDAD LOS ALAMOS</t>
+          <t xml:space="preserve">ARRIENDO SOFTWARE FARMACIA Y OPTICA MUNICIPAL</t>
         </is>
       </c>
       <c r="C17" s="0" t="inlineStr">
@@ -2702,12 +1880,12 @@
       </c>
       <c r="D17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">I MUNICIPALIDAD DE LOS ALAMOS DEPTO COMUNAL</t>
+          <t xml:space="preserve">MUNICIPALIDAD DE HUALPEN</t>
         </is>
       </c>
       <c r="E17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Administración y Finanzas</t>
+          <t xml:space="preserve">Dirección de Salud</t>
         </is>
       </c>
       <c r="F17" s="0" t="inlineStr">
@@ -2717,20 +1895,20 @@
       </c>
       <c r="G17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Los Alamos</t>
+          <t xml:space="preserve">Hualpén</t>
         </is>
       </c>
       <c r="H17" s="2">
-        <v>46258.628264</v>
+        <v>46258.511505</v>
       </c>
       <c r="I17" s="2">
-        <v>46268.500694</v>
+        <v>46268.600694</v>
       </c>
       <c r="J17" s="0">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K17" s="3">
-        <v>70000000.0</v>
+        <v>10000000.0</v>
       </c>
       <c r="L17" s="0" t="inlineStr">
         <is>
@@ -2744,12 +1922,12 @@
       </c>
       <c r="N17" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de entorno operativo</t>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de gestión</t>
         </is>
       </c>
       <c r="O17" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 Global · Software de sistema operativo</t>
+          <t xml:space="preserve">1 Unidad · Software de gestión de adquisiciones</t>
         </is>
       </c>
       <c r="P17" s="2"/>
@@ -2764,31 +1942,34 @@
           <t xml:space="preserve">No</t>
         </is>
       </c>
-      <c r="T17" s="4"/>
+      <c r="T17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Se prohíbe absolutamente al adjudicatario ceder o transferir, sea a título gratuito u oneroso, total o parcialmente a terceros los derechos y obligaciones que asuman en virtud de la presente propuesta, y en especial los establecidos en el contrato defini</t>
+        </is>
+      </c>
       <c r="U17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Encargado de soporte informatico</t>
+          <t xml:space="preserve">CARLOS CARES MORALES</t>
         </is>
       </c>
       <c r="V17" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">La   necesidad      de      contratar    “ADQUISICION SERVICIO   DE SISTEMA     INFORMATIVO    DE     GESTION   DOCUMENTAL – MUNICIPALIDAD   LOS     ALAMOS”, conforme     a           Bases  
-Administrativas, Técnicas y Anexos adjuntos.</t>
+          <t xml:space="preserve">SERVICIO DE ARRIENDO, IMPLEMENTACION, PUESTA EN MARCHA Y MANTENCION SOFTWARE EN GESTION FARMACIA Y OPTICA COMUNAL DE LA MUNICIPALIDAD DE HUALPEN</t>
         </is>
       </c>
       <c r="W17" s="5" t="str">
-        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=3945-20-LE26","descargar bases")</f>
+        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=4429-95-LE26","descargar bases")</f>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">4429-95-LE26</t>
+          <t xml:space="preserve">4429-96-LE26</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ARRIENDO SOFTWARE FARMACIA Y OPTICA MUNICIPAL</t>
+          <t xml:space="preserve">SISTEMA INFORMATICO WEB PARA CENTROS DE SALUD</t>
         </is>
       </c>
       <c r="C18" s="0" t="inlineStr">
@@ -2817,16 +1998,16 @@
         </is>
       </c>
       <c r="H18" s="2">
-        <v>46258.511505</v>
+        <v>46258.631748</v>
       </c>
       <c r="I18" s="2">
         <v>46268.600694</v>
       </c>
       <c r="J18" s="0">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K18" s="3">
-        <v>10000000.0</v>
+        <v>32500000.0</v>
       </c>
       <c r="L18" s="0" t="inlineStr">
         <is>
@@ -2845,7 +2026,7 @@
       </c>
       <c r="O18" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 Unidad · Software de gestión de adquisiciones</t>
+          <t xml:space="preserve">1 Unidad · Paquetes de software para oficinas</t>
         </is>
       </c>
       <c r="P18" s="2"/>
@@ -2862,7 +2043,7 @@
       </c>
       <c r="T18" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Se prohíbe absolutamente al adjudicatario ceder o transferir, sea a título gratuito u oneroso, total o parcialmente a terceros los derechos y obligaciones que asuman en virtud de la presente propuesta, y en especial los establecidos en el contrato defini</t>
+          <t xml:space="preserve">Se prohíbe absolutamente al adjudicatario ceder o transferir, sea a título gratuito u oneroso, total o parcialmente a terceros los derechos y obligaciones que asuman en virtud de la presente propuesta, y en especial los establecidos en el contrato defin</t>
         </is>
       </c>
       <c r="U18" s="0" t="inlineStr">
@@ -2872,22 +2053,22 @@
       </c>
       <c r="V18" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">SERVICIO DE ARRIENDO, IMPLEMENTACION, PUESTA EN MARCHA Y MANTENCION SOFTWARE EN GESTION FARMACIA Y OPTICA COMUNAL DE LA MUNICIPALIDAD DE HUALPEN</t>
+          <t xml:space="preserve">Servicio de Sistema Informático Web para la Gestión de Calidad, Seguridad del Paciente, Acreditación y Autorización Sanitaria de los Establecimientos dependientes de la Dirección de Salud Municipal de Hualpén</t>
         </is>
       </c>
       <c r="W18" s="5" t="str">
-        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=4429-95-LE26","descargar bases")</f>
+        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=4429-96-LE26","descargar bases")</f>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">4429-96-LE26</t>
+          <t xml:space="preserve">1431841-53-LE26</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">SISTEMA INFORMATICO WEB PARA CENTROS DE SALUD</t>
+          <t xml:space="preserve">ADQUISICIÓN DE CREDITOS GOOGLE CLOUD PLATFORM</t>
         </is>
       </c>
       <c r="C19" s="0" t="inlineStr">
@@ -2897,35 +2078,35 @@
       </c>
       <c r="D19" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">MUNICIPALIDAD DE HUALPEN</t>
+          <t xml:space="preserve">I MUNICIPALIDAD DE RECOLETA</t>
         </is>
       </c>
       <c r="E19" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dirección de Salud</t>
+          <t xml:space="preserve">DIRECCION  DE COMPRAS PUBLICAS</t>
         </is>
       </c>
       <c r="F19" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t xml:space="preserve">Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="G19" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hualpén</t>
+          <t xml:space="preserve">Recoleta</t>
         </is>
       </c>
       <c r="H19" s="2">
-        <v>46258.631748</v>
+        <v>46253.435475</v>
       </c>
       <c r="I19" s="2">
-        <v>46268.600694</v>
+        <v>46268.625</v>
       </c>
       <c r="J19" s="0">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K19" s="3">
-        <v>32500000.0</v>
+        <v>15000000.0</v>
       </c>
       <c r="L19" s="0" t="inlineStr">
         <is>
@@ -2939,19 +2120,19 @@
       </c>
       <c r="N19" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de gestión</t>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de aplicaciones de red</t>
         </is>
       </c>
       <c r="O19" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 Unidad · Paquetes de software para oficinas</t>
+          <t xml:space="preserve">1 Global · Software de servidor de aplicaciones</t>
         </is>
       </c>
       <c r="P19" s="2"/>
       <c r="Q19" s="2"/>
       <c r="R19" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">36 meses</t>
+          <t xml:space="preserve">12 meses</t>
         </is>
       </c>
       <c r="S19" s="0" t="inlineStr">
@@ -2961,32 +2142,32 @@
       </c>
       <c r="T19" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Se prohíbe absolutamente al adjudicatario ceder o transferir, sea a título gratuito u oneroso, total o parcialmente a terceros los derechos y obligaciones que asuman en virtud de la presente propuesta, y en especial los establecidos en el contrato defin</t>
+          <t xml:space="preserve">El adjudicatario no podrá subcontratar, ceder ni transferir en forma alguna, total ni parcialmente, los derechos y obligaciones que nacen del desarrollo de esta licitación y, en especial, los establecidos en el respectivo contrato que se celebre con la</t>
         </is>
       </c>
       <c r="U19" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">CARLOS CARES MORALES</t>
+          <t xml:space="preserve">Carlos Barraza</t>
         </is>
       </c>
       <c r="V19" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Servicio de Sistema Informático Web para la Gestión de Calidad, Seguridad del Paciente, Acreditación y Autorización Sanitaria de los Establecimientos dependientes de la Dirección de Salud Municipal de Hualpén</t>
+          <t xml:space="preserve">La Municipalidad de Recoleta, a través de su Dirección de Tecnologías de la Información, requiere la adquisición de créditos para Google Cloud Platform GCP por un período de un año, con el fin de soportar la operación, desarrollo y escalabilidad de la aplicación Tarjeta Vecino y otras plataformas municipales críticas, garantizando alta disponibilidad, seguridad, continuidad operativa y cumplimiento de la normativa vigente en materia de ciberseguridad y protección de datos personales.</t>
         </is>
       </c>
       <c r="W19" s="5" t="str">
-        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=4429-96-LE26","descargar bases")</f>
+        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=1431841-53-LE26","descargar bases")</f>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1431841-53-LE26</t>
+          <t xml:space="preserve">3506-88-LP26</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADQUISICIÓN DE CREDITOS GOOGLE CLOUD PLATFORM</t>
+          <t xml:space="preserve">ADQUISICION DE SOFTWARE DE GESTION MUNICIPAL</t>
         </is>
       </c>
       <c r="C20" s="0" t="inlineStr">
@@ -2996,35 +2177,31 @@
       </c>
       <c r="D20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">I MUNICIPALIDAD DE RECOLETA</t>
+          <t xml:space="preserve">I MUNICIPALIDAD DE TOCOPILLA</t>
         </is>
       </c>
       <c r="E20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">DIRECCION  DE COMPRAS PUBLICAS</t>
+          <t xml:space="preserve">UNIDAD DE ADQUISICIONES</t>
         </is>
       </c>
       <c r="F20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región Metropolitana de Santiago</t>
-        </is>
-      </c>
-      <c r="G20" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Recoleta</t>
-        </is>
-      </c>
+          <t xml:space="preserve">Región de Antofagasta </t>
+        </is>
+      </c>
+      <c r="G20" s="0"/>
       <c r="H20" s="2">
-        <v>46253.435475</v>
+        <v>46248.4375</v>
       </c>
       <c r="I20" s="2">
         <v>46268.625</v>
       </c>
       <c r="J20" s="0">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K20" s="3">
-        <v>15000000.0</v>
+        <v>269000000.0</v>
       </c>
       <c r="L20" s="0" t="inlineStr">
         <is>
@@ -3033,24 +2210,24 @@
       </c>
       <c r="M20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">LE</t>
+          <t xml:space="preserve">LP</t>
         </is>
       </c>
       <c r="N20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de aplicaciones de red</t>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de gestión</t>
         </is>
       </c>
       <c r="O20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 Global · Software de servidor de aplicaciones</t>
+          <t xml:space="preserve">1 Unidad · Software de gestión de licencias</t>
         </is>
       </c>
       <c r="P20" s="2"/>
       <c r="Q20" s="2"/>
       <c r="R20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">12 meses</t>
+          <t xml:space="preserve">24 meses</t>
         </is>
       </c>
       <c r="S20" s="0" t="inlineStr">
@@ -3059,101 +2236,6 @@
         </is>
       </c>
       <c r="T20" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">El adjudicatario no podrá subcontratar, ceder ni transferir en forma alguna, total ni parcialmente, los derechos y obligaciones que nacen del desarrollo de esta licitación y, en especial, los establecidos en el respectivo contrato que se celebre con la</t>
-        </is>
-      </c>
-      <c r="U20" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Carlos Barraza</t>
-        </is>
-      </c>
-      <c r="V20" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">La Municipalidad de Recoleta, a través de su Dirección de Tecnologías de la Información, requiere la adquisición de créditos para Google Cloud Platform GCP por un período de un año, con el fin de soportar la operación, desarrollo y escalabilidad de la aplicación Tarjeta Vecino y otras plataformas municipales críticas, garantizando alta disponibilidad, seguridad, continuidad operativa y cumplimiento de la normativa vigente en materia de ciberseguridad y protección de datos personales.</t>
-        </is>
-      </c>
-      <c r="W20" s="5" t="str">
-        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=1431841-53-LE26","descargar bases")</f>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3506-88-LP26</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ADQUISICION DE SOFTWARE DE GESTION MUNICIPAL</t>
-        </is>
-      </c>
-      <c r="C21" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Publicada</t>
-        </is>
-      </c>
-      <c r="D21" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">I MUNICIPALIDAD DE TOCOPILLA</t>
-        </is>
-      </c>
-      <c r="E21" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UNIDAD DE ADQUISICIONES</t>
-        </is>
-      </c>
-      <c r="F21" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
-        </is>
-      </c>
-      <c r="G21" s="0"/>
-      <c r="H21" s="2">
-        <v>46248.4375</v>
-      </c>
-      <c r="I21" s="2">
-        <v>46268.625</v>
-      </c>
-      <c r="J21" s="0">
-        <v>3</v>
-      </c>
-      <c r="K21" s="3">
-        <v>269000000.0</v>
-      </c>
-      <c r="L21" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CLP</t>
-        </is>
-      </c>
-      <c r="M21" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LP</t>
-        </is>
-      </c>
-      <c r="N21" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de gestión</t>
-        </is>
-      </c>
-      <c r="O21" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1 Unidad · Software de gestión de licencias</t>
-        </is>
-      </c>
-      <c r="P21" s="2"/>
-      <c r="Q21" s="2"/>
-      <c r="R21" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24 meses</t>
-        </is>
-      </c>
-      <c r="S21" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">No</t>
-        </is>
-      </c>
-      <c r="T21" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">En la presente licitación solo se permitirá la subcontratación de servicios 
 puntuales como arriendo de maquinarias y equipos. Queda prohibida la subcontratación 
@@ -3161,29 +2243,118 @@
 del</t>
         </is>
       </c>
-      <c r="U21" s="0" t="inlineStr">
+      <c r="U20" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">DYLAN VALLEJOS</t>
         </is>
       </c>
+      <c r="V20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Se requiere el ADQUISICION DE SOFTWARE DE GESTION MUNICIPAL”. Esta adquisición debe considerar todo los especificado en las Bases Administrativas y Especificaciones técnicas</t>
+        </is>
+      </c>
+      <c r="W20" s="5" t="str">
+        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=3506-88-LP26","descargar bases")</f>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">761391-124-L126</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DE/54/GUB/PLATAFORMA DE PREPARACIÓN PARA EL EXAMEN TOEIC LISTENING AND READING</t>
+        </is>
+      </c>
+      <c r="C21" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Publicada</t>
+        </is>
+      </c>
+      <c r="D21" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+        </is>
+      </c>
+      <c r="E21" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Base Aérea El Bosque</t>
+        </is>
+      </c>
+      <c r="F21" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="G21" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">El Bosque</t>
+        </is>
+      </c>
+      <c r="H21" s="2">
+        <v>46255.420208</v>
+      </c>
+      <c r="I21" s="2">
+        <v>46268.625</v>
+      </c>
+      <c r="J21" s="0">
+        <v>2</v>
+      </c>
+      <c r="K21" s="3">
+        <v>1989000.0</v>
+      </c>
+      <c r="L21" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CLP</t>
+        </is>
+      </c>
+      <c r="M21" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L1</t>
+        </is>
+      </c>
+      <c r="N21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Educación, formación, entrenamiento y capacitación / Sistemas educativos complementarios / Educación de adultos</t>
+        </is>
+      </c>
+      <c r="O21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13 Unidad · Capacitación a empleados</t>
+        </is>
+      </c>
+      <c r="P21" s="2"/>
+      <c r="Q21" s="2"/>
+      <c r="R21" s="0"/>
+      <c r="S21" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="T21" s="4"/>
+      <c r="U21" s="0"/>
       <c r="V21" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Se requiere el ADQUISICION DE SOFTWARE DE GESTION MUNICIPAL”. Esta adquisición debe considerar todo los especificado en las Bases Administrativas y Especificaciones técnicas</t>
+          <t xml:space="preserve">DE/54/GUB/PLATAFORMA DE PREPARACIÓN PARA EL EXAMEN TOEIC LISTENING AND READING
+SE ADJUNTAN BASES TÉCNICAS 
+SE ADJUNTAN ANEXOS EDITABLES</t>
         </is>
       </c>
       <c r="W21" s="5" t="str">
-        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=3506-88-LP26","descargar bases")</f>
+        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=761391-124-L126","descargar bases")</f>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">761391-124-L126</t>
+          <t xml:space="preserve">3477-77-LE26</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">DE/54/GUB/PLATAFORMA DE PREPARACIÓN PARA EL EXAMEN TOEIC LISTENING AND READING</t>
+          <t xml:space="preserve">“INSTALACIÓN DE PUNTOS DE RED EN UDEL” SECCIÓN DE INFORMÁTICA MUNICIPAL</t>
         </is>
       </c>
       <c r="C22" s="0" t="inlineStr">
@@ -3193,35 +2364,35 @@
       </c>
       <c r="D22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+          <t xml:space="preserve">I MUNICIPALIDAD DE VILCUN</t>
         </is>
       </c>
       <c r="E22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Base Aérea El Bosque</t>
+          <t xml:space="preserve"> Area Municipal</t>
         </is>
       </c>
       <c r="F22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región Metropolitana de Santiago</t>
+          <t xml:space="preserve">Región de la Araucanía </t>
         </is>
       </c>
       <c r="G22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">El Bosque</t>
+          <t xml:space="preserve">Vilcún</t>
         </is>
       </c>
       <c r="H22" s="2">
-        <v>46255.420208</v>
+        <v>46255.680382</v>
       </c>
       <c r="I22" s="2">
-        <v>46268.625</v>
+        <v>46268.645833</v>
       </c>
       <c r="J22" s="0">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K22" s="3">
-        <v>1989000.0</v>
+        <v>8000000.0</v>
       </c>
       <c r="L22" s="0" t="inlineStr">
         <is>
@@ -3230,17 +2401,17 @@
       </c>
       <c r="M22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">L1</t>
+          <t xml:space="preserve">LE</t>
         </is>
       </c>
       <c r="N22" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Educación, formación, entrenamiento y capacitación / Sistemas educativos complementarios / Educación de adultos</t>
+          <t xml:space="preserve">Servicios profesionales, administrativos y consultorías de gestión empresarial / Servicios de recursos humanos / Servicios de personal temporal</t>
         </is>
       </c>
       <c r="O22" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">13 Unidad · Capacitación a empleados</t>
+          <t xml:space="preserve">1 Global · Especialistas temporales en redes computacionales</t>
         </is>
       </c>
       <c r="P22" s="2"/>
@@ -3252,27 +2423,30 @@
         </is>
       </c>
       <c r="T22" s="4"/>
-      <c r="U22" s="0"/>
+      <c r="U22" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cristian Sepulveda</t>
+        </is>
+      </c>
       <c r="V22" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">DE/54/GUB/PLATAFORMA DE PREPARACIÓN PARA EL EXAMEN TOEIC LISTENING AND READING
-SE ADJUNTAN BASES TÉCNICAS 
-SE ADJUNTAN ANEXOS EDITABLES</t>
+          <t xml:space="preserve">“INSTALACIÓN DE PUNTOS DE RED EN UDEL”
+SECCIÓN DE INFORMÁTICA MUNICIPAL. SEGUN BASES ADJUNTAS.</t>
         </is>
       </c>
       <c r="W22" s="5" t="str">
-        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=761391-124-L126","descargar bases")</f>
+        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=3477-77-LE26","descargar bases")</f>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">3477-77-LE26</t>
+          <t xml:space="preserve">730566-21-LP26</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">“INSTALACIÓN DE PUNTOS DE RED EN UDEL” SECCIÓN DE INFORMÁTICA MUNICIPAL</t>
+          <t xml:space="preserve">RENOVACIÓN DE PLATAFORMA WIFI</t>
         </is>
       </c>
       <c r="C23" s="0" t="inlineStr">
@@ -3282,89 +2456,94 @@
       </c>
       <c r="D23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">I MUNICIPALIDAD DE VILCUN</t>
+          <t xml:space="preserve">SUBSECRETARIA DE EVALUACION SOCIAL</t>
         </is>
       </c>
       <c r="E23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Area Municipal</t>
+          <t xml:space="preserve">Subsecretaría de Evaluación Social</t>
         </is>
       </c>
       <c r="F23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t xml:space="preserve">Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="G23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vilcún</t>
+          <t xml:space="preserve">Santiago</t>
         </is>
       </c>
       <c r="H23" s="2">
-        <v>46255.680382</v>
+        <v>46258.64419</v>
       </c>
       <c r="I23" s="2">
         <v>46268.645833</v>
       </c>
       <c r="J23" s="0">
-        <v>3</v>
-      </c>
-      <c r="K23" s="3">
-        <v>8000000.0</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="K23" s="3"/>
       <c r="L23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">CLP</t>
+          <t xml:space="preserve">USD</t>
         </is>
       </c>
       <c r="M23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">LE</t>
+          <t xml:space="preserve">LP</t>
         </is>
       </c>
       <c r="N23" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Servicios profesionales, administrativos y consultorías de gestión empresarial / Servicios de recursos humanos / Servicios de personal temporal</t>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Equipos, plataformas y accesorios de redes multimedia, voz y datos / Equipos de servicio de red, Tecnologías de la información, telecomunicaciones y radiodifusión / Equipos, plataformas y accesorios de redes multimedia, voz y datos / Plataformas de mensajería por móvil</t>
         </is>
       </c>
       <c r="O23" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 Global · Especialistas temporales en redes computacionales</t>
+          <t xml:space="preserve">100 Unidad · Dispositivos de acceso de red digital de servicios integrados (RDSI) · 1 Unidad · Plataforma de mensajería unificada</t>
         </is>
       </c>
       <c r="P23" s="2"/>
       <c r="Q23" s="2"/>
-      <c r="R23" s="0"/>
+      <c r="R23" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">36 meses</t>
+        </is>
+      </c>
       <c r="S23" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">No</t>
         </is>
       </c>
-      <c r="T23" s="4"/>
+      <c r="T23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Según punto 9 de las bases adjuntas</t>
+        </is>
+      </c>
       <c r="U23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cristian Sepulveda</t>
+          <t xml:space="preserve">Fabián Abarca</t>
         </is>
       </c>
       <c r="V23" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">“INSTALACIÓN DE PUNTOS DE RED EN UDEL”
-SECCIÓN DE INFORMÁTICA MUNICIPAL. SEGUN BASES ADJUNTAS.</t>
+          <t xml:space="preserve">Su objeto es actualizar tecnológicamente y optimizar el estándar de conexión, efectuando una adquisición habilitante y estratégica que optimizará el tiempo del equipo de TI, garantizará una conectividad segura y de baja latencia para los usuarios, y alineará a la institución con los estándares de ciberseguridad y rendimiento que demandan los servicios públicos modernos.</t>
         </is>
       </c>
       <c r="W23" s="5" t="str">
-        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=3477-77-LE26","descargar bases")</f>
+        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=730566-21-LP26","descargar bases")</f>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">730566-21-LP26</t>
+          <t xml:space="preserve">2427-73-LE26</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">RENOVACIÓN DE PLATAFORMA WIFI</t>
+          <t xml:space="preserve">SUMINISTRO DE MARKETING DIGITAL PARA REDES SOCIALES DEL MUNICIPIO DE VALPARAÍSO</t>
         </is>
       </c>
       <c r="C24" s="0" t="inlineStr">
@@ -3374,94 +2553,84 @@
       </c>
       <c r="D24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">SUBSECRETARIA DE EVALUACION SOCIAL</t>
+          <t xml:space="preserve">I MUNICIPALIDAD DE VALPARAISO</t>
         </is>
       </c>
       <c r="E24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Subsecretaría de Evaluación Social</t>
+          <t xml:space="preserve">ABASTECIMIENTO</t>
         </is>
       </c>
       <c r="F24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región Metropolitana de Santiago</t>
-        </is>
-      </c>
-      <c r="G24" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Santiago</t>
-        </is>
-      </c>
+          <t xml:space="preserve">Región de Valparaíso </t>
+        </is>
+      </c>
+      <c r="G24" s="0"/>
       <c r="H24" s="2">
-        <v>46258.64419</v>
+        <v>46258.560174</v>
       </c>
       <c r="I24" s="2">
-        <v>46268.645833</v>
+        <v>46268.666667</v>
       </c>
       <c r="J24" s="0">
-        <v>3</v>
-      </c>
-      <c r="K24" s="3"/>
+        <v>2</v>
+      </c>
+      <c r="K24" s="3">
+        <v>14000000.0</v>
+      </c>
       <c r="L24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">USD</t>
+          <t xml:space="preserve">CLP</t>
         </is>
       </c>
       <c r="M24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">LP</t>
+          <t xml:space="preserve">LE</t>
         </is>
       </c>
       <c r="N24" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Equipos, plataformas y accesorios de redes multimedia, voz y datos / Equipos de servicio de red, Tecnologías de la información, telecomunicaciones y radiodifusión / Equipos, plataformas y accesorios de redes multimedia, voz y datos / Plataformas de mensajería por móvil</t>
+          <t xml:space="preserve">Servicios profesionales, administrativos y consultorías de gestión empresarial / Servicios para la comercialización y distribución / Ventas y marketing</t>
         </is>
       </c>
       <c r="O24" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">100 Unidad · Dispositivos de acceso de red digital de servicios integrados (RDSI) · 1 Unidad · Plataforma de mensajería unificada</t>
+          <t xml:space="preserve">1 Unidad · Agencias de marketing de ventas, incluidas las impresiones</t>
         </is>
       </c>
       <c r="P24" s="2"/>
       <c r="Q24" s="2"/>
-      <c r="R24" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">36 meses</t>
-        </is>
-      </c>
+      <c r="R24" s="0"/>
       <c r="S24" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">No</t>
         </is>
       </c>
-      <c r="T24" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Según punto 9 de las bases adjuntas</t>
-        </is>
-      </c>
+      <c r="T24" s="4"/>
       <c r="U24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fabián Abarca</t>
+          <t xml:space="preserve">CHRISTOPHER GEEP</t>
         </is>
       </c>
       <c r="V24" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Su objeto es actualizar tecnológicamente y optimizar el estándar de conexión, efectuando una adquisición habilitante y estratégica que optimizará el tiempo del equipo de TI, garantizará una conectividad segura y de baja latencia para los usuarios, y alineará a la institución con los estándares de ciberseguridad y rendimiento que demandan los servicios públicos modernos.</t>
+          <t xml:space="preserve">Pedido 24 Gabinete - Imagen Corporativa.</t>
         </is>
       </c>
       <c r="W24" s="5" t="str">
-        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=730566-21-LP26","descargar bases")</f>
+        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=2427-73-LE26","descargar bases")</f>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2427-73-LE26</t>
+          <t xml:space="preserve">2258-146-LP26</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">SUMINISTRO DE MARKETING DIGITAL PARA REDES SOCIALES DEL MUNICIPIO DE VALPARAÍSO</t>
+          <t xml:space="preserve">AUDIFONOS DIGITAL PAC.GES HIPOACUSIA BILATERAL</t>
         </is>
       </c>
       <c r="C25" s="0" t="inlineStr">
@@ -3471,32 +2640,34 @@
       </c>
       <c r="D25" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">I MUNICIPALIDAD DE VALPARAISO</t>
+          <t xml:space="preserve">SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="E25" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ABASTECIMIENTO</t>
+          <t xml:space="preserve">Abastecimiento Principal</t>
         </is>
       </c>
       <c r="F25" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
-        </is>
-      </c>
-      <c r="G25" s="0"/>
+          <t xml:space="preserve">Región de Antofagasta </t>
+        </is>
+      </c>
+      <c r="G25" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Antofagasta</t>
+        </is>
+      </c>
       <c r="H25" s="2">
-        <v>46258.560174</v>
+        <v>46248.581736</v>
       </c>
       <c r="I25" s="2">
-        <v>46268.666667</v>
+        <v>46268.675</v>
       </c>
       <c r="J25" s="0">
-        <v>3</v>
-      </c>
-      <c r="K25" s="3">
-        <v>14000000.0</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="K25" s="3"/>
       <c r="L25" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">CLP</t>
@@ -3504,22 +2675,26 @@
       </c>
       <c r="M25" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">LE</t>
+          <t xml:space="preserve">LP</t>
         </is>
       </c>
       <c r="N25" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Servicios profesionales, administrativos y consultorías de gestión empresarial / Servicios para la comercialización y distribución / Ventas y marketing</t>
+          <t xml:space="preserve">Equipamiento y suministros médicos / Ayuda para personas con discapacidad / Artículos de ayuda para la comunicación de discapacitados</t>
         </is>
       </c>
       <c r="O25" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 Unidad · Agencias de marketing de ventas, incluidas las impresiones</t>
+          <t xml:space="preserve">900 Unidad · Audífonos para personas con discapacidad física · 504 Unidad · Audífonos para personas con discapacidad física</t>
         </is>
       </c>
       <c r="P25" s="2"/>
       <c r="Q25" s="2"/>
-      <c r="R25" s="0"/>
+      <c r="R25" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12 meses</t>
+        </is>
+      </c>
       <c r="S25" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">No</t>
@@ -3528,27 +2703,27 @@
       <c r="T25" s="4"/>
       <c r="U25" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">CHRISTOPHER GEEP</t>
+          <t xml:space="preserve">Sebastian Castillo Eitner</t>
         </is>
       </c>
       <c r="V25" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pedido 24 Gabinete - Imagen Corporativa.</t>
+          <t xml:space="preserve">Cotizar valores netos</t>
         </is>
       </c>
       <c r="W25" s="5" t="str">
-        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=2427-73-LE26","descargar bases")</f>
+        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=2258-146-LP26","descargar bases")</f>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2258-146-LP26</t>
+          <t xml:space="preserve">1483311-2-LP26</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUDIFONOS DIGITAL PAC.GES HIPOACUSIA BILATERAL</t>
+          <t xml:space="preserve">SERVICIO DE ARRIENDO DE SOFTWARE DE REMUNERACIONES</t>
         </is>
       </c>
       <c r="C26" s="0" t="inlineStr">
@@ -3558,34 +2733,32 @@
       </c>
       <c r="D26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t xml:space="preserve">SERVICIO LOCAL DE EDUCACIÓN PÚBLICA LOS VIÑEDOS</t>
         </is>
       </c>
       <c r="E26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Abastecimiento Principal</t>
+          <t xml:space="preserve">SERVICIO LOCAL DE EDUCACIÓN PÚBLICA LOS VIÑEDOS</t>
         </is>
       </c>
       <c r="F26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
-        </is>
-      </c>
-      <c r="G26" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Antofagasta</t>
-        </is>
-      </c>
+          <t xml:space="preserve">Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="G26" s="0"/>
       <c r="H26" s="2">
-        <v>46248.581736</v>
+        <v>46248.714144</v>
       </c>
       <c r="I26" s="2">
-        <v>46268.675</v>
+        <v>46268.708333</v>
       </c>
       <c r="J26" s="0">
-        <v>3</v>
-      </c>
-      <c r="K26" s="3"/>
+        <v>2</v>
+      </c>
+      <c r="K26" s="3">
+        <v>202000000.0</v>
+      </c>
       <c r="L26" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">CLP</t>
@@ -3598,19 +2771,19 @@
       </c>
       <c r="N26" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Equipamiento y suministros médicos / Ayuda para personas con discapacidad / Artículos de ayuda para la comunicación de discapacitados</t>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de gestión</t>
         </is>
       </c>
       <c r="O26" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">900 Unidad · Audífonos para personas con discapacidad física · 504 Unidad · Audífonos para personas con discapacidad física</t>
+          <t xml:space="preserve">1 Unidad · Software de gestión de recursos humanos · 1 Unidad · Software de gestión de recursos humanos</t>
         </is>
       </c>
       <c r="P26" s="2"/>
       <c r="Q26" s="2"/>
       <c r="R26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">12 meses</t>
+          <t xml:space="preserve">24 meses</t>
         </is>
       </c>
       <c r="S26" s="0" t="inlineStr">
@@ -3621,27 +2794,27 @@
       <c r="T26" s="4"/>
       <c r="U26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sebastian Castillo Eitner</t>
+          <t xml:space="preserve">Francisca Pérez Godoy</t>
         </is>
       </c>
       <c r="V26" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cotizar valores netos</t>
+          <t xml:space="preserve">Adquirir servicio de arriendo de software de remuneraciones y gestión de personas P01 y P02, con el objeto de administrar la gestión del personal contratado y particularmente en lo que se refiere al pago de remuneraciones de los funcionarios y funcionarias nivel central, docentes y asistentes de la educación del Slep Los Viñedos.</t>
         </is>
       </c>
       <c r="W26" s="5" t="str">
-        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=2258-146-LP26","descargar bases")</f>
+        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=1483311-2-LP26","descargar bases")</f>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1483311-2-LP26</t>
+          <t xml:space="preserve">1422051-25-LE26</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">SERVICIO DE ARRIENDO DE SOFTWARE DE REMUNERACIONES</t>
+          <t xml:space="preserve">Contratación Servicio Plataforma de Gestión RRHH</t>
         </is>
       </c>
       <c r="C27" s="0" t="inlineStr">
@@ -3651,12 +2824,12 @@
       </c>
       <c r="D27" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">SERVICIO LOCAL DE EDUCACIÓN PÚBLICA LOS VIÑEDOS</t>
+          <t xml:space="preserve">JUNTA DE ALCALDES PROVIDENCIA LAS CONDES LA REINA</t>
         </is>
       </c>
       <c r="E27" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">SERVICIO LOCAL DE EDUCACIÓN PÚBLICA LOS VIÑEDOS</t>
+          <t xml:space="preserve">JUNTA DE ALCALDES PROVIDENCIA LAS CONDES LA REINA</t>
         </is>
       </c>
       <c r="F27" s="0" t="inlineStr">
@@ -3666,16 +2839,16 @@
       </c>
       <c r="G27" s="0"/>
       <c r="H27" s="2">
-        <v>46248.714144</v>
+        <v>46253.682894</v>
       </c>
       <c r="I27" s="2">
-        <v>46268.708333</v>
+        <v>46268.75</v>
       </c>
       <c r="J27" s="0">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K27" s="3">
-        <v>202000000.0</v>
+        <v>32000000.0</v>
       </c>
       <c r="L27" s="0" t="inlineStr">
         <is>
@@ -3684,7 +2857,7 @@
       </c>
       <c r="M27" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">LP</t>
+          <t xml:space="preserve">LE</t>
         </is>
       </c>
       <c r="N27" s="4" t="inlineStr">
@@ -3694,14 +2867,14 @@
       </c>
       <c r="O27" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 Unidad · Software de gestión de recursos humanos · 1 Unidad · Software de gestión de recursos humanos</t>
+          <t xml:space="preserve">1 Unidad · Software de gestión de recursos humanos</t>
         </is>
       </c>
       <c r="P27" s="2"/>
       <c r="Q27" s="2"/>
       <c r="R27" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24 meses</t>
+          <t xml:space="preserve">24 horas</t>
         </is>
       </c>
       <c r="S27" s="0" t="inlineStr">
@@ -3712,27 +2885,27 @@
       <c r="T27" s="4"/>
       <c r="U27" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Francisca Pérez Godoy</t>
+          <t xml:space="preserve">Hector Fuentealba Riquelme</t>
         </is>
       </c>
       <c r="V27" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adquirir servicio de arriendo de software de remuneraciones y gestión de personas P01 y P02, con el objeto de administrar la gestión del personal contratado y particularmente en lo que se refiere al pago de remuneraciones de los funcionarios y funcionarias nivel central, docentes y asistentes de la educación del Slep Los Viñedos.</t>
+          <t xml:space="preserve">Implementar una plataforma integral de gestión de personas para la Junta de Alcaldes, orientada a dar solución a los requerimientos derivados de las funciones comunes y diarias de la institución.</t>
         </is>
       </c>
       <c r="W27" s="5" t="str">
-        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=1483311-2-LP26","descargar bases")</f>
+        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=1422051-25-LE26","descargar bases")</f>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1422051-25-LE26</t>
+          <t xml:space="preserve">727202-69-LE26</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contratación Servicio Plataforma de Gestión RRHH</t>
+          <t xml:space="preserve">ADQUISICIÓN E IMPLEMENTACIÓN DE TÓTEMS</t>
         </is>
       </c>
       <c r="C28" s="0" t="inlineStr">
@@ -3742,31 +2915,35 @@
       </c>
       <c r="D28" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">JUNTA DE ALCALDES PROVIDENCIA LAS CONDES LA REINA</t>
+          <t xml:space="preserve">I MUNICIPALIDAD DE VICUNA</t>
         </is>
       </c>
       <c r="E28" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">JUNTA DE ALCALDES PROVIDENCIA LAS CONDES LA REINA</t>
+          <t xml:space="preserve">Secplan</t>
         </is>
       </c>
       <c r="F28" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región Metropolitana de Santiago</t>
-        </is>
-      </c>
-      <c r="G28" s="0"/>
+          <t xml:space="preserve">Región de Coquimbo </t>
+        </is>
+      </c>
+      <c r="G28" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vicuña</t>
+        </is>
+      </c>
       <c r="H28" s="2">
-        <v>46253.682894</v>
+        <v>46253.654167</v>
       </c>
       <c r="I28" s="2">
-        <v>46268.75</v>
+        <v>46269.375</v>
       </c>
       <c r="J28" s="0">
         <v>3</v>
       </c>
       <c r="K28" s="3">
-        <v>32000000.0</v>
+        <v>13000000.0</v>
       </c>
       <c r="L28" s="0" t="inlineStr">
         <is>
@@ -3780,19 +2957,19 @@
       </c>
       <c r="N28" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de gestión</t>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Equipos informáticos y accesorios / Pantallas o monitores de computador</t>
         </is>
       </c>
       <c r="O28" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 Unidad · Software de gestión de recursos humanos</t>
+          <t xml:space="preserve">1 Global · Monitores de pantalla táctil</t>
         </is>
       </c>
       <c r="P28" s="2"/>
       <c r="Q28" s="2"/>
       <c r="R28" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24 horas</t>
+          <t xml:space="preserve">60 días</t>
         </is>
       </c>
       <c r="S28" s="0" t="inlineStr">
@@ -3803,27 +2980,27 @@
       <c r="T28" s="4"/>
       <c r="U28" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hector Fuentealba Riquelme</t>
+          <t xml:space="preserve">Mario Aros Carvajal</t>
         </is>
       </c>
       <c r="V28" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Implementar una plataforma integral de gestión de personas para la Junta de Alcaldes, orientada a dar solución a los requerimientos derivados de las funciones comunes y diarias de la institución.</t>
+          <t xml:space="preserve">Adquisición e implementación de tótems interactivos con inteligencia artificial y sistema de gestión de contenidos para el museo del Observatorio Mamalluca, conforme a la documentación técnica adjunta.</t>
         </is>
       </c>
       <c r="W28" s="5" t="str">
-        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=1422051-25-LE26","descargar bases")</f>
+        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=727202-69-LE26","descargar bases")</f>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">727202-69-LE26</t>
+          <t xml:space="preserve">3553-29-LE26</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADQUISICIÓN E IMPLEMENTACIÓN DE TÓTEMS</t>
+          <t xml:space="preserve">Serv. jurídicos de Ley 21.719 y prot. de datos</t>
         </is>
       </c>
       <c r="C29" s="0" t="inlineStr">
@@ -3833,35 +3010,35 @@
       </c>
       <c r="D29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">I MUNICIPALIDAD DE VICUNA</t>
+          <t xml:space="preserve">MINISTERIO DE BIENES NACIONALES</t>
         </is>
       </c>
       <c r="E29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Secplan</t>
+          <t xml:space="preserve">MINISTERIO DE BIENES NACIONALES</t>
         </is>
       </c>
       <c r="F29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t xml:space="preserve">Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="G29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vicuña</t>
+          <t xml:space="preserve">Santiago Centro</t>
         </is>
       </c>
       <c r="H29" s="2">
-        <v>46253.654167</v>
+        <v>46258.536296</v>
       </c>
       <c r="I29" s="2">
-        <v>46269.375</v>
+        <v>46269.5</v>
       </c>
       <c r="J29" s="0">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K29" s="3">
-        <v>13000000.0</v>
+        <v>40856640.0</v>
       </c>
       <c r="L29" s="0" t="inlineStr">
         <is>
@@ -3875,19 +3052,19 @@
       </c>
       <c r="N29" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Equipos informáticos y accesorios / Pantallas o monitores de computador</t>
+          <t xml:space="preserve">Organizaciones sociales, laborales y clubes / Organizaciones, asociaciones y movimientos cívicos / Organizaciones de beneficencia</t>
         </is>
       </c>
       <c r="O29" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 Global · Monitores de pantalla táctil</t>
+          <t xml:space="preserve">1 Unidad · Servicios de asistencia legal y judicial</t>
         </is>
       </c>
       <c r="P29" s="2"/>
       <c r="Q29" s="2"/>
       <c r="R29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">60 días</t>
+          <t xml:space="preserve">90 días</t>
         </is>
       </c>
       <c r="S29" s="0" t="inlineStr">
@@ -3898,27 +3075,27 @@
       <c r="T29" s="4"/>
       <c r="U29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mario Aros Carvajal</t>
+          <t xml:space="preserve">Stefan Andrés Goecke Ruz</t>
         </is>
       </c>
       <c r="V29" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adquisición e implementación de tótems interactivos con inteligencia artificial y sistema de gestión de contenidos para el museo del Observatorio Mamalluca, conforme a la documentación técnica adjunta.</t>
+          <t xml:space="preserve">El objeto de la contratación es contar con un marco institucional actualizado, coherente y articulado con la normativa vigente, mediante el levantamiento de información, análisis de brechas normativasoperativas y la propuesta de un cuerpo regulatorio interno directrices, protocolos y manuales en el Ministerio de Bienes Nacionales incluyendo las SEREMIS frente a las nuevas exigencias de la Ley.</t>
         </is>
       </c>
       <c r="W29" s="5" t="str">
-        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=727202-69-LE26","descargar bases")</f>
+        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=3553-29-LE26","descargar bases")</f>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">3553-29-LE26</t>
+          <t xml:space="preserve">1469-173-L126</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Serv. jurídicos de Ley 21.719 y prot. de datos</t>
+          <t xml:space="preserve">Sistema de gestión de Libro de Obras Digital, para PIBV</t>
         </is>
       </c>
       <c r="C30" s="0" t="inlineStr">
@@ -3928,35 +3105,35 @@
       </c>
       <c r="D30" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">MINISTERIO DE BIENES NACIONALES</t>
+          <t xml:space="preserve">UNIVERSIDAD DE TALCA</t>
         </is>
       </c>
       <c r="E30" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">MINISTERIO DE BIENES NACIONALES</t>
+          <t xml:space="preserve">Universidad de Talca</t>
         </is>
       </c>
       <c r="F30" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región Metropolitana de Santiago</t>
+          <t xml:space="preserve">Región del Maule </t>
         </is>
       </c>
       <c r="G30" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Santiago Centro</t>
+          <t xml:space="preserve">Talca</t>
         </is>
       </c>
       <c r="H30" s="2">
-        <v>46258.536296</v>
+        <v>46259.516007</v>
       </c>
       <c r="I30" s="2">
-        <v>46269.5</v>
+        <v>46269.625</v>
       </c>
       <c r="J30" s="0">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K30" s="3">
-        <v>40856640.0</v>
+        <v>2500000.0</v>
       </c>
       <c r="L30" s="0" t="inlineStr">
         <is>
@@ -3965,55 +3142,47 @@
       </c>
       <c r="M30" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">LE</t>
+          <t xml:space="preserve">L1</t>
         </is>
       </c>
       <c r="N30" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Organizaciones sociales, laborales y clubes / Organizaciones, asociaciones y movimientos cívicos / Organizaciones de beneficencia</t>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de consultas y gestión de datos</t>
         </is>
       </c>
       <c r="O30" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 Unidad · Servicios de asistencia legal y judicial</t>
+          <t xml:space="preserve">1 Unidad · Software de búsqueda o recuperación de información</t>
         </is>
       </c>
       <c r="P30" s="2"/>
       <c r="Q30" s="2"/>
-      <c r="R30" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">90 días</t>
-        </is>
-      </c>
+      <c r="R30" s="0"/>
       <c r="S30" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">No</t>
         </is>
       </c>
       <c r="T30" s="4"/>
-      <c r="U30" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Stefan Andrés Goecke Ruz</t>
-        </is>
-      </c>
+      <c r="U30" s="0"/>
       <c r="V30" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">El objeto de la contratación es contar con un marco institucional actualizado, coherente y articulado con la normativa vigente, mediante el levantamiento de información, análisis de brechas normativasoperativas y la propuesta de un cuerpo regulatorio interno directrices, protocolos y manuales en el Ministerio de Bienes Nacionales incluyendo las SEREMIS frente a las nuevas exigencias de la Ley.</t>
+          <t xml:space="preserve">La Universidad de Talca requiere del servicio de plataforma de Libro de Obra Digital para continuar con el requerimiento del Convenio PIBV, por un periodo de 15 meses.</t>
         </is>
       </c>
       <c r="W30" s="5" t="str">
-        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=3553-29-LE26","descargar bases")</f>
+        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=1469-173-L126","descargar bases")</f>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1469-173-L126</t>
+          <t xml:space="preserve">869591-9-LR26</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sistema de gestión de Libro de Obras Digital, para PIBV</t>
+          <t xml:space="preserve">CONTRATACIÓN DEL DESARROLLO DE LA PLATAFORMA MODULAR DE COMPRAS NUEVOS MECANISMOS PARA LA DIRECCIÓN DE COMPRAS Y CONTRATACIÓN PÚBLICA.</t>
         </is>
       </c>
       <c r="C31" s="0" t="inlineStr">
@@ -4023,84 +3192,94 @@
       </c>
       <c r="D31" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">UNIVERSIDAD DE TALCA</t>
+          <t xml:space="preserve">DIRECCION DE COMPRAS Y CONTRATACION PUBLICA</t>
         </is>
       </c>
       <c r="E31" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Universidad de Talca</t>
+          <t xml:space="preserve">Calidad del Gasto en las Compras Públicas</t>
         </is>
       </c>
       <c r="F31" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t xml:space="preserve">Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="G31" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Talca</t>
+          <t xml:space="preserve">Santiago Centro</t>
         </is>
       </c>
       <c r="H31" s="2">
-        <v>46259.516007</v>
+        <v>46233.318056</v>
       </c>
       <c r="I31" s="2">
         <v>46269.625</v>
       </c>
       <c r="J31" s="0">
-        <v>4</v>
-      </c>
-      <c r="K31" s="3">
-        <v>2500000.0</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="K31" s="3"/>
       <c r="L31" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">CLP</t>
+          <t xml:space="preserve">CLF</t>
         </is>
       </c>
       <c r="M31" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">L1</t>
+          <t xml:space="preserve">LR</t>
         </is>
       </c>
       <c r="N31" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de consultas y gestión de datos</t>
+          <t xml:space="preserve">Servicios profesionales, administrativos y consultorías de gestión empresarial / Servicios de recursos humanos / Contratación de personal</t>
         </is>
       </c>
       <c r="O31" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 Unidad · Software de búsqueda o recuperación de información</t>
+          <t xml:space="preserve">1 Unidad · Desarrolladores de software</t>
         </is>
       </c>
       <c r="P31" s="2"/>
       <c r="Q31" s="2"/>
-      <c r="R31" s="0"/>
+      <c r="R31" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25 meses</t>
+        </is>
+      </c>
       <c r="S31" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">No</t>
         </is>
       </c>
-      <c r="T31" s="4"/>
-      <c r="U31" s="0"/>
+      <c r="T31" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ver clausula 10 de las bases especiales</t>
+        </is>
+      </c>
+      <c r="U31" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Miguel Herrera</t>
+        </is>
+      </c>
       <c r="V31" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">La Universidad de Talca requiere del servicio de plataforma de Libro de Obra Digital para continuar con el requerimiento del Convenio PIBV, por un periodo de 15 meses.</t>
+          <t xml:space="preserve">CONTRATACIÓN DEL DESARROLLO DE LA PLATAFORMA MODULAR DE COMPRAS (NUEVOS MECANISMOS) PARA LA DIRECCIÓN DE COMPRAS Y CONTRATACIÓN PÚBLICA.</t>
         </is>
       </c>
       <c r="W31" s="5" t="str">
-        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=1469-173-L126","descargar bases")</f>
+        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=869591-9-LR26","descargar bases")</f>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">869591-9-LR26</t>
+          <t xml:space="preserve">1641-323-LE26</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">CONTRATACIÓN DEL DESARROLLO DE LA PLATAFORMA MODULAR DE COMPRAS NUEVOS MECANISMOS PARA LA DIRECCIÓN DE COMPRAS Y CONTRATACIÓN PÚBLICA.</t>
+          <t xml:space="preserve">FMM - SUMINISTRO DE LICENCIA DE SOFTWARE AUTOCAD PARA OBRAS</t>
         </is>
       </c>
       <c r="C32" s="0" t="inlineStr">
@@ -4110,12 +3289,12 @@
       </c>
       <c r="D32" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">DIRECCION DE COMPRAS Y CONTRATACION PUBLICA</t>
+          <t xml:space="preserve">SERVICIO DE SALUD OCCIDENTE HOSPITAL SAN JUAN DE DIOS</t>
         </is>
       </c>
       <c r="E32" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Calidad del Gasto en las Compras Públicas</t>
+          <t xml:space="preserve">SERVICIO DE SALUD OCCIDENTE HOSPITAL SAN JUAN DE D</t>
         </is>
       </c>
       <c r="F32" s="0" t="inlineStr">
@@ -4123,46 +3302,42 @@
           <t xml:space="preserve">Región Metropolitana de Santiago</t>
         </is>
       </c>
-      <c r="G32" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Santiago Centro</t>
-        </is>
-      </c>
+      <c r="G32" s="0"/>
       <c r="H32" s="2">
-        <v>46233.318056</v>
+        <v>46259.479363</v>
       </c>
       <c r="I32" s="2">
-        <v>46269.625</v>
+        <v>46269.666667</v>
       </c>
       <c r="J32" s="0">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K32" s="3"/>
       <c r="L32" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">CLF</t>
+          <t xml:space="preserve">CLP</t>
         </is>
       </c>
       <c r="M32" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">LR</t>
+          <t xml:space="preserve">LE</t>
         </is>
       </c>
       <c r="N32" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Servicios profesionales, administrativos y consultorías de gestión empresarial / Servicios de recursos humanos / Contratación de personal</t>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software específico para la industria</t>
         </is>
       </c>
       <c r="O32" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 Unidad · Desarrolladores de software</t>
+          <t xml:space="preserve">7 Unidad · Software de diseño asistido por computador (CAD) · 2 Unidad · Software de diseño asistido por computador (CAD)</t>
         </is>
       </c>
       <c r="P32" s="2"/>
       <c r="Q32" s="2"/>
       <c r="R32" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">25 meses</t>
+          <t xml:space="preserve">36 meses</t>
         </is>
       </c>
       <c r="S32" s="0" t="inlineStr">
@@ -4170,106 +3345,13 @@
           <t xml:space="preserve">No</t>
         </is>
       </c>
-      <c r="T32" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ver clausula 10 de las bases especiales</t>
-        </is>
-      </c>
+      <c r="T32" s="4"/>
       <c r="U32" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Miguel Herrera</t>
+          <t xml:space="preserve">Beatriz Romero Lopez</t>
         </is>
       </c>
       <c r="V32" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CONTRATACIÓN DEL DESARROLLO DE LA PLATAFORMA MODULAR DE COMPRAS (NUEVOS MECANISMOS) PARA LA DIRECCIÓN DE COMPRAS Y CONTRATACIÓN PÚBLICA.</t>
-        </is>
-      </c>
-      <c r="W32" s="5" t="str">
-        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=869591-9-LR26","descargar bases")</f>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1641-323-LE26</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FMM - SUMINISTRO DE LICENCIA DE SOFTWARE AUTOCAD PARA OBRAS</t>
-        </is>
-      </c>
-      <c r="C33" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Publicada</t>
-        </is>
-      </c>
-      <c r="D33" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SERVICIO DE SALUD OCCIDENTE HOSPITAL SAN JUAN DE DIOS</t>
-        </is>
-      </c>
-      <c r="E33" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SERVICIO DE SALUD OCCIDENTE HOSPITAL SAN JUAN DE D</t>
-        </is>
-      </c>
-      <c r="F33" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Región Metropolitana de Santiago</t>
-        </is>
-      </c>
-      <c r="G33" s="0"/>
-      <c r="H33" s="2">
-        <v>46259.479363</v>
-      </c>
-      <c r="I33" s="2">
-        <v>46269.666667</v>
-      </c>
-      <c r="J33" s="0">
-        <v>4</v>
-      </c>
-      <c r="K33" s="3"/>
-      <c r="L33" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CLP</t>
-        </is>
-      </c>
-      <c r="M33" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LE</t>
-        </is>
-      </c>
-      <c r="N33" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software específico para la industria</t>
-        </is>
-      </c>
-      <c r="O33" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7 Unidad · Software de diseño asistido por computador (CAD) · 2 Unidad · Software de diseño asistido por computador (CAD)</t>
-        </is>
-      </c>
-      <c r="P33" s="2"/>
-      <c r="Q33" s="2"/>
-      <c r="R33" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">36 meses</t>
-        </is>
-      </c>
-      <c r="S33" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">No</t>
-        </is>
-      </c>
-      <c r="T33" s="4"/>
-      <c r="U33" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Beatriz Romero Lopez</t>
-        </is>
-      </c>
-      <c r="V33" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">La contratación de “SUMINISTRO DE LICENCIA DE SOFTWARE AUTOCAD PARA OBRAS” tiene por objeto, cumplir de manera continua la labor asistencial que ha sido encomendada a nuestra Institución, estableciendo las condiciones que permitan alcanzar la combinación más ventajosa entre todos los beneficios del bien o servicio a adquirir, y todos sus costos asociados, presentes y futuros (Art. 37° del Reglamento), según el siguiente detalle:
 ÍTEM N°1: SUMINISTRO DE LICENCIA DE SOFTWARE AUTOCAD PARA OBRAS
@@ -4278,19 +3360,108 @@
 1.2SUMINISTRO DE LICENCIAS DE SOFTWARE AUTOCADUNIDAD2</t>
         </is>
       </c>
+      <c r="W32" s="5" t="str">
+        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=1641-323-LE26","descargar bases")</f>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3530-19-L126</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Adquisición del servicio de mantenimiento y reparación para el reemplazo completo del tablero eléctrico trifásico.</t>
+        </is>
+      </c>
+      <c r="C33" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Publicada</t>
+        </is>
+      </c>
+      <c r="D33" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="E33" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Regimiento N 2 "Maipo"</t>
+        </is>
+      </c>
+      <c r="F33" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Valparaíso </t>
+        </is>
+      </c>
+      <c r="G33" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Valparaíso</t>
+        </is>
+      </c>
+      <c r="H33" s="2">
+        <v>46261.608252</v>
+      </c>
+      <c r="I33" s="2">
+        <v>46269.708333</v>
+      </c>
+      <c r="J33" s="0">
+        <v>3</v>
+      </c>
+      <c r="K33" s="3">
+        <v>4000000.0</v>
+      </c>
+      <c r="L33" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CLP</t>
+        </is>
+      </c>
+      <c r="M33" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L1</t>
+        </is>
+      </c>
+      <c r="N33" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Maquinaria para generación y distribución de energía / Generación de energía / Equipo para control de producción de energía</t>
+        </is>
+      </c>
+      <c r="O33" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 Unidad · Paneles de control eléctrico para generadores</t>
+        </is>
+      </c>
+      <c r="P33" s="2"/>
+      <c r="Q33" s="2"/>
+      <c r="R33" s="0"/>
+      <c r="S33" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="T33" s="4"/>
+      <c r="U33" s="0"/>
+      <c r="V33" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Adquisición del servicio de mantenimiento y reparación para el
+reemplazo completo del tablero eléctrico trifásico perteneciente al
+Regimiento N°2 "Maipo".</t>
+        </is>
+      </c>
       <c r="W33" s="5" t="str">
-        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=1641-323-LE26","descargar bases")</f>
+        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=3530-19-L126","descargar bases")</f>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">3530-19-L126</t>
+          <t xml:space="preserve">1171234-5-LE26</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adquisición del servicio de mantenimiento y reparación para el reemplazo completo del tablero eléctrico trifásico.</t>
+          <t xml:space="preserve">SERVICIOS DE IMPLEMENTACIÓN SOFTWARE CEDOC MNBA</t>
         </is>
       </c>
       <c r="C34" s="0" t="inlineStr">
@@ -4300,35 +3471,35 @@
       </c>
       <c r="D34" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">DIVISION LOGISTICA DEL EJERCITO</t>
+          <t xml:space="preserve">SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="E34" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Regimiento N 2 "Maipo"</t>
+          <t xml:space="preserve">MUSEO NACIONAL DE BELLAS ARTES DOS</t>
         </is>
       </c>
       <c r="F34" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t xml:space="preserve">Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="G34" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valparaíso</t>
+          <t xml:space="preserve">Santiago</t>
         </is>
       </c>
       <c r="H34" s="2">
-        <v>46261.608252</v>
+        <v>46259.655556</v>
       </c>
       <c r="I34" s="2">
-        <v>46269.708333</v>
+        <v>46269.833333</v>
       </c>
       <c r="J34" s="0">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K34" s="3">
-        <v>4000000.0</v>
+        <v>27000000.0</v>
       </c>
       <c r="L34" s="0" t="inlineStr">
         <is>
@@ -4337,17 +3508,17 @@
       </c>
       <c r="M34" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">L1</t>
+          <t xml:space="preserve">LE</t>
         </is>
       </c>
       <c r="N34" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Maquinaria para generación y distribución de energía / Generación de energía / Equipo para control de producción de energía</t>
+          <t xml:space="preserve">Servicios basados en ingeniería, ciencias sociales y tecnología de la información / Servicios informáticos / Administración de sistemas</t>
         </is>
       </c>
       <c r="O34" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 Unidad · Paneles de control eléctrico para generadores</t>
+          <t xml:space="preserve">1 Unidad · Instalación de sistemas</t>
         </is>
       </c>
       <c r="P34" s="2"/>
@@ -4358,28 +3529,34 @@
           <t xml:space="preserve">No</t>
         </is>
       </c>
-      <c r="T34" s="4"/>
-      <c r="U34" s="0"/>
+      <c r="T34" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DE ACUERDO A LO SEÑALADO EN BASES DE LICTACIÓN ADJUNTAS</t>
+        </is>
+      </c>
+      <c r="U34" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manuel  Arenas Bustos</t>
+        </is>
+      </c>
       <c r="V34" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adquisición del servicio de mantenimiento y reparación para el
-reemplazo completo del tablero eléctrico trifásico perteneciente al
-Regimiento N°2 "Maipo".</t>
+          <t xml:space="preserve">CONTRATACIÓN DE LOS SERVICIOS DE IMPLEMENTACIÓN DE SOFTWARE, CONSERVACIÓN, SISTEMATIZACIÓN Y ACCESO A LOS ACERVOS PATRIMONIALES DEL CENTRO DE DOCUMENTACIÓN ANGÉLICA PÉREZ GERMAIN”</t>
         </is>
       </c>
       <c r="W34" s="5" t="str">
-        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=3530-19-L126","descargar bases")</f>
+        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=1171234-5-LE26","descargar bases")</f>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1171234-5-LE26</t>
+          <t xml:space="preserve">2981-242-LE26</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">SERVICIOS DE IMPLEMENTACIÓN SOFTWARE CEDOC MNBA</t>
+          <t xml:space="preserve">ADQUISICIÓN DE ESTRUCTURA TÓTEM Y LETRAS VOLUMETRICAS DE METAL</t>
         </is>
       </c>
       <c r="C35" s="0" t="inlineStr">
@@ -4389,12 +3566,12 @@
       </c>
       <c r="D35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
+          <t xml:space="preserve">POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="E35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">MUSEO NACIONAL DE BELLAS ARTES DOS</t>
+          <t xml:space="preserve">DEPARTAMENTO ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="F35" s="0" t="inlineStr">
@@ -4404,20 +3581,20 @@
       </c>
       <c r="G35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Santiago</t>
+          <t xml:space="preserve">Santiago Centro</t>
         </is>
       </c>
       <c r="H35" s="2">
-        <v>46259.655556</v>
+        <v>46261.612338</v>
       </c>
       <c r="I35" s="2">
-        <v>46269.833333</v>
+        <v>46272.625</v>
       </c>
       <c r="J35" s="0">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K35" s="3">
-        <v>27000000.0</v>
+        <v>60000000.0</v>
       </c>
       <c r="L35" s="0" t="inlineStr">
         <is>
@@ -4431,12 +3608,12 @@
       </c>
       <c r="N35" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Servicios basados en ingeniería, ciencias sociales y tecnología de la información / Servicios informáticos / Administración de sistemas</t>
+          <t xml:space="preserve">Productos impresos y publicaciones / Etiquetado y accesorios / Etiquetado</t>
         </is>
       </c>
       <c r="O35" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 Unidad · Instalación de sistemas</t>
+          <t xml:space="preserve">1 Unidad no definida · Placas metálicas indicadoras del nombre</t>
         </is>
       </c>
       <c r="P35" s="2"/>
@@ -4449,32 +3626,32 @@
       </c>
       <c r="T35" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">DE ACUERDO A LO SEÑALADO EN BASES DE LICTACIÓN ADJUNTAS</t>
+          <t xml:space="preserve">SEGÚN RESOLEX N° 668 DE 26.AGO.026, DEPADM</t>
         </is>
       </c>
       <c r="U35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Manuel  Arenas Bustos</t>
+          <t xml:space="preserve">NICOLE PÉREZ RIVERA</t>
         </is>
       </c>
       <c r="V35" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">CONTRATACIÓN DE LOS SERVICIOS DE IMPLEMENTACIÓN DE SOFTWARE, CONSERVACIÓN, SISTEMATIZACIÓN Y ACCESO A LOS ACERVOS PATRIMONIALES DEL CENTRO DE DOCUMENTACIÓN ANGÉLICA PÉREZ GERMAIN”</t>
+          <t xml:space="preserve">LA POLICÍA DE INVESTIGACIONES DE CHILE, REQUIERE ADQUIRIR 1 ESTRUCTURA TÓTEM, 64 LETRAS VOLUMÉTRICAS, 4 ICONOS DE MARCA REGISTRADA, PARA IDENTIFICAR EL FRONTIS DEL NUEVO EDIFICIO PDI COMPLEJO METROPOLITANO UBICADO EN AGUSTINAS 640, SANTIAGO CENTRO</t>
         </is>
       </c>
       <c r="W35" s="5" t="str">
-        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=1171234-5-LE26","descargar bases")</f>
+        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=2981-242-LE26","descargar bases")</f>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2981-242-LE26</t>
+          <t xml:space="preserve">3820-25-LE26</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADQUISICIÓN DE ESTRUCTURA TÓTEM Y LETRAS VOLUMETRICAS DE METAL</t>
+          <t xml:space="preserve">ADQUISICION Y RENOVACION DE LICENCIAS DE SOFTWARE</t>
         </is>
       </c>
       <c r="C36" s="0" t="inlineStr">
@@ -4484,35 +3661,35 @@
       </c>
       <c r="D36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t xml:space="preserve">I MUNICIPALIDAD DE SANTA MARIA</t>
         </is>
       </c>
       <c r="E36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEPARTAMENTO ADMINISTRATIVO</t>
+          <t xml:space="preserve">I MUNICIPALIDAD DE SANTA MARIA</t>
         </is>
       </c>
       <c r="F36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región Metropolitana de Santiago</t>
+          <t xml:space="preserve">Región de Valparaíso </t>
         </is>
       </c>
       <c r="G36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Santiago Centro</t>
+          <t xml:space="preserve">Santa María</t>
         </is>
       </c>
       <c r="H36" s="2">
-        <v>46261.612338</v>
+        <v>46260.491898</v>
       </c>
       <c r="I36" s="2">
         <v>46272.625</v>
       </c>
       <c r="J36" s="0">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K36" s="3">
-        <v>60000000.0</v>
+        <v>16000000.0</v>
       </c>
       <c r="L36" s="0" t="inlineStr">
         <is>
@@ -4526,12 +3703,12 @@
       </c>
       <c r="N36" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Productos impresos y publicaciones / Etiquetado y accesorios / Etiquetado</t>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de gestión</t>
         </is>
       </c>
       <c r="O36" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 Unidad no definida · Placas metálicas indicadoras del nombre</t>
+          <t xml:space="preserve">1 Unidad · Software de gestión de licencias</t>
         </is>
       </c>
       <c r="P36" s="2"/>
@@ -4542,34 +3719,30 @@
           <t xml:space="preserve">No</t>
         </is>
       </c>
-      <c r="T36" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SEGÚN RESOLEX N° 668 DE 26.AGO.026, DEPADM</t>
-        </is>
-      </c>
+      <c r="T36" s="4"/>
       <c r="U36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICOLE PÉREZ RIVERA</t>
+          <t xml:space="preserve">Ninoska Pino</t>
         </is>
       </c>
       <c r="V36" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">LA POLICÍA DE INVESTIGACIONES DE CHILE, REQUIERE ADQUIRIR 1 ESTRUCTURA TÓTEM, 64 LETRAS VOLUMÉTRICAS, 4 ICONOS DE MARCA REGISTRADA, PARA IDENTIFICAR EL FRONTIS DEL NUEVO EDIFICIO PDI COMPLEJO METROPOLITANO UBICADO EN AGUSTINAS 640, SANTIAGO CENTRO</t>
+          <t xml:space="preserve">Renovación de 06 unidades de Licencia de AUTOCAD 2026 o 2027 Including Specializad toolsets  Ad Commercial New Including Specialized toolsets Ad Commercial New Single-user y una (01)  nueva Licencia de AUTOCAD 2026 o 2027 Including Specializad toolsets Ad Commercial New Including Specialized toolsets Ad Commercial New Single-user</t>
         </is>
       </c>
       <c r="W36" s="5" t="str">
-        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=2981-242-LE26","descargar bases")</f>
+        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=3820-25-LE26","descargar bases")</f>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">3820-25-LE26</t>
+          <t xml:space="preserve">564162-115-L126</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADQUISICION Y RENOVACION DE LICENCIAS DE SOFTWARE</t>
+          <t xml:space="preserve">Solicitud N°92870 - Bolsas, etiquetas y cajas con impresión digital - CC112 / PS1772</t>
         </is>
       </c>
       <c r="C37" s="0" t="inlineStr">
@@ -4579,35 +3752,35 @@
       </c>
       <c r="D37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">I MUNICIPALIDAD DE SANTA MARIA</t>
+          <t xml:space="preserve">UNIVERSIDAD DE SANTIAGO DE CHILE</t>
         </is>
       </c>
       <c r="E37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">I MUNICIPALIDAD DE SANTA MARIA</t>
+          <t xml:space="preserve">VICERRECTORIA DE INVESTIGACION Y DESARROLLO</t>
         </is>
       </c>
       <c r="F37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t xml:space="preserve">Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="G37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Santa María</t>
+          <t xml:space="preserve">Estación Central</t>
         </is>
       </c>
       <c r="H37" s="2">
-        <v>46260.491898</v>
+        <v>46265.7214</v>
       </c>
       <c r="I37" s="2">
         <v>46272.625</v>
       </c>
       <c r="J37" s="0">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K37" s="3">
-        <v>16000000.0</v>
+        <v>5210000.0</v>
       </c>
       <c r="L37" s="0" t="inlineStr">
         <is>
@@ -4616,17 +3789,17 @@
       </c>
       <c r="M37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">LE</t>
+          <t xml:space="preserve">L1</t>
         </is>
       </c>
       <c r="N37" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de gestión</t>
+          <t xml:space="preserve">Equipamiento para manejo y estiba de materiales / Materiales para envasado / Cajas, bolsas y sacos para envasado, Productos de papel / Productos de papel / Papel fantasía, Productos impresos y publicaciones / Etiquetado y accesorios / Etiquetas</t>
         </is>
       </c>
       <c r="O37" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 Unidad · Software de gestión de licencias</t>
+          <t xml:space="preserve">1 Unidad · Cajas para empaquetado · 1 Unidad · Cajas para empaquetado · 1 Unidad · Papel, bolsas o cajas de regalo · y 2 más</t>
         </is>
       </c>
       <c r="P37" s="2"/>
@@ -4638,18 +3811,14 @@
         </is>
       </c>
       <c r="T37" s="4"/>
-      <c r="U37" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ninoska Pino</t>
-        </is>
-      </c>
+      <c r="U37" s="0"/>
       <c r="V37" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Renovación de 06 unidades de Licencia de AUTOCAD 2026 o 2027 Including Specializad toolsets  Ad Commercial New Including Specialized toolsets Ad Commercial New Single-user y una (01)  nueva Licencia de AUTOCAD 2026 o 2027 Including Specializad toolsets Ad Commercial New Including Specialized toolsets Ad Commercial New Single-user</t>
+          <t xml:space="preserve">La Universidad de Santiago de chile requiere la compra de bolsas, etiquetas y cajas con impresión digital según especificaciones técnicas.</t>
         </is>
       </c>
       <c r="W37" s="5" t="str">
-        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=3820-25-LE26","descargar bases")</f>
+        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=564162-115-L126","descargar bases")</f>
       </c>
     </row>
     <row r="38">
@@ -4695,7 +3864,7 @@
         <v>46272.625</v>
       </c>
       <c r="J38" s="0">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K38" s="3"/>
       <c r="L38" s="0" t="inlineStr">
@@ -4788,7 +3957,7 @@
         <v>46272.625</v>
       </c>
       <c r="J39" s="0">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K39" s="3">
         <v>4728.0</v>
@@ -4843,12 +4012,12 @@
     <row r="40">
       <c r="A40" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">564162-115-L126</t>
+          <t xml:space="preserve">2324-109-LE26</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Solicitud N°92870 - Bolsas, etiquetas y cajas con impresión digital - CC112 / PS1772</t>
+          <t xml:space="preserve">LICITACION PÚBLICA N° 52026 “CONTRATACION DE SOFTWARE CONTROL DE OBRAS Y GESTION DE PROYECTOS PARA LA INSPECCION DE OBRAS MUNICIPALES POR 3 AÑOS”</t>
         </is>
       </c>
       <c r="C40" s="0" t="inlineStr">
@@ -4858,36 +4027,34 @@
       </c>
       <c r="D40" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">UNIVERSIDAD DE SANTIAGO DE CHILE</t>
+          <t xml:space="preserve">I MUNICIPALIDAD DE PUERTO MONTT</t>
         </is>
       </c>
       <c r="E40" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">VICERRECTORIA DE INVESTIGACION Y DESARROLLO</t>
+          <t xml:space="preserve">Departamento de Licitaciones y gestión de Abastecimiento </t>
         </is>
       </c>
       <c r="F40" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región Metropolitana de Santiago</t>
+          <t xml:space="preserve">Región de los Lagos </t>
         </is>
       </c>
       <c r="G40" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Estación Central</t>
+          <t xml:space="preserve">Puerto Montt</t>
         </is>
       </c>
       <c r="H40" s="2">
-        <v>46265.7214</v>
+        <v>46262.428762</v>
       </c>
       <c r="I40" s="2">
-        <v>46272.625</v>
+        <v>46272.625694</v>
       </c>
       <c r="J40" s="0">
-        <v>7</v>
-      </c>
-      <c r="K40" s="3">
-        <v>5210000.0</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="K40" s="3"/>
       <c r="L40" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">CLP</t>
@@ -4895,47 +4062,59 @@
       </c>
       <c r="M40" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">L1</t>
+          <t xml:space="preserve">LE</t>
         </is>
       </c>
       <c r="N40" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Equipamiento para manejo y estiba de materiales / Materiales para envasado / Cajas, bolsas y sacos para envasado, Productos de papel / Productos de papel / Papel fantasía, Productos impresos y publicaciones / Etiquetado y accesorios / Etiquetas</t>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de gestión</t>
         </is>
       </c>
       <c r="O40" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 Unidad · Cajas para empaquetado · 1 Unidad · Cajas para empaquetado · 1 Unidad · Papel, bolsas o cajas de regalo · y 2 más</t>
+          <t xml:space="preserve">1 Global · Programas de gestión de proyectos</t>
         </is>
       </c>
       <c r="P40" s="2"/>
       <c r="Q40" s="2"/>
-      <c r="R40" s="0"/>
+      <c r="R40" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">36 meses</t>
+        </is>
+      </c>
       <c r="S40" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">No</t>
         </is>
       </c>
-      <c r="T40" s="4"/>
-      <c r="U40" s="0"/>
+      <c r="T40" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SEGUN ARTICULO BASES ADMINISTRATIVAS.</t>
+        </is>
+      </c>
+      <c r="U40" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JAVIERA  TORRES</t>
+        </is>
+      </c>
       <c r="V40" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">La Universidad de Santiago de chile requiere la compra de bolsas, etiquetas y cajas con impresión digital según especificaciones técnicas.</t>
+          <t xml:space="preserve">LICITACION PÚBLICA N° 5/2026 “CONTRATACION DE SOFTWARE CONTROL DE OBRAS Y GESTION DE PROYECTOS PARA LA INSPECCION DE OBRAS MUNICIPALES POR 3 AÑOS”</t>
         </is>
       </c>
       <c r="W40" s="5" t="str">
-        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=564162-115-L126","descargar bases")</f>
+        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=2324-109-LE26","descargar bases")</f>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2324-109-LE26</t>
+          <t xml:space="preserve">29-69-LE26</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">LICITACION PÚBLICA N° 52026 “CONTRATACION DE SOFTWARE CONTROL DE OBRAS Y GESTION DE PROYECTOS PARA LA INSPECCION DE OBRAS MUNICIPALES POR 3 AÑOS”</t>
+          <t xml:space="preserve">SERVICIO DE TRANSMISIÓN ELECTRÓNICA DE DATOS</t>
         </is>
       </c>
       <c r="C41" s="0" t="inlineStr">
@@ -4945,32 +4124,32 @@
       </c>
       <c r="D41" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">I MUNICIPALIDAD DE PUERTO MONTT</t>
+          <t xml:space="preserve">FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="E41" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Departamento de Licitaciones y gestión de Abastecimiento </t>
+          <t xml:space="preserve">Comando Logístico</t>
         </is>
       </c>
       <c r="F41" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t xml:space="preserve">Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="G41" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Puerto Montt</t>
+          <t xml:space="preserve">El Bosque</t>
         </is>
       </c>
       <c r="H41" s="2">
-        <v>46262.428762</v>
+        <v>46258.61147</v>
       </c>
       <c r="I41" s="2">
         <v>46272.625694</v>
       </c>
       <c r="J41" s="0">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K41" s="3"/>
       <c r="L41" s="0" t="inlineStr">
@@ -4985,54 +4164,46 @@
       </c>
       <c r="N41" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de gestión</t>
+          <t xml:space="preserve">Servicios de perforación de minería, petróleo y gas / Servicios gestión y proceso de datos e información sobre petróleo y gas / Servicios de comunicación de datos del campo petrolífero</t>
         </is>
       </c>
       <c r="O41" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 Global · Programas de gestión de proyectos</t>
+          <t xml:space="preserve">1 Unidad · Servicios de transmisión de datos de registro</t>
         </is>
       </c>
       <c r="P41" s="2"/>
       <c r="Q41" s="2"/>
-      <c r="R41" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">36 meses</t>
-        </is>
-      </c>
+      <c r="R41" s="0"/>
       <c r="S41" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">No</t>
         </is>
       </c>
-      <c r="T41" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SEGUN ARTICULO BASES ADMINISTRATIVAS.</t>
-        </is>
-      </c>
+      <c r="T41" s="4"/>
       <c r="U41" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">JAVIERA  TORRES</t>
+          <t xml:space="preserve">Francisco Parra Guarda</t>
         </is>
       </c>
       <c r="V41" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">LICITACION PÚBLICA N° 5/2026 “CONTRATACION DE SOFTWARE CONTROL DE OBRAS Y GESTION DE PROYECTOS PARA LA INSPECCION DE OBRAS MUNICIPALES POR 3 AÑOS”</t>
+          <t xml:space="preserve">SERVICIO DE TRANSMISIÓN ELECTRÓNICA DE DATOS ENTRE LA FUERZA AÉREA DE CHILE Y EL SERVICIO NACIONAL DE ADUANAS.</t>
         </is>
       </c>
       <c r="W41" s="5" t="str">
-        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=2324-109-LE26","descargar bases")</f>
+        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=29-69-LE26","descargar bases")</f>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">29-69-LE26</t>
+          <t xml:space="preserve">2446-251-LE26</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">SERVICIO DE TRANSMISIÓN ELECTRÓNICA DE DATOS</t>
+          <t xml:space="preserve">IMPLEMENTACION PLATAFORMA E-LEARNING</t>
         </is>
       </c>
       <c r="C42" s="0" t="inlineStr">
@@ -5042,34 +4213,36 @@
       </c>
       <c r="D42" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+          <t xml:space="preserve">I MUNICIPALIDAD DE COQUIMBO</t>
         </is>
       </c>
       <c r="E42" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Comando Logístico</t>
+          <t xml:space="preserve">IMUNI_COQUIMBO</t>
         </is>
       </c>
       <c r="F42" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región Metropolitana de Santiago</t>
+          <t xml:space="preserve">Región de Coquimbo </t>
         </is>
       </c>
       <c r="G42" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">El Bosque</t>
+          <t xml:space="preserve">Coquimbo</t>
         </is>
       </c>
       <c r="H42" s="2">
-        <v>46258.61147</v>
+        <v>46262.432604</v>
       </c>
       <c r="I42" s="2">
-        <v>46272.625694</v>
+        <v>46272.63125</v>
       </c>
       <c r="J42" s="0">
-        <v>7</v>
-      </c>
-      <c r="K42" s="3"/>
+        <v>6</v>
+      </c>
+      <c r="K42" s="3">
+        <v>14000000.0</v>
+      </c>
       <c r="L42" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">CLP</t>
@@ -5082,17 +4255,21 @@
       </c>
       <c r="N42" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Servicios de perforación de minería, petróleo y gas / Servicios gestión y proceso de datos e información sobre petróleo y gas / Servicios de comunicación de datos del campo petrolífero</t>
+          <t xml:space="preserve">Educación, formación, entrenamiento y capacitación / Servicios de orientación y tecnología educativa / Tecnología educativa</t>
         </is>
       </c>
       <c r="O42" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 Unidad · Servicios de transmisión de datos de registro</t>
+          <t xml:space="preserve">1 Unidad · E-learning</t>
         </is>
       </c>
       <c r="P42" s="2"/>
       <c r="Q42" s="2"/>
-      <c r="R42" s="0"/>
+      <c r="R42" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">730 días</t>
+        </is>
+      </c>
       <c r="S42" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">No</t>
@@ -5101,27 +4278,28 @@
       <c r="T42" s="4"/>
       <c r="U42" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Francisco Parra Guarda</t>
+          <t xml:space="preserve">ENCARGADO DEPTO DE DESARROLLO HUMANO</t>
         </is>
       </c>
       <c r="V42" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">SERVICIO DE TRANSMISIÓN ELECTRÓNICA DE DATOS ENTRE LA FUERZA AÉREA DE CHILE Y EL SERVICIO NACIONAL DE ADUANAS.</t>
+          <t xml:space="preserve">La presente licitación tiene por objeto el regular el servicio de implementación de plataforma e-learning para la enseñanza del idioma inglés, en virtud a lo solicitado en las presentes Bases Administrativas y Especificaciones Técnicas.
+Se deja expresa constancia que los oferentes deberán ofertar la totalidad de productos requeridos. El incumplimiento de esta disposición facultará al municipio para declarar inadmisibles a dichas ofertas.</t>
         </is>
       </c>
       <c r="W42" s="5" t="str">
-        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=29-69-LE26","descargar bases")</f>
+        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=2446-251-LE26","descargar bases")</f>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2446-251-LE26</t>
+          <t xml:space="preserve">2490-81-LP26</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">IMPLEMENTACION PLATAFORMA E-LEARNING</t>
+          <t xml:space="preserve">“RENOVACIÓN Y ADQUISICIÓN DE SOFTWARE DE LICENCIAS AUTODESK O EQUIVALENTE 2026-2027”</t>
         </is>
       </c>
       <c r="C43" s="0" t="inlineStr">
@@ -5131,61 +4309,59 @@
       </c>
       <c r="D43" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">I MUNICIPALIDAD DE COQUIMBO</t>
+          <t xml:space="preserve">I MUNICIPALIDAD DE PROVIDENCIA</t>
         </is>
       </c>
       <c r="E43" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">IMUNI_COQUIMBO</t>
+          <t xml:space="preserve">Dirección de Secpla</t>
         </is>
       </c>
       <c r="F43" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t xml:space="preserve">Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="G43" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Coquimbo</t>
+          <t xml:space="preserve">Providencia</t>
         </is>
       </c>
       <c r="H43" s="2">
-        <v>46262.432604</v>
+        <v>46251.6036</v>
       </c>
       <c r="I43" s="2">
-        <v>46272.63125</v>
+        <v>46272.631944</v>
       </c>
       <c r="J43" s="0">
-        <v>7</v>
-      </c>
-      <c r="K43" s="3">
-        <v>14000000.0</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="K43" s="3"/>
       <c r="L43" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">CLP</t>
+          <t xml:space="preserve">USD</t>
         </is>
       </c>
       <c r="M43" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">LE</t>
+          <t xml:space="preserve">LP</t>
         </is>
       </c>
       <c r="N43" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Educación, formación, entrenamiento y capacitación / Servicios de orientación y tecnología educativa / Tecnología educativa</t>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de gestión</t>
         </is>
       </c>
       <c r="O43" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 Unidad · E-learning</t>
+          <t xml:space="preserve">1 Global · Software de gestión de licencias</t>
         </is>
       </c>
       <c r="P43" s="2"/>
       <c r="Q43" s="2"/>
       <c r="R43" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">730 días</t>
+          <t xml:space="preserve">12 meses</t>
         </is>
       </c>
       <c r="S43" s="0" t="inlineStr">
@@ -5196,28 +4372,27 @@
       <c r="T43" s="4"/>
       <c r="U43" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ENCARGADO DEPTO DE DESARROLLO HUMANO</t>
+          <t xml:space="preserve">GONZALO SALAZAR</t>
         </is>
       </c>
       <c r="V43" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">La presente licitación tiene por objeto el regular el servicio de implementación de plataforma e-learning para la enseñanza del idioma inglés, en virtud a lo solicitado en las presentes Bases Administrativas y Especificaciones Técnicas.
-Se deja expresa constancia que los oferentes deberán ofertar la totalidad de productos requeridos. El incumplimiento de esta disposición facultará al municipio para declarar inadmisibles a dichas ofertas.</t>
+          <t xml:space="preserve">La Municipalidad de Providencia requiere contratar el servicio de “RENOVACIÓN Y ADQUISICIÓN DE SOFTWARE DE LICENCIAS AUTODESK O EQUIVALENTE PERÍODO 2026-2027”, con el objeto de contar con la renovación, compra y soporte necesario del licenciamiento de AutoCAD o software equivalente para arquitectos y funcionarios revisores de planos, agrupando dichas licencias en un solo contrato anual por la totalidad de las licencias.</t>
         </is>
       </c>
       <c r="W43" s="5" t="str">
-        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=2446-251-LE26","descargar bases")</f>
+        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=2490-81-LP26","descargar bases")</f>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2490-81-LP26</t>
+          <t xml:space="preserve">1007793-15-LE26</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">“RENOVACIÓN Y ADQUISICIÓN DE SOFTWARE DE LICENCIAS AUTODESK O EQUIVALENTE 2026-2027”</t>
+          <t xml:space="preserve">SOLUCIÓN INFORMÁTICA INSTITUCIONAL PARA EL CFT</t>
         </is>
       </c>
       <c r="C44" s="0" t="inlineStr">
@@ -5227,59 +4402,61 @@
       </c>
       <c r="D44" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">I MUNICIPALIDAD DE PROVIDENCIA</t>
+          <t xml:space="preserve">CENTRO DE FORMACION TECNICA ESTATAL DE LA REGION DE LOS LAGOS</t>
         </is>
       </c>
       <c r="E44" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dirección de Secpla</t>
+          <t xml:space="preserve">Rectoría</t>
         </is>
       </c>
       <c r="F44" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región Metropolitana de Santiago</t>
+          <t xml:space="preserve">Región de los Lagos </t>
         </is>
       </c>
       <c r="G44" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Providencia</t>
+          <t xml:space="preserve">Llanquihue</t>
         </is>
       </c>
       <c r="H44" s="2">
-        <v>46251.6036</v>
+        <v>46253.503472</v>
       </c>
       <c r="I44" s="2">
-        <v>46272.631944</v>
+        <v>46272.645833</v>
       </c>
       <c r="J44" s="0">
-        <v>7</v>
-      </c>
-      <c r="K44" s="3"/>
+        <v>6</v>
+      </c>
+      <c r="K44" s="3">
+        <v>11300000.0</v>
+      </c>
       <c r="L44" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">USD</t>
+          <t xml:space="preserve">CLP</t>
         </is>
       </c>
       <c r="M44" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">LP</t>
+          <t xml:space="preserve">LE</t>
         </is>
       </c>
       <c r="N44" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de gestión</t>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Programas de desarrollo</t>
         </is>
       </c>
       <c r="O44" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 Global · Software de gestión de licencias</t>
+          <t xml:space="preserve">1 Unidad · Software de desarrollo de plataforma Web · 1 Unidad · Software de desarrollo de plataforma Web · 1 Unidad · Software de desarrollo de plataforma Web</t>
         </is>
       </c>
       <c r="P44" s="2"/>
       <c r="Q44" s="2"/>
       <c r="R44" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">12 meses</t>
+          <t xml:space="preserve">24 meses</t>
         </is>
       </c>
       <c r="S44" s="0" t="inlineStr">
@@ -5287,30 +4464,34 @@
           <t xml:space="preserve">No</t>
         </is>
       </c>
-      <c r="T44" s="4"/>
+      <c r="T44" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Revisar Res.Ex.98 que aprueba bases de licitación.</t>
+        </is>
+      </c>
       <c r="U44" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">GONZALO SALAZAR</t>
+          <t xml:space="preserve">Marcela Bravo Novoa</t>
         </is>
       </c>
       <c r="V44" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">La Municipalidad de Providencia requiere contratar el servicio de “RENOVACIÓN Y ADQUISICIÓN DE SOFTWARE DE LICENCIAS AUTODESK O EQUIVALENTE PERÍODO 2026-2027”, con el objeto de contar con la renovación, compra y soporte necesario del licenciamiento de AutoCAD o software equivalente para arquitectos y funcionarios revisores de planos, agrupando dichas licencias en un solo contrato anual por la totalidad de las licencias.</t>
+          <t xml:space="preserve">Se requiere la adquisición de una solución informática institucional para la gestión de iniciativas de vinculación con el medio del CFT Estatal de la Región de Los Lagos.</t>
         </is>
       </c>
       <c r="W44" s="5" t="str">
-        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=2490-81-LP26","descargar bases")</f>
+        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=1007793-15-LE26","descargar bases")</f>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1007793-15-LE26</t>
+          <t xml:space="preserve">1978-44-LE26</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">SOLUCIÓN INFORMÁTICA INSTITUCIONAL PARA EL CFT</t>
+          <t xml:space="preserve">ADQUISICIÓN DE SOLUCIÓN XDR PARA CIBERSEGURIDAD AVANZADA SERVICIO DE SALUD MAULE</t>
         </is>
       </c>
       <c r="C45" s="0" t="inlineStr">
@@ -5320,35 +4501,35 @@
       </c>
       <c r="D45" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">CENTRO DE FORMACION TECNICA ESTATAL DE LA REGION DE LOS LAGOS</t>
+          <t xml:space="preserve">SERVICIO DE SALUD DEL MAULE</t>
         </is>
       </c>
       <c r="E45" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rectoría</t>
+          <t xml:space="preserve">Servicio de Salud del Maule</t>
         </is>
       </c>
       <c r="F45" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t xml:space="preserve">Región del Maule </t>
         </is>
       </c>
       <c r="G45" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Llanquihue</t>
+          <t xml:space="preserve">Maule</t>
         </is>
       </c>
       <c r="H45" s="2">
-        <v>46253.503472</v>
+        <v>46259.473611</v>
       </c>
       <c r="I45" s="2">
         <v>46272.645833</v>
       </c>
       <c r="J45" s="0">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K45" s="3">
-        <v>11300000.0</v>
+        <v>21500000.0</v>
       </c>
       <c r="L45" s="0" t="inlineStr">
         <is>
@@ -5362,12 +4543,12 @@
       </c>
       <c r="N45" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Programas de desarrollo</t>
+          <t xml:space="preserve">Servicios basados en ingeniería, ciencias sociales y tecnología de la información / Servicios informáticos / Administración de sistemas</t>
         </is>
       </c>
       <c r="O45" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 Unidad · Software de desarrollo de plataforma Web · 1 Unidad · Software de desarrollo de plataforma Web · 1 Unidad · Software de desarrollo de plataforma Web</t>
+          <t xml:space="preserve">1 Unidad · Seguridad para computadores, redes e Internet</t>
         </is>
       </c>
       <c r="P45" s="2"/>
@@ -5384,32 +4565,32 @@
       </c>
       <c r="T45" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Revisar Res.Ex.98 que aprueba bases de licitación.</t>
+          <t xml:space="preserve">De acuerdo a Resolución Exenta Nº3560 de fecha 21 de agosto de 2026</t>
         </is>
       </c>
       <c r="U45" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marcela Bravo Novoa</t>
+          <t xml:space="preserve">Héctor Bastidas</t>
         </is>
       </c>
       <c r="V45" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Se requiere la adquisición de una solución informática institucional para la gestión de iniciativas de vinculación con el medio del CFT Estatal de la Región de Los Lagos.</t>
+          <t xml:space="preserve">Esta licitación tiene por objeto contratar, por un período de 24 meses, la suscripción y el licenciamiento de una solución XDR para la protección de 1.000 endpoints del Servicio de Salud del Maule. La contratación comprende el despliegue, la puesta en marcha, el soporte técnico, la capacitación y los servicios profesionales asociados, incluyendo la protección de los endpoints, la detección y respuesta extendida frente a amenazas, y la administración centralizada de la plataforma. Lo anterior tiene por finalidad fortalecer la seguridad institucional, proporcionar una protección proactiva frente a amenazas avanzadas y contribuir a la continuidad operativa de la infraestructura tecnológica, los sistemas de información de salud y los servicios críticos del Servicio de Salud del Maule.</t>
         </is>
       </c>
       <c r="W45" s="5" t="str">
-        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=1007793-15-LE26","descargar bases")</f>
+        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=1978-44-LE26","descargar bases")</f>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1978-44-LE26</t>
+          <t xml:space="preserve">2422-149-L126</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADQUISICIÓN DE SOLUCIÓN XDR PARA CIBERSEGURIDAD AVANZADA SERVICIO DE SALUD MAULE</t>
+          <t xml:space="preserve">SOL. 945841, SERVISIO DE FABRICACION E INSTALACION DE TABLERO PARA BALNEARIO</t>
         </is>
       </c>
       <c r="C46" s="0" t="inlineStr">
@@ -5419,35 +4600,35 @@
       </c>
       <c r="D46" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">SERVICIO DE SALUD DEL MAULE</t>
+          <t xml:space="preserve">I MUNICIPALIDAD DE PUENTE ALTO</t>
         </is>
       </c>
       <c r="E46" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Servicio de Salud del Maule</t>
+          <t xml:space="preserve">I MUNICIPALIDAD DE PUENTE ALTO</t>
         </is>
       </c>
       <c r="F46" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t xml:space="preserve">Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="G46" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Maule</t>
+          <t xml:space="preserve">Puente Alto</t>
         </is>
       </c>
       <c r="H46" s="2">
-        <v>46259.473611</v>
+        <v>46265.753669</v>
       </c>
       <c r="I46" s="2">
-        <v>46272.645833</v>
+        <v>46272.65</v>
       </c>
       <c r="J46" s="0">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K46" s="3">
-        <v>21500000.0</v>
+        <v>4000000.0</v>
       </c>
       <c r="L46" s="0" t="inlineStr">
         <is>
@@ -5456,48 +4637,36 @@
       </c>
       <c r="M46" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">LE</t>
+          <t xml:space="preserve">L1</t>
         </is>
       </c>
       <c r="N46" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Servicios basados en ingeniería, ciencias sociales y tecnología de la información / Servicios informáticos / Administración de sistemas</t>
+          <t xml:space="preserve">Servicios de producción y fabricación industrial / Fabricación de maquinarias y equipos de transporte / Fabricación de maquinarias</t>
         </is>
       </c>
       <c r="O46" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 Unidad · Seguridad para computadores, redes e Internet</t>
+          <t xml:space="preserve">1 Kit · Servicios de fabricación de calderas para central eléctrica</t>
         </is>
       </c>
       <c r="P46" s="2"/>
       <c r="Q46" s="2"/>
-      <c r="R46" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24 meses</t>
-        </is>
-      </c>
+      <c r="R46" s="0"/>
       <c r="S46" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">No</t>
         </is>
       </c>
-      <c r="T46" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">De acuerdo a Resolución Exenta Nº3560 de fecha 21 de agosto de 2026</t>
-        </is>
-      </c>
-      <c r="U46" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Héctor Bastidas</t>
-        </is>
-      </c>
+      <c r="T46" s="4"/>
+      <c r="U46" s="0"/>
       <c r="V46" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Esta licitación tiene por objeto contratar, por un período de 24 meses, la suscripción y el licenciamiento de una solución XDR para la protección de 1.000 endpoints del Servicio de Salud del Maule. La contratación comprende el despliegue, la puesta en marcha, el soporte técnico, la capacitación y los servicios profesionales asociados, incluyendo la protección de los endpoints, la detección y respuesta extendida frente a amenazas, y la administración centralizada de la plataforma. Lo anterior tiene por finalidad fortalecer la seguridad institucional, proporcionar una protección proactiva frente a amenazas avanzadas y contribuir a la continuidad operativa de la infraestructura tecnológica, los sistemas de información de salud y los servicios críticos del Servicio de Salud del Maule.</t>
+          <t xml:space="preserve">NECESIDAD DE SERVICIO, PARA ACONDICIONAMIENTO DE AMBIENTE DE LA PISCINA TEMPERADA BALNEARIO MUNICIPAL, SE REQUIERE SERVICIO DE FABRICACION, INSTALACION Y PUESTA EN MARCHA DE TABLERO DE FUERZA Y COMANDO DE MOTOR TRIFASICO.</t>
         </is>
       </c>
       <c r="W46" s="5" t="str">
-        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=1978-44-LE26","descargar bases")</f>
+        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=2422-149-L126","descargar bases")</f>
       </c>
     </row>
     <row r="47">
@@ -5543,7 +4712,7 @@
         <v>46272.666667</v>
       </c>
       <c r="J47" s="0">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K47" s="3">
         <v>29790000.0</v>
@@ -5642,7 +4811,7 @@
         <v>46272.666667</v>
       </c>
       <c r="J48" s="0">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K48" s="3">
         <v>272160000.0</v>
@@ -5741,7 +4910,7 @@
         <v>46272.666667</v>
       </c>
       <c r="J49" s="0">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K49" s="3">
         <v>927900000.0</v>
@@ -5792,12 +4961,12 @@
     <row r="50">
       <c r="A50" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">932-25-LE26</t>
+          <t xml:space="preserve">932-22-L126</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">SERVICIO DE MANTENIMIENTO PREVENTIVO Y CORRECTIVO HABITUAL DEL SISTEMA ELÉCTRICO  CORRIENTES DÉBILES E INFRAESTRUCTURA DE DATOS PARA EL CENTRO DEPORTIVO COMUNITARIO  DE  RANCAGUA</t>
+          <t xml:space="preserve">SERVICIO DE REPARACIÓN DE LUMINARIAS, INSTALACIONES ELECTRICAS Y NORMALIZACIÓN DE TABLERO ELECTRONICO DEL COMPLEJO DEPORTIVO HERMOGENES LIZANA, DEL INSTITUTO NACIONAL DE DEPORTES DE O¨HIGGINS.</t>
         </is>
       </c>
       <c r="C50" s="0" t="inlineStr">
@@ -5826,16 +4995,16 @@
         </is>
       </c>
       <c r="H50" s="2">
-        <v>46260.589688</v>
+        <v>46265.704213</v>
       </c>
       <c r="I50" s="2">
         <v>46272.666667</v>
       </c>
       <c r="J50" s="0">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K50" s="3">
-        <v>30000000.0</v>
+        <v>5200000.0</v>
       </c>
       <c r="L50" s="0" t="inlineStr">
         <is>
@@ -5844,7 +5013,7 @@
       </c>
       <c r="M50" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">LE</t>
+          <t xml:space="preserve">L1</t>
         </is>
       </c>
       <c r="N50" s="4" t="inlineStr">
@@ -5854,128 +5023,128 @@
       </c>
       <c r="O50" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 Unidad · Servicio de mantenimiento de equipo de fabricación</t>
+          <t xml:space="preserve">1 Unidad · Servicio de reparación de equipo de fabricación</t>
         </is>
       </c>
       <c r="P50" s="2"/>
       <c r="Q50" s="2"/>
-      <c r="R50" s="0" t="inlineStr">
+      <c r="R50" s="0"/>
+      <c r="S50" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="T50" s="4"/>
+      <c r="U50" s="0"/>
+      <c r="V50" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EL IND DE RANCAGUA,  REQUIERE CONTRATAR  EL "SERVICIO DE REPARACIÓN DE LUMINARIAS, INSTALACIONES ELECTRICAS Y NORMALIZACIÓN DE TABLERO ELECTRONICO DEL COMPLEJO DEPORTIVO HERMOGENES LIZANA, DEL INSTITUTO NACIONAL DE DEPORTES DE O¨HIGGINS",  mediante un proceso de Licitación Publica, siendo necesario, aprobar,  previamente, las Bases Administrativas, Técnicas y Anexos que regulan dicho proceso de contratación.</t>
+        </is>
+      </c>
+      <c r="W50" s="5" t="str">
+        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=932-22-L126","descargar bases")</f>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">932-25-LE26</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SERVICIO DE MANTENIMIENTO PREVENTIVO Y CORRECTIVO HABITUAL DEL SISTEMA ELÉCTRICO  CORRIENTES DÉBILES E INFRAESTRUCTURA DE DATOS PARA EL CENTRO DEPORTIVO COMUNITARIO  DE  RANCAGUA</t>
+        </is>
+      </c>
+      <c r="C51" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Publicada</t>
+        </is>
+      </c>
+      <c r="D51" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+        </is>
+      </c>
+      <c r="E51" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">I.N.D. REGION VI</t>
+        </is>
+      </c>
+      <c r="F51" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región del Libertador General Bernardo O´Higgins</t>
+        </is>
+      </c>
+      <c r="G51" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rancagua</t>
+        </is>
+      </c>
+      <c r="H51" s="2">
+        <v>46260.589688</v>
+      </c>
+      <c r="I51" s="2">
+        <v>46272.666667</v>
+      </c>
+      <c r="J51" s="0">
+        <v>6</v>
+      </c>
+      <c r="K51" s="3">
+        <v>30000000.0</v>
+      </c>
+      <c r="L51" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CLP</t>
+        </is>
+      </c>
+      <c r="M51" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LE</t>
+        </is>
+      </c>
+      <c r="N51" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Servicios de producción y fabricación industrial / Servicios de apoyo o soporte a la fabricación / Servicios de mantenimiento y reparación de equipo de fabricación</t>
+        </is>
+      </c>
+      <c r="O51" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 Unidad · Servicio de mantenimiento de equipo de fabricación</t>
+        </is>
+      </c>
+      <c r="P51" s="2"/>
+      <c r="Q51" s="2"/>
+      <c r="R51" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">12 meses</t>
         </is>
       </c>
-      <c r="S50" s="0" t="inlineStr">
+      <c r="S51" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">No</t>
         </is>
       </c>
-      <c r="T50" s="4" t="inlineStr">
+      <c r="T51" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">11.8 Subcontratación de los servicios.
 No se contempla la subcontratación de los servicios, el adjudicado deberá prestar en forma directa los servicios que por esta licitación le sean adjudicados, ya sea por sí mismo,o a través de sus empleados si los t</t>
         </is>
       </c>
-      <c r="U50" s="0" t="inlineStr">
+      <c r="U51" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Cristina Alfonso Aguirre</t>
         </is>
       </c>
-      <c r="V50" s="4" t="inlineStr">
+      <c r="V51" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">EL IND DE RANCAGUA, REQUIERE LA CONTRATACIÓN DEL SERVICIO DE MANTENIMIENTO PREVENTIVO Y CORRECTIVO HABITUAL DEL SISTEMA ELÉCTRICO 
 CORRIENTES DÉBILES E INFRAESTRUCTURA DE DATOS PARA EL CENTRO DEPORTIVO COMUNITARIO  DE 
 RANCAGUA , mediante un proceso de Licitación Pública, siendo necesario aprobar, previamente, las Bases Administrativas, Técnicas y Anexos que regularán dicho proceso de contratación.</t>
         </is>
       </c>
-      <c r="W50" s="5" t="str">
+      <c r="W51" s="5" t="str">
         <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=932-25-LE26","descargar bases")</f>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">932-22-L126</t>
-        </is>
-      </c>
-      <c r="B51" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SERVICIO DE REPARACIÓN DE LUMINARIAS, INSTALACIONES ELECTRICAS Y NORMALIZACIÓN DE TABLERO ELECTRONICO DEL COMPLEJO DEPORTIVO HERMOGENES LIZANA, DEL INSTITUTO NACIONAL DE DEPORTES DE O¨HIGGINS.</t>
-        </is>
-      </c>
-      <c r="C51" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Publicada</t>
-        </is>
-      </c>
-      <c r="D51" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
-        </is>
-      </c>
-      <c r="E51" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">I.N.D. REGION VI</t>
-        </is>
-      </c>
-      <c r="F51" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Región del Libertador General Bernardo O´Higgins</t>
-        </is>
-      </c>
-      <c r="G51" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Rancagua</t>
-        </is>
-      </c>
-      <c r="H51" s="2">
-        <v>46265.704213</v>
-      </c>
-      <c r="I51" s="2">
-        <v>46272.666667</v>
-      </c>
-      <c r="J51" s="0">
-        <v>7</v>
-      </c>
-      <c r="K51" s="3">
-        <v>5200000.0</v>
-      </c>
-      <c r="L51" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CLP</t>
-        </is>
-      </c>
-      <c r="M51" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">L1</t>
-        </is>
-      </c>
-      <c r="N51" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Servicios de producción y fabricación industrial / Servicios de apoyo o soporte a la fabricación / Servicios de mantenimiento y reparación de equipo de fabricación</t>
-        </is>
-      </c>
-      <c r="O51" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1 Unidad · Servicio de reparación de equipo de fabricación</t>
-        </is>
-      </c>
-      <c r="P51" s="2"/>
-      <c r="Q51" s="2"/>
-      <c r="R51" s="0"/>
-      <c r="S51" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">No</t>
-        </is>
-      </c>
-      <c r="T51" s="4"/>
-      <c r="U51" s="0"/>
-      <c r="V51" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">EL IND DE RANCAGUA,  REQUIERE CONTRATAR  EL "SERVICIO DE REPARACIÓN DE LUMINARIAS, INSTALACIONES ELECTRICAS Y NORMALIZACIÓN DE TABLERO ELECTRONICO DEL COMPLEJO DEPORTIVO HERMOGENES LIZANA, DEL INSTITUTO NACIONAL DE DEPORTES DE O¨HIGGINS",  mediante un proceso de Licitación Publica, siendo necesario, aprobar,  previamente, las Bases Administrativas, Técnicas y Anexos que regulan dicho proceso de contratación.</t>
-        </is>
-      </c>
-      <c r="W51" s="5" t="str">
-        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=932-22-L126","descargar bases")</f>
       </c>
     </row>
     <row r="52">
@@ -6021,7 +5190,7 @@
         <v>46272.706944</v>
       </c>
       <c r="J52" s="0">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K52" s="3">
         <v>1500000.0</v>
@@ -6108,7 +5277,7 @@
         <v>46273.375</v>
       </c>
       <c r="J53" s="0">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K53" s="3"/>
       <c r="L53" s="0" t="inlineStr">
@@ -6214,7 +5383,7 @@
         <v>46273.416667</v>
       </c>
       <c r="J54" s="0">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K54" s="3">
         <v>124000000.0</v>
@@ -6313,7 +5482,7 @@
         <v>46273.625</v>
       </c>
       <c r="J55" s="0">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K55" s="3">
         <v>3000000.0</v>
@@ -6401,7 +5570,7 @@
         <v>46273.625694</v>
       </c>
       <c r="J56" s="0">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K56" s="3"/>
       <c r="L56" s="0" t="inlineStr">
@@ -6492,7 +5661,7 @@
         <v>46273.645833</v>
       </c>
       <c r="J57" s="0">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K57" s="3">
         <v>19980000.0</v>
@@ -6587,7 +5756,7 @@
         <v>46273.645833</v>
       </c>
       <c r="J58" s="0">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K58" s="3">
         <v>52270.0</v>
@@ -6682,7 +5851,7 @@
         <v>46273.666667</v>
       </c>
       <c r="J59" s="0">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K59" s="3">
         <v>7000000.0</v>
@@ -6768,7 +5937,7 @@
         <v>46273.666667</v>
       </c>
       <c r="J60" s="0">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K60" s="3"/>
       <c r="L60" s="0" t="inlineStr">
@@ -6865,7 +6034,7 @@
         <v>46273.666667</v>
       </c>
       <c r="J61" s="0">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K61" s="3">
         <v>5000000.0</v>
@@ -6952,7 +6121,7 @@
         <v>46274.375</v>
       </c>
       <c r="J62" s="0">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K62" s="3"/>
       <c r="L62" s="0" t="inlineStr">
@@ -7041,7 +6210,7 @@
         <v>46274.463194</v>
       </c>
       <c r="J63" s="0">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K63" s="3"/>
       <c r="L63" s="0" t="inlineStr">
@@ -7134,7 +6303,7 @@
         <v>46274.5</v>
       </c>
       <c r="J64" s="0">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K64" s="3">
         <v>7167631.0</v>
@@ -7229,7 +6398,7 @@
         <v>46274.625</v>
       </c>
       <c r="J65" s="0">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K65" s="3">
         <v>1800000.0</v>
@@ -7316,7 +6485,7 @@
         <v>46274.625</v>
       </c>
       <c r="J66" s="0">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K66" s="3">
         <v>30754000.0</v>
@@ -7409,7 +6578,7 @@
         <v>46274.645833</v>
       </c>
       <c r="J67" s="0">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K67" s="3">
         <v>180329688.0</v>
@@ -7504,7 +6673,7 @@
         <v>46274.666667</v>
       </c>
       <c r="J68" s="0">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K68" s="3">
         <v>232851.0</v>
@@ -7599,7 +6768,7 @@
         <v>46275.5</v>
       </c>
       <c r="J69" s="0">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K69" s="3"/>
       <c r="L69" s="0" t="inlineStr">
@@ -7688,7 +6857,7 @@
         <v>46275.625</v>
       </c>
       <c r="J70" s="0">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K70" s="3">
         <v>240000000.0</v>
@@ -7783,7 +6952,7 @@
         <v>46275.625</v>
       </c>
       <c r="J71" s="0">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K71" s="3">
         <v>26000000.0</v>
@@ -7878,7 +7047,7 @@
         <v>46275.666667</v>
       </c>
       <c r="J72" s="0">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K72" s="3"/>
       <c r="L72" s="0" t="inlineStr">
@@ -7971,7 +7140,7 @@
         <v>46276.416667</v>
       </c>
       <c r="J73" s="0">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K73" s="3">
         <v>13000000.0</v>
@@ -8071,7 +7240,7 @@
         <v>46276.625</v>
       </c>
       <c r="J74" s="0">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K74" s="3"/>
       <c r="L74" s="0" t="inlineStr">
@@ -8164,7 +7333,7 @@
         <v>46276.666667</v>
       </c>
       <c r="J75" s="0">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K75" s="3"/>
       <c r="L75" s="0" t="inlineStr">
@@ -8257,7 +7426,7 @@
         <v>46276.666667</v>
       </c>
       <c r="J76" s="0">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K76" s="3"/>
       <c r="L76" s="0" t="inlineStr">
@@ -8354,7 +7523,7 @@
         <v>46276.747222</v>
       </c>
       <c r="J77" s="0">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K77" s="3"/>
       <c r="L77" s="0" t="inlineStr">
@@ -8448,7 +7617,7 @@
         <v>46279.625</v>
       </c>
       <c r="J78" s="0">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K78" s="3">
         <v>540000000.0</v>
@@ -8543,7 +7712,7 @@
         <v>46279.625</v>
       </c>
       <c r="J79" s="0">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K79" s="3"/>
       <c r="L79" s="0" t="inlineStr">
@@ -8634,7 +7803,7 @@
         <v>46279.625</v>
       </c>
       <c r="J80" s="0">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K80" s="3"/>
       <c r="L80" s="0" t="inlineStr">
@@ -8723,7 +7892,7 @@
         <v>46279.625694</v>
       </c>
       <c r="J81" s="0">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K81" s="3"/>
       <c r="L81" s="0" t="inlineStr">
@@ -8812,7 +7981,7 @@
         <v>46279.666667</v>
       </c>
       <c r="J82" s="0">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K82" s="3">
         <v>225000000.0</v>
@@ -8907,7 +8076,7 @@
         <v>46280.458333</v>
       </c>
       <c r="J83" s="0">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K83" s="3">
         <v>163000000.0</v>
@@ -9004,7 +8173,7 @@
         <v>46280.5</v>
       </c>
       <c r="J84" s="0">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K84" s="3">
         <v>132232000.0</v>
@@ -9095,7 +8264,7 @@
         <v>46280.625</v>
       </c>
       <c r="J85" s="0">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K85" s="3">
         <v>295121.0</v>
@@ -9194,7 +8363,7 @@
         <v>46280.6375</v>
       </c>
       <c r="J86" s="0">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K86" s="3"/>
       <c r="L86" s="0" t="inlineStr">
@@ -9287,7 +8456,7 @@
         <v>46281.583333</v>
       </c>
       <c r="J87" s="0">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K87" s="3">
         <v>204000000.0</v>
@@ -9378,7 +8547,7 @@
         <v>46281.625</v>
       </c>
       <c r="J88" s="0">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K88" s="3">
         <v>22500000.0</v>
@@ -9473,7 +8642,7 @@
         <v>46281.729167</v>
       </c>
       <c r="J89" s="0">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K89" s="3">
         <v>388644480.0</v>
@@ -9568,7 +8737,7 @@
         <v>46282.375</v>
       </c>
       <c r="J90" s="0">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K90" s="3">
         <v>80000000.0</v>
@@ -9663,7 +8832,7 @@
         <v>46282.4375</v>
       </c>
       <c r="J91" s="0">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K91" s="3">
         <v>177000000.0</v>
@@ -9758,7 +8927,7 @@
         <v>46286.625694</v>
       </c>
       <c r="J92" s="0">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K92" s="3">
         <v>453590167.0</v>
@@ -9849,7 +9018,7 @@
         <v>46286.645833</v>
       </c>
       <c r="J93" s="0">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K93" s="3"/>
       <c r="L93" s="0" t="inlineStr">
@@ -9938,7 +9107,7 @@
         <v>46286.666667</v>
       </c>
       <c r="J94" s="0">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K94" s="3"/>
       <c r="L94" s="0" t="inlineStr">
@@ -10034,7 +9203,7 @@
         <v>46286.666667</v>
       </c>
       <c r="J95" s="0">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K95" s="3"/>
       <c r="L95" s="0" t="inlineStr">
@@ -10131,7 +9300,7 @@
         <v>46287.625</v>
       </c>
       <c r="J96" s="0">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K96" s="3">
         <v>366678654.0</v>
@@ -10227,7 +9396,7 @@
         <v>46287.625</v>
       </c>
       <c r="J97" s="0">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K97" s="3"/>
       <c r="L97" s="0" t="inlineStr">
@@ -10320,7 +9489,7 @@
         <v>46287.625694</v>
       </c>
       <c r="J98" s="0">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K98" s="3">
         <v>10000000.0</v>
@@ -10411,7 +9580,7 @@
         <v>46287.645833</v>
       </c>
       <c r="J99" s="0">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K99" s="3">
         <v>346885000.0</v>
@@ -10506,7 +9675,7 @@
         <v>46289.625</v>
       </c>
       <c r="J100" s="0">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K100" s="3"/>
       <c r="L100" s="0" t="inlineStr">
@@ -10602,7 +9771,7 @@
         <v>46289.729167</v>
       </c>
       <c r="J101" s="0">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K101" s="3">
         <v>414000000.0</v>
@@ -10699,7 +9868,7 @@
         <v>46290.625</v>
       </c>
       <c r="J102" s="0">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K102" s="3"/>
       <c r="L102" s="0" t="inlineStr">
@@ -10792,7 +9961,7 @@
         <v>46293.645833</v>
       </c>
       <c r="J103" s="0">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="K103" s="3">
         <v>450000000.0</v>
@@ -10883,7 +10052,7 @@
         <v>46293.75</v>
       </c>
       <c r="J104" s="0">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="K104" s="3"/>
       <c r="L104" s="0" t="inlineStr">
@@ -10981,7 +10150,7 @@
         <v>46295.625</v>
       </c>
       <c r="J105" s="0">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K105" s="3">
         <v>24000.0</v>
@@ -11081,7 +10250,7 @@
         <v>46297.625</v>
       </c>
       <c r="J106" s="0">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="K106" s="3">
         <v>565250.0</v>
@@ -11180,7 +10349,7 @@
         <v>46301.625</v>
       </c>
       <c r="J107" s="0">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K107" s="3">
         <v>11000.0</v>
@@ -11279,7 +10448,7 @@
         <v>46304.458333</v>
       </c>
       <c r="J108" s="0">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K108" s="3"/>
       <c r="L108" s="0" t="inlineStr">
@@ -11545,12 +10714,12 @@
     <row r="4">
       <c r="A4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2448-116-L126</t>
+          <t xml:space="preserve">2713-159-LE26</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">MANTENIMIENTO Y ACTUALIZACIÓN DE SOFTWARE DE CONTROL RESOLUTIVIDAD.</t>
+          <t xml:space="preserve">DAF-informatica sevicio plataforma documental</t>
         </is>
       </c>
       <c r="C4" s="0">
@@ -11558,12 +10727,12 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Software de sistemas de archivado de película radiográfica médica</t>
+          <t xml:space="preserve">Programas de gestión de documentos</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Equipamiento y suministros médicos / Productos para imágenes y de medicina nuclear / Artículos para archivar información e imágenes radiológicas</t>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de gestión de contenidos</t>
         </is>
       </c>
       <c r="F4" s="0">
@@ -11576,19 +10745,19 @@
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">CONTRATACIÓN DE SERVICIO DE MANTENIMIENTO EVOLUTIVO Y ACTUALIZACIÓN DE SOFTWARE DE CONTROL PARA EQUIPO OFTALMOLÓGICO OCT</t>
+          <t xml:space="preserve">servicio integral en modalidad SaaS para la continuidad, ampliación, migración y soporte técnico de la Plataforma Documental y de Correspondencia,por 48 meses, DAF/Informatica solicitud folio 961</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2713-159-LE26</t>
+          <t xml:space="preserve">869591-10-LP26</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">DAF-informatica sevicio plataforma documental</t>
+          <t xml:space="preserve">CONTRATACIÓN DEL SERVICIO DE DISEÑO Y DESARROLLO DEL NUEVO PORTAL API Y CAPA DE DATOS DE NEGOCIO PARA MERCADO PÚBLICO</t>
         </is>
       </c>
       <c r="C5" s="0">
@@ -11596,12 +10765,12 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Programas de gestión de documentos</t>
+          <t xml:space="preserve">Desarrolladores de software</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de gestión de contenidos</t>
+          <t xml:space="preserve">Servicios profesionales, administrativos y consultorías de gestión empresarial / Servicios de recursos humanos / Contratación de personal</t>
         </is>
       </c>
       <c r="F5" s="0">
@@ -11614,19 +10783,19 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">servicio integral en modalidad SaaS para la continuidad, ampliación, migración y soporte técnico de la Plataforma Documental y de Correspondencia,por 48 meses, DAF/Informatica solicitud folio 961</t>
+          <t xml:space="preserve">CONTRATACIÓN DEL SERVICIO DE DISEÑO Y DESARROLLO DEL NUEVO PORTAL API Y CAPA DE DATOS DE NEGOCIO PARA MERCADO PÚBLICO</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">869591-10-LP26</t>
+          <t xml:space="preserve">587-37-LE26</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">CONTRATACIÓN DEL SERVICIO DE DISEÑO Y DESARROLLO DEL NUEVO PORTAL API Y CAPA DE DATOS DE NEGOCIO PARA MERCADO PÚBLICO</t>
+          <t xml:space="preserve">SELICO 326-2026. Renovación Software Estadístico</t>
         </is>
       </c>
       <c r="C6" s="0">
@@ -11634,12 +10803,12 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Desarrolladores de software</t>
+          <t xml:space="preserve">Software de gestión de licencias</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Servicios profesionales, administrativos y consultorías de gestión empresarial / Servicios de recursos humanos / Contratación de personal</t>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de gestión</t>
         </is>
       </c>
       <c r="F6" s="0">
@@ -11647,24 +10816,24 @@
       </c>
       <c r="G6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unidad</t>
+          <t xml:space="preserve">Global</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">CONTRATACIÓN DEL SERVICIO DE DISEÑO Y DESARROLLO DEL NUEVO PORTAL API Y CAPA DE DATOS DE NEGOCIO PARA MERCADO PÚBLICO</t>
+          <t xml:space="preserve">Renovación de licencias de uso de software estadístico Statistics Smart Pack IBM SPSS (o equivalente), por doce (12) meses.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">587-37-LE26</t>
+          <t xml:space="preserve">1110404-154-LE26</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">SELICO 326-2026. Renovación Software Estadístico</t>
+          <t xml:space="preserve">ADQUISICIÓN DE LICENCIAS PERMANENTES DE SOFTWARE FACTORY IO PARA LA ESPECIALIDAD DE ELECTRÓNICA DEL LICEO POLITÉCNICO ARICA SERVICIO LOCAL DE EDUCACIÓN PÚBLICA CHINCHORRO</t>
         </is>
       </c>
       <c r="C7" s="0">
@@ -11672,37 +10841,37 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Software de gestión de licencias</t>
+          <t xml:space="preserve">Software de mapa electrónico</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de gestión</t>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software educativo o de referencia</t>
         </is>
       </c>
       <c r="F7" s="0">
-        <v>1.0</v>
+        <v>15.0</v>
       </c>
       <c r="G7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Global</t>
+          <t xml:space="preserve">Unidad</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Renovación de licencias de uso de software estadístico Statistics Smart Pack IBM SPSS (o equivalente), por doce (12) meses.</t>
+          <t xml:space="preserve">ADQUISICIÓN DE LICENCIAS PERMANENTES DE SOFTWARE FACTORY I/O PARA LA ESPECIALIDAD DE ELECTRÓNICA DEL LICEO POLITÉCNICO ARICA, SERVICIO LOCAL DE EDUCACIÓN PÚBLICA CHINCHORRO</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1110404-154-LE26</t>
+          <t xml:space="preserve">885-74-LP26</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADQUISICIÓN DE LICENCIAS PERMANENTES DE SOFTWARE FACTORY IO PARA LA ESPECIALIDAD DE ELECTRÓNICA DEL LICEO POLITÉCNICO ARICA SERVICIO LOCAL DE EDUCACIÓN PÚBLICA CHINCHORRO</t>
+          <t xml:space="preserve">Servicio de actualización de software arquitectura y migración de base de datos del Sistema DIP.</t>
         </is>
       </c>
       <c r="C8" s="0">
@@ -11710,16 +10879,16 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Software de mapa electrónico</t>
+          <t xml:space="preserve">Desarrolladores de software</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software educativo o de referencia</t>
+          <t xml:space="preserve">Servicios profesionales, administrativos y consultorías de gestión empresarial / Servicios de recursos humanos / Contratación de personal</t>
         </is>
       </c>
       <c r="F8" s="0">
-        <v>15.0</v>
+        <v>1.0</v>
       </c>
       <c r="G8" s="0" t="inlineStr">
         <is>
@@ -11728,19 +10897,19 @@
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADQUISICIÓN DE LICENCIAS PERMANENTES DE SOFTWARE FACTORY I/O PARA LA ESPECIALIDAD DE ELECTRÓNICA DEL LICEO POLITÉCNICO ARICA, SERVICIO LOCAL DE EDUCACIÓN PÚBLICA CHINCHORRO</t>
+          <t xml:space="preserve">equipo especializado para apoyar a la Contraloría General de la República en la actualización de software, arquitectura y migración de la base de datos del Sistema de Declaraciones de Intereses y Patrimonio — DIP.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">885-74-LP26</t>
+          <t xml:space="preserve">1113265-12-LE26</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Servicio de actualización de software arquitectura y migración de base de datos del Sistema DIP.</t>
+          <t xml:space="preserve">ADQUISICIÓN E IMPLEMENTACIÓN DE PLATAFORMA</t>
         </is>
       </c>
       <c r="C9" s="0">
@@ -11748,12 +10917,12 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Desarrolladores de software</t>
+          <t xml:space="preserve">Software de gestión de licencias</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Servicios profesionales, administrativos y consultorías de gestión empresarial / Servicios de recursos humanos / Contratación de personal</t>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de gestión</t>
         </is>
       </c>
       <c r="F9" s="0">
@@ -11766,19 +10935,19 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">equipo especializado para apoyar a la Contraloría General de la República en la actualización de software, arquitectura y migración de la base de datos del Sistema de Declaraciones de Intereses y Patrimonio — DIP.</t>
+          <t xml:space="preserve">ADQUISICIÓN E IMPLEMENTACIÓN DE PLATAFORMA DE GESTIÓN ESTRATÉGICA DE LA PERMANENCIA ESTUDIANTIL PARA EL CENTRO DE FORMACIÓN TÉCNICA ESTATAL DE LA REGIÓN DE ANTOFAGASTA</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1113265-12-LE26</t>
+          <t xml:space="preserve">1233623-38-LE26</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADQUISICIÓN E IMPLEMENTACIÓN DE PLATAFORMA</t>
+          <t xml:space="preserve">ADQUISICIÓN DE SOFTWARE AEC COLLECTION 2025</t>
         </is>
       </c>
       <c r="C10" s="0">
@@ -11786,12 +10955,12 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Software de gestión de licencias</t>
+          <t xml:space="preserve">Software de acceso</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de gestión</t>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software para trabajo en redes</t>
         </is>
       </c>
       <c r="F10" s="0">
@@ -11799,24 +10968,24 @@
       </c>
       <c r="G10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unidad</t>
+          <t xml:space="preserve">Global</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADQUISICIÓN E IMPLEMENTACIÓN DE PLATAFORMA DE GESTIÓN ESTRATÉGICA DE LA PERMANENCIA ESTUDIANTIL PARA EL CENTRO DE FORMACIÓN TÉCNICA ESTATAL DE LA REGIÓN DE ANTOFAGASTA</t>
+          <t xml:space="preserve">“ADQUISICIÓN DE SOFTWARE AEC COLLECTION 2026, EQUIVALENTE O SUPERIOR, PARA EL SERVICIO LOCAL DE EDUCACIÓN PÚBLICA LICANCABUR”.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1233623-38-LE26</t>
+          <t xml:space="preserve">652-37-LP26</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADQUISICIÓN DE SOFTWARE AEC COLLECTION 2025</t>
+          <t xml:space="preserve">ARRIENDO SERVIDOR INFORMATICO PARA PROGRAMA SISSA.</t>
         </is>
       </c>
       <c r="C11" s="0">
@@ -11824,12 +10993,12 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Software de acceso</t>
+          <t xml:space="preserve">Servidores</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software para trabajo en redes</t>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Equipos informáticos y accesorios / Computadores</t>
         </is>
       </c>
       <c r="F11" s="0">
@@ -11837,24 +11006,24 @@
       </c>
       <c r="G11" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Global</t>
+          <t xml:space="preserve">Unidad</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">“ADQUISICIÓN DE SOFTWARE AEC COLLECTION 2026, EQUIVALENTE O SUPERIOR, PARA EL SERVICIO LOCAL DE EDUCACIÓN PÚBLICA LICANCABUR”.</t>
+          <t xml:space="preserve">CONVENIO ARRIENDO SERVIDOR INFORMATICO PARA ELPROGRAMA SISSA POR UN PERIODO DE 36 MESES, SERVICIO DE SALUD ARAUCO PARA EL SERVICIO DE SALUD ARAUCANIA SUR, SEGUN REQUERIMIENTOS TECNICOS ADJUNTOS.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">652-37-LP26</t>
+          <t xml:space="preserve">609-25-LE26</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ARRIENDO SERVIDOR INFORMATICO PARA PROGRAMA SISSA.</t>
+          <t xml:space="preserve">ACTUALIZACIÓN DEL SGSI DE INDAP- CIBERSEGURIDAD</t>
         </is>
       </c>
       <c r="C12" s="0">
@@ -11862,12 +11031,12 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Servidores</t>
+          <t xml:space="preserve">Asesorías Informáticas</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Equipos informáticos y accesorios / Computadores</t>
+          <t xml:space="preserve">Servicios profesionales, administrativos y consultorías de gestión empresarial / Consultorías o asesorías en gestión empresarial / Servicios de consultoría en gestión de empresas</t>
         </is>
       </c>
       <c r="F12" s="0">
@@ -11879,44 +11048,6 @@
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CONVENIO ARRIENDO SERVIDOR INFORMATICO PARA ELPROGRAMA SISSA POR UN PERIODO DE 36 MESES, SERVICIO DE SALUD ARAUCO PARA EL SERVICIO DE SALUD ARAUCANIA SUR, SEGUN REQUERIMIENTOS TECNICOS ADJUNTOS.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">609-25-LE26</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ACTUALIZACIÓN DEL SGSI DE INDAP- CIBERSEGURIDAD</t>
-        </is>
-      </c>
-      <c r="C13" s="0">
-        <v>1</v>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Asesorías Informáticas</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Servicios profesionales, administrativos y consultorías de gestión empresarial / Consultorías o asesorías en gestión empresarial / Servicios de consultoría en gestión de empresas</t>
-        </is>
-      </c>
-      <c r="F13" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="G13" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Unidad</t>
-        </is>
-      </c>
-      <c r="H13" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">ACTUALIZACIÓN DEL SGSI
 DE INDAP, MODELADO DE PROCESOS, MATRIZ DE RIESGO, IDENTIFICACIÓN E IMPLEMENTACIÓN DE
@@ -11924,15 +11055,53 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1075956-9-LE26</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">42 CUPOS - CURSO NUEVA LEY DE PROTECCIÓN DE DATOS PERSONALES: INTRODUCCIÓN Y PRINCIPIOS” SEGÚN BASES DE LICITACIÓN Y ANEXOS QUE SE ADJUNTAN - PRESUPUESTO ESTIMADO  15.000.000. -</t>
+        </is>
+      </c>
+      <c r="C13" s="0">
+        <v>1</v>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Formación, capacitación y entrenamiento de personal</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Servicios profesionales, administrativos y consultorías de gestión empresarial / Servicios de recursos humanos / Consultorías para el desarrollo de recursos humanos</t>
+        </is>
+      </c>
+      <c r="F13" s="0">
+        <v>42.0</v>
+      </c>
+      <c r="G13" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidad</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">42 CUPOS - CURSO NUEVA LEY DE PROTECCIÓN DE DATOS PERSONALES: INTRODUCCIÓN Y PRINCIPIOS” SEGÚN BASES DE LICITACIÓN Y ANEXOS QUE SE ADJUNTAN - PRESUPUESTO ESTIMADO 15.000.000. -</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1075956-9-LE26</t>
+          <t xml:space="preserve">1057532-72-LE26</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">42 CUPOS - CURSO NUEVA LEY DE PROTECCIÓN DE DATOS PERSONALES: INTRODUCCIÓN Y PRINCIPIOS” SEGÚN BASES DE LICITACIÓN Y ANEXOS QUE SE ADJUNTAN - PRESUPUESTO ESTIMADO  15.000.000. -</t>
+          <t xml:space="preserve">SUSCRIPCIÓN LICENCIAS SOFTWARE CAD ARCHICAD COLLABORATE O EQUIVALENTE PARA EL SERVICIO DE SALUD OSORNO</t>
         </is>
       </c>
       <c r="C14" s="0">
@@ -11940,16 +11109,16 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Formación, capacitación y entrenamiento de personal</t>
+          <t xml:space="preserve">Software de diseño asistido por computador (CAD)</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Servicios profesionales, administrativos y consultorías de gestión empresarial / Servicios de recursos humanos / Consultorías para el desarrollo de recursos humanos</t>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software específico para la industria</t>
         </is>
       </c>
       <c r="F14" s="0">
-        <v>42.0</v>
+        <v>6.0</v>
       </c>
       <c r="G14" s="0" t="inlineStr">
         <is>
@@ -11958,19 +11127,19 @@
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">42 CUPOS - CURSO NUEVA LEY DE PROTECCIÓN DE DATOS PERSONALES: INTRODUCCIÓN Y PRINCIPIOS” SEGÚN BASES DE LICITACIÓN Y ANEXOS QUE SE ADJUNTAN - PRESUPUESTO ESTIMADO 15.000.000. -</t>
+          <t xml:space="preserve">Licencias de Software CAD (Archicad Collaborate o Equivalente), con suscripción de 12 meses, con pago en 12 cuotas.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1057532-72-LE26</t>
+          <t xml:space="preserve">564953-62-LP26</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">SUSCRIPCIÓN LICENCIAS SOFTWARE CAD ARCHICAD COLLABORATE O EQUIVALENTE PARA EL SERVICIO DE SALUD OSORNO</t>
+          <t xml:space="preserve">ACTUALIZACIÓN PLATAFORMA ERP PARA LA CORPORACIÓN</t>
         </is>
       </c>
       <c r="C15" s="0">
@@ -11978,16 +11147,16 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Software de diseño asistido por computador (CAD)</t>
+          <t xml:space="preserve">Software de planificación de recursos empresariales (ERP)</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software específico para la industria</t>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de planificación de recursos empresariales (ERP) y contabilidad financiera</t>
         </is>
       </c>
       <c r="F15" s="0">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
       <c r="G15" s="0" t="inlineStr">
         <is>
@@ -11995,44 +11164,6 @@
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Licencias de Software CAD (Archicad Collaborate o Equivalente), con suscripción de 12 meses, con pago en 12 cuotas.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">564953-62-LP26</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ACTUALIZACIÓN PLATAFORMA ERP PARA LA CORPORACIÓN</t>
-        </is>
-      </c>
-      <c r="C16" s="0">
-        <v>1</v>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Software de planificación de recursos empresariales (ERP)</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de planificación de recursos empresariales (ERP) y contabilidad financiera</t>
-        </is>
-      </c>
-      <c r="F16" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="G16" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Unidad</t>
-        </is>
-      </c>
-      <c r="H16" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">ACTUALIZACIÓN PLATAFORMA ERP
 PARA LA CORPORACIÓN DE EDUCACIÓN
@@ -12040,15 +11171,53 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3945-20-LE26</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADQUISICION SERVICIO DE SISTEMA INFORMATIVO DE GESTION DOCUMENTAL - MUNICIPALIDAD LOS ALAMOS</t>
+        </is>
+      </c>
+      <c r="C16" s="0">
+        <v>1</v>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Software de sistema operativo</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de entorno operativo</t>
+        </is>
+      </c>
+      <c r="F16" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G16" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Global</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Se requiere contratar SERVICIO DE SISTEMA INFORMATICO DE GESTION DOCUMENTAL- MUNICIPALIDAD LOS ALAMOS”,   por un periodo de 36 meses, según Bases Administrativas, técnicas y anexos adjuntos.</t>
+        </is>
+      </c>
+    </row>
     <row r="17">
       <c r="A17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">3945-20-LE26</t>
+          <t xml:space="preserve">4429-95-LE26</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADQUISICION SERVICIO DE SISTEMA INFORMATIVO DE GESTION DOCUMENTAL - MUNICIPALIDAD LOS ALAMOS</t>
+          <t xml:space="preserve">ARRIENDO SOFTWARE FARMACIA Y OPTICA MUNICIPAL</t>
         </is>
       </c>
       <c r="C17" s="0">
@@ -12056,12 +11225,12 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Software de sistema operativo</t>
+          <t xml:space="preserve">Software de gestión de adquisiciones</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de entorno operativo</t>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de gestión</t>
         </is>
       </c>
       <c r="F17" s="0">
@@ -12069,24 +11238,24 @@
       </c>
       <c r="G17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Global</t>
+          <t xml:space="preserve">Unidad</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Se requiere contratar SERVICIO DE SISTEMA INFORMATICO DE GESTION DOCUMENTAL- MUNICIPALIDAD LOS ALAMOS”,   por un periodo de 36 meses, según Bases Administrativas, técnicas y anexos adjuntos.</t>
+          <t xml:space="preserve">SERVICIO DE ARRIENDO , IMPLEMENTACIÓN PUESTA EN MARCHA Y MANTENCIÓN SOFTWARE EN GESTIÓN Y FARMACIA Y ÓPTICA MUNICIPAL</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">4429-95-LE26</t>
+          <t xml:space="preserve">4429-96-LE26</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ARRIENDO SOFTWARE FARMACIA Y OPTICA MUNICIPAL</t>
+          <t xml:space="preserve">SISTEMA INFORMATICO WEB PARA CENTROS DE SALUD</t>
         </is>
       </c>
       <c r="C18" s="0">
@@ -12094,7 +11263,7 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Software de gestión de adquisiciones</t>
+          <t xml:space="preserve">Paquetes de software para oficinas</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
@@ -12112,19 +11281,19 @@
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">SERVICIO DE ARRIENDO , IMPLEMENTACIÓN PUESTA EN MARCHA Y MANTENCIÓN SOFTWARE EN GESTIÓN Y FARMACIA Y ÓPTICA MUNICIPAL</t>
+          <t xml:space="preserve">SISTEMA INFORMATICO WEB PARA GESTION DE CALIDAD. SEGUN BASES ADMINISTRATIVAS Y TECNICAS ESPECIALES ADJUNTAS.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">4429-96-LE26</t>
+          <t xml:space="preserve">1431841-53-LE26</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">SISTEMA INFORMATICO WEB PARA CENTROS DE SALUD</t>
+          <t xml:space="preserve">ADQUISICIÓN DE CREDITOS GOOGLE CLOUD PLATFORM</t>
         </is>
       </c>
       <c r="C19" s="0">
@@ -12132,12 +11301,12 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Paquetes de software para oficinas</t>
+          <t xml:space="preserve">Software de servidor de aplicaciones</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de gestión</t>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de aplicaciones de red</t>
         </is>
       </c>
       <c r="F19" s="0">
@@ -12145,24 +11314,24 @@
       </c>
       <c r="G19" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unidad</t>
+          <t xml:space="preserve">Global</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">SISTEMA INFORMATICO WEB PARA GESTION DE CALIDAD. SEGUN BASES ADMINISTRATIVAS Y TECNICAS ESPECIALES ADJUNTAS.</t>
+          <t xml:space="preserve">Valor Neto Total de la ADQUISICIÓN DE CRÉDITOS PARA GOOGLE CLOUD PLATFORM (GCP) PARA LA MUNICIPALIDAD DE RECOLETA</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1431841-53-LE26</t>
+          <t xml:space="preserve">3506-88-LP26</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADQUISICIÓN DE CREDITOS GOOGLE CLOUD PLATFORM</t>
+          <t xml:space="preserve">ADQUISICION DE SOFTWARE DE GESTION MUNICIPAL</t>
         </is>
       </c>
       <c r="C20" s="0">
@@ -12170,12 +11339,12 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Software de servidor de aplicaciones</t>
+          <t xml:space="preserve">Software de gestión de licencias</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de aplicaciones de red</t>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de gestión</t>
         </is>
       </c>
       <c r="F20" s="0">
@@ -12183,24 +11352,24 @@
       </c>
       <c r="G20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Global</t>
+          <t xml:space="preserve">Unidad</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valor Neto Total de la ADQUISICIÓN DE CRÉDITOS PARA GOOGLE CLOUD PLATFORM (GCP) PARA LA MUNICIPALIDAD DE RECOLETA</t>
+          <t xml:space="preserve">ADQUISICION DE SOFTWARE DE GESTION MUNICIPAL</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">3506-88-LP26</t>
+          <t xml:space="preserve">761391-124-L126</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADQUISICION DE SOFTWARE DE GESTION MUNICIPAL</t>
+          <t xml:space="preserve">DE/54/GUB/PLATAFORMA DE PREPARACIÓN PARA EL EXAMEN TOEIC LISTENING AND READING</t>
         </is>
       </c>
       <c r="C21" s="0">
@@ -12208,16 +11377,16 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Software de gestión de licencias</t>
+          <t xml:space="preserve">Capacitación a empleados</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de gestión</t>
+          <t xml:space="preserve">Educación, formación, entrenamiento y capacitación / Sistemas educativos complementarios / Educación de adultos</t>
         </is>
       </c>
       <c r="F21" s="0">
-        <v>1.0</v>
+        <v>13.0</v>
       </c>
       <c r="G21" s="0" t="inlineStr">
         <is>
@@ -12226,19 +11395,19 @@
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADQUISICION DE SOFTWARE DE GESTION MUNICIPAL</t>
+          <t xml:space="preserve">PLATAFORMA DE PREPARACIÓN PARA EL EXAMEN TOEIC LISTENING AND READING</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">761391-124-L126</t>
+          <t xml:space="preserve">3477-77-LE26</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">DE/54/GUB/PLATAFORMA DE PREPARACIÓN PARA EL EXAMEN TOEIC LISTENING AND READING</t>
+          <t xml:space="preserve">“INSTALACIÓN DE PUNTOS DE RED EN UDEL” SECCIÓN DE INFORMÁTICA MUNICIPAL</t>
         </is>
       </c>
       <c r="C22" s="0">
@@ -12246,37 +11415,37 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Capacitación a empleados</t>
+          <t xml:space="preserve">Especialistas temporales en redes computacionales</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Educación, formación, entrenamiento y capacitación / Sistemas educativos complementarios / Educación de adultos</t>
+          <t xml:space="preserve">Servicios profesionales, administrativos y consultorías de gestión empresarial / Servicios de recursos humanos / Servicios de personal temporal</t>
         </is>
       </c>
       <c r="F22" s="0">
-        <v>13.0</v>
+        <v>1.0</v>
       </c>
       <c r="G22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unidad</t>
+          <t xml:space="preserve">Global</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">PLATAFORMA DE PREPARACIÓN PARA EL EXAMEN TOEIC LISTENING AND READING</t>
+          <t xml:space="preserve">SEGUN REQUERIMIENTOS ADJUNTOS</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">3477-77-LE26</t>
+          <t xml:space="preserve">730566-21-LP26</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">“INSTALACIÓN DE PUNTOS DE RED EN UDEL” SECCIÓN DE INFORMÁTICA MUNICIPAL</t>
+          <t xml:space="preserve">RENOVACIÓN DE PLATAFORMA WIFI</t>
         </is>
       </c>
       <c r="C23" s="0">
@@ -12284,25 +11453,25 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Especialistas temporales en redes computacionales</t>
+          <t xml:space="preserve">Dispositivos de acceso de red digital de servicios integrados (RDSI)</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Servicios profesionales, administrativos y consultorías de gestión empresarial / Servicios de recursos humanos / Servicios de personal temporal</t>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Equipos, plataformas y accesorios de redes multimedia, voz y datos / Equipos de servicio de red</t>
         </is>
       </c>
       <c r="F23" s="0">
-        <v>1.0</v>
+        <v>100.0</v>
       </c>
       <c r="G23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Global</t>
+          <t xml:space="preserve">Unidad</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEGUN REQUERIMIENTOS ADJUNTOS</t>
+          <t xml:space="preserve">access point Tecnología Wi-Fi 6E (802.11ax); Triple radio:( 2.4 GHz, 5 GHz y 6 GHz); Hasta 3.5 Gbps de throughput agregado; Gestión centralizada; Puerto Ethernet multigigabit 5GE; Alimentación PoE+; soporte para WPA3; soporte con 3 años 24/7</t>
         </is>
       </c>
     </row>
@@ -12318,20 +11487,20 @@
         </is>
       </c>
       <c r="C24" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dispositivos de acceso de red digital de servicios integrados (RDSI)</t>
+          <t xml:space="preserve">Plataforma de mensajería unificada</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Equipos, plataformas y accesorios de redes multimedia, voz y datos / Equipos de servicio de red</t>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Equipos, plataformas y accesorios de redes multimedia, voz y datos / Plataformas de mensajería por móvil</t>
         </is>
       </c>
       <c r="F24" s="0">
-        <v>100.0</v>
+        <v>1.0</v>
       </c>
       <c r="G24" s="0" t="inlineStr">
         <is>
@@ -12340,32 +11509,32 @@
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">access point Tecnología Wi-Fi 6E (802.11ax); Triple radio:( 2.4 GHz, 5 GHz y 6 GHz); Hasta 3.5 Gbps de throughput agregado; Gestión centralizada; Puerto Ethernet multigigabit 5GE; Alimentación PoE+; soporte para WPA3; soporte con 3 años 24/7</t>
+          <t xml:space="preserve">plataforma de gestión centralizada para Access point ofertados con las siguientes características: Gestión centralizada de Access point,Automatización de configuraciones,Gestión de políticas, Backup centralizados, Administración multi-dispositivo</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">730566-21-LP26</t>
+          <t xml:space="preserve">2427-73-LE26</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">RENOVACIÓN DE PLATAFORMA WIFI</t>
+          <t xml:space="preserve">SUMINISTRO DE MARKETING DIGITAL PARA REDES SOCIALES DEL MUNICIPIO DE VALPARAÍSO</t>
         </is>
       </c>
       <c r="C25" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plataforma de mensajería unificada</t>
+          <t xml:space="preserve">Agencias de marketing de ventas, incluidas las impresiones</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Equipos, plataformas y accesorios de redes multimedia, voz y datos / Plataformas de mensajería por móvil</t>
+          <t xml:space="preserve">Servicios profesionales, administrativos y consultorías de gestión empresarial / Servicios para la comercialización y distribución / Ventas y marketing</t>
         </is>
       </c>
       <c r="F25" s="0">
@@ -12378,19 +11547,19 @@
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">plataforma de gestión centralizada para Access point ofertados con las siguientes características: Gestión centralizada de Access point,Automatización de configuraciones,Gestión de políticas, Backup centralizados, Administración multi-dispositivo</t>
+          <t xml:space="preserve">SUMINISTRO DE MARKETING DIGITAL PARA REDES SOCIALES DEL MUNICIPIO DE VALPARAÍSO, SEGÚN BASES TÉCNICAS ADJUNTAS.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2427-73-LE26</t>
+          <t xml:space="preserve">2258-146-LP26</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">SUMINISTRO DE MARKETING DIGITAL PARA REDES SOCIALES DEL MUNICIPIO DE VALPARAÍSO</t>
+          <t xml:space="preserve">AUDIFONOS DIGITAL PAC.GES HIPOACUSIA BILATERAL</t>
         </is>
       </c>
       <c r="C26" s="0">
@@ -12398,16 +11567,16 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Agencias de marketing de ventas, incluidas las impresiones</t>
+          <t xml:space="preserve">Audífonos para personas con discapacidad física</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Servicios profesionales, administrativos y consultorías de gestión empresarial / Servicios para la comercialización y distribución / Ventas y marketing</t>
+          <t xml:space="preserve">Equipamiento y suministros médicos / Ayuda para personas con discapacidad / Artículos de ayuda para la comunicación de discapacitados</t>
         </is>
       </c>
       <c r="F26" s="0">
-        <v>1.0</v>
+        <v>900.0</v>
       </c>
       <c r="G26" s="0" t="inlineStr">
         <is>
@@ -12416,7 +11585,7 @@
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">SUMINISTRO DE MARKETING DIGITAL PARA REDES SOCIALES DEL MUNICIPIO DE VALPARAÍSO, SEGÚN BASES TÉCNICAS ADJUNTAS.</t>
+          <t xml:space="preserve">Audífonos digitales para tratamiento pacientes Ges hipoacusia bilateral, perdida leve a moderada</t>
         </is>
       </c>
     </row>
@@ -12432,7 +11601,7 @@
         </is>
       </c>
       <c r="C27" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
@@ -12445,7 +11614,7 @@
         </is>
       </c>
       <c r="F27" s="0">
-        <v>900.0</v>
+        <v>504.0</v>
       </c>
       <c r="G27" s="0" t="inlineStr">
         <is>
@@ -12454,36 +11623,36 @@
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Audífonos digitales para tratamiento pacientes Ges hipoacusia bilateral, perdida leve a moderada</t>
+          <t xml:space="preserve">Audífonos digitales para tratamiento pacientes Ges hipoacusia bilateral, perdida moderada a profunda</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2258-146-LP26</t>
+          <t xml:space="preserve">1483311-2-LP26</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUDIFONOS DIGITAL PAC.GES HIPOACUSIA BILATERAL</t>
+          <t xml:space="preserve">SERVICIO DE ARRIENDO DE SOFTWARE DE REMUNERACIONES</t>
         </is>
       </c>
       <c r="C28" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Audífonos para personas con discapacidad física</t>
+          <t xml:space="preserve">Software de gestión de recursos humanos</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Equipamiento y suministros médicos / Ayuda para personas con discapacidad / Artículos de ayuda para la comunicación de discapacitados</t>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de gestión</t>
         </is>
       </c>
       <c r="F28" s="0">
-        <v>504.0</v>
+        <v>1.0</v>
       </c>
       <c r="G28" s="0" t="inlineStr">
         <is>
@@ -12492,7 +11661,7 @@
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Audífonos digitales para tratamiento pacientes Ges hipoacusia bilateral, perdida moderada a profunda</t>
+          <t xml:space="preserve">SERVICIO DE ARRIENDO DE SOFTWARE DE REMUNERACIONES Y GESTIÓN DE PERSONAS P01, SERVICIO LOCAL DE EDUCACIÓN PÚBLICA LOS VIÑEDOS</t>
         </is>
       </c>
     </row>
@@ -12508,7 +11677,7 @@
         </is>
       </c>
       <c r="C29" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
@@ -12530,23 +11699,23 @@
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">SERVICIO DE ARRIENDO DE SOFTWARE DE REMUNERACIONES Y GESTIÓN DE PERSONAS P01, SERVICIO LOCAL DE EDUCACIÓN PÚBLICA LOS VIÑEDOS</t>
+          <t xml:space="preserve">SERVICIO DE ARRIENDO DE SOFTWARE DE REMUNERACIONES Y GESTIÓN DE PERSONAS P02, SERVICIO LOCAL DE EDUCACIÓN PÚBLICA LOS VIÑEDOS</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1483311-2-LP26</t>
+          <t xml:space="preserve">1422051-25-LE26</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">SERVICIO DE ARRIENDO DE SOFTWARE DE REMUNERACIONES</t>
+          <t xml:space="preserve">Contratación Servicio Plataforma de Gestión RRHH</t>
         </is>
       </c>
       <c r="C30" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
@@ -12568,19 +11737,19 @@
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">SERVICIO DE ARRIENDO DE SOFTWARE DE REMUNERACIONES Y GESTIÓN DE PERSONAS P02, SERVICIO LOCAL DE EDUCACIÓN PÚBLICA LOS VIÑEDOS</t>
+          <t xml:space="preserve">Software de Gestión para Recursos Humanos.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1422051-25-LE26</t>
+          <t xml:space="preserve">727202-69-LE26</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contratación Servicio Plataforma de Gestión RRHH</t>
+          <t xml:space="preserve">ADQUISICIÓN E IMPLEMENTACIÓN DE TÓTEMS</t>
         </is>
       </c>
       <c r="C31" s="0">
@@ -12588,12 +11757,12 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Software de gestión de recursos humanos</t>
+          <t xml:space="preserve">Monitores de pantalla táctil</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de gestión</t>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Equipos informáticos y accesorios / Pantallas o monitores de computador</t>
         </is>
       </c>
       <c r="F31" s="0">
@@ -12601,24 +11770,24 @@
       </c>
       <c r="G31" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unidad</t>
+          <t xml:space="preserve">Global</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Software de Gestión para Recursos Humanos.</t>
+          <t xml:space="preserve">ADQUISICIÓN E IMPLEMENTACIÓN DE TÓTEMS INTERACTIVOS, CONFORME A LA DOCUMENTACIÓN ADJUNTA.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">727202-69-LE26</t>
+          <t xml:space="preserve">3553-29-LE26</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADQUISICIÓN E IMPLEMENTACIÓN DE TÓTEMS</t>
+          <t xml:space="preserve">Serv. jurídicos de Ley 21.719 y prot. de datos</t>
         </is>
       </c>
       <c r="C32" s="0">
@@ -12626,12 +11795,12 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Monitores de pantalla táctil</t>
+          <t xml:space="preserve">Servicios de asistencia legal y judicial</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Equipos informáticos y accesorios / Pantallas o monitores de computador</t>
+          <t xml:space="preserve">Organizaciones sociales, laborales y clubes / Organizaciones, asociaciones y movimientos cívicos / Organizaciones de beneficencia</t>
         </is>
       </c>
       <c r="F32" s="0">
@@ -12639,24 +11808,24 @@
       </c>
       <c r="G32" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Global</t>
+          <t xml:space="preserve">Unidad</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADQUISICIÓN E IMPLEMENTACIÓN DE TÓTEMS INTERACTIVOS, CONFORME A LA DOCUMENTACIÓN ADJUNTA.</t>
+          <t xml:space="preserve">Servicios profesionales para auditoría de brechas, actualización de cumplimiento normativo en el Ministerio de Bienes Nacionales y diseño de sistema de gestión de protección de datos personales para la implementación de la ley 21.719.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">3553-29-LE26</t>
+          <t xml:space="preserve">1469-173-L126</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Serv. jurídicos de Ley 21.719 y prot. de datos</t>
+          <t xml:space="preserve">Sistema de gestión de Libro de Obras Digital, para PIBV</t>
         </is>
       </c>
       <c r="C33" s="0">
@@ -12664,12 +11833,12 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Servicios de asistencia legal y judicial</t>
+          <t xml:space="preserve">Software de búsqueda o recuperación de información</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Organizaciones sociales, laborales y clubes / Organizaciones, asociaciones y movimientos cívicos / Organizaciones de beneficencia</t>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de consultas y gestión de datos</t>
         </is>
       </c>
       <c r="F33" s="0">
@@ -12682,19 +11851,19 @@
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Servicios profesionales para auditoría de brechas, actualización de cumplimiento normativo en el Ministerio de Bienes Nacionales y diseño de sistema de gestión de protección de datos personales para la implementación de la ley 21.719.</t>
+          <t xml:space="preserve">La Universidad de Talca requiere del servicio de plataforma de Libro de Obra Digital para continuar con el requerimiento del Convenio PIBV, por un periodo de 15 meses.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1469-173-L126</t>
+          <t xml:space="preserve">869591-9-LR26</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sistema de gestión de Libro de Obras Digital, para PIBV</t>
+          <t xml:space="preserve">CONTRATACIÓN DEL DESARROLLO DE LA PLATAFORMA MODULAR DE COMPRAS NUEVOS MECANISMOS PARA LA DIRECCIÓN DE COMPRAS Y CONTRATACIÓN PÚBLICA.</t>
         </is>
       </c>
       <c r="C34" s="0">
@@ -12702,12 +11871,12 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Software de búsqueda o recuperación de información</t>
+          <t xml:space="preserve">Desarrolladores de software</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de consultas y gestión de datos</t>
+          <t xml:space="preserve">Servicios profesionales, administrativos y consultorías de gestión empresarial / Servicios de recursos humanos / Contratación de personal</t>
         </is>
       </c>
       <c r="F34" s="0">
@@ -12720,19 +11889,19 @@
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">La Universidad de Talca requiere del servicio de plataforma de Libro de Obra Digital para continuar con el requerimiento del Convenio PIBV, por un periodo de 15 meses.</t>
+          <t xml:space="preserve">CONTRATACIÓN DEL DESARROLLO DE LA PLATAFORMA MODULAR DE COMPRAS (NUEVOS MECANISMOS) PARA LA DIRECCIÓN DE COMPRAS Y CONTRATACIÓN PÚBLICA.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">869591-9-LR26</t>
+          <t xml:space="preserve">1641-323-LE26</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">CONTRATACIÓN DEL DESARROLLO DE LA PLATAFORMA MODULAR DE COMPRAS NUEVOS MECANISMOS PARA LA DIRECCIÓN DE COMPRAS Y CONTRATACIÓN PÚBLICA.</t>
+          <t xml:space="preserve">FMM - SUMINISTRO DE LICENCIA DE SOFTWARE AUTOCAD PARA OBRAS</t>
         </is>
       </c>
       <c r="C35" s="0">
@@ -12740,16 +11909,16 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Desarrolladores de software</t>
+          <t xml:space="preserve">Software de diseño asistido por computador (CAD)</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Servicios profesionales, administrativos y consultorías de gestión empresarial / Servicios de recursos humanos / Contratación de personal</t>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software específico para la industria</t>
         </is>
       </c>
       <c r="F35" s="0">
-        <v>1.0</v>
+        <v>7.0</v>
       </c>
       <c r="G35" s="0" t="inlineStr">
         <is>
@@ -12758,7 +11927,7 @@
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">CONTRATACIÓN DEL DESARROLLO DE LA PLATAFORMA MODULAR DE COMPRAS (NUEVOS MECANISMOS) PARA LA DIRECCIÓN DE COMPRAS Y CONTRATACIÓN PÚBLICA.</t>
+          <t xml:space="preserve">10-013-004-0155 @ SUMINISTRO DE LICENCIAS DE SOFTWARE AUTOCAD LT</t>
         </is>
       </c>
     </row>
@@ -12774,7 +11943,7 @@
         </is>
       </c>
       <c r="C36" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
@@ -12787,7 +11956,7 @@
         </is>
       </c>
       <c r="F36" s="0">
-        <v>7.0</v>
+        <v>2.0</v>
       </c>
       <c r="G36" s="0" t="inlineStr">
         <is>
@@ -12796,36 +11965,36 @@
       </c>
       <c r="H36" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">10-013-004-0155 @ SUMINISTRO DE LICENCIAS DE SOFTWARE AUTOCAD LT</t>
+          <t xml:space="preserve">10-013-004-0156 @ SUMINISTRO DE LICENCIAS DE SOFTWARE AUTOCAD</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1641-323-LE26</t>
+          <t xml:space="preserve">3530-19-L126</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FMM - SUMINISTRO DE LICENCIA DE SOFTWARE AUTOCAD PARA OBRAS</t>
+          <t xml:space="preserve">Adquisición del servicio de mantenimiento y reparación para el reemplazo completo del tablero eléctrico trifásico.</t>
         </is>
       </c>
       <c r="C37" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Software de diseño asistido por computador (CAD)</t>
+          <t xml:space="preserve">Paneles de control eléctrico para generadores</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software específico para la industria</t>
+          <t xml:space="preserve">Maquinaria para generación y distribución de energía / Generación de energía / Equipo para control de producción de energía</t>
         </is>
       </c>
       <c r="F37" s="0">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G37" s="0" t="inlineStr">
         <is>
@@ -12834,19 +12003,19 @@
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">10-013-004-0156 @ SUMINISTRO DE LICENCIAS DE SOFTWARE AUTOCAD</t>
+          <t xml:space="preserve">Adquisición del servicio de mantenimiento y reparación para el reemplazo completo del tablero eléctrico trifásico perteneciente al Regimiento N°2 "Maipo".</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">3530-19-L126</t>
+          <t xml:space="preserve">1171234-5-LE26</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adquisición del servicio de mantenimiento y reparación para el reemplazo completo del tablero eléctrico trifásico.</t>
+          <t xml:space="preserve">SERVICIOS DE IMPLEMENTACIÓN SOFTWARE CEDOC MNBA</t>
         </is>
       </c>
       <c r="C38" s="0">
@@ -12854,12 +12023,12 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Paneles de control eléctrico para generadores</t>
+          <t xml:space="preserve">Instalación de sistemas</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Maquinaria para generación y distribución de energía / Generación de energía / Equipo para control de producción de energía</t>
+          <t xml:space="preserve">Servicios basados en ingeniería, ciencias sociales y tecnología de la información / Servicios informáticos / Administración de sistemas</t>
         </is>
       </c>
       <c r="F38" s="0">
@@ -12872,19 +12041,19 @@
       </c>
       <c r="H38" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adquisición del servicio de mantenimiento y reparación para el reemplazo completo del tablero eléctrico trifásico perteneciente al Regimiento N°2 "Maipo".</t>
+          <t xml:space="preserve">IMPLEMENTACIÓN DE SOFTWARE CONSERVACIÓN, SISTEMATIZACIÓN Y ACCESO A LOS ACERVOS PATRIMONIALES DEL CENTRO DE DOCUMENTACIÓN ANGÉLICA PÉREZ GERMAIN</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1171234-5-LE26</t>
+          <t xml:space="preserve">2981-242-LE26</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">SERVICIOS DE IMPLEMENTACIÓN SOFTWARE CEDOC MNBA</t>
+          <t xml:space="preserve">ADQUISICIÓN DE ESTRUCTURA TÓTEM Y LETRAS VOLUMETRICAS DE METAL</t>
         </is>
       </c>
       <c r="C39" s="0">
@@ -12892,12 +12061,12 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Instalación de sistemas</t>
+          <t xml:space="preserve">Placas metálicas indicadoras del nombre</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Servicios basados en ingeniería, ciencias sociales y tecnología de la información / Servicios informáticos / Administración de sistemas</t>
+          <t xml:space="preserve">Productos impresos y publicaciones / Etiquetado y accesorios / Etiquetado</t>
         </is>
       </c>
       <c r="F39" s="0">
@@ -12905,24 +12074,24 @@
       </c>
       <c r="G39" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unidad</t>
+          <t xml:space="preserve">Unidad no definida</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">IMPLEMENTACIÓN DE SOFTWARE CONSERVACIÓN, SISTEMATIZACIÓN Y ACCESO A LOS ACERVOS PATRIMONIALES DEL CENTRO DE DOCUMENTACIÓN ANGÉLICA PÉREZ GERMAIN</t>
+          <t xml:space="preserve">FABRICACION, INSTALACION Y HABILITACION DE ESTRUCTURA TÓTEM Y LETRAS VOLUMETRICAS PDI, SEGUN ESPECIFICACIONES TECNICAS ADJUNTAS</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2981-242-LE26</t>
+          <t xml:space="preserve">3820-25-LE26</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADQUISICIÓN DE ESTRUCTURA TÓTEM Y LETRAS VOLUMETRICAS DE METAL</t>
+          <t xml:space="preserve">ADQUISICION Y RENOVACION DE LICENCIAS DE SOFTWARE</t>
         </is>
       </c>
       <c r="C40" s="0">
@@ -12930,12 +12099,12 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Placas metálicas indicadoras del nombre</t>
+          <t xml:space="preserve">Software de gestión de licencias</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Productos impresos y publicaciones / Etiquetado y accesorios / Etiquetado</t>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de gestión</t>
         </is>
       </c>
       <c r="F40" s="0">
@@ -12943,24 +12112,24 @@
       </c>
       <c r="G40" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unidad no definida</t>
+          <t xml:space="preserve">Unidad</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FABRICACION, INSTALACION Y HABILITACION DE ESTRUCTURA TÓTEM Y LETRAS VOLUMETRICAS PDI, SEGUN ESPECIFICACIONES TECNICAS ADJUNTAS</t>
+          <t xml:space="preserve">Renovación y  Adquisición de  Licencias AUTOCAD 2026 o 2027 Including Specialized Toolsets, y Renovación y  Adquisición de  Licencias de AUTOCAD LT 2026 o 2027” para el Departamento de Secpla, de Obras y Oficina de Electricidad y programa revit</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">3820-25-LE26</t>
+          <t xml:space="preserve">564162-115-L126</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADQUISICION Y RENOVACION DE LICENCIAS DE SOFTWARE</t>
+          <t xml:space="preserve">Solicitud N°92870 - Bolsas, etiquetas y cajas con impresión digital - CC112 / PS1772</t>
         </is>
       </c>
       <c r="C41" s="0">
@@ -12968,12 +12137,12 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Software de gestión de licencias</t>
+          <t xml:space="preserve">Cajas para empaquetado</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de gestión</t>
+          <t xml:space="preserve">Equipamiento para manejo y estiba de materiales / Materiales para envasado / Cajas, bolsas y sacos para envasado</t>
         </is>
       </c>
       <c r="F41" s="0">
@@ -12986,32 +12155,32 @@
       </c>
       <c r="H41" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Renovación y  Adquisición de  Licencias AUTOCAD 2026 o 2027 Including Specialized Toolsets, y Renovación y  Adquisición de  Licencias de AUTOCAD LT 2026 o 2027” para el Departamento de Secpla, de Obras y Oficina de Electricidad y programa revit</t>
+          <t xml:space="preserve">800 Cajas de cartón y 800 juego tabiques con impresión.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">584105-34-LE26</t>
+          <t xml:space="preserve">564162-115-L126</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Licitacion licencia de software</t>
+          <t xml:space="preserve">Solicitud N°92870 - Bolsas, etiquetas y cajas con impresión digital - CC112 / PS1772</t>
         </is>
       </c>
       <c r="C42" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Desarrolladores de software</t>
+          <t xml:space="preserve">Cajas para empaquetado</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Servicios profesionales, administrativos y consultorías de gestión empresarial / Servicios de recursos humanos / Contratación de personal</t>
+          <t xml:space="preserve">Equipamiento para manejo y estiba de materiales / Materiales para envasado / Cajas, bolsas y sacos para envasado</t>
         </is>
       </c>
       <c r="F42" s="0">
@@ -13024,36 +12193,36 @@
       </c>
       <c r="H42" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">LICITACIÓN PÚBLICA PARA LA “ADQUISICIÓN DE LICENCIA DE SOFTWARE NECESARIO PARA LA PLANIFICACIÓN ENERGÉTICA DE LA SUBSECRETARÍA DE ENERGÍA</t>
+          <t xml:space="preserve">850 cajas de cartón y 850 juego tabiques con impresión.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">721-29-LP26</t>
+          <t xml:space="preserve">564162-115-L126</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Respaldo y recuperación plataforma de servidores</t>
+          <t xml:space="preserve">Solicitud N°92870 - Bolsas, etiquetas y cajas con impresión digital - CC112 / PS1772</t>
         </is>
       </c>
       <c r="C43" s="0">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Servidores de acceso</t>
+          <t xml:space="preserve">Papel, bolsas o cajas de regalo</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Equipos, plataformas y accesorios de redes multimedia, voz y datos / Equipos de servicio de red</t>
+          <t xml:space="preserve">Productos de papel / Productos de papel / Papel fantasía</t>
         </is>
       </c>
       <c r="F43" s="0">
-        <v>24.0</v>
+        <v>1.0</v>
       </c>
       <c r="G43" s="0" t="inlineStr">
         <is>
@@ -13062,7 +12231,7 @@
       </c>
       <c r="H43" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Servicio de respaldo y recuperación de su plataforma de servidores. Ofertar por el VALOR NETO MENSUAL DEL SERVICIO (valor de un mes de servicio) e indicar el detalle en el Anexo N°4 “Oferta Económica y Plazo de Implementación”</t>
+          <t xml:space="preserve">Bolsas de papel para botellas. 1.000 unidades.</t>
         </is>
       </c>
     </row>
@@ -13078,16 +12247,16 @@
         </is>
       </c>
       <c r="C44" s="0">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cajas para empaquetado</t>
+          <t xml:space="preserve">Etiquetas autoadhesivas</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Equipamiento para manejo y estiba de materiales / Materiales para envasado / Cajas, bolsas y sacos para envasado</t>
+          <t xml:space="preserve">Productos impresos y publicaciones / Etiquetado y accesorios / Etiquetas</t>
         </is>
       </c>
       <c r="F44" s="0">
@@ -13100,7 +12269,8 @@
       </c>
       <c r="H44" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">800 Cajas de cartón y 800 juego tabiques con impresión.</t>
+          <t xml:space="preserve">Etiquetas frontales. 5.081 unidades con impresión digital.
+Contraetiquetas. 5.081 unidades con impresión digital.</t>
         </is>
       </c>
     </row>
@@ -13116,16 +12286,16 @@
         </is>
       </c>
       <c r="C45" s="0">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cajas para empaquetado</t>
+          <t xml:space="preserve">Etiquetas autoadhesivas</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Equipamiento para manejo y estiba de materiales / Materiales para envasado / Cajas, bolsas y sacos para envasado</t>
+          <t xml:space="preserve">Productos impresos y publicaciones / Etiquetado y accesorios / Etiquetas</t>
         </is>
       </c>
       <c r="F45" s="0">
@@ -13138,32 +12308,32 @@
       </c>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">850 cajas de cartón y 850 juego tabiques con impresión.</t>
+          <t xml:space="preserve">Etiquetas colgantes para botellas de vino. 5.081 unidades.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">564162-115-L126</t>
+          <t xml:space="preserve">584105-34-LE26</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Solicitud N°92870 - Bolsas, etiquetas y cajas con impresión digital - CC112 / PS1772</t>
+          <t xml:space="preserve">Licitacion licencia de software</t>
         </is>
       </c>
       <c r="C46" s="0">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Papel, bolsas o cajas de regalo</t>
+          <t xml:space="preserve">Desarrolladores de software</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Productos de papel / Productos de papel / Papel fantasía</t>
+          <t xml:space="preserve">Servicios profesionales, administrativos y consultorías de gestión empresarial / Servicios de recursos humanos / Contratación de personal</t>
         </is>
       </c>
       <c r="F46" s="0">
@@ -13176,36 +12346,36 @@
       </c>
       <c r="H46" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bolsas de papel para botellas. 1.000 unidades.</t>
+          <t xml:space="preserve">LICITACIÓN PÚBLICA PARA LA “ADQUISICIÓN DE LICENCIA DE SOFTWARE NECESARIO PARA LA PLANIFICACIÓN ENERGÉTICA DE LA SUBSECRETARÍA DE ENERGÍA</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">564162-115-L126</t>
+          <t xml:space="preserve">721-29-LP26</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Solicitud N°92870 - Bolsas, etiquetas y cajas con impresión digital - CC112 / PS1772</t>
+          <t xml:space="preserve">Respaldo y recuperación plataforma de servidores</t>
         </is>
       </c>
       <c r="C47" s="0">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Etiquetas autoadhesivas</t>
+          <t xml:space="preserve">Servidores de acceso</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Productos impresos y publicaciones / Etiquetado y accesorios / Etiquetas</t>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Equipos, plataformas y accesorios de redes multimedia, voz y datos / Equipos de servicio de red</t>
         </is>
       </c>
       <c r="F47" s="0">
-        <v>1.0</v>
+        <v>24.0</v>
       </c>
       <c r="G47" s="0" t="inlineStr">
         <is>
@@ -13214,33 +12384,32 @@
       </c>
       <c r="H47" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Etiquetas frontales. 5.081 unidades con impresión digital.
-Contraetiquetas. 5.081 unidades con impresión digital.</t>
+          <t xml:space="preserve">Servicio de respaldo y recuperación de su plataforma de servidores. Ofertar por el VALOR NETO MENSUAL DEL SERVICIO (valor de un mes de servicio) e indicar el detalle en el Anexo N°4 “Oferta Económica y Plazo de Implementación”</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">564162-115-L126</t>
+          <t xml:space="preserve">2324-109-LE26</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Solicitud N°92870 - Bolsas, etiquetas y cajas con impresión digital - CC112 / PS1772</t>
+          <t xml:space="preserve">LICITACION PÚBLICA N° 52026 “CONTRATACION DE SOFTWARE CONTROL DE OBRAS Y GESTION DE PROYECTOS PARA LA INSPECCION DE OBRAS MUNICIPALES POR 3 AÑOS”</t>
         </is>
       </c>
       <c r="C48" s="0">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Etiquetas autoadhesivas</t>
+          <t xml:space="preserve">Programas de gestión de proyectos</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Productos impresos y publicaciones / Etiquetado y accesorios / Etiquetas</t>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de gestión</t>
         </is>
       </c>
       <c r="F48" s="0">
@@ -13248,24 +12417,24 @@
       </c>
       <c r="G48" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unidad</t>
+          <t xml:space="preserve">Global</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Etiquetas colgantes para botellas de vino. 5.081 unidades.</t>
+          <t xml:space="preserve">CONTRATCION DE SISTEMA DE PLATAFORMA CONTROL DE OBRAS Y GESTION PARA LA INSPECCION TECNICA DE OBRAS DE PROYECTOS FISCALIZADOS POR DIRECCION DE OBRAS MUNICIPALES.  (SEGÚN TERMINOS TECNICOS DE REFERENCIA ADJUNTA)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2324-109-LE26</t>
+          <t xml:space="preserve">29-69-LE26</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">LICITACION PÚBLICA N° 52026 “CONTRATACION DE SOFTWARE CONTROL DE OBRAS Y GESTION DE PROYECTOS PARA LA INSPECCION DE OBRAS MUNICIPALES POR 3 AÑOS”</t>
+          <t xml:space="preserve">SERVICIO DE TRANSMISIÓN ELECTRÓNICA DE DATOS</t>
         </is>
       </c>
       <c r="C49" s="0">
@@ -13273,12 +12442,12 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Programas de gestión de proyectos</t>
+          <t xml:space="preserve">Servicios de transmisión de datos de registro</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de gestión</t>
+          <t xml:space="preserve">Servicios de perforación de minería, petróleo y gas / Servicios gestión y proceso de datos e información sobre petróleo y gas / Servicios de comunicación de datos del campo petrolífero</t>
         </is>
       </c>
       <c r="F49" s="0">
@@ -13286,24 +12455,24 @@
       </c>
       <c r="G49" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Global</t>
+          <t xml:space="preserve">Unidad</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">CONTRATCION DE SISTEMA DE PLATAFORMA CONTROL DE OBRAS Y GESTION PARA LA INSPECCION TECNICA DE OBRAS DE PROYECTOS FISCALIZADOS POR DIRECCION DE OBRAS MUNICIPALES.  (SEGÚN TERMINOS TECNICOS DE REFERENCIA ADJUNTA)</t>
+          <t xml:space="preserve">SERVICIO DE TRANSMISIÓN ELECTRÓNICA DE DATOS ENTRE LA FUERZA AÉREA DE CHILE Y EL SERVICIO NACIONAL DE ADUANAS.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">29-69-LE26</t>
+          <t xml:space="preserve">2446-251-LE26</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">SERVICIO DE TRANSMISIÓN ELECTRÓNICA DE DATOS</t>
+          <t xml:space="preserve">IMPLEMENTACION PLATAFORMA E-LEARNING</t>
         </is>
       </c>
       <c r="C50" s="0">
@@ -13311,12 +12480,12 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Servicios de transmisión de datos de registro</t>
+          <t xml:space="preserve">E-learning</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Servicios de perforación de minería, petróleo y gas / Servicios gestión y proceso de datos e información sobre petróleo y gas / Servicios de comunicación de datos del campo petrolífero</t>
+          <t xml:space="preserve">Educación, formación, entrenamiento y capacitación / Servicios de orientación y tecnología educativa / Tecnología educativa</t>
         </is>
       </c>
       <c r="F50" s="0">
@@ -13329,19 +12498,19 @@
       </c>
       <c r="H50" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">SERVICIO DE TRANSMISIÓN ELECTRÓNICA DE DATOS ENTRE LA FUERZA AÉREA DE CHILE Y EL SERVICIO NACIONAL DE ADUANAS.</t>
+          <t xml:space="preserve">PROGRAMA DE IMPLEMENTACIÓN PLATAFORMA E-LEARNING PARA ENSEÑANZA DE IDIOMA INGLÉS, SEGÚN ESPECIFICACIONES TÉCNICAS ADJUNTAS</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2446-251-LE26</t>
+          <t xml:space="preserve">2490-81-LP26</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">IMPLEMENTACION PLATAFORMA E-LEARNING</t>
+          <t xml:space="preserve">“RENOVACIÓN Y ADQUISICIÓN DE SOFTWARE DE LICENCIAS AUTODESK O EQUIVALENTE 2026-2027”</t>
         </is>
       </c>
       <c r="C51" s="0">
@@ -13349,12 +12518,12 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">E-learning</t>
+          <t xml:space="preserve">Software de gestión de licencias</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Educación, formación, entrenamiento y capacitación / Servicios de orientación y tecnología educativa / Tecnología educativa</t>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de gestión</t>
         </is>
       </c>
       <c r="F51" s="0">
@@ -13362,24 +12531,24 @@
       </c>
       <c r="G51" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unidad</t>
+          <t xml:space="preserve">Global</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">PROGRAMA DE IMPLEMENTACIÓN PLATAFORMA E-LEARNING PARA ENSEÑANZA DE IDIOMA INGLÉS, SEGÚN ESPECIFICACIONES TÉCNICAS ADJUNTAS</t>
+          <t xml:space="preserve">VALOR NETO TOTAL PARA EL SERVICIO “RENOVACIÓN Y ADQUISICIÓN DE SOFTWARE DE LICENCIAS AUTODESK O EQUIVALENTE 2026-2027”, EN USD, SEGÚN LO OFERTADO EN FORMULARIO N°4.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2490-81-LP26</t>
+          <t xml:space="preserve">1007793-15-LE26</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">“RENOVACIÓN Y ADQUISICIÓN DE SOFTWARE DE LICENCIAS AUTODESK O EQUIVALENTE 2026-2027”</t>
+          <t xml:space="preserve">SOLUCIÓN INFORMÁTICA INSTITUCIONAL PARA EL CFT</t>
         </is>
       </c>
       <c r="C52" s="0">
@@ -13387,12 +12556,12 @@
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Software de gestión de licencias</t>
+          <t xml:space="preserve">Software de desarrollo de plataforma Web</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Software de gestión</t>
+          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Programas de desarrollo</t>
         </is>
       </c>
       <c r="F52" s="0">
@@ -13400,12 +12569,12 @@
       </c>
       <c r="G52" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Global</t>
+          <t xml:space="preserve">Unidad</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">VALOR NETO TOTAL PARA EL SERVICIO “RENOVACIÓN Y ADQUISICIÓN DE SOFTWARE DE LICENCIAS AUTODESK O EQUIVALENTE 2026-2027”, EN USD, SEGÚN LO OFERTADO EN FORMULARIO N°4.</t>
+          <t xml:space="preserve">Solución informática para la gestión de iniciativas de Vinculación con el Medio.</t>
         </is>
       </c>
     </row>
@@ -13421,7 +12590,7 @@
         </is>
       </c>
       <c r="C53" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
@@ -13443,7 +12612,7 @@
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Solución informática para la gestión de iniciativas de Vinculación con el Medio.</t>
+          <t xml:space="preserve">Implementación y puesta en marcha de la solución</t>
         </is>
       </c>
     </row>
@@ -13459,7 +12628,7 @@
         </is>
       </c>
       <c r="C54" s="0">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
@@ -13481,32 +12650,32 @@
       </c>
       <c r="H54" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Implementación y puesta en marcha de la solución</t>
+          <t xml:space="preserve">Soporte técnico por 24 meses.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1007793-15-LE26</t>
+          <t xml:space="preserve">1978-44-LE26</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">SOLUCIÓN INFORMÁTICA INSTITUCIONAL PARA EL CFT</t>
+          <t xml:space="preserve">ADQUISICIÓN DE SOLUCIÓN XDR PARA CIBERSEGURIDAD AVANZADA SERVICIO DE SALUD MAULE</t>
         </is>
       </c>
       <c r="C55" s="0">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Software de desarrollo de plataforma Web</t>
+          <t xml:space="preserve">Seguridad para computadores, redes e Internet</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tecnologías de la información, telecomunicaciones y radiodifusión / Software / Programas de desarrollo</t>
+          <t xml:space="preserve">Servicios basados en ingeniería, ciencias sociales y tecnología de la información / Servicios informáticos / Administración de sistemas</t>
         </is>
       </c>
       <c r="F55" s="0">
@@ -13519,19 +12688,19 @@
       </c>
       <c r="H55" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Soporte técnico por 24 meses.</t>
+          <t xml:space="preserve">Suscripción y el licenciamiento de una solución XDR para Servicio de Salud Maule.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1978-44-LE26</t>
+          <t xml:space="preserve">2422-149-L126</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADQUISICIÓN DE SOLUCIÓN XDR PARA CIBERSEGURIDAD AVANZADA SERVICIO DE SALUD MAULE</t>
+          <t xml:space="preserve">SOL. 945841, SERVISIO DE FABRICACION E INSTALACION DE TABLERO PARA BALNEARIO</t>
         </is>
       </c>
       <c r="C56" s="0">
@@ -13539,12 +12708,12 @@
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seguridad para computadores, redes e Internet</t>
+          <t xml:space="preserve">Servicios de fabricación de calderas para central eléctrica</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Servicios basados en ingeniería, ciencias sociales y tecnología de la información / Servicios informáticos / Administración de sistemas</t>
+          <t xml:space="preserve">Servicios de producción y fabricación industrial / Fabricación de maquinarias y equipos de transporte / Fabricación de maquinarias</t>
         </is>
       </c>
       <c r="F56" s="0">
@@ -13552,12 +12721,12 @@
       </c>
       <c r="G56" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unidad</t>
+          <t xml:space="preserve">Kit</t>
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Suscripción y el licenciamiento de una solución XDR para Servicio de Salud Maule.</t>
+          <t xml:space="preserve">PARA ACONDICIONAMIENTO DE AMBIENTE DE LA PISCINA TEMPERADA BALNERAIO MUNICIPAL SE REQUIERE SERVICIO DE FABRICACION, INSTLACION Y PUESTA EN MARCHA DE TABLERO DE FUERZA Y COMANDO DE MOTOR TRIFASICO, SEGUN ESPECIFICACIONES TECNICAS ADJUNTAS.</t>
         </is>
       </c>
     </row>
@@ -13678,12 +12847,12 @@
     <row r="60">
       <c r="A60" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">932-25-LE26</t>
+          <t xml:space="preserve">932-22-L126</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">SERVICIO DE MANTENIMIENTO PREVENTIVO Y CORRECTIVO HABITUAL DEL SISTEMA ELÉCTRICO  CORRIENTES DÉBILES E INFRAESTRUCTURA DE DATOS PARA EL CENTRO DEPORTIVO COMUNITARIO  DE  RANCAGUA</t>
+          <t xml:space="preserve">SERVICIO DE REPARACIÓN DE LUMINARIAS, INSTALACIONES ELECTRICAS Y NORMALIZACIÓN DE TABLERO ELECTRONICO DEL COMPLEJO DEPORTIVO HERMOGENES LIZANA, DEL INSTITUTO NACIONAL DE DEPORTES DE O¨HIGGINS.</t>
         </is>
       </c>
       <c r="C60" s="0">
@@ -13691,7 +12860,7 @@
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Servicio de mantenimiento de equipo de fabricación</t>
+          <t xml:space="preserve">Servicio de reparación de equipo de fabricación</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
@@ -13709,46 +12878,46 @@
       </c>
       <c r="H60" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">DE SERVICIO DE REPARACIÓN DE LUMINARIAS, INSTALACIONES ELÉCTRICAS Y NORMALIZACIÓN DE TABLERO ELECTRÓNICO EN EL COMPLEJO DEPORTIVO HERMÓGENES LIZANA, DEL INSTITUTO NACIONAL DE DEPORTES, REGIÓN DE OHIGGINS, De acuerdo a especificaciones adjuntas.-</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">932-25-LE26</t>
+        </is>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SERVICIO DE MANTENIMIENTO PREVENTIVO Y CORRECTIVO HABITUAL DEL SISTEMA ELÉCTRICO  CORRIENTES DÉBILES E INFRAESTRUCTURA DE DATOS PARA EL CENTRO DEPORTIVO COMUNITARIO  DE  RANCAGUA</t>
+        </is>
+      </c>
+      <c r="C61" s="0">
+        <v>1</v>
+      </c>
+      <c r="D61" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Servicio de mantenimiento de equipo de fabricación</t>
+        </is>
+      </c>
+      <c r="E61" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Servicios de producción y fabricación industrial / Servicios de apoyo o soporte a la fabricación / Servicios de mantenimiento y reparación de equipo de fabricación</t>
+        </is>
+      </c>
+      <c r="F61" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G61" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidad</t>
+        </is>
+      </c>
+      <c r="H61" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">Servicio de Mantenimiento preventivo y correctivo Habitual del sistema eléctrico, corrientes débiles e infraestructura
 de datos para el centro deportivo comunitario de Rancagua, de acuerdo  a especificaciones en documento adjunto al formulario de requeri</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">932-22-L126</t>
-        </is>
-      </c>
-      <c r="B61" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SERVICIO DE REPARACIÓN DE LUMINARIAS, INSTALACIONES ELECTRICAS Y NORMALIZACIÓN DE TABLERO ELECTRONICO DEL COMPLEJO DEPORTIVO HERMOGENES LIZANA, DEL INSTITUTO NACIONAL DE DEPORTES DE O¨HIGGINS.</t>
-        </is>
-      </c>
-      <c r="C61" s="0">
-        <v>1</v>
-      </c>
-      <c r="D61" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Servicio de reparación de equipo de fabricación</t>
-        </is>
-      </c>
-      <c r="E61" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Servicios de producción y fabricación industrial / Servicios de apoyo o soporte a la fabricación / Servicios de mantenimiento y reparación de equipo de fabricación</t>
-        </is>
-      </c>
-      <c r="F61" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="G61" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Unidad</t>
-        </is>
-      </c>
-      <c r="H61" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DE SERVICIO DE REPARACIÓN DE LUMINARIAS, INSTALACIONES ELÉCTRICAS Y NORMALIZACIÓN DE TABLERO ELECTRÓNICO EN EL COMPLEJO DEPORTIVO HERMÓGENES LIZANA, DEL INSTITUTO NACIONAL DE DEPORTES, REGIÓN DE OHIGGINS, De acuerdo a especificaciones adjuntas.-</t>
         </is>
       </c>
     </row>

--- a/web/descargas/licitaciones.xlsx
+++ b/web/descargas/licitaciones.xlsx
@@ -219,95 +219,8 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2422-149-L126</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SOL. 945841, SERVISIO DE FABRICACION E INSTALACION DE TABLERO PARA BALNEARIO</t>
-        </is>
-      </c>
-      <c r="C2" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Publicada</t>
-        </is>
-      </c>
-      <c r="D2" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">I MUNICIPALIDAD DE PUENTE ALTO</t>
-        </is>
-      </c>
-      <c r="E2" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">I MUNICIPALIDAD DE PUENTE ALTO</t>
-        </is>
-      </c>
-      <c r="F2" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Región Metropolitana de Santiago</t>
-        </is>
-      </c>
-      <c r="G2" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Puente Alto</t>
-        </is>
-      </c>
-      <c r="H2" s="2">
-        <v>46265.753669</v>
-      </c>
-      <c r="I2" s="2">
-        <v>46272.65</v>
-      </c>
-      <c r="J2" s="0">
-        <v>6</v>
-      </c>
-      <c r="K2" s="3">
-        <v>4000000.0</v>
-      </c>
-      <c r="L2" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CLP</t>
-        </is>
-      </c>
-      <c r="M2" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">L1</t>
-        </is>
-      </c>
-      <c r="N2" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Servicios de producción y fabricación industrial / Fabricación de maquinarias y equipos de transporte / Fabricación de maquinarias</t>
-        </is>
-      </c>
-      <c r="O2" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1 Kit · Servicios de fabricación de calderas para central eléctrica</t>
-        </is>
-      </c>
-      <c r="P2" s="2"/>
-      <c r="Q2" s="2"/>
-      <c r="R2" s="0"/>
-      <c r="S2" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">No</t>
-        </is>
-      </c>
-      <c r="T2" s="4"/>
-      <c r="U2" s="0"/>
-      <c r="V2" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NECESIDAD DE SERVICIO, PARA ACONDICIONAMIENTO DE AMBIENTE DE LA PISCINA TEMPERADA BALNEARIO MUNICIPAL, SE REQUIERE SERVICIO DE FABRICACION, INSTALACION Y PUESTA EN MARCHA DE TABLERO DE FUERZA Y COMANDO DE MOTOR TRIFASICO.</t>
-        </is>
-      </c>
-      <c r="W2" s="5" t="str">
-        <f>HYPERLINK("https://www.mercadopublico.cl/Procurement/Modules/RFB/DetailsAcquisition.aspx?idlicitacion=2422-149-L126","descargar bases")</f>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:W2"/>
+  <autoFilter ref="A1:W1"/>
 </worksheet>
 </file>
 
